--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\NSFW\LinkBoardV2\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D34EAFA-850A-47AF-8921-1B03682C5956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6941B669-C80E-4B83-9012-30912983EED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="NSFW_Links" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NSFW_Links!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NSFW_Links!$A$1:$K$146</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="733">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -1215,750 +1215,6 @@
     <t>positions</t>
   </si>
   <si>
-    <t>piper perri, phoenix marie</t>
-  </si>
-  <si>
-    <t>gia dimarco, ariel x</t>
-  </si>
-  <si>
-    <t>ash, allie</t>
-  </si>
-  <si>
-    <t>amber rayne, isis love</t>
-  </si>
-  <si>
-    <t>wenona, jessie cox, isis love</t>
-  </si>
-  <si>
-    <t>sasha sparks, lacie hart</t>
-  </si>
-  <si>
-    <t>riley reid, melissa moore</t>
-  </si>
-  <si>
-    <t>riley reid, ryan reid</t>
-  </si>
-  <si>
-    <t>lauren phillps, ashley lane</t>
-  </si>
-  <si>
-    <t>aiden starr, madison young</t>
-  </si>
-  <si>
-    <t>jewell marceau, nyssa nevers</t>
-  </si>
-  <si>
-    <t>casey calvert, katja kassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kara price, nikki daniels </t>
-  </si>
-  <si>
-    <t xml:space="preserve">chanel preston, cherie deville </t>
-  </si>
-  <si>
-    <t>claire adams, tricia oaks</t>
-  </si>
-  <si>
-    <t>alex, bonnie</t>
-  </si>
-  <si>
-    <t>sensi pearl, isis love</t>
-  </si>
-  <si>
-    <t>cassandra cruz, samantha sin</t>
-  </si>
-  <si>
-    <t>unknown, unknown</t>
-  </si>
-  <si>
-    <t>belle noir, bonnie day</t>
-  </si>
-  <si>
-    <t>riley reid, carter cruise</t>
-  </si>
-  <si>
-    <t>queensnake, holly</t>
-  </si>
-  <si>
-    <t>riley reid, jill kassidy</t>
-  </si>
-  <si>
-    <t>jessica, tanita</t>
-  </si>
-  <si>
-    <t>casey calvert, tommy king</t>
-  </si>
-  <si>
-    <t>stevie moon, lily thot</t>
-  </si>
-  <si>
-    <t>queensnake, tanita</t>
-  </si>
-  <si>
-    <t>michelle, drea</t>
-  </si>
-  <si>
-    <t>gangbang, blackout contacts, body clothespin, flogging, nipple clamps, drinking game</t>
-  </si>
-  <si>
-    <t>flogging, vibrator, pegging, spanking, face riding, leash</t>
-  </si>
-  <si>
-    <t>flogging, flame, switchdom, wax, body clothespin, nipple clamps</t>
-  </si>
-  <si>
-    <t>2f, flogging, lesbian fisting, tongue clothespin, ass up face down, anal cum</t>
-  </si>
-  <si>
-    <t>abduction, blowjob, flogging, spanking, inverted face fuck, piv</t>
-  </si>
-  <si>
-    <t>nipple clamps, flogging, tit pull, stepping, wax, fingering</t>
-  </si>
-  <si>
-    <t>flogging, nipple weights, ball gag, blindfold, nipple string, fingering</t>
-  </si>
-  <si>
-    <t>crotch chain walk, nipple clamps, enema, blindfold, anal hook, spiked wheel</t>
-  </si>
-  <si>
-    <t>piss, gas mask, asphyxiation, nipple suction, nipple suction, oiled</t>
-  </si>
-  <si>
-    <t>ball gag, flogging, nipples binder clips, fucking machine, clit suction, tits suction cups</t>
-  </si>
-  <si>
-    <t>chastity, ball gag, anal hook, spanking, enema, pegging</t>
-  </si>
-  <si>
-    <t>tape gag, flogging, cunnilingus, oiled, strapon, tit torture</t>
-  </si>
-  <si>
-    <t>sounding, multiple girls, trampling, enema, pegging, feet</t>
-  </si>
-  <si>
-    <t>ball gag, body clothespin, spanking, water pouring, public indoors, humiliation</t>
-  </si>
-  <si>
-    <t>bite gag, flogging, nipple clamps, shaving, spanking, body clothespin</t>
-  </si>
-  <si>
-    <t>electric, flogging, anal hook, nipple sticks, oiled, caning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spreader bar, whipping, pussy clamps, rope gag, pussy hook, dildo stick </t>
-  </si>
-  <si>
-    <t>tit slap, bite gag, flogging, rubber band toes, spiked wheel, vibrator</t>
-  </si>
-  <si>
-    <t>2f, lesbian strapon pretzel, toilet, toe in pussy, inverted ass fuck</t>
-  </si>
-  <si>
-    <t>kidnapping, pussy eating, tape gag, blowjob, vibrator</t>
-  </si>
-  <si>
-    <t>flogging, tape gag, wax, nipple clamps, ball gag</t>
-  </si>
-  <si>
-    <t>bite gag, blindfold, tape gag, caning, fingering, vibrator</t>
-  </si>
-  <si>
-    <t>flogging, vibrator, stepping, dildo stick, tit pull, suspended</t>
-  </si>
-  <si>
-    <t>spanking, dildo stick, anal hook, open mouth gag, vibrator, caning</t>
-  </si>
-  <si>
-    <t>2f, blowjob, anal, squirt, pussy eating, piv</t>
-  </si>
-  <si>
-    <t>bite gag, caning, nipple clamps, flogging, dildo stick, vibrator</t>
-  </si>
-  <si>
-    <t>game, whipping, mental torture</t>
-  </si>
-  <si>
-    <t>body clothespin, flogging, cbt, feet, pegging, wax</t>
-  </si>
-  <si>
-    <t>2f, jav, body clothespin, oiled, fondling, pussy eating</t>
-  </si>
-  <si>
-    <t>pussy eating, fondling, face sitting, fingering, dildo, cunnilingus</t>
-  </si>
-  <si>
-    <t>panty gag, nipple suction, flame, spike wheel, nipple clamps, spanking</t>
-  </si>
-  <si>
-    <t>flogging, cage, caning, body clothespin, hitachi, metal bondage</t>
-  </si>
-  <si>
-    <t>spanking, flogging, nipple clamps, nipple suction, fingering, ball gag</t>
-  </si>
-  <si>
-    <t>pussy clamps, flogging, nipple clamps, caning, rope gag, ball gag</t>
-  </si>
-  <si>
-    <t>spanking, butt plug, electric, flogging, strapon, ball gag</t>
-  </si>
-  <si>
-    <t>pussy eating, nipple clamps, nipple suction, ball gag, flogging, nipple string</t>
-  </si>
-  <si>
-    <t>flogging, feet on dick, pegging, hot wax, heels worship, pussy eating</t>
-  </si>
-  <si>
-    <t>nipple clothespin, ball gag, pussy hair pulling , straight jacket, fingering, sensory deprivation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remote control, spanking, anal beads, electric, wax, strapon </t>
-  </si>
-  <si>
-    <t>flogging, nipple clamps, blindfold, dildo stick, anal, wax</t>
-  </si>
-  <si>
-    <t>flogging, nipple clamps, electric, blindfold, strapon, spreader bar</t>
-  </si>
-  <si>
-    <t>tit slap, vibrator, flogging, nipple clamps, fucking machine, dildo stick vibrator</t>
-  </si>
-  <si>
-    <t>tit bite, flogging , blowjob, oiled, nipple clamps, piv</t>
-  </si>
-  <si>
-    <t>2f, spanking, flogging, nipple clamps, ball gag, crotch rope</t>
-  </si>
-  <si>
-    <t>face sitting, pussy eating, nipple sucking, fondling, fingering</t>
-  </si>
-  <si>
-    <t>spanking, face sitting, fondling, nipple sucking</t>
-  </si>
-  <si>
-    <t>metal constraints, anal hook, wiregag, inflatable gag, fucking machine, shocking pussy</t>
-  </si>
-  <si>
-    <t>2f, tied together, butt plug, dildo stick, vibrator, caning</t>
-  </si>
-  <si>
-    <t>butt plug, rimjob, pegging, anal fingering, viper, handjob</t>
-  </si>
-  <si>
-    <t>fisting, oiled, foot in ass, vibrator</t>
-  </si>
-  <si>
-    <t>crotch rope walk, tiger balm, nipple clamps, ball gag, fondling</t>
-  </si>
-  <si>
-    <t>caning, nipple clamps, ball gag, blowjob, pussy eating</t>
-  </si>
-  <si>
-    <t>flogging, nipple clamps, electric, paddle</t>
-  </si>
-  <si>
-    <t>spanking, pegging, body clothespin, panty gag</t>
-  </si>
-  <si>
-    <t>ball gag, cock ring, body clothespin, flogging, pegging, 2f-1m</t>
-  </si>
-  <si>
-    <t>ball gag, flogging, wax, pegging, cock ring, feet</t>
-  </si>
-  <si>
-    <t>2f, metal bondage, vibrator, panty gag, tape, tit torture</t>
-  </si>
-  <si>
-    <t>enema, panty gag, ball gag, towel on face, shibari, multiple girls</t>
-  </si>
-  <si>
-    <t>fisting, strapon, anal</t>
-  </si>
-  <si>
-    <t>humbler, cigg, flogging, pegging, electric glass butt plug</t>
-  </si>
-  <si>
-    <t>cnc, gangbang, panty gag, blowjob, dp, duct tape</t>
-  </si>
-  <si>
-    <t>tit slap, nipple clamps, flogging, wax, fingering, body clothespin</t>
-  </si>
-  <si>
-    <t>strapon, spanking, pussy eating, feet, toe in pussy, inverted ass fuck</t>
-  </si>
-  <si>
-    <t>nipple clamps, shocking, water boarding, bite gag, caning, flogging</t>
-  </si>
-  <si>
-    <t>electric, body clothespin, open mouth gag, ball gag, nipple suction, vibrator</t>
-  </si>
-  <si>
-    <t>pussy biting, high heel, nipple pinching, flogging, enema, rope gag</t>
-  </si>
-  <si>
-    <t>dildo stick, nipple clamps, rubber band feet, nipple clothespin, vibrator, ball gag</t>
-  </si>
-  <si>
-    <t>fondling, blindfold, flogging, spanking, vibrator, ball gag</t>
-  </si>
-  <si>
-    <t>nose hook, caning, open mouth gag, shaving, pussy clamps, panty gag</t>
-  </si>
-  <si>
-    <t>nipple clothespin, panty gag, fucking machine, flogging, nipple suction, dildo stick vibrator</t>
-  </si>
-  <si>
-    <t>open mouth gag, nose hook, dildo stick, chastity belt, suffocation, spreader bar</t>
-  </si>
-  <si>
-    <t>blindfold, nipple clamps, butt plug, vibrator, strapon, pussy eating</t>
-  </si>
-  <si>
-    <t>caning, funnel gag, flogging, fingering</t>
-  </si>
-  <si>
-    <t>flogging, ball gag, nipple sticks, nipple clamps, vibrator</t>
-  </si>
-  <si>
-    <t>pinned, undressing, piv, fondling</t>
-  </si>
-  <si>
-    <t>oiled, massage, fingering, orgasm, fit girl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nipple suction, flogging, fucking machine, piv, vibrator, strapon </t>
-  </si>
-  <si>
-    <t>leash, spanking, cigg, flogging, cfnm, outdoors</t>
-  </si>
-  <si>
-    <t>ball gag, spanking, flogging, vibrator</t>
-  </si>
-  <si>
-    <t>blowjob, piv, fingering, inverted face fuck, fondling</t>
-  </si>
-  <si>
-    <t>blowjob, pussy eating, piv</t>
-  </si>
-  <si>
-    <t>blowjob, piv, stripping</t>
-  </si>
-  <si>
-    <t>blindfold, flogging, ball gag, pegging, spanking, cunnilingus</t>
-  </si>
-  <si>
-    <t>flogging, cunnilingus, pegging, body clothespin, spanking, 2f-1m</t>
-  </si>
-  <si>
-    <t>body licking, bikini, foot worship, call girls, non nude, multiple girls</t>
-  </si>
-  <si>
-    <t>outdoor, head mask, flogging, ice pussy, anal hook, tunnel gag</t>
-  </si>
-  <si>
-    <t>dildo stick, nipple clamps, pussy slap, flogging</t>
-  </si>
-  <si>
-    <t>bite gag, tit pull, whipping, caning, pussy plugged, vibrator</t>
-  </si>
-  <si>
-    <t>fucking machine, flogging, exhibitionism, lesbian spanking, fingering, chain in pussy and ass</t>
-  </si>
-  <si>
-    <t>flogging, chastity, lolipop plug, pegging, wax, femdom service</t>
-  </si>
-  <si>
-    <t>spanking, spitting, chastity, cuck, pegging</t>
-  </si>
-  <si>
-    <t>1f-2m, flogging, ball gag, electric, oiled, pussy clamps</t>
-  </si>
-  <si>
-    <t>massage, foursome, pussy eating, bbc, piv, fondling</t>
-  </si>
-  <si>
-    <t>nipple clamps, dildo plug, body clothespin, pussy fisting</t>
-  </si>
-  <si>
-    <t>1f-2m, blowjob, piv, fondling</t>
-  </si>
-  <si>
-    <t>bbc, blowjob, pussy eating, piv</t>
-  </si>
-  <si>
-    <t>blowjob, anal, creampie, fingering</t>
-  </si>
-  <si>
-    <t>trampling, high heel, feet</t>
-  </si>
-  <si>
-    <t>spanking, pussy eating, fingering, scissoring, pussy grinding</t>
-  </si>
-  <si>
-    <t>oiled, footjob, piv, facial</t>
-  </si>
-  <si>
-    <t>blowjob, piv, fondling</t>
-  </si>
-  <si>
-    <t>ball gag, stripping, flogging, caning, vibrator</t>
-  </si>
-  <si>
-    <t>crotch rope walk, crotch chain walk, hot sauce lathering, whip</t>
-  </si>
-  <si>
-    <t>ball gag, spanking, flogging, dildo stick, anal hook</t>
-  </si>
-  <si>
-    <t>oiled, blowjob, piv, anal, choking, slapping</t>
-  </si>
-  <si>
-    <t>oiled, fucking machine, left alone</t>
-  </si>
-  <si>
-    <t>chastity, pa piercing</t>
-  </si>
-  <si>
-    <t>bite gag, blowjob, tit job</t>
-  </si>
-  <si>
-    <t>gangbang, piss drinking, double penetration, fingering, anal, blowjob</t>
-  </si>
-  <si>
-    <t>nipple clamps, tit slap, blowjob, flogging, piv, anal</t>
-  </si>
-  <si>
-    <t>butt plug, strapon, dildo stick, fisting</t>
-  </si>
-  <si>
-    <t>fisting, ass eating, pussy eating, fingering, anal fingering, kissing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ball gag, nipple clamps, needles, tape gag, sybian, strapon </t>
-  </si>
-  <si>
-    <t>flogging, rubber band feet, piv, vibrator</t>
-  </si>
-  <si>
-    <t>bite gag, stapler, flogging</t>
-  </si>
-  <si>
-    <t>2f, liplocker gag</t>
-  </si>
-  <si>
-    <t>leather, mummy, cock ring, oiled, handjob, cum eating</t>
-  </si>
-  <si>
-    <t>cigg, pantyhose, tit slap, vibrator</t>
-  </si>
-  <si>
-    <t>gangbang, bukkake, stripping, bbc</t>
-  </si>
-  <si>
-    <t>standing, lay down legs to side, doggy</t>
-  </si>
-  <si>
-    <t>suspended, missionary, 69</t>
-  </si>
-  <si>
-    <t>pillory, bent backward, wodden horse</t>
-  </si>
-  <si>
-    <t>arms up tied, horizontal pretzel, double 69</t>
-  </si>
-  <si>
-    <t>frog, kneel down frog, pretzel</t>
-  </si>
-  <si>
-    <t>kneeling vertical, pretzel vertical, lay down</t>
-  </si>
-  <si>
-    <t>sitting split, vertical pretzel, inverted split</t>
-  </si>
-  <si>
-    <t>tightrope, bent on wheel, doggy</t>
-  </si>
-  <si>
-    <t>hogtied, arms up tied, lay down</t>
-  </si>
-  <si>
-    <t>doggy, lay down, kneeling</t>
-  </si>
-  <si>
-    <t>wooden horse, bent, doggy</t>
-  </si>
-  <si>
-    <t>lay down, doggy, kneeling</t>
-  </si>
-  <si>
-    <t>arms up tied, face down horizontal split, kneeling down vertical</t>
-  </si>
-  <si>
-    <t>suspended, lay down</t>
-  </si>
-  <si>
-    <t>lay down face down, ass up face down, standing</t>
-  </si>
-  <si>
-    <t>missionary, lay down diamond, split face down suspended</t>
-  </si>
-  <si>
-    <t>x vertical, doggy, m legs</t>
-  </si>
-  <si>
-    <t>horizontal pretzel, head in toilet, double 619</t>
-  </si>
-  <si>
-    <t>arms up tied, vertical m legs, joined legs up</t>
-  </si>
-  <si>
-    <t>pretzel, ass up face up, spread eagle</t>
-  </si>
-  <si>
-    <t>pretzel, one bar prison, split</t>
-  </si>
-  <si>
-    <t>arms up tied, inverted hogtied, pretzel</t>
-  </si>
-  <si>
-    <t>standing, kneeling vertical, hogtied</t>
-  </si>
-  <si>
-    <t>full nelson, pretzel, 69</t>
-  </si>
-  <si>
-    <t>inverted bent, pretzel, suspended fetal</t>
-  </si>
-  <si>
-    <t>standing, legs up joined, doggy</t>
-  </si>
-  <si>
-    <t>lay down, doggy, standing</t>
-  </si>
-  <si>
-    <t>standing, lay down, spread eagle</t>
-  </si>
-  <si>
-    <t>spread eagle, pretzel, doggy</t>
-  </si>
-  <si>
-    <t>69, spread eagle, lay down</t>
-  </si>
-  <si>
-    <t>missionary legs up, suspended sitting, frog</t>
-  </si>
-  <si>
-    <t>against wall, missionary legs up, inside cage</t>
-  </si>
-  <si>
-    <t>lay down face down, m legs, missionary legs up</t>
-  </si>
-  <si>
-    <t>lay down, ass up face down, inverted</t>
-  </si>
-  <si>
-    <t>ass up face down, missionary legs up, suspended</t>
-  </si>
-  <si>
-    <t>kneeling vertical, seperated legs up</t>
-  </si>
-  <si>
-    <t>standing, suspended face down, bent</t>
-  </si>
-  <si>
-    <t>lay down legs side, lay down face down, lay down face up</t>
-  </si>
-  <si>
-    <t>pretzel vertical, suspended, bent suspended</t>
-  </si>
-  <si>
-    <t>lay on side one leg up, standing, doggy</t>
-  </si>
-  <si>
-    <t>sitting split, lay down</t>
-  </si>
-  <si>
-    <t>kneeling down vertical, doggy, standing</t>
-  </si>
-  <si>
-    <t>standing, missionary suspended, hogtied</t>
-  </si>
-  <si>
-    <t>leg up standing, 69, inverted</t>
-  </si>
-  <si>
-    <t>inverted, lay down, on knees</t>
-  </si>
-  <si>
-    <t>kneeling down, a legs standing</t>
-  </si>
-  <si>
-    <t>spit roast, centipede, 69</t>
-  </si>
-  <si>
-    <t>standing, doggy, missionary</t>
-  </si>
-  <si>
-    <t>bent, suspended fetal, spread eagle</t>
-  </si>
-  <si>
-    <t>suspended upside down, doggy, sitting</t>
-  </si>
-  <si>
-    <t>sitting, doggy, lay down</t>
-  </si>
-  <si>
-    <t>lay down, doggy</t>
-  </si>
-  <si>
-    <t>lay down, sitting, upside down</t>
-  </si>
-  <si>
-    <t>lay down, frog, lay down face down</t>
-  </si>
-  <si>
-    <t>missionary legs up, lay down, face sitting</t>
-  </si>
-  <si>
-    <t>joined legs up, lay down, face sitting</t>
-  </si>
-  <si>
-    <t>lay down, wall fuck, over table</t>
-  </si>
-  <si>
-    <t>lay down, doggy, missionary legs up</t>
-  </si>
-  <si>
-    <t>ass up face down, doggy, missionary</t>
-  </si>
-  <si>
-    <t>missionary, inverted, missionary legs up</t>
-  </si>
-  <si>
-    <t>hogtied, stand over rod</t>
-  </si>
-  <si>
-    <t>69, spread eagle, chair</t>
-  </si>
-  <si>
-    <t>standing one leg up, inverted on chair, m legs</t>
-  </si>
-  <si>
-    <t>hogtied, a shape, lay down</t>
-  </si>
-  <si>
-    <t>arms up split, spread eagle</t>
-  </si>
-  <si>
-    <t>lay down, wooden horse, hogtied</t>
-  </si>
-  <si>
-    <t>burried, lay down legs to side, standing</t>
-  </si>
-  <si>
-    <t>lay down, ass up face down, wheel barrow</t>
-  </si>
-  <si>
-    <t>lay down legs up, vertical pillory</t>
-  </si>
-  <si>
-    <t>kneeling bent back, kneeling vertical</t>
-  </si>
-  <si>
-    <t>doggy, missionary, cowgirl</t>
-  </si>
-  <si>
-    <t>spread eagle, missionary</t>
-  </si>
-  <si>
-    <t>kneeling, doggy, standing</t>
-  </si>
-  <si>
-    <t>hogtied, stomach laydown</t>
-  </si>
-  <si>
-    <t>69, 619, full nelson</t>
-  </si>
-  <si>
-    <t>sitting , missionary, doggy</t>
-  </si>
-  <si>
-    <t>standing, pretzel, lay down</t>
-  </si>
-  <si>
-    <t>lay down, missionary, standing</t>
-  </si>
-  <si>
-    <t>stand on ice, wooden horse, bent froward</t>
-  </si>
-  <si>
-    <t>hogtied, crucified, under net</t>
-  </si>
-  <si>
-    <t>bent, lay down</t>
-  </si>
-  <si>
-    <t>doggy, spread eagle, joined legs up</t>
-  </si>
-  <si>
-    <t>69, doggy, lay down</t>
-  </si>
-  <si>
-    <t>leg up standing, m legs</t>
-  </si>
-  <si>
-    <t>on knees, spit roast, reverse cowgirl</t>
-  </si>
-  <si>
-    <t>lay down legs up, doggy, missionary</t>
-  </si>
-  <si>
-    <t>reverse cowgirl, inverted, pretzel</t>
-  </si>
-  <si>
-    <t>lay down, face sitting</t>
-  </si>
-  <si>
-    <t>face sitting, 69, m legs</t>
-  </si>
-  <si>
-    <t>lay down, missionary, cowgirl</t>
-  </si>
-  <si>
-    <t>on knees, doggy, inverted</t>
-  </si>
-  <si>
-    <t>arms up against wall, leg up standing</t>
-  </si>
-  <si>
-    <t>on knees, doggy, top doggy</t>
-  </si>
-  <si>
-    <t>spit roast, cowgirl, inverted sofa</t>
-  </si>
-  <si>
-    <t>standing, reverse cowgirl, missionary legs up</t>
-  </si>
-  <si>
-    <t>right angle, pretzel, doggy</t>
-  </si>
-  <si>
-    <t>ass up face down, suspended, face sitting</t>
-  </si>
-  <si>
-    <t>pretzel, cowgirl, sybian</t>
-  </si>
-  <si>
-    <t>stand, lay down</t>
-  </si>
-  <si>
-    <t>tightrope, lay down</t>
-  </si>
-  <si>
-    <t>strip pole, on knees</t>
-  </si>
-  <si>
     <t>https://tube.perverzija.com/studio/kink/</t>
   </si>
   <si>
@@ -2106,9 +1362,6 @@
     <t>lot of long length videos across several categories</t>
   </si>
   <si>
-    <t>https://pornzog.com</t>
-  </si>
-  <si>
     <t>general videos mainly for random cases, not big studios</t>
   </si>
   <si>
@@ -2127,136 +1380,886 @@
     <t>https://curebdsm.com/stars/Lily%20LaBeau</t>
   </si>
   <si>
-    <t>suspended, flogging, nipple clamps, kink.com, spanking, lesdom</t>
-  </si>
-  <si>
-    <t>suspended, pretzel, missionary</t>
-  </si>
-  <si>
-    <t>chastity, feet, pegging, humbler, slave, pet play</t>
-  </si>
-  <si>
-    <t>humbler vertical, arched, lay down</t>
-  </si>
-  <si>
-    <t>ball gag, anal hook, piv, anal, blowjob, body clothespin</t>
-  </si>
-  <si>
-    <t>doggy, spread eagle, suspended</t>
-  </si>
-  <si>
-    <t>suspended, flogging, pegging, gangbang, slave, feet</t>
-  </si>
-  <si>
-    <t>suspended, doggy, lay down</t>
-  </si>
-  <si>
-    <t>oiled, vibrator, fucking machine, orgasm, ice, fingering</t>
-  </si>
-  <si>
-    <t>lay down, spread eagle, kneeling down vertical</t>
-  </si>
-  <si>
-    <t>pegging, ball gag, gangbang, foot worship, cbt, wax</t>
-  </si>
-  <si>
-    <t>face sitting, missionary, kneeling down vertical</t>
-  </si>
-  <si>
-    <t>chastity, feet, pegging, face sitting, cage, mummy</t>
-  </si>
-  <si>
-    <t>doggy, kneeling, doggy</t>
-  </si>
-  <si>
-    <t>side fuck, reverse cowgirl, prone bone</t>
-  </si>
-  <si>
-    <t>prone bone, side fuck, doggy</t>
-  </si>
-  <si>
-    <t>cute, piv, anal, bukkake, blowjob</t>
-  </si>
-  <si>
-    <t>missionary, doggy</t>
-  </si>
-  <si>
-    <t>teacher-student, blowjob, piv, anal, petite, plaid</t>
-  </si>
-  <si>
-    <t>missionary, doggy, reverse cowgirl</t>
-  </si>
-  <si>
-    <t>flogging, pegging, caning, cbt, body clothespin, nipple clamps</t>
-  </si>
-  <si>
-    <t>spit roast, doggy, kneeling down vertical</t>
-  </si>
-  <si>
-    <t>fucking machine, gangbang, vibrator, blowjob, femdom, lesdom</t>
-  </si>
-  <si>
-    <t>lay down, face sitting, spit roast</t>
-  </si>
-  <si>
-    <t>chastity, pegging, blowjob, pov, anal fingering, viper</t>
-  </si>
-  <si>
-    <t>doggy, missionary, wheel barrow</t>
-  </si>
-  <si>
-    <t>balls behind ass, handjob, human dildo, suffocation, oiled, pegging</t>
-  </si>
-  <si>
-    <t>standing, doggy, sitting</t>
-  </si>
-  <si>
-    <t>pegging, chastity, femboy, ball bite, canning, pet play</t>
-  </si>
-  <si>
-    <t>doggy, inverted, arched</t>
-  </si>
-  <si>
-    <t>chastity, permanent chastity, torture, denial, cumshot, feet</t>
-  </si>
-  <si>
-    <t>doggy, lay down, standing</t>
-  </si>
-  <si>
-    <t>spanking, pegging, nipple clamps, vibrator</t>
-  </si>
-  <si>
-    <t>ball gag, vibrator, lesdom, oiled, fisting, nipple clamps</t>
-  </si>
-  <si>
-    <t>pretzel, missionary, suspended</t>
-  </si>
-  <si>
-    <t>humiliation, chastity, feet on head, outdoors, ball kicking, feminization</t>
-  </si>
-  <si>
-    <t>doggy, bent, sitting</t>
-  </si>
-  <si>
-    <t>japanese, foot worship, cbt, flogging, pegging, gangbang</t>
-  </si>
-  <si>
-    <t>suspended, kneeling vertical, standing</t>
-  </si>
-  <si>
-    <t>oiled, flogging, nipple clamps, ball gag, blowjob, lesdom</t>
-  </si>
-  <si>
-    <t>pretzel, suspended, standing</t>
-  </si>
-  <si>
-    <t>oiled, flogging, body clothespin, wheel, nipple clamps, vibrator</t>
-  </si>
-  <si>
-    <t>lay down, suspended face down, bent</t>
-  </si>
-  <si>
-    <t>lilys full length bdsm videos but smaller collection and not very exciting</t>
+    <t>gangbang,blackout contacts,body clothespin,flogging,nipple clamps,drinking game</t>
+  </si>
+  <si>
+    <t>standing,lay down legs to side,doggy</t>
+  </si>
+  <si>
+    <t>flogging,vibrator,pegging,spanking,face riding,leash</t>
+  </si>
+  <si>
+    <t>suspended,missionary,69</t>
+  </si>
+  <si>
+    <t>suspended,flogging,nipple clamps,kink.com,spanking,lesdom</t>
+  </si>
+  <si>
+    <t>suspended,pretzel,missionary</t>
+  </si>
+  <si>
+    <t>chastity,feet,pegging,humbler,slave,pet play</t>
+  </si>
+  <si>
+    <t>humbler vertical,arched,lay down</t>
+  </si>
+  <si>
+    <t>ball gag,anal hook,piv,anal,blowjob,body clothespin</t>
+  </si>
+  <si>
+    <t>doggy,spread eagle,suspended</t>
+  </si>
+  <si>
+    <t>flogging,flame,switchdom,wax,body clothespin,nipple clamps</t>
+  </si>
+  <si>
+    <t>pillory,bent backward,wodden horse</t>
+  </si>
+  <si>
+    <t>piper perri,phoenix marie</t>
+  </si>
+  <si>
+    <t>2f,flogging,lesbian fisting,tongue clothespin,ass up face down,anal cum</t>
+  </si>
+  <si>
+    <t>arms up tied,horizontal pretzel,double 69</t>
+  </si>
+  <si>
+    <t>abduction,blowjob,flogging,spanking,inverted face fuck,piv</t>
+  </si>
+  <si>
+    <t>frog,kneel down frog,pretzel</t>
+  </si>
+  <si>
+    <t>nipple clamps,flogging,tit pull,stepping,wax,fingering</t>
+  </si>
+  <si>
+    <t>kneeling vertical,pretzel vertical,lay down</t>
+  </si>
+  <si>
+    <t>flogging,nipple weights,ball gag,blindfold,nipple string,fingering</t>
+  </si>
+  <si>
+    <t>sitting split,vertical pretzel,inverted split</t>
+  </si>
+  <si>
+    <t>crotch chain walk,nipple clamps,enema,blindfold,anal hook,spiked wheel</t>
+  </si>
+  <si>
+    <t>tightrope,bent on wheel,doggy</t>
+  </si>
+  <si>
+    <t>piss,gas mask,asphyxiation,nipple suction,nipple suction,oiled</t>
+  </si>
+  <si>
+    <t>ball gag,flogging,nipples binder clips,fucking machine,clit suction,tits suction cups</t>
+  </si>
+  <si>
+    <t>hogtied,arms up tied,lay down</t>
+  </si>
+  <si>
+    <t>chastity,ball gag,anal hook,spanking,enema,pegging</t>
+  </si>
+  <si>
+    <t>doggy,lay down,kneeling</t>
+  </si>
+  <si>
+    <t>suspended,flogging,pegging,gangbang,slave,feet</t>
+  </si>
+  <si>
+    <t>suspended,doggy,lay down</t>
+  </si>
+  <si>
+    <t>oiled,vibrator,fucking machine,orgasm,ice,fingering</t>
+  </si>
+  <si>
+    <t>lay down,spread eagle,kneeling down vertical</t>
+  </si>
+  <si>
+    <t>pegging,ball gag,gangbang,foot worship,cbt,wax</t>
+  </si>
+  <si>
+    <t>face sitting,missionary,kneeling down vertical</t>
+  </si>
+  <si>
+    <t>chastity,feet,pegging,face sitting,cage,mummy</t>
+  </si>
+  <si>
+    <t>doggy,kneeling,doggy</t>
+  </si>
+  <si>
+    <t>side fuck,reverse cowgirl,prone bone</t>
+  </si>
+  <si>
+    <t>prone bone,side fuck,doggy</t>
+  </si>
+  <si>
+    <t>gia dimarco,ariel x</t>
+  </si>
+  <si>
+    <t>tape gag,flogging,cunnilingus,oiled,strapon,tit torture</t>
+  </si>
+  <si>
+    <t>wooden horse,bent,doggy</t>
+  </si>
+  <si>
+    <t>cute,piv,anal,bukkake,blowjob</t>
+  </si>
+  <si>
+    <t>missionary,doggy</t>
+  </si>
+  <si>
+    <t>sounding,multiple girls,trampling,enema,pegging,feet</t>
+  </si>
+  <si>
+    <t>lay down,doggy,kneeling</t>
+  </si>
+  <si>
+    <t>ball gag,body clothespin,spanking,water pouring,public indoors,humiliation</t>
+  </si>
+  <si>
+    <t>arms up tied,face down horizontal split,kneeling down vertical</t>
+  </si>
+  <si>
+    <t>bite gag,flogging,nipple clamps,shaving,spanking,body clothespin</t>
+  </si>
+  <si>
+    <t>suspended,lay down</t>
+  </si>
+  <si>
+    <t>electric,flogging,anal hook,nipple sticks,oiled,caning</t>
+  </si>
+  <si>
+    <t>lay down face down,ass up face down,standing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spreader bar,whipping,pussy clamps,rope gag,pussy hook,dildo stick </t>
+  </si>
+  <si>
+    <t>missionary,lay down diamond,split face down suspended</t>
+  </si>
+  <si>
+    <t>tit slap,bite gag,flogging,rubber band toes,spiked wheel,vibrator</t>
+  </si>
+  <si>
+    <t>x vertical,doggy,m legs</t>
+  </si>
+  <si>
+    <t>ash,allie</t>
+  </si>
+  <si>
+    <t>2f,lesbian strapon pretzel,toilet,toe in pussy,inverted ass fuck</t>
+  </si>
+  <si>
+    <t>horizontal pretzel,head in toilet,double 619</t>
+  </si>
+  <si>
+    <t>kidnapping,pussy eating,tape gag,blowjob,vibrator</t>
+  </si>
+  <si>
+    <t>arms up tied,vertical m legs,joined legs up</t>
+  </si>
+  <si>
+    <t>flogging,tape gag,wax,nipple clamps,ball gag</t>
+  </si>
+  <si>
+    <t>pretzel,ass up face up,spread eagle</t>
+  </si>
+  <si>
+    <t>bite gag,blindfold,tape gag,caning,fingering,vibrator</t>
+  </si>
+  <si>
+    <t>pretzel,one bar prison,split</t>
+  </si>
+  <si>
+    <t>flogging,vibrator,stepping,dildo stick,tit pull,suspended</t>
+  </si>
+  <si>
+    <t>arms up tied,inverted hogtied,pretzel</t>
+  </si>
+  <si>
+    <t>spanking,dildo stick,anal hook,open mouth gag,vibrator,caning</t>
+  </si>
+  <si>
+    <t>standing,kneeling vertical,hogtied</t>
+  </si>
+  <si>
+    <t>2f,blowjob,anal,squirt,pussy eating,piv</t>
+  </si>
+  <si>
+    <t>full nelson,pretzel,69</t>
+  </si>
+  <si>
+    <t>bite gag,caning,nipple clamps,flogging,dildo stick,vibrator</t>
+  </si>
+  <si>
+    <t>inverted bent,pretzel,suspended fetal</t>
+  </si>
+  <si>
+    <t>game,whipping,mental torture</t>
+  </si>
+  <si>
+    <t>standing,legs up joined,doggy</t>
+  </si>
+  <si>
+    <t>teacher-student,blowjob,piv,anal,petite,plaid</t>
+  </si>
+  <si>
+    <t>missionary,doggy,reverse cowgirl</t>
+  </si>
+  <si>
+    <t>flogging,pegging,caning,cbt,body clothespin,nipple clamps</t>
+  </si>
+  <si>
+    <t>spit roast,doggy,kneeling down vertical</t>
+  </si>
+  <si>
+    <t>fucking machine,gangbang,vibrator,blowjob,femdom,lesdom</t>
+  </si>
+  <si>
+    <t>lay down,face sitting,spit roast</t>
+  </si>
+  <si>
+    <t>chastity,pegging,blowjob,pov,anal fingering,viper</t>
+  </si>
+  <si>
+    <t>doggy,missionary,wheel barrow</t>
+  </si>
+  <si>
+    <t>balls behind ass,handjob,human dildo,suffocation,oiled,pegging</t>
+  </si>
+  <si>
+    <t>standing,doggy,sitting</t>
+  </si>
+  <si>
+    <t>pegging,chastity,femboy,ball bite,canning,pet play</t>
+  </si>
+  <si>
+    <t>doggy,inverted,arched</t>
+  </si>
+  <si>
+    <t>chastity,permanent chastity,torture,denial,cumshot,feet</t>
+  </si>
+  <si>
+    <t>doggy,lay down,standing</t>
+  </si>
+  <si>
+    <t>spanking,pegging,nipple clamps,vibrator</t>
+  </si>
+  <si>
+    <t>lay down,doggy,standing</t>
+  </si>
+  <si>
+    <t>body clothespin,flogging,cbt,feet,pegging,wax</t>
+  </si>
+  <si>
+    <t>standing,lay down,spread eagle</t>
+  </si>
+  <si>
+    <t>unknown,unknown</t>
+  </si>
+  <si>
+    <t>2f,jav,body clothespin,oiled,fondling,pussy eating</t>
+  </si>
+  <si>
+    <t>spread eagle,pretzel,doggy</t>
+  </si>
+  <si>
+    <t>pussy eating,fondling,face sitting,fingering,dildo,cunnilingus</t>
+  </si>
+  <si>
+    <t>69,spread eagle,lay down</t>
+  </si>
+  <si>
+    <t>panty gag,nipple suction,flame,spike wheel,nipple clamps,spanking</t>
+  </si>
+  <si>
+    <t>missionary legs up,suspended sitting,frog</t>
+  </si>
+  <si>
+    <t>amber rayne,isis love</t>
+  </si>
+  <si>
+    <t>flogging,cage,caning,body clothespin,hitachi,metal bondage</t>
+  </si>
+  <si>
+    <t>against wall,missionary legs up,inside cage</t>
+  </si>
+  <si>
+    <t>spanking,flogging,nipple clamps,nipple suction,fingering,ball gag</t>
+  </si>
+  <si>
+    <t>lay down face down,m legs,missionary legs up</t>
+  </si>
+  <si>
+    <t>pussy clamps,flogging,nipple clamps,caning,rope gag,ball gag</t>
+  </si>
+  <si>
+    <t>lay down,ass up face down,inverted</t>
+  </si>
+  <si>
+    <t>spanking,butt plug,electric,flogging,strapon,ball gag</t>
+  </si>
+  <si>
+    <t>ass up face down,missionary legs up,suspended</t>
+  </si>
+  <si>
+    <t>wenona,jessie cox,isis love</t>
+  </si>
+  <si>
+    <t>pussy eating,nipple clamps,nipple suction,ball gag,flogging,nipple string</t>
+  </si>
+  <si>
+    <t>flogging,feet on dick,pegging,hot wax,heels worship,pussy eating</t>
+  </si>
+  <si>
+    <t>kneeling vertical,seperated legs up</t>
+  </si>
+  <si>
+    <t>nipple clothespin,ball gag,pussy hair pulling ,straight jacket,fingering,sensory deprivation</t>
+  </si>
+  <si>
+    <t>standing,suspended face down,bent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remote control,spanking,anal beads,electric,wax,strapon </t>
+  </si>
+  <si>
+    <t>lay down legs side,lay down face down,lay down face up</t>
+  </si>
+  <si>
+    <t>flogging,nipple clamps,blindfold,dildo stick,anal,wax</t>
+  </si>
+  <si>
+    <t>pretzel vertical,suspended,bent suspended</t>
+  </si>
+  <si>
+    <t>flogging,nipple clamps,electric,blindfold,strapon,spreader bar</t>
+  </si>
+  <si>
+    <t>lay on side one leg up,standing,doggy</t>
+  </si>
+  <si>
+    <t>tit slap,vibrator,flogging,nipple clamps,fucking machine,dildo stick vibrator</t>
+  </si>
+  <si>
+    <t>sitting split,lay down</t>
+  </si>
+  <si>
+    <t>tit bite,flogging ,blowjob,oiled,nipple clamps,piv</t>
+  </si>
+  <si>
+    <t>kneeling down vertical,doggy,standing</t>
+  </si>
+  <si>
+    <t>sasha sparks,lacie hart</t>
+  </si>
+  <si>
+    <t>2f,spanking,flogging,nipple clamps,ball gag,crotch rope</t>
+  </si>
+  <si>
+    <t>standing,missionary suspended,hogtied</t>
+  </si>
+  <si>
+    <t>riley reid,melissa moore</t>
+  </si>
+  <si>
+    <t>face sitting,pussy eating,nipple sucking,fondling,fingering</t>
+  </si>
+  <si>
+    <t>leg up standing,69,inverted</t>
+  </si>
+  <si>
+    <t>riley reid,ryan reid</t>
+  </si>
+  <si>
+    <t>spanking,face sitting,fondling,nipple sucking</t>
+  </si>
+  <si>
+    <t>inverted,lay down,on knees</t>
+  </si>
+  <si>
+    <t>metal constraints,anal hook,wiregag,inflatable gag,fucking machine,shocking pussy</t>
+  </si>
+  <si>
+    <t>kneeling down,a legs standing</t>
+  </si>
+  <si>
+    <t>lauren phillps,ashley lane</t>
+  </si>
+  <si>
+    <t>2f,tied together,butt plug,dildo stick,vibrator,caning</t>
+  </si>
+  <si>
+    <t>spit roast,centipede,69</t>
+  </si>
+  <si>
+    <t>butt plug,rimjob,pegging,anal fingering,viper,handjob</t>
+  </si>
+  <si>
+    <t>standing,doggy,missionary</t>
+  </si>
+  <si>
+    <t>fisting,oiled,foot in ass,vibrator</t>
+  </si>
+  <si>
+    <t>crotch rope walk,tiger balm,nipple clamps,ball gag,fondling</t>
+  </si>
+  <si>
+    <t>caning,nipple clamps,ball gag,blowjob,pussy eating</t>
+  </si>
+  <si>
+    <t>bent,suspended fetal,spread eagle</t>
+  </si>
+  <si>
+    <t>flogging,nipple clamps,electric,paddle</t>
+  </si>
+  <si>
+    <t>ball gag,vibrator,lesdom,oiled,fisting,nipple clamps</t>
+  </si>
+  <si>
+    <t>pretzel,missionary,suspended</t>
+  </si>
+  <si>
+    <t>humiliation,chastity,feet on head,outdoors,ball kicking,feminization</t>
+  </si>
+  <si>
+    <t>doggy,bent,sitting</t>
+  </si>
+  <si>
+    <t>spanking,pegging,body clothespin,panty gag</t>
+  </si>
+  <si>
+    <t>suspended upside down,doggy,sitting</t>
+  </si>
+  <si>
+    <t>aiden starr,madison young</t>
+  </si>
+  <si>
+    <t>ball gag,cock ring,body clothespin,flogging,pegging,2f-1m</t>
+  </si>
+  <si>
+    <t>sitting,doggy,lay down</t>
+  </si>
+  <si>
+    <t>ball gag,flogging,wax,pegging,cock ring,feet</t>
+  </si>
+  <si>
+    <t>lay down,doggy</t>
+  </si>
+  <si>
+    <t>2f,metal bondage,vibrator,panty gag,tape,tit torture</t>
+  </si>
+  <si>
+    <t>lay down,sitting,upside down</t>
+  </si>
+  <si>
+    <t>jewell marceau,nyssa nevers</t>
+  </si>
+  <si>
+    <t>enema,panty gag,ball gag,towel on face,shibari,multiple girls</t>
+  </si>
+  <si>
+    <t>lay down,frog,lay down face down</t>
+  </si>
+  <si>
+    <t>casey calvert,katja kassin</t>
+  </si>
+  <si>
+    <t>fisting,strapon,anal</t>
+  </si>
+  <si>
+    <t>missionary legs up,lay down,face sitting</t>
+  </si>
+  <si>
+    <t>humbler,cigg,flogging,pegging,electric glass butt plug</t>
+  </si>
+  <si>
+    <t>joined legs up,lay down,face sitting</t>
+  </si>
+  <si>
+    <t>cnc,gangbang,panty gag,blowjob,dp,duct tape</t>
+  </si>
+  <si>
+    <t>lay down,wall fuck,over table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kara price,nikki daniels </t>
+  </si>
+  <si>
+    <t>tit slap,nipple clamps,flogging,wax,fingering,body clothespin</t>
+  </si>
+  <si>
+    <t>lay down,doggy,missionary legs up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chanel preston,cherie deville </t>
+  </si>
+  <si>
+    <t>strapon,spanking,pussy eating,feet,toe in pussy,inverted ass fuck</t>
+  </si>
+  <si>
+    <t>ass up face down,doggy,missionary</t>
+  </si>
+  <si>
+    <t>claire adams,tricia oaks</t>
+  </si>
+  <si>
+    <t>nipple clamps,shocking,water boarding,bite gag,caning,flogging</t>
+  </si>
+  <si>
+    <t>missionary,inverted,missionary legs up</t>
+  </si>
+  <si>
+    <t>electric,body clothespin,open mouth gag,ball gag,nipple suction,vibrator</t>
+  </si>
+  <si>
+    <t>hogtied,stand over rod</t>
+  </si>
+  <si>
+    <t>pussy biting,high heel,nipple pinching,flogging,enema,rope gag</t>
+  </si>
+  <si>
+    <t>69,spread eagle,chair</t>
+  </si>
+  <si>
+    <t>dildo stick,nipple clamps,rubber band feet,nipple clothespin,vibrator,ball gag</t>
+  </si>
+  <si>
+    <t>standing one leg up,inverted on chair,m legs</t>
+  </si>
+  <si>
+    <t>fondling,blindfold,flogging,spanking,vibrator,ball gag</t>
+  </si>
+  <si>
+    <t>hogtied,a shape,lay down</t>
+  </si>
+  <si>
+    <t>nose hook,caning,open mouth gag,shaving,pussy clamps,panty gag</t>
+  </si>
+  <si>
+    <t>arms up split,spread eagle</t>
+  </si>
+  <si>
+    <t>nipple clothespin,panty gag,fucking machine,flogging,nipple suction,dildo stick vibrator</t>
+  </si>
+  <si>
+    <t>lay down,wooden horse,hogtied</t>
+  </si>
+  <si>
+    <t>open mouth gag,nose hook,dildo stick,chastity belt,suffocation,spreader bar</t>
+  </si>
+  <si>
+    <t>burried,lay down legs to side,standing</t>
+  </si>
+  <si>
+    <t>alex,bonnie</t>
+  </si>
+  <si>
+    <t>blindfold,nipple clamps,butt plug,vibrator,strapon,pussy eating</t>
+  </si>
+  <si>
+    <t>lay down,ass up face down,wheel barrow</t>
+  </si>
+  <si>
+    <t>caning,funnel gag,flogging,fingering</t>
+  </si>
+  <si>
+    <t>lay down legs up,vertical pillory</t>
+  </si>
+  <si>
+    <t>flogging,ball gag,nipple sticks,nipple clamps,vibrator</t>
+  </si>
+  <si>
+    <t>kneeling bent back,kneeling vertical</t>
+  </si>
+  <si>
+    <t>pinned,undressing,piv,fondling</t>
+  </si>
+  <si>
+    <t>doggy,missionary,cowgirl</t>
+  </si>
+  <si>
+    <t>oiled,massage,fingering,orgasm,fit girl</t>
+  </si>
+  <si>
+    <t>sensi pearl,isis love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nipple suction,flogging,fucking machine,piv,vibrator,strapon </t>
+  </si>
+  <si>
+    <t>spread eagle,missionary</t>
+  </si>
+  <si>
+    <t>leash,spanking,cigg,flogging,cfnm,outdoors</t>
+  </si>
+  <si>
+    <t>kneeling,doggy,standing</t>
+  </si>
+  <si>
+    <t>ball gag,spanking,flogging,vibrator</t>
+  </si>
+  <si>
+    <t>hogtied,stomach laydown</t>
+  </si>
+  <si>
+    <t>blowjob,piv,fingering,inverted face fuck,fondling</t>
+  </si>
+  <si>
+    <t>blowjob,pussy eating,piv</t>
+  </si>
+  <si>
+    <t>69,619,full nelson</t>
+  </si>
+  <si>
+    <t>blowjob,piv,stripping</t>
+  </si>
+  <si>
+    <t>sitting ,missionary,doggy</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://pornzog</t>
+  </si>
+  <si>
+    <t>japanese,foot worship,cbt,flogging,pegging,gangbang</t>
+  </si>
+  <si>
+    <t>suspended,kneeling vertical,standing</t>
+  </si>
+  <si>
+    <t>blindfold,flogging,ball gag,pegging,spanking,cunnilingus</t>
+  </si>
+  <si>
+    <t>cassandra cruz,samantha sin</t>
+  </si>
+  <si>
+    <t>flogging,cunnilingus,pegging,body clothespin,spanking,2f-1m</t>
+  </si>
+  <si>
+    <t>standing,pretzel,lay down</t>
+  </si>
+  <si>
+    <t>body licking,bikini,foot worship,call girls,non nude,multiple girls</t>
+  </si>
+  <si>
+    <t>lay down,missionary,standing</t>
+  </si>
+  <si>
+    <t>outdoor,head mask,flogging,ice pussy,anal hook,tunnel gag</t>
+  </si>
+  <si>
+    <t>stand on ice,wooden horse,bent froward</t>
+  </si>
+  <si>
+    <t>dildo stick,nipple clamps,pussy slap,flogging</t>
+  </si>
+  <si>
+    <t>bite gag,tit pull,whipping,caning,pussy plugged,vibrator</t>
+  </si>
+  <si>
+    <t>hogtied,crucified,under net</t>
+  </si>
+  <si>
+    <t>belle noir,bonnie day</t>
+  </si>
+  <si>
+    <t>fucking machine,flogging,exhibitionism,lesbian spanking,fingering,chain in pussy and ass</t>
+  </si>
+  <si>
+    <t>bent,lay down</t>
+  </si>
+  <si>
+    <t>flogging,chastity,lolipop plug,pegging,wax,femdom service</t>
+  </si>
+  <si>
+    <t>spanking,spitting,chastity,cuck,pegging</t>
+  </si>
+  <si>
+    <t>1f-2m,flogging,ball gag,electric,oiled,pussy clamps</t>
+  </si>
+  <si>
+    <t>doggy,spread eagle,joined legs up</t>
+  </si>
+  <si>
+    <t>riley reid,carter cruise</t>
+  </si>
+  <si>
+    <t>massage,foursome,pussy eating,bbc,piv,fondling</t>
+  </si>
+  <si>
+    <t>69,doggy,lay down</t>
+  </si>
+  <si>
+    <t>nipple clamps,dildo plug,body clothespin,pussy fisting</t>
+  </si>
+  <si>
+    <t>leg up standing,m legs</t>
+  </si>
+  <si>
+    <t>1f-2m,blowjob,piv,fondling</t>
+  </si>
+  <si>
+    <t>on knees,spit roast,reverse cowgirl</t>
+  </si>
+  <si>
+    <t>bbc,blowjob,pussy eating,piv</t>
+  </si>
+  <si>
+    <t>lay down legs up,doggy,missionary</t>
+  </si>
+  <si>
+    <t>blowjob,anal,creampie,fingering</t>
+  </si>
+  <si>
+    <t>reverse cowgirl,inverted,pretzel</t>
+  </si>
+  <si>
+    <t>queensnake,holly</t>
+  </si>
+  <si>
+    <t>trampling,high heel,feet</t>
+  </si>
+  <si>
+    <t>lay down,face sitting</t>
+  </si>
+  <si>
+    <t>riley reid,jill kassidy</t>
+  </si>
+  <si>
+    <t>spanking,pussy eating,fingering,scissoring,pussy grinding</t>
+  </si>
+  <si>
+    <t>face sitting,69,m legs</t>
+  </si>
+  <si>
+    <t>oiled,footjob,piv,facial</t>
+  </si>
+  <si>
+    <t>lay down,missionary,cowgirl</t>
+  </si>
+  <si>
+    <t>blowjob,piv,fondling</t>
+  </si>
+  <si>
+    <t>on knees,doggy,inverted</t>
+  </si>
+  <si>
+    <t>ball gag,stripping,flogging,caning,vibrator</t>
+  </si>
+  <si>
+    <t>arms up against wall,leg up standing</t>
+  </si>
+  <si>
+    <t>jessica,tanita</t>
+  </si>
+  <si>
+    <t>crotch rope walk,crotch chain walk,hot sauce lathering,whip</t>
+  </si>
+  <si>
+    <t>ball gag,spanking,flogging,dildo stick,anal hook</t>
+  </si>
+  <si>
+    <t>oiled,blowjob,piv,anal,choking,slapping</t>
+  </si>
+  <si>
+    <t>on knees,doggy,top doggy</t>
+  </si>
+  <si>
+    <t>oiled,fucking machine,left alone</t>
+  </si>
+  <si>
+    <t>chastity,pa piercing</t>
+  </si>
+  <si>
+    <t>bite gag,blowjob,tit job</t>
+  </si>
+  <si>
+    <t>oiled,flogging,nipple clamps,ball gag,blowjob,lesdom</t>
+  </si>
+  <si>
+    <t>pretzel,suspended,standing</t>
+  </si>
+  <si>
+    <t>oiled,flogging,body clothespin,wheel,nipple clamps,vibrator</t>
+  </si>
+  <si>
+    <t>lay down,suspended face down,bent</t>
+  </si>
+  <si>
+    <t>lily's full length bdsm videos but smaller collection and not very exciting</t>
+  </si>
+  <si>
+    <t>gangbang,piss drinking,double penetration,fingering,anal,blowjob</t>
+  </si>
+  <si>
+    <t>spit roast,cowgirl,inverted sofa</t>
+  </si>
+  <si>
+    <t>nipple clamps,tit slap,blowjob,flogging,piv,anal</t>
+  </si>
+  <si>
+    <t>standing,reverse cowgirl,missionary legs up</t>
+  </si>
+  <si>
+    <t>casey calvert,tommy king</t>
+  </si>
+  <si>
+    <t>butt plug,strapon,dildo stick,fisting</t>
+  </si>
+  <si>
+    <t>right angle,pretzel,doggy</t>
+  </si>
+  <si>
+    <t>stevie moon,lily thot</t>
+  </si>
+  <si>
+    <t>fisting,ass eating,pussy eating,fingering,anal fingering,kissing</t>
+  </si>
+  <si>
+    <t>ass up face down,suspended,face sitting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ball gag,nipple clamps,needles,tape gag,sybian,strapon </t>
+  </si>
+  <si>
+    <t>pretzel,cowgirl,sybian</t>
+  </si>
+  <si>
+    <t>flogging,rubber band feet,piv,vibrator</t>
+  </si>
+  <si>
+    <t>queensnake,tanita</t>
+  </si>
+  <si>
+    <t>bite gag,stapler,flogging</t>
+  </si>
+  <si>
+    <t>michelle,drea</t>
+  </si>
+  <si>
+    <t>2f,liplocker gag</t>
+  </si>
+  <si>
+    <t>stand,lay down</t>
+  </si>
+  <si>
+    <t>leather,mummy,cock ring,oiled,handjob,cum eating</t>
+  </si>
+  <si>
+    <t>tightrope,lay down</t>
+  </si>
+  <si>
+    <t>cigg,pantyhose,tit slap,vibrator</t>
+  </si>
+  <si>
+    <t>gangbang,bukkake,stripping,bbc</t>
+  </si>
+  <si>
+    <t>strip pole,on knees</t>
   </si>
 </sst>
 </file>
@@ -2339,7 +2342,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6161"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6161"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2626,13 +2643,17 @@
   <dimension ref="A1:K146"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.7109375" style="1" customWidth="1"/>
-    <col min="2" max="5" width="11.140625" style="1"/>
-    <col min="6" max="6" width="52.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="47" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="1"/>
+    <col min="4" max="4" width="17.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="50.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24" style="1" customWidth="1"/>
     <col min="8" max="9" width="11.140625" style="1"/>
-    <col min="10" max="10" width="43.7109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.140625" style="1"/>
+    <col min="10" max="10" width="48.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2670,7 +2691,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>292</v>
       </c>
@@ -2687,10 +2708,10 @@
         <v>57</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>531</v>
+        <v>440</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>49</v>
@@ -2723,10 +2744,10 @@
         <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>532</v>
+        <v>442</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>49</v>
@@ -2744,25 +2765,25 @@
     </row>
     <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>632</v>
+        <v>384</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>688</v>
+        <v>443</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>689</v>
+        <v>444</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>49</v>
@@ -2771,7 +2792,7 @@
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>635</v>
+        <v>387</v>
       </c>
       <c r="K4" s="2" t="str" cm="1">
         <f t="array" ref="K4">_xlfn.REGEXEXTRACT(A4,"(?&lt;=//)[^/]+")</f>
@@ -2780,25 +2801,25 @@
     </row>
     <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>636</v>
+        <v>388</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>690</v>
+        <v>445</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>691</v>
+        <v>446</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>49</v>
@@ -2807,34 +2828,34 @@
         <v>8</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>637</v>
+        <v>389</v>
       </c>
       <c r="K5" s="2" t="str" cm="1">
         <f t="array" ref="K5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>638</v>
+        <v>390</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>692</v>
+        <v>447</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>693</v>
+        <v>448</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>49</v>
@@ -2843,7 +2864,7 @@
         <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>639</v>
+        <v>391</v>
       </c>
       <c r="K6" s="2" t="str" cm="1">
         <f t="array" ref="K6">_xlfn.REGEXEXTRACT(A6,"(?&lt;=//)[^/]+")</f>
@@ -2867,10 +2888,10 @@
         <v>57</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>533</v>
+        <v>450</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>49</v>
@@ -2886,7 +2907,7 @@
         <v>punishworld.com</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -2897,16 +2918,16 @@
         <v>208</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>384</v>
+        <v>451</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>534</v>
+        <v>453</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>49</v>
@@ -2922,7 +2943,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>295</v>
       </c>
@@ -2939,10 +2960,10 @@
         <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>535</v>
+        <v>455</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>49</v>
@@ -2975,10 +2996,10 @@
         <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>536</v>
+        <v>457</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>49</v>
@@ -2994,7 +3015,7 @@
         <v>m.hqporner.com</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -3011,10 +3032,10 @@
         <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>537</v>
+        <v>459</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
@@ -3047,10 +3068,10 @@
         <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>538</v>
+        <v>461</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>49</v>
@@ -3066,7 +3087,7 @@
         <v>m.hqporner.com</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>87</v>
       </c>
@@ -3083,7 +3104,7 @@
         <v>58</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>95</v>
@@ -3119,10 +3140,10 @@
         <v>57</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>539</v>
+        <v>464</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>49</v>
@@ -3155,10 +3176,10 @@
         <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>422</v>
+        <v>465</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>540</v>
+        <v>466</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>49</v>
@@ -3174,27 +3195,27 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="B16" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>541</v>
+        <v>468</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>49</v>
@@ -3203,34 +3224,34 @@
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="K16" s="2" t="str" cm="1">
         <f t="array" ref="K16">_xlfn.REGEXEXTRACT(A16,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>640</v>
+        <v>394</v>
       </c>
       <c r="B17" s="2">
         <v>0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>73</v>
+        <v>385</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>634</v>
+        <v>395</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>396</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>694</v>
+        <v>469</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>695</v>
+        <v>470</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>49</v>
@@ -3239,34 +3260,34 @@
         <v>7</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>641</v>
+        <v>397</v>
       </c>
       <c r="K17" s="2" t="str" cm="1">
         <f t="array" ref="K17">_xlfn.REGEXEXTRACT(A17,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>642</v>
+        <v>398</v>
       </c>
       <c r="B18" s="2">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>633</v>
+        <v>73</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>643</v>
+        <v>386</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>644</v>
+        <v>75</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>696</v>
+        <v>471</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>697</v>
+        <v>472</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -3275,34 +3296,34 @@
         <v>7</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>645</v>
+        <v>399</v>
       </c>
       <c r="K18" s="2" t="str" cm="1">
         <f t="array" ref="K18">_xlfn.REGEXEXTRACT(A18,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>646</v>
+        <v>400</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>385</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>698</v>
+        <v>473</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>699</v>
+        <v>474</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>49</v>
@@ -3311,34 +3332,32 @@
         <v>7</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>647</v>
+        <v>401</v>
       </c>
       <c r="K19" s="2" t="str" cm="1">
         <f t="array" ref="K19">_xlfn.REGEXEXTRACT(A19,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>648</v>
+        <v>402</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>700</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>701</v>
+        <v>475</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>49</v>
@@ -3347,7 +3366,7 @@
         <v>7</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>649</v>
+        <v>404</v>
       </c>
       <c r="K20" s="2" t="str" cm="1">
         <f t="array" ref="K20">_xlfn.REGEXEXTRACT(A20,"(?&lt;=//)[^/]+")</f>
@@ -3356,23 +3375,23 @@
     </row>
     <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>650</v>
+        <v>405</v>
       </c>
       <c r="B21" s="2">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>651</v>
+        <v>403</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>702</v>
+        <v>476</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>49</v>
@@ -3381,32 +3400,34 @@
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>652</v>
+        <v>406</v>
       </c>
       <c r="K21" s="2" t="str" cm="1">
         <f t="array" ref="K21">_xlfn.REGEXEXTRACT(A21,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>653</v>
+        <v>376</v>
       </c>
       <c r="B22" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>633</v>
+        <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>634</v>
+        <v>477</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F22" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>478</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>703</v>
+        <v>479</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>49</v>
@@ -3415,34 +3436,34 @@
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>654</v>
+        <v>377</v>
       </c>
       <c r="K22" s="2" t="str" cm="1">
         <f t="array" ref="K22">_xlfn.REGEXEXTRACT(A22,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>655</v>
+        <v>407</v>
       </c>
       <c r="B23" s="2">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>173</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>704</v>
+        <v>480</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>705</v>
+        <v>481</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>49</v>
@@ -3451,7 +3472,7 @@
         <v>7</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>656</v>
+        <v>408</v>
       </c>
       <c r="K23" s="2" t="str" cm="1">
         <f t="array" ref="K23">_xlfn.REGEXEXTRACT(A23,"(?&lt;=//)[^/]+")</f>
@@ -3475,10 +3496,10 @@
         <v>75</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>542</v>
+        <v>483</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>319</v>
@@ -3511,10 +3532,10 @@
         <v>57</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>425</v>
+        <v>484</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>543</v>
+        <v>485</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>49</v>
@@ -3547,10 +3568,10 @@
         <v>57</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>426</v>
+        <v>486</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>49</v>
@@ -3583,10 +3604,10 @@
         <v>58</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>545</v>
+        <v>489</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>49</v>
@@ -3619,10 +3640,10 @@
         <v>58</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>428</v>
+        <v>490</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>546</v>
+        <v>491</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>49</v>
@@ -3638,7 +3659,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>63</v>
       </c>
@@ -3655,10 +3676,10 @@
         <v>57</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>429</v>
+        <v>492</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>547</v>
+        <v>493</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>49</v>
@@ -3685,16 +3706,16 @@
         <v>55</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>386</v>
+        <v>494</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>430</v>
+        <v>495</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>548</v>
+        <v>496</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>49</v>
@@ -3710,7 +3731,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>37</v>
       </c>
@@ -3727,10 +3748,10 @@
         <v>56</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>431</v>
+        <v>497</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>549</v>
+        <v>498</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>49</v>
@@ -3763,10 +3784,10 @@
         <v>57</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>432</v>
+        <v>499</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>49</v>
@@ -3782,7 +3803,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -3799,10 +3820,10 @@
         <v>57</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>433</v>
+        <v>501</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>551</v>
+        <v>502</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>49</v>
@@ -3818,7 +3839,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>124</v>
       </c>
@@ -3835,10 +3856,10 @@
         <v>57</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>434</v>
+        <v>503</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>552</v>
+        <v>504</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>49</v>
@@ -3854,7 +3875,7 @@
         <v>m.hqporner.com</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
@@ -3871,10 +3892,10 @@
         <v>57</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>435</v>
+        <v>505</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>553</v>
+        <v>506</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>49</v>
@@ -3907,10 +3928,10 @@
         <v>173</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>436</v>
+        <v>507</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>554</v>
+        <v>508</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>49</v>
@@ -3943,10 +3964,10 @@
         <v>57</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>437</v>
+        <v>509</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>555</v>
+        <v>510</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>49</v>
@@ -3979,10 +4000,10 @@
         <v>57</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>438</v>
+        <v>511</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>556</v>
+        <v>512</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>314</v>
@@ -3998,27 +4019,27 @@
         <v>punishworld.com</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>363</v>
+        <v>409</v>
       </c>
       <c r="B39" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>364</v>
+        <v>187</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>439</v>
+        <v>513</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>558</v>
+        <v>514</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>49</v>
@@ -4027,34 +4048,34 @@
         <v>6</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="K39" s="2" t="str" cm="1">
         <f t="array" ref="K39">_xlfn.REGEXEXTRACT(A39,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>657</v>
+        <v>411</v>
       </c>
       <c r="B40" s="2">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>633</v>
+        <v>326</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>187</v>
+        <v>386</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>706</v>
+        <v>515</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>707</v>
+        <v>516</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>49</v>
@@ -4063,34 +4084,34 @@
         <v>6</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>658</v>
+        <v>412</v>
       </c>
       <c r="K40" s="2" t="str" cm="1">
         <f t="array" ref="K40">_xlfn.REGEXEXTRACT(A40,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>www.txxx.porn</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>659</v>
+        <v>413</v>
       </c>
       <c r="B41" s="2">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>326</v>
+        <v>226</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>708</v>
+        <v>517</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>709</v>
+        <v>518</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>49</v>
@@ -4099,34 +4120,34 @@
         <v>6</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>660</v>
+        <v>414</v>
       </c>
       <c r="K41" s="2" t="str" cm="1">
         <f t="array" ref="K41">_xlfn.REGEXEXTRACT(A41,"(?&lt;=//)[^/]+")</f>
         <v>www.txxx.porn</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>661</v>
+        <v>415</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>226</v>
+        <v>385</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>710</v>
+        <v>519</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>711</v>
+        <v>520</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>49</v>
@@ -4135,34 +4156,34 @@
         <v>6</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>662</v>
+        <v>416</v>
       </c>
       <c r="K42" s="2" t="str" cm="1">
         <f t="array" ref="K42">_xlfn.REGEXEXTRACT(A42,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>663</v>
+        <v>417</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>712</v>
+        <v>521</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>713</v>
+        <v>522</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>49</v>
@@ -4171,34 +4192,34 @@
         <v>6</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>664</v>
+        <v>418</v>
       </c>
       <c r="K43" s="2" t="str" cm="1">
         <f t="array" ref="K43">_xlfn.REGEXEXTRACT(A43,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>665</v>
+        <v>419</v>
       </c>
       <c r="B44" s="2">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>714</v>
+        <v>523</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>715</v>
+        <v>524</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>49</v>
@@ -4207,34 +4228,34 @@
         <v>6</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>666</v>
+        <v>420</v>
       </c>
       <c r="K44" s="2" t="str" cm="1">
         <f t="array" ref="K44">_xlfn.REGEXEXTRACT(A44,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>667</v>
+        <v>421</v>
       </c>
       <c r="B45" s="2">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>716</v>
+        <v>525</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>717</v>
+        <v>526</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>49</v>
@@ -4243,34 +4264,34 @@
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>668</v>
+        <v>422</v>
       </c>
       <c r="K45" s="2" t="str" cm="1">
         <f t="array" ref="K45">_xlfn.REGEXEXTRACT(A45,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>669</v>
+        <v>423</v>
       </c>
       <c r="B46" s="2">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>633</v>
+        <v>326</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>718</v>
+        <v>527</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>719</v>
+        <v>528</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>49</v>
@@ -4279,34 +4300,34 @@
         <v>6</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>670</v>
+        <v>424</v>
       </c>
       <c r="K46" s="2" t="str" cm="1">
         <f t="array" ref="K46">_xlfn.REGEXEXTRACT(A46,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>671</v>
+        <v>363</v>
       </c>
       <c r="B47" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>326</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>634</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>720</v>
+        <v>529</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>49</v>
@@ -4315,14 +4336,14 @@
         <v>6</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>672</v>
+        <v>365</v>
       </c>
       <c r="K47" s="2" t="str" cm="1">
         <f t="array" ref="K47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
         <v>www.porntry.com</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>317</v>
       </c>
@@ -4333,16 +4354,16 @@
         <v>318</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>328</v>
+        <v>531</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>319</v>
@@ -4358,7 +4379,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>331</v>
       </c>
@@ -4369,16 +4390,16 @@
         <v>328</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>328</v>
+        <v>531</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>441</v>
+        <v>534</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>49</v>
@@ -4411,10 +4432,10 @@
         <v>57</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>442</v>
+        <v>536</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>49</v>
@@ -4441,16 +4462,16 @@
         <v>62</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>387</v>
+        <v>538</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>49</v>
@@ -4483,10 +4504,10 @@
         <v>58</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>444</v>
+        <v>541</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>49</v>
@@ -4502,7 +4523,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>279</v>
       </c>
@@ -4519,10 +4540,10 @@
         <v>57</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>445</v>
+        <v>543</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>49</v>
@@ -4555,10 +4576,10 @@
         <v>58</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>446</v>
+        <v>545</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>49</v>
@@ -4585,13 +4606,13 @@
         <v>62</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>388</v>
+        <v>547</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>447</v>
+        <v>548</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>82</v>
@@ -4627,10 +4648,10 @@
         <v>75</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>448</v>
+        <v>549</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>49</v>
@@ -4646,7 +4667,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>134</v>
       </c>
@@ -4663,10 +4684,10 @@
         <v>57</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>449</v>
+        <v>551</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>49</v>
@@ -4682,7 +4703,7 @@
         <v>curebdsm.com</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>27</v>
       </c>
@@ -4699,10 +4720,10 @@
         <v>58</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>450</v>
+        <v>553</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>49</v>
@@ -4735,10 +4756,10 @@
         <v>57</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>451</v>
+        <v>555</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>49</v>
@@ -4754,7 +4775,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>25</v>
       </c>
@@ -4771,10 +4792,10 @@
         <v>58</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>452</v>
+        <v>557</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>49</v>
@@ -4807,10 +4828,10 @@
         <v>57</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>453</v>
+        <v>559</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>49</v>
@@ -4843,10 +4864,10 @@
         <v>57</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>454</v>
+        <v>561</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>49</v>
@@ -4873,16 +4894,16 @@
         <v>65</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>389</v>
+        <v>563</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>455</v>
+        <v>564</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>49</v>
@@ -4909,16 +4930,16 @@
         <v>196</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>390</v>
+        <v>566</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>456</v>
+        <v>567</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>49</v>
@@ -4934,7 +4955,7 @@
         <v>spankbang.com</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>40</v>
       </c>
@@ -4945,16 +4966,16 @@
         <v>185</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>391</v>
+        <v>569</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>457</v>
+        <v>570</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>49</v>
@@ -4987,10 +5008,10 @@
         <v>57</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>458</v>
+        <v>572</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>49</v>
@@ -5006,7 +5027,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>28</v>
       </c>
@@ -5017,16 +5038,16 @@
         <v>64</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>392</v>
+        <v>574</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>459</v>
+        <v>575</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>49</v>
@@ -5042,7 +5063,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>329</v>
       </c>
@@ -5059,7 +5080,7 @@
         <v>75</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>460</v>
+        <v>577</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>578</v>
@@ -5078,7 +5099,7 @@
         <v>beeg.com</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>340</v>
       </c>
@@ -5095,7 +5116,7 @@
         <v>342</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>461</v>
+        <v>579</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>60</v>
@@ -5114,7 +5135,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>142</v>
       </c>
@@ -5131,7 +5152,7 @@
         <v>57</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>462</v>
+        <v>580</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>109</v>
@@ -5167,10 +5188,10 @@
         <v>57</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>463</v>
+        <v>581</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>49</v>
@@ -5186,7 +5207,7 @@
         <v>txxx.com</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>338</v>
       </c>
@@ -5203,7 +5224,7 @@
         <v>75</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>464</v>
+        <v>583</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>327</v>
@@ -5222,27 +5243,27 @@
         <v>xhamster44.desi</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>366</v>
+        <v>425</v>
       </c>
       <c r="B73" s="2">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>465</v>
+        <v>584</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>49</v>
@@ -5251,34 +5272,34 @@
         <v>5</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="K73" s="2" t="str" cm="1">
         <f t="array" ref="K73">_xlfn.REGEXEXTRACT(A73,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="B74" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>466</v>
+        <v>586</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>49</v>
@@ -5287,34 +5308,34 @@
         <v>5</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="K74" s="2" t="str" cm="1">
         <f t="array" ref="K74">_xlfn.REGEXEXTRACT(A74,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B75" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>73</v>
+        <v>326</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>467</v>
+        <v>588</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>49</v>
@@ -5323,7 +5344,7 @@
         <v>5</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="K75" s="2" t="str" cm="1">
         <f t="array" ref="K75">_xlfn.REGEXEXTRACT(A75,"(?&lt;=//)[^/]+")</f>
@@ -5332,25 +5353,25 @@
     </row>
     <row r="76" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>673</v>
+        <v>369</v>
       </c>
       <c r="B76" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>674</v>
+        <v>326</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>675</v>
+        <v>590</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>721</v>
+        <v>591</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>722</v>
+        <v>592</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>49</v>
@@ -5359,34 +5380,34 @@
         <v>5</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>676</v>
+        <v>370</v>
       </c>
       <c r="K76" s="2" t="str" cm="1">
         <f t="array" ref="K76">_xlfn.REGEXEXTRACT(A76,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>677</v>
+        <v>378</v>
       </c>
       <c r="B77" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>633</v>
+        <v>73</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>634</v>
+        <v>379</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>723</v>
+        <v>593</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>724</v>
+        <v>594</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>49</v>
@@ -5395,11 +5416,11 @@
         <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>678</v>
+        <v>380</v>
       </c>
       <c r="K77" s="2" t="str" cm="1">
         <f t="array" ref="K77">_xlfn.REGEXEXTRACT(A77,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -5419,10 +5440,10 @@
         <v>57</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>468</v>
+        <v>595</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>49</v>
@@ -5438,7 +5459,7 @@
         <v>punishbang.com</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>321</v>
       </c>
@@ -5449,16 +5470,16 @@
         <v>322</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>394</v>
+        <v>597</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>469</v>
+        <v>598</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>49</v>
@@ -5474,7 +5495,7 @@
         <v>punishbang.com</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>114</v>
       </c>
@@ -5485,16 +5506,16 @@
         <v>111</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>395</v>
+        <v>600</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>470</v>
+        <v>601</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>49</v>
@@ -5510,7 +5531,7 @@
         <v>pornxp.com</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>35</v>
       </c>
@@ -5527,10 +5548,10 @@
         <v>75</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>471</v>
+        <v>603</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>49</v>
@@ -5563,10 +5584,10 @@
         <v>172</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>472</v>
+        <v>605</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>49</v>
@@ -5582,7 +5603,7 @@
         <v>m.hqporner.com</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>274</v>
       </c>
@@ -5593,16 +5614,16 @@
         <v>145</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>396</v>
+        <v>607</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>473</v>
+        <v>608</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>49</v>
@@ -5618,7 +5639,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>16</v>
       </c>
@@ -5629,16 +5650,16 @@
         <v>112</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>397</v>
+        <v>610</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>474</v>
+        <v>611</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>49</v>
@@ -5654,7 +5675,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>272</v>
       </c>
@@ -5665,16 +5686,16 @@
         <v>62</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>398</v>
+        <v>613</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>475</v>
+        <v>614</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>49</v>
@@ -5690,7 +5711,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>20</v>
       </c>
@@ -5707,10 +5728,10 @@
         <v>57</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>476</v>
+        <v>616</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>49</v>
@@ -5726,7 +5747,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>33</v>
       </c>
@@ -5743,10 +5764,10 @@
         <v>58</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>477</v>
+        <v>618</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>592</v>
+        <v>619</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>49</v>
@@ -5779,10 +5800,10 @@
         <v>57</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>478</v>
+        <v>620</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>49</v>
@@ -5798,7 +5819,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>7</v>
       </c>
@@ -5815,10 +5836,10 @@
         <v>57</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>479</v>
+        <v>622</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>49</v>
@@ -5834,7 +5855,7 @@
         <v>spankbang.party</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>34</v>
       </c>
@@ -5851,10 +5872,10 @@
         <v>57</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>480</v>
+        <v>624</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>595</v>
+        <v>625</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>49</v>
@@ -5887,10 +5908,10 @@
         <v>57</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>481</v>
+        <v>626</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>49</v>
@@ -5906,7 +5927,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>11</v>
       </c>
@@ -5923,10 +5944,10 @@
         <v>57</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>482</v>
+        <v>628</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>49</v>
@@ -5942,7 +5963,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>127</v>
       </c>
@@ -5953,16 +5974,16 @@
         <v>328</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>399</v>
+        <v>630</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>220</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>483</v>
+        <v>631</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>598</v>
+        <v>632</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>49</v>
@@ -5995,10 +6016,10 @@
         <v>57</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>484</v>
+        <v>633</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>599</v>
+        <v>634</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>49</v>
@@ -6014,7 +6035,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>31</v>
       </c>
@@ -6031,10 +6052,10 @@
         <v>57</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>485</v>
+        <v>635</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>600</v>
+        <v>636</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>49</v>
@@ -6067,10 +6088,10 @@
         <v>172</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>486</v>
+        <v>637</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>601</v>
+        <v>638</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>49</v>
@@ -6103,7 +6124,7 @@
         <v>175</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>487</v>
+        <v>639</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>72</v>
@@ -6122,7 +6143,7 @@
         <v>txxx.me</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>123</v>
       </c>
@@ -6133,16 +6154,16 @@
         <v>62</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>400</v>
+        <v>640</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>488</v>
+        <v>641</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>602</v>
+        <v>642</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>49</v>
@@ -6175,10 +6196,10 @@
         <v>75</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>489</v>
+        <v>643</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>603</v>
+        <v>644</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>49</v>
@@ -6194,7 +6215,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>135</v>
       </c>
@@ -6211,10 +6232,10 @@
         <v>57</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>490</v>
+        <v>645</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>604</v>
+        <v>646</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>49</v>
@@ -6247,7 +6268,7 @@
         <v>57</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>491</v>
+        <v>647</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>199</v>
@@ -6266,7 +6287,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>140</v>
       </c>
@@ -6283,10 +6304,10 @@
         <v>172</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>492</v>
+        <v>648</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>49</v>
@@ -6302,7 +6323,7 @@
         <v>www.porndead.org</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>0</v>
       </c>
@@ -6319,10 +6340,10 @@
         <v>173</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>493</v>
+        <v>650</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>49</v>
@@ -6338,27 +6359,27 @@
         <v>xhamster18.desi</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="B104" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>75</v>
+        <v>403</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>494</v>
+        <v>652</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>582</v>
+        <v>652</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>49</v>
@@ -6367,34 +6388,34 @@
         <v>4</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="K104" s="2" t="str" cm="1">
         <f t="array" ref="K104">_xlfn.REGEXEXTRACT(A104,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>netfapx.net</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>374</v>
+        <v>653</v>
       </c>
       <c r="B105" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>75</v>
+        <v>403</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>495</v>
+        <v>652</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>607</v>
+        <v>652</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>49</v>
@@ -6403,63 +6424,71 @@
         <v>4</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="K105" s="2" t="str" cm="1">
         <f t="array" ref="K105">_xlfn.REGEXEXTRACT(A105,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>pornzog</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>679</v>
+        <v>434</v>
       </c>
       <c r="B106" s="2">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>634</v>
+        <v>386</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>655</v>
+      </c>
       <c r="H106" s="2" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="I106" s="2">
         <v>4</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>680</v>
+        <v>435</v>
       </c>
       <c r="K106" s="2" t="str" cm="1">
         <f t="array" ref="K106">_xlfn.REGEXEXTRACT(A106,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
+        <v>www.tubegalore.com</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>681</v>
+        <v>371</v>
       </c>
       <c r="B107" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>633</v>
+        <v>326</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>634</v>
+        <v>372</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>594</v>
+      </c>
       <c r="H107" s="2" t="s">
         <v>49</v>
       </c>
@@ -6467,47 +6496,47 @@
         <v>4</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>682</v>
+        <v>373</v>
       </c>
       <c r="K107" s="2" t="str" cm="1">
         <f t="array" ref="K107">_xlfn.REGEXEXTRACT(A107,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>683</v>
+        <v>374</v>
       </c>
       <c r="B108" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>633</v>
+        <v>326</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>634</v>
+        <v>657</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>725</v>
+        <v>658</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>726</v>
+        <v>659</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I108" s="2">
         <v>4</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>684</v>
+        <v>375</v>
       </c>
       <c r="K108" s="2" t="str" cm="1">
         <f t="array" ref="K108">_xlfn.REGEXEXTRACT(A108,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -6521,16 +6550,16 @@
         <v>328</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>402</v>
+        <v>531</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>496</v>
+        <v>660</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>608</v>
+        <v>661</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>319</v>
@@ -6546,7 +6575,7 @@
         <v>www.eporner.com</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>23</v>
       </c>
@@ -6563,10 +6592,10 @@
         <v>57</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>497</v>
+        <v>662</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>609</v>
+        <v>663</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>49</v>
@@ -6582,7 +6611,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>137</v>
       </c>
@@ -6599,7 +6628,7 @@
         <v>57</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>498</v>
+        <v>664</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>72</v>
@@ -6635,10 +6664,10 @@
         <v>57</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>499</v>
+        <v>665</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>610</v>
+        <v>666</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>49</v>
@@ -6654,7 +6683,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>36</v>
       </c>
@@ -6665,16 +6694,16 @@
         <v>208</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>403</v>
+        <v>667</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>500</v>
+        <v>668</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>611</v>
+        <v>669</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>49</v>
@@ -6690,7 +6719,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>247</v>
       </c>
@@ -6707,10 +6736,10 @@
         <v>75</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>501</v>
+        <v>670</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>557</v>
+        <v>528</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>49</v>
@@ -6726,7 +6755,7 @@
         <v>pervtube.net</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>79</v>
       </c>
@@ -6743,10 +6772,10 @@
         <v>75</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>502</v>
+        <v>671</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>49</v>
@@ -6779,10 +6808,10 @@
         <v>57</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>503</v>
+        <v>672</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>612</v>
+        <v>673</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>49</v>
@@ -6809,16 +6838,16 @@
         <v>328</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>404</v>
+        <v>674</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>504</v>
+        <v>675</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>613</v>
+        <v>676</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>49</v>
@@ -6834,7 +6863,7 @@
         <v>spankbang.com</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>83</v>
       </c>
@@ -6851,10 +6880,10 @@
         <v>56</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>505</v>
+        <v>677</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>614</v>
+        <v>678</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>92</v>
@@ -6870,7 +6899,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>130</v>
       </c>
@@ -6887,10 +6916,10 @@
         <v>172</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>506</v>
+        <v>679</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>615</v>
+        <v>680</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>49</v>
@@ -6906,7 +6935,7 @@
         <v>spankbang.com</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>1</v>
       </c>
@@ -6923,10 +6952,10 @@
         <v>172</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>507</v>
+        <v>681</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>616</v>
+        <v>682</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>49</v>
@@ -6942,7 +6971,7 @@
         <v>www.pornhub.com</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>141</v>
       </c>
@@ -6959,10 +6988,10 @@
         <v>172</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>508</v>
+        <v>683</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>617</v>
+        <v>684</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>49</v>
@@ -6989,16 +7018,16 @@
         <v>89</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>405</v>
+        <v>685</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>509</v>
+        <v>686</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>618</v>
+        <v>687</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>49</v>
@@ -7025,16 +7054,16 @@
         <v>170</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>406</v>
+        <v>688</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>510</v>
+        <v>689</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>619</v>
+        <v>690</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>49</v>
@@ -7067,10 +7096,10 @@
         <v>173</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>511</v>
+        <v>691</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>620</v>
+        <v>692</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>49</v>
@@ -7086,7 +7115,7 @@
         <v>www.pornhub.com</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>2</v>
       </c>
@@ -7103,10 +7132,10 @@
         <v>172</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>512</v>
+        <v>693</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>621</v>
+        <v>694</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>49</v>
@@ -7122,7 +7151,7 @@
         <v>www.pornhub.com</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>122</v>
       </c>
@@ -7139,10 +7168,10 @@
         <v>57</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>513</v>
+        <v>695</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>622</v>
+        <v>696</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>49</v>
@@ -7158,7 +7187,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>88</v>
       </c>
@@ -7169,13 +7198,13 @@
         <v>89</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>407</v>
+        <v>697</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>514</v>
+        <v>698</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>109</v>
@@ -7194,7 +7223,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>6</v>
       </c>
@@ -7211,7 +7240,7 @@
         <v>57</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>515</v>
+        <v>699</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>59</v>
@@ -7247,10 +7276,10 @@
         <v>172</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>516</v>
+        <v>700</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>623</v>
+        <v>701</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>49</v>
@@ -7266,7 +7295,7 @@
         <v>www.tnaflix.com</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>24</v>
       </c>
@@ -7283,7 +7312,7 @@
         <v>57</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>517</v>
+        <v>702</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>52</v>
@@ -7319,7 +7348,7 @@
         <v>75</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>518</v>
+        <v>703</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>203</v>
@@ -7355,7 +7384,7 @@
         <v>75</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>519</v>
+        <v>704</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>72</v>
@@ -7374,15 +7403,15 @@
         <v>www.porntopedia.com</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>685</v>
+        <v>436</v>
       </c>
       <c r="B133" s="2">
         <v>0</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>159</v>
@@ -7391,10 +7420,10 @@
         <v>57</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>727</v>
+        <v>705</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>728</v>
+        <v>706</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>49</v>
@@ -7403,22 +7432,22 @@
         <v>3</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>686</v>
+        <v>437</v>
       </c>
       <c r="K133" s="2" t="str" cm="1">
         <f t="array" ref="K133">_xlfn.REGEXEXTRACT(A133,"(?&lt;=//)[^/]+")</f>
         <v>curebdsm.com</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>687</v>
+        <v>438</v>
       </c>
       <c r="B134" s="2">
         <v>0</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>183</v>
@@ -7427,10 +7456,10 @@
         <v>57</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>729</v>
+        <v>707</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>730</v>
+        <v>708</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>49</v>
@@ -7439,7 +7468,7 @@
         <v>3</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="K134" s="2" t="str" cm="1">
         <f t="array" ref="K134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
@@ -7463,10 +7492,10 @@
         <v>172</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>520</v>
+        <v>710</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>624</v>
+        <v>711</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>49</v>
@@ -7499,10 +7528,10 @@
         <v>57</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>521</v>
+        <v>712</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>625</v>
+        <v>713</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>49</v>
@@ -7518,7 +7547,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>270</v>
       </c>
@@ -7529,16 +7558,16 @@
         <v>226</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>408</v>
+        <v>714</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>522</v>
+        <v>715</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>626</v>
+        <v>716</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>49</v>
@@ -7565,16 +7594,16 @@
         <v>111</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>409</v>
+        <v>717</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>523</v>
+        <v>718</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>627</v>
+        <v>719</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>49</v>
@@ -7590,7 +7619,7 @@
         <v>m.hqporner.com</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>32</v>
       </c>
@@ -7607,10 +7636,10 @@
         <v>58</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>524</v>
+        <v>720</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>628</v>
+        <v>721</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>49</v>
@@ -7626,7 +7655,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>133</v>
       </c>
@@ -7643,7 +7672,7 @@
         <v>57</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>525</v>
+        <v>722</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>258</v>
@@ -7662,7 +7691,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>143</v>
       </c>
@@ -7673,13 +7702,13 @@
         <v>89</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>410</v>
+        <v>723</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>526</v>
+        <v>724</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>72</v>
@@ -7709,16 +7738,16 @@
         <v>328</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>411</v>
+        <v>725</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>527</v>
+        <v>726</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>629</v>
+        <v>727</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>49</v>
@@ -7751,7 +7780,7 @@
         <v>75</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>528</v>
+        <v>728</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>72</v>
@@ -7770,7 +7799,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>121</v>
       </c>
@@ -7790,7 +7819,7 @@
         <v>233</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>630</v>
+        <v>729</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>49</v>
@@ -7806,7 +7835,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>86</v>
       </c>
@@ -7817,13 +7846,13 @@
         <v>89</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>407</v>
+        <v>697</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>529</v>
+        <v>730</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>90</v>
@@ -7842,7 +7871,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>3</v>
       </c>
@@ -7859,10 +7888,10 @@
         <v>172</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>530</v>
+        <v>731</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>631</v>
+        <v>732</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>49</v>
@@ -7879,7 +7908,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:K146">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -7887,7 +7915,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I146">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7898,34 +7926,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" xr:uid="{3912BFEB-29DA-41C3-81EA-F50133C54869}"/>
-    <hyperlink ref="A5" r:id="rId2" xr:uid="{016BBFCB-7CA0-4556-9291-B202D76528E2}"/>
-    <hyperlink ref="A6" r:id="rId3" xr:uid="{90436A3A-82BF-4B2F-93C4-C70860B1A2E9}"/>
-    <hyperlink ref="A17" r:id="rId4" xr:uid="{3F9EF594-E9C5-4A8A-981B-7DAF6343A093}"/>
-    <hyperlink ref="A18" r:id="rId5" xr:uid="{73BFE0EB-6035-4F26-8FC9-3230954892DC}"/>
-    <hyperlink ref="A19" r:id="rId6" xr:uid="{F2522A6F-05B7-4E59-9DE2-BDE5AC3F9A42}"/>
-    <hyperlink ref="A20" r:id="rId7" xr:uid="{668CCD11-CD40-422F-88BE-4D4512636759}"/>
-    <hyperlink ref="A21" r:id="rId8" xr:uid="{EBE0C692-194C-4247-9786-07E7103A28FA}"/>
-    <hyperlink ref="A22" r:id="rId9" xr:uid="{A703687B-E0BF-4D3B-A512-49B210EC8CCC}"/>
-    <hyperlink ref="A23" r:id="rId10" xr:uid="{601766C6-8C7A-4DE5-8D24-10669D2E68E8}"/>
-    <hyperlink ref="A40" r:id="rId11" xr:uid="{FA811D1C-BEE3-49D1-94B3-6C07DFB0AB80}"/>
-    <hyperlink ref="A41" r:id="rId12" xr:uid="{D14EBC35-D3AC-4306-9127-E6DB2B22049E}"/>
-    <hyperlink ref="A42" r:id="rId13" xr:uid="{E4FF822D-1F7B-4696-84EC-D4A991B4B383}"/>
-    <hyperlink ref="A43" r:id="rId14" xr:uid="{1D3927F0-D446-4BA6-BE7D-E37A483397D7}"/>
-    <hyperlink ref="A44" r:id="rId15" xr:uid="{AC181324-98DF-4069-AEC4-22147166C802}"/>
-    <hyperlink ref="A45" r:id="rId16" xr:uid="{6FB25E4B-033D-4201-9995-BD4B004EFB0B}"/>
-    <hyperlink ref="A46" r:id="rId17" xr:uid="{5D65FAA4-B689-4D13-ABC2-51A7F2C3669D}"/>
-    <hyperlink ref="A47" r:id="rId18" xr:uid="{339F2384-76F5-49FC-9877-9C4677731123}"/>
-    <hyperlink ref="A76" r:id="rId19" xr:uid="{1A69C0C7-CF39-4A11-8644-5A2D8C271278}"/>
-    <hyperlink ref="A77" r:id="rId20" xr:uid="{A82DE0C5-3A96-4C1E-B868-D11A1E9A197F}"/>
-    <hyperlink ref="A106" r:id="rId21" xr:uid="{9A4E0B28-0BBD-4274-ABA4-01B58B6CFD3C}"/>
-    <hyperlink ref="A107" r:id="rId22" xr:uid="{2302420C-3D1E-4E8B-A4F7-7DF3CFF2CFC4}"/>
-    <hyperlink ref="A108" r:id="rId23" xr:uid="{5ADB3A1D-9592-4CD4-A6EC-D1145F3ADF54}"/>
-    <hyperlink ref="A133" r:id="rId24" xr:uid="{789F306D-E48B-466E-8250-B1D026EF19E5}"/>
-    <hyperlink ref="A134" r:id="rId25" xr:uid="{4BF1481E-3CA0-4A41-80DE-AD544EF3629D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId26"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6941B669-C80E-4B83-9012-30912983EED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A222CD5-FD0C-4C0D-9991-AB458C137A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,30 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="795">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -2260,6 +2238,192 @@
   </si>
   <si>
     <t>strip pole,on knees</t>
+  </si>
+  <si>
+    <t>heavyfetish.com</t>
+  </si>
+  <si>
+    <t>www.eporner.com</t>
+  </si>
+  <si>
+    <t>tube.perverzija.com</t>
+  </si>
+  <si>
+    <t>www.fuq.com</t>
+  </si>
+  <si>
+    <t>www.tubebdsm.com</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/femdom</t>
+  </si>
+  <si>
+    <t>pegging,humiliation,2f-1m,chastity,milking,latex,humbler</t>
+  </si>
+  <si>
+    <t>standing,doggy,</t>
+  </si>
+  <si>
+    <t>general femdom kinky videos,some large studios but overall mid to high quality</t>
+  </si>
+  <si>
+    <t>https://xhamster44.desi/videos/clean-and-clear-xhUNQAP?pw=</t>
+  </si>
+  <si>
+    <t>spanking,wedgie,enema,oiled,vibrator,strapon</t>
+  </si>
+  <si>
+    <t>standing,inverted pussy over face,missionary</t>
+  </si>
+  <si>
+    <t>spanking at 1m,wedgie at 2m,hair tied to wedgie,enema at 3m,inverted pussy over face at 5m,missionary at 9m</t>
+  </si>
+  <si>
+    <t>xhamster44.desi</t>
+  </si>
+  <si>
+    <t>punishworld.com</t>
+  </si>
+  <si>
+    <t>bdsmstreak.com</t>
+  </si>
+  <si>
+    <t>m.hqporner.com</t>
+  </si>
+  <si>
+    <t>www.pornhits.com</t>
+  </si>
+  <si>
+    <t>spankbang.com</t>
+  </si>
+  <si>
+    <t>www.txxx.porn</t>
+  </si>
+  <si>
+    <t>beeg.com</t>
+  </si>
+  <si>
+    <t>www.porntry.com</t>
+  </si>
+  <si>
+    <t>abjav.com</t>
+  </si>
+  <si>
+    <t>abxxx.com</t>
+  </si>
+  <si>
+    <t>www.tnaflix.com</t>
+  </si>
+  <si>
+    <t>pornxp.com</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/bdsm-extreme</t>
+  </si>
+  <si>
+    <t>ball gag,gangbang,pretzel,fisting</t>
+  </si>
+  <si>
+    <t>missionary,laying down,pretzel</t>
+  </si>
+  <si>
+    <t>general type of common bdsm videos with woman on woman as well</t>
+  </si>
+  <si>
+    <t>https://www.tubebdsm.com/category/strap-on-femdom</t>
+  </si>
+  <si>
+    <t>pegging,humiliation,2f-1m,chastity</t>
+  </si>
+  <si>
+    <t>doggy,missionary,laying down</t>
+  </si>
+  <si>
+    <t>decent low and mid quality femdom porn no studios</t>
+  </si>
+  <si>
+    <t>https://abbdsm.com/video/141957/hot-submissive-teen-18-babe-gets-ass-destroyed-in-anal-sex-domination-fuck/</t>
+  </si>
+  <si>
+    <t>teen,fingering,butt plug,spanking,side fuck,anal</t>
+  </si>
+  <si>
+    <t>doggy,side fuck,full nelson</t>
+  </si>
+  <si>
+    <t>spanking at 3m,full nelson at end</t>
+  </si>
+  <si>
+    <t>abbdsm.com</t>
+  </si>
+  <si>
+    <t>https://xhamster44.desi/videos/chastity-gloves-and-condoms-how-many-until-he-doesnt-feel-anything-xhTMLsQ?pw=</t>
+  </si>
+  <si>
+    <t>malice jade</t>
+  </si>
+  <si>
+    <t>chastity,gloves,condoms,edging</t>
+  </si>
+  <si>
+    <t>sitting</t>
+  </si>
+  <si>
+    <t>malice jade from reddit,uncage at 2m</t>
+  </si>
+  <si>
+    <t>curebdsm.com</t>
+  </si>
+  <si>
+    <t>hcbdsm.com</t>
+  </si>
+  <si>
+    <t>www.porntrex.com</t>
+  </si>
+  <si>
+    <t>txxx.com</t>
+  </si>
+  <si>
+    <t>punishbang.com</t>
+  </si>
+  <si>
+    <t>spankbang.party</t>
+  </si>
+  <si>
+    <t>txxx.me</t>
+  </si>
+  <si>
+    <t>www.porndead.org</t>
+  </si>
+  <si>
+    <t>xhamster18.desi</t>
+  </si>
+  <si>
+    <t>netfapx.net</t>
+  </si>
+  <si>
+    <t>pornzog</t>
+  </si>
+  <si>
+    <t>www.tubegalore.com</t>
+  </si>
+  <si>
+    <t>pervtube.net</t>
+  </si>
+  <si>
+    <t>www.pornhub.com</t>
+  </si>
+  <si>
+    <t>anyporn.com</t>
+  </si>
+  <si>
+    <t>www.porntopedia.com</t>
+  </si>
+  <si>
+    <t>www.peekvids.com</t>
+  </si>
+  <si>
+    <t>www.omg.xxx</t>
   </si>
 </sst>
 </file>
@@ -2342,14 +2506,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6161"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -2640,7 +2797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <dimension ref="A1:K146"/>
+  <dimension ref="A1:K152"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" style="1" customWidth="1"/>
@@ -2722,9 +2879,8 @@
       <c r="J2" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="K2" s="2" t="str" cm="1">
-        <f t="array" ref="K2">_xlfn.REGEXEXTRACT(A2,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+      <c r="K2" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -2758,9 +2914,8 @@
       <c r="J3" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="K3" s="2" t="str" cm="1">
-        <f t="array" ref="K3">_xlfn.REGEXEXTRACT(A3,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+      <c r="K3" s="2" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2794,9 +2949,8 @@
       <c r="J4" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="K4" s="2" t="str" cm="1">
-        <f t="array" ref="K4">_xlfn.REGEXEXTRACT(A4,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+      <c r="K4" s="2" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2830,9 +2984,8 @@
       <c r="J5" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="K5" s="2" t="str" cm="1">
-        <f t="array" ref="K5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+      <c r="K5" s="2" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -2866,104 +3019,101 @@
       <c r="J6" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="K6" s="2" t="str" cm="1">
-        <f t="array" ref="K6">_xlfn.REGEXEXTRACT(A6,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="K6" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>298</v>
+        <v>738</v>
       </c>
       <c r="B7" s="2">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>328</v>
+        <v>386</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>449</v>
+        <v>739</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>450</v>
+        <v>740</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="K7" s="2" t="str" cm="1">
-        <f t="array" ref="K7">_xlfn.REGEXEXTRACT(A7,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>741</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>742</v>
       </c>
       <c r="B8" s="2">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>208</v>
+        <v>111</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>451</v>
+        <v>328</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>452</v>
+        <v>743</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>453</v>
+        <v>744</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K8" s="2" t="str" cm="1">
-        <f t="array" ref="K8">_xlfn.REGEXEXTRACT(A8,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B9" s="2">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>145</v>
+        <v>328</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>49</v>
@@ -2972,34 +3122,33 @@
         <v>7</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="K9" s="2" t="str" cm="1">
-        <f t="array" ref="K9">_xlfn.REGEXEXTRACT(A9,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>299</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>260</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2">
+        <v>85</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>49</v>
@@ -3008,34 +3157,33 @@
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="K10" s="2" t="str" cm="1">
-        <f t="array" ref="K10">_xlfn.REGEXEXTRACT(A10,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>295</v>
       </c>
       <c r="B11" s="2">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>211</v>
+        <v>296</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
@@ -3044,34 +3192,33 @@
         <v>7</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="2" t="str" cm="1">
-        <f t="array" ref="K11">_xlfn.REGEXEXTRACT(A11,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>297</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>126</v>
+        <v>260</v>
       </c>
       <c r="B12" s="2">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>49</v>
@@ -3080,34 +3227,33 @@
         <v>7</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K12" s="2" t="str" cm="1">
-        <f t="array" ref="K12">_xlfn.REGEXEXTRACT(A12,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>94</v>
+        <v>211</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>459</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>49</v>
@@ -3116,34 +3262,33 @@
         <v>7</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K13" s="2" t="str" cm="1">
-        <f t="array" ref="K13">_xlfn.REGEXEXTRACT(A13,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B14" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>49</v>
@@ -3152,34 +3297,33 @@
         <v>7</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="K14" s="2" t="str" cm="1">
-        <f t="array" ref="K14">_xlfn.REGEXEXTRACT(A14,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>245</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>355</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>261</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>466</v>
+        <v>95</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>49</v>
@@ -3188,34 +3332,33 @@
         <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K15" s="2" t="str" cm="1">
-        <f t="array" ref="K15">_xlfn.REGEXEXTRACT(A15,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>392</v>
+        <v>129</v>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>386</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>49</v>
@@ -3224,34 +3367,33 @@
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="K16" s="2" t="str" cm="1">
-        <f t="array" ref="K16">_xlfn.REGEXEXTRACT(A16,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>235</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>385</v>
+        <v>73</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>395</v>
+        <v>261</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>396</v>
+        <v>75</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>49</v>
@@ -3260,16 +3402,15 @@
         <v>7</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="K17" s="2" t="str" cm="1">
-        <f t="array" ref="K17">_xlfn.REGEXEXTRACT(A17,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B18" s="2">
         <v>0</v>
@@ -3284,10 +3425,10 @@
         <v>75</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -3296,16 +3437,15 @@
         <v>7</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="K18" s="2" t="str" cm="1">
-        <f t="array" ref="K18">_xlfn.REGEXEXTRACT(A18,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -3314,16 +3454,16 @@
         <v>385</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>75</v>
+        <v>396</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>49</v>
@@ -3332,32 +3472,33 @@
         <v>7</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="K19" s="2" t="str" cm="1">
-        <f t="array" ref="K19">_xlfn.REGEXEXTRACT(A19,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>385</v>
+        <v>73</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>386</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F20" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>471</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>49</v>
@@ -3366,16 +3507,15 @@
         <v>7</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="K20" s="2" t="str" cm="1">
-        <f t="array" ref="K20">_xlfn.REGEXEXTRACT(A20,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>399</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B21" s="2">
         <v>0</v>
@@ -3387,11 +3527,13 @@
         <v>386</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>473</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>49</v>
@@ -3400,34 +3542,31 @@
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="K21" s="2" t="str" cm="1">
-        <f t="array" ref="K21">_xlfn.REGEXEXTRACT(A21,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="B22" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>65</v>
+        <v>385</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>477</v>
+        <v>386</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>478</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>49</v>
@@ -3436,16 +3575,15 @@
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K22" s="2" t="str" cm="1">
-        <f t="array" ref="K22">_xlfn.REGEXEXTRACT(A22,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>404</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B23" s="2">
         <v>0</v>
@@ -3457,13 +3595,11 @@
         <v>386</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>480</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>49</v>
@@ -3472,142 +3608,138 @@
         <v>7</v>
       </c>
       <c r="J23" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="K23" s="2" t="str" cm="1">
-        <f t="array" ref="K23">_xlfn.REGEXEXTRACT(A23,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="K25" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B26" s="2">
         <v>113</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="I24" s="2">
-        <v>6</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="K24" s="2" t="str" cm="1">
-        <f t="array" ref="K24">_xlfn.REGEXEXTRACT(A24,"(?&lt;=//)[^/]+")</f>
-        <v>abjav.com</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="2">
-        <v>83</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" s="2">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K25" s="2" t="str" cm="1">
-        <f t="array" ref="K25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B26" s="2">
-        <v>66</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="I26" s="2">
         <v>6</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K26" s="2" t="str" cm="1">
-        <f t="array" ref="K26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>337</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>263</v>
+        <v>77</v>
       </c>
       <c r="B27" s="2">
+        <v>83</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>49</v>
@@ -3616,34 +3748,33 @@
         <v>6</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="K27" s="2" t="str" cm="1">
-        <f t="array" ref="K27">_xlfn.REGEXEXTRACT(A27,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>105</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>9</v>
+        <v>289</v>
       </c>
       <c r="B28" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>49</v>
@@ -3652,34 +3783,33 @@
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K28" s="2" t="str" cm="1">
-        <f t="array" ref="K28">_xlfn.REGEXEXTRACT(A28,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>263</v>
       </c>
       <c r="B29" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>62</v>
+        <v>240</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>49</v>
@@ -3688,34 +3818,33 @@
         <v>6</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K29" s="2" t="str" cm="1">
-        <f t="array" ref="K29">_xlfn.REGEXEXTRACT(A29,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B30" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>494</v>
+        <v>255</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>49</v>
@@ -3724,34 +3853,33 @@
         <v>6</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K30" s="2" t="str" cm="1">
-        <f t="array" ref="K30">_xlfn.REGEXEXTRACT(A30,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>256</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>212</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>49</v>
@@ -3760,34 +3888,33 @@
         <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K31" s="2" t="str" cm="1">
-        <f t="array" ref="K31">_xlfn.REGEXEXTRACT(A31,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>97</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>238</v>
+        <v>494</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>49</v>
@@ -3796,34 +3923,33 @@
         <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K32" s="2" t="str" cm="1">
-        <f t="array" ref="K32">_xlfn.REGEXEXTRACT(A32,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>96</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>49</v>
@@ -3832,34 +3958,33 @@
         <v>6</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="K33" s="2" t="str" cm="1">
-        <f t="array" ref="K33">_xlfn.REGEXEXTRACT(A33,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="B34" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>49</v>
@@ -3868,34 +3993,33 @@
         <v>6</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="K34" s="2" t="str" cm="1">
-        <f t="array" ref="K34">_xlfn.REGEXEXTRACT(A34,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>239</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>205</v>
+        <v>93</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>49</v>
@@ -3904,34 +4028,33 @@
         <v>6</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="K35" s="2" t="str" cm="1">
-        <f t="array" ref="K35">_xlfn.REGEXEXTRACT(A35,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B36" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>49</v>
@@ -3940,34 +4063,33 @@
         <v>6</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="K36" s="2" t="str" cm="1">
-        <f t="array" ref="K36">_xlfn.REGEXEXTRACT(A36,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B37" s="2">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>49</v>
@@ -3976,70 +4098,68 @@
         <v>6</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="K37" s="2" t="str" cm="1">
-        <f t="array" ref="K37">_xlfn.REGEXEXTRACT(A37,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>207</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>313</v>
+        <v>136</v>
       </c>
       <c r="B38" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>328</v>
+        <v>171</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>314</v>
+        <v>49</v>
       </c>
       <c r="I38" s="2">
         <v>6</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="K38" s="2" t="str" cm="1">
-        <f t="array" ref="K38">_xlfn.REGEXEXTRACT(A38,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>409</v>
+        <v>10</v>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>385</v>
+        <v>64</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>49</v>
@@ -4048,70 +4168,68 @@
         <v>6</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="K39" s="2" t="str" cm="1">
-        <f t="array" ref="K39">_xlfn.REGEXEXTRACT(A39,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>193</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>411</v>
+        <v>313</v>
       </c>
       <c r="B40" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>386</v>
+        <v>328</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>49</v>
+        <v>314</v>
       </c>
       <c r="I40" s="2">
         <v>6</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="K40" s="2" t="str" cm="1">
-        <f t="array" ref="K40">_xlfn.REGEXEXTRACT(A40,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B41" s="2">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>226</v>
+        <v>385</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>386</v>
+        <v>187</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>49</v>
@@ -4120,22 +4238,21 @@
         <v>6</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K41" s="2" t="str" cm="1">
-        <f t="array" ref="K41">_xlfn.REGEXEXTRACT(A41,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>386</v>
@@ -4144,10 +4261,10 @@
         <v>75</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>49</v>
@@ -4156,34 +4273,33 @@
         <v>6</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="K42" s="2" t="str" cm="1">
-        <f t="array" ref="K42">_xlfn.REGEXEXTRACT(A42,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>385</v>
+        <v>226</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>386</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>49</v>
@@ -4192,16 +4308,15 @@
         <v>6</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="K43" s="2" t="str" cm="1">
-        <f t="array" ref="K43">_xlfn.REGEXEXTRACT(A43,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>414</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B44" s="2">
         <v>0</v>
@@ -4216,10 +4331,10 @@
         <v>75</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>49</v>
@@ -4228,16 +4343,15 @@
         <v>6</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="K44" s="2" t="str" cm="1">
-        <f t="array" ref="K44">_xlfn.REGEXEXTRACT(A44,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>416</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B45" s="2">
         <v>0</v>
@@ -4252,10 +4366,10 @@
         <v>75</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>49</v>
@@ -4264,34 +4378,33 @@
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="K45" s="2" t="str" cm="1">
-        <f t="array" ref="K45">_xlfn.REGEXEXTRACT(A45,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>418</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B46" s="2">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>386</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>49</v>
@@ -4300,34 +4413,33 @@
         <v>6</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K46" s="2" t="str" cm="1">
-        <f t="array" ref="K46">_xlfn.REGEXEXTRACT(A46,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="B47" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>49</v>
@@ -4336,286 +4448,278 @@
         <v>6</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K47" s="2" t="str" cm="1">
-        <f t="array" ref="K47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>422</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>317</v>
+        <v>423</v>
       </c>
       <c r="B48" s="2">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>531</v>
+        <v>386</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I48" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="K48" s="2" t="str" cm="1">
-        <f t="array" ref="K48">_xlfn.REGEXEXTRACT(A48,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B49" s="2">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>531</v>
+        <v>364</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I49" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="K49" s="2" t="str" cm="1">
-        <f t="array" ref="K49">_xlfn.REGEXEXTRACT(A49,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>302</v>
+        <v>759</v>
       </c>
       <c r="B50" s="2">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>303</v>
+        <v>385</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>304</v>
+        <v>386</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>536</v>
+        <v>760</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>537</v>
+        <v>761</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I50" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K50" s="2" t="str" cm="1">
-        <f t="array" ref="K50">_xlfn.REGEXEXTRACT(A50,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>762</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>300</v>
+        <v>763</v>
       </c>
       <c r="B51" s="2">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>62</v>
+        <v>385</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>538</v>
+        <v>386</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>539</v>
+        <v>764</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>540</v>
+        <v>765</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I51" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K51" s="2" t="str" cm="1">
-        <f t="array" ref="K51">_xlfn.REGEXEXTRACT(A51,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>766</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>286</v>
+        <v>767</v>
       </c>
       <c r="B52" s="2">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>541</v>
+        <v>768</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>542</v>
+        <v>769</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I52" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K52" s="2" t="str" cm="1">
-        <f t="array" ref="K52">_xlfn.REGEXEXTRACT(A52,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>770</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>279</v>
+        <v>772</v>
       </c>
       <c r="B53" s="2">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>65</v>
+        <v>773</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>280</v>
+        <v>773</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" s="2">
+        <v>6</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B54" s="2">
+        <v>129</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="2">
-        <v>5</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K53" s="2" t="str" cm="1">
-        <f t="array" ref="K53">_xlfn.REGEXEXTRACT(A53,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B54" s="2">
-        <v>60</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="I54" s="2">
         <v>5</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="K54" s="2" t="str" cm="1">
-        <f t="array" ref="K54">_xlfn.REGEXEXTRACT(A54,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>21</v>
+        <v>331</v>
       </c>
       <c r="B55" s="2">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>62</v>
+        <v>328</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>49</v>
@@ -4624,34 +4728,33 @@
         <v>5</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K55" s="2" t="str" cm="1">
-        <f t="array" ref="K55">_xlfn.REGEXEXTRACT(A55,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>42</v>
+        <v>302</v>
       </c>
       <c r="B56" s="2">
+        <v>116</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>49</v>
@@ -4660,34 +4763,33 @@
         <v>5</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="K56" s="2" t="str" cm="1">
-        <f t="array" ref="K56">_xlfn.REGEXEXTRACT(A56,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="B57" s="2">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>183</v>
+        <v>538</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>49</v>
@@ -4696,34 +4798,33 @@
         <v>5</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K57" s="2" t="str" cm="1">
-        <f t="array" ref="K57">_xlfn.REGEXEXTRACT(A57,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>301</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>27</v>
+        <v>286</v>
       </c>
       <c r="B58" s="2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>328</v>
+        <v>65</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>49</v>
@@ -4732,34 +4833,33 @@
         <v>5</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K58" s="2" t="str" cm="1">
-        <f t="array" ref="K58">_xlfn.REGEXEXTRACT(A58,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>288</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>17</v>
+        <v>279</v>
       </c>
       <c r="B59" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>49</v>
@@ -4768,34 +4868,33 @@
         <v>5</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="K59" s="2" t="str" cm="1">
-        <f t="array" ref="K59">_xlfn.REGEXEXTRACT(A59,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
       <c r="B60" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>49</v>
@@ -4804,34 +4903,33 @@
         <v>5</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K60" s="2" t="str" cm="1">
-        <f t="array" ref="K60">_xlfn.REGEXEXTRACT(A60,"(?&lt;=//)[^/]+")</f>
-        <v>hcbdsm.com</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B61" s="2">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>231</v>
+        <v>547</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>560</v>
+        <v>82</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>49</v>
@@ -4840,34 +4938,33 @@
         <v>5</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="K61" s="2" t="str" cm="1">
-        <f t="array" ref="K61">_xlfn.REGEXEXTRACT(A61,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>84</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>357</v>
+        <v>42</v>
       </c>
       <c r="B62" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>358</v>
+        <v>214</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>49</v>
@@ -4876,34 +4973,33 @@
         <v>5</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="K62" s="2" t="str" cm="1">
-        <f t="array" ref="K62">_xlfn.REGEXEXTRACT(A62,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntrex.com</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B63" s="2">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>563</v>
+        <v>183</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>49</v>
@@ -4912,34 +5008,33 @@
         <v>5</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="K63" s="2" t="str" cm="1">
-        <f t="array" ref="K63">_xlfn.REGEXEXTRACT(A63,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>252</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B64" s="2">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>196</v>
+        <v>328</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>566</v>
+        <v>328</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>49</v>
@@ -4948,34 +5043,33 @@
         <v>5</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K64" s="2" t="str" cm="1">
-        <f t="array" ref="K64">_xlfn.REGEXEXTRACT(A64,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B65" s="2">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>185</v>
+        <v>65</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>569</v>
+        <v>242</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>49</v>
@@ -4984,34 +5078,33 @@
         <v>5</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="K65" s="2" t="str" cm="1">
-        <f t="array" ref="K65">_xlfn.REGEXEXTRACT(A65,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B66" s="2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>64</v>
+        <v>240</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>49</v>
@@ -5020,34 +5113,33 @@
         <v>5</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K66" s="2" t="str" cm="1">
-        <f t="array" ref="K66">_xlfn.REGEXEXTRACT(A66,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B67" s="2">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>574</v>
+        <v>231</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>49</v>
@@ -5056,34 +5148,33 @@
         <v>5</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K67" s="2" t="str" cm="1">
-        <f t="array" ref="K67">_xlfn.REGEXEXTRACT(A67,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="B68" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>328</v>
+        <v>226</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>49</v>
@@ -5092,34 +5183,33 @@
         <v>5</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="K68" s="2" t="str" cm="1">
-        <f t="array" ref="K68">_xlfn.REGEXEXTRACT(A68,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>340</v>
+        <v>128</v>
       </c>
       <c r="B69" s="2">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>341</v>
+        <v>65</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>328</v>
+        <v>563</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>342</v>
+        <v>57</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>60</v>
+        <v>565</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>49</v>
@@ -5128,34 +5218,33 @@
         <v>5</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="K69" s="2" t="str" cm="1">
-        <f t="array" ref="K69">_xlfn.REGEXEXTRACT(A69,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="B70" s="2">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>149</v>
+        <v>566</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>109</v>
+        <v>568</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>49</v>
@@ -5164,34 +5253,33 @@
         <v>5</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K70" s="2" t="str" cm="1">
-        <f t="array" ref="K70">_xlfn.REGEXEXTRACT(A70,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="B71" s="2">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>146</v>
+        <v>569</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>49</v>
@@ -5200,70 +5288,68 @@
         <v>5</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K71" s="2" t="str" cm="1">
-        <f t="array" ref="K71">_xlfn.REGEXEXTRACT(A71,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="B72" s="2">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>328</v>
+        <v>64</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>328</v>
+        <v>70</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>327</v>
+        <v>573</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I72" s="2">
         <v>5</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K72" s="2" t="str" cm="1">
-        <f t="array" ref="K72">_xlfn.REGEXEXTRACT(A72,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>425</v>
+        <v>28</v>
       </c>
       <c r="B73" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>426</v>
+        <v>64</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>427</v>
+        <v>574</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>49</v>
@@ -5272,34 +5358,33 @@
         <v>5</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="K73" s="2" t="str" cm="1">
-        <f t="array" ref="K73">_xlfn.REGEXEXTRACT(A73,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>99</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>429</v>
+        <v>329</v>
       </c>
       <c r="B74" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>385</v>
+        <v>328</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>386</v>
+        <v>328</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>49</v>
@@ -5308,34 +5393,33 @@
         <v>5</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="K74" s="2" t="str" cm="1">
-        <f t="array" ref="K74">_xlfn.REGEXEXTRACT(A74,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="B75" s="2">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>367</v>
+        <v>328</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>75</v>
+        <v>342</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>589</v>
+        <v>60</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>49</v>
@@ -5344,34 +5428,33 @@
         <v>5</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="K75" s="2" t="str" cm="1">
-        <f t="array" ref="K75">_xlfn.REGEXEXTRACT(A75,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>369</v>
+        <v>142</v>
       </c>
       <c r="B76" s="2">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>326</v>
+        <v>148</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>590</v>
+        <v>149</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>592</v>
+        <v>109</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>49</v>
@@ -5380,34 +5463,33 @@
         <v>5</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="K76" s="2" t="str" cm="1">
-        <f t="array" ref="K76">_xlfn.REGEXEXTRACT(A76,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>378</v>
+        <v>132</v>
       </c>
       <c r="B77" s="2">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>379</v>
+        <v>146</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>49</v>
@@ -5416,19 +5498,18 @@
         <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="K77" s="2" t="str" cm="1">
-        <f t="array" ref="K77">_xlfn.REGEXEXTRACT(A77,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B78" s="2">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>328</v>
@@ -5437,229 +5518,223 @@
         <v>328</v>
       </c>
       <c r="E78" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I78" s="2">
+        <v>5</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B79" s="2">
+        <v>0</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I78" s="2">
-        <v>4</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="K78" s="2" t="str" cm="1">
-        <f t="array" ref="K78">_xlfn.REGEXEXTRACT(A78,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B79" s="2">
-        <v>170</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I79" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="K79" s="2" t="str" cm="1">
-        <f t="array" ref="K79">_xlfn.REGEXEXTRACT(A79,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>114</v>
+        <v>429</v>
       </c>
       <c r="B80" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>111</v>
+        <v>385</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>600</v>
+        <v>386</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>602</v>
+        <v>587</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I80" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K80" s="2" t="str" cm="1">
-        <f t="array" ref="K80">_xlfn.REGEXEXTRACT(A80,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>430</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>35</v>
+        <v>366</v>
       </c>
       <c r="B81" s="2">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>73</v>
+        <v>326</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>74</v>
+        <v>367</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>603</v>
+        <v>588</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I81" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K81" s="2" t="str" cm="1">
-        <f t="array" ref="K81">_xlfn.REGEXEXTRACT(A81,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="B82" s="2">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>308</v>
+        <v>590</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I82" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="K82" s="2" t="str" cm="1">
-        <f t="array" ref="K82">_xlfn.REGEXEXTRACT(A82,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>274</v>
+        <v>378</v>
       </c>
       <c r="B83" s="2">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>607</v>
+        <v>379</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>608</v>
+        <v>593</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I83" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K83" s="2" t="str" cm="1">
-        <f t="array" ref="K83">_xlfn.REGEXEXTRACT(A83,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>380</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>16</v>
+        <v>324</v>
       </c>
       <c r="B84" s="2">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>112</v>
+        <v>328</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>610</v>
+        <v>328</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>49</v>
@@ -5668,34 +5743,33 @@
         <v>4</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K84" s="2" t="str" cm="1">
-        <f t="array" ref="K84">_xlfn.REGEXEXTRACT(A84,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>325</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>272</v>
+        <v>321</v>
       </c>
       <c r="B85" s="2">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>62</v>
+        <v>322</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>49</v>
@@ -5704,34 +5778,33 @@
         <v>4</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K85" s="2" t="str" cm="1">
-        <f t="array" ref="K85">_xlfn.REGEXEXTRACT(A85,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="B86" s="2">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>213</v>
+        <v>600</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>49</v>
@@ -5740,34 +5813,33 @@
         <v>4</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K86" s="2" t="str" cm="1">
-        <f t="array" ref="K86">_xlfn.REGEXEXTRACT(A86,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>115</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B87" s="2">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>49</v>
@@ -5776,34 +5848,33 @@
         <v>4</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K87" s="2" t="str" cm="1">
-        <f t="array" ref="K87">_xlfn.REGEXEXTRACT(A87,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>13</v>
+        <v>306</v>
       </c>
       <c r="B88" s="2">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>65</v>
+        <v>307</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>49</v>
@@ -5812,34 +5883,33 @@
         <v>4</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="K88" s="2" t="str" cm="1">
-        <f t="array" ref="K88">_xlfn.REGEXEXTRACT(A88,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>7</v>
+        <v>274</v>
       </c>
       <c r="B89" s="2">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>328</v>
+        <v>607</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>49</v>
@@ -5848,34 +5918,33 @@
         <v>4</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K89" s="2" t="str" cm="1">
-        <f t="array" ref="K89">_xlfn.REGEXEXTRACT(A89,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
+        <v>275</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B90" s="2">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>229</v>
+        <v>610</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>49</v>
@@ -5884,34 +5953,33 @@
         <v>4</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="K90" s="2" t="str" cm="1">
-        <f t="array" ref="K90">_xlfn.REGEXEXTRACT(A90,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>61</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>22</v>
+        <v>272</v>
       </c>
       <c r="B91" s="2">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>223</v>
+        <v>613</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>49</v>
@@ -5920,34 +5988,33 @@
         <v>4</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K91" s="2" t="str" cm="1">
-        <f t="array" ref="K91">_xlfn.REGEXEXTRACT(A91,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>273</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B92" s="2">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>49</v>
@@ -5956,34 +6023,33 @@
         <v>4</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="K92" s="2" t="str" cm="1">
-        <f t="array" ref="K92">_xlfn.REGEXEXTRACT(A92,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>66</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="B93" s="2">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>328</v>
+        <v>205</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>630</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>220</v>
+        <v>58</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>49</v>
@@ -5992,34 +6058,33 @@
         <v>4</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K93" s="2" t="str" cm="1">
-        <f t="array" ref="K93">_xlfn.REGEXEXTRACT(A93,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
+        <v>250</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="B94" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>49</v>
@@ -6028,34 +6093,33 @@
         <v>4</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K94" s="2" t="str" cm="1">
-        <f t="array" ref="K94">_xlfn.REGEXEXTRACT(A94,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>251</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B95" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>49</v>
@@ -6064,34 +6128,33 @@
         <v>4</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K95" s="2" t="str" cm="1">
-        <f t="array" ref="K95">_xlfn.REGEXEXTRACT(A95,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="B96" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>49</v>
@@ -6100,34 +6163,33 @@
         <v>4</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="K96" s="2" t="str" cm="1">
-        <f t="array" ref="K96">_xlfn.REGEXEXTRACT(A96,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>230</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="B97" s="2">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>175</v>
+        <v>57</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>72</v>
+        <v>627</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>49</v>
@@ -6136,34 +6198,33 @@
         <v>4</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="K97" s="2" t="str" cm="1">
-        <f t="array" ref="K97">_xlfn.REGEXEXTRACT(A97,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
+        <v>224</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="B98" s="2">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>640</v>
+        <v>216</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>49</v>
@@ -6172,34 +6233,33 @@
         <v>4</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="K98" s="2" t="str" cm="1">
-        <f t="array" ref="K98">_xlfn.REGEXEXTRACT(A98,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>352</v>
+        <v>127</v>
       </c>
       <c r="B99" s="2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>117</v>
+        <v>328</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>353</v>
+        <v>630</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>49</v>
@@ -6208,34 +6268,33 @@
         <v>4</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="K99" s="2" t="str" cm="1">
-        <f t="array" ref="K99">_xlfn.REGEXEXTRACT(A99,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B100" s="2">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>49</v>
@@ -6244,34 +6303,33 @@
         <v>4</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="K100" s="2" t="str" cm="1">
-        <f t="array" ref="K100">_xlfn.REGEXEXTRACT(A100,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B101" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>160</v>
+        <v>68</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>199</v>
+        <v>636</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>49</v>
@@ -6280,34 +6338,33 @@
         <v>4</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K101" s="2" t="str" cm="1">
-        <f t="array" ref="K101">_xlfn.REGEXEXTRACT(A101,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>144</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B102" s="2">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>49</v>
@@ -6316,34 +6373,33 @@
         <v>4</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="K102" s="2" t="str" cm="1">
-        <f t="array" ref="K102">_xlfn.REGEXEXTRACT(A102,"(?&lt;=//)[^/]+")</f>
-        <v>www.porndead.org</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="B103" s="2">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>651</v>
+        <v>72</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>49</v>
@@ -6352,34 +6408,33 @@
         <v>4</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K103" s="2" t="str" cm="1">
-        <f t="array" ref="K103">_xlfn.REGEXEXTRACT(A103,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster18.desi</v>
+        <v>181</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>431</v>
+        <v>123</v>
       </c>
       <c r="B104" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>385</v>
+        <v>62</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>386</v>
+        <v>640</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>403</v>
+        <v>57</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>49</v>
@@ -6388,34 +6443,33 @@
         <v>4</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="K104" s="2" t="str" cm="1">
-        <f t="array" ref="K104">_xlfn.REGEXEXTRACT(A104,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>653</v>
+        <v>352</v>
       </c>
       <c r="B105" s="2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>385</v>
+        <v>117</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>386</v>
+        <v>353</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>403</v>
+        <v>75</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>49</v>
@@ -6424,70 +6478,68 @@
         <v>4</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="K105" s="2" t="str" cm="1">
-        <f t="array" ref="K105">_xlfn.REGEXEXTRACT(A105,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog</v>
+        <v>354</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>434</v>
+        <v>135</v>
       </c>
       <c r="B106" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>385</v>
+        <v>160</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>386</v>
+        <v>159</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I106" s="2">
         <v>4</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="K106" s="2" t="str" cm="1">
-        <f t="array" ref="K106">_xlfn.REGEXEXTRACT(A106,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>371</v>
+        <v>4</v>
       </c>
       <c r="B107" s="2">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>326</v>
+        <v>160</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>372</v>
+        <v>158</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>594</v>
+        <v>199</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>49</v>
@@ -6496,34 +6548,33 @@
         <v>4</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="K107" s="2" t="str" cm="1">
-        <f t="array" ref="K107">_xlfn.REGEXEXTRACT(A107,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="B108" s="2">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>326</v>
+        <v>154</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>657</v>
+        <v>69</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>49</v>
@@ -6532,286 +6583,278 @@
         <v>4</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="K108" s="2" t="str" cm="1">
-        <f t="array" ref="K108">_xlfn.REGEXEXTRACT(A108,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="B109" s="2">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>328</v>
+        <v>209</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>531</v>
+        <v>149</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I109" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="K109" s="2" t="str" cm="1">
-        <f t="array" ref="K109">_xlfn.REGEXEXTRACT(A109,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>150</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>23</v>
+        <v>431</v>
       </c>
       <c r="B110" s="2">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>113</v>
+        <v>385</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>215</v>
+        <v>386</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>57</v>
+        <v>403</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I110" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K110" s="2" t="str" cm="1">
-        <f t="array" ref="K110">_xlfn.REGEXEXTRACT(A110,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>432</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>137</v>
+        <v>653</v>
       </c>
       <c r="B111" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>62</v>
+        <v>385</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>57</v>
+        <v>403</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>72</v>
+        <v>652</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I111" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="K111" s="2" t="str" cm="1">
-        <f t="array" ref="K111">_xlfn.REGEXEXTRACT(A111,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>310</v>
+        <v>434</v>
       </c>
       <c r="B112" s="2">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>64</v>
+        <v>385</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>311</v>
+        <v>386</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="I112" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K112" s="2" t="str" cm="1">
-        <f t="array" ref="K112">_xlfn.REGEXEXTRACT(A112,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>36</v>
+        <v>371</v>
       </c>
       <c r="B113" s="2">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>208</v>
+        <v>326</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>667</v>
+        <v>372</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>669</v>
+        <v>594</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I113" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K113" s="2" t="str" cm="1">
-        <f t="array" ref="K113">_xlfn.REGEXEXTRACT(A113,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>247</v>
+        <v>374</v>
       </c>
       <c r="B114" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>73</v>
+        <v>326</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>248</v>
+        <v>657</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>528</v>
+        <v>659</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I114" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="K114" s="2" t="str" cm="1">
-        <f t="array" ref="K114">_xlfn.REGEXEXTRACT(A114,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="B115" s="2">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>73</v>
+        <v>328</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>80</v>
+        <v>531</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>594</v>
+        <v>661</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="I115" s="2">
         <v>3</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K115" s="2" t="str" cm="1">
-        <f t="array" ref="K115">_xlfn.REGEXEXTRACT(A115,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B116" s="2">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>49</v>
@@ -6820,34 +6863,33 @@
         <v>3</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K116" s="2" t="str" cm="1">
-        <f t="array" ref="K116">_xlfn.REGEXEXTRACT(A116,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>332</v>
+        <v>137</v>
       </c>
       <c r="B117" s="2">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>328</v>
+        <v>62</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>674</v>
+        <v>183</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>175</v>
+        <v>57</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>676</v>
+        <v>72</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>49</v>
@@ -6856,70 +6898,68 @@
         <v>3</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K117" s="2" t="str" cm="1">
-        <f t="array" ref="K117">_xlfn.REGEXEXTRACT(A117,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="B118" s="2">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>85</v>
+        <v>311</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="I118" s="2">
         <v>3</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K118" s="2" t="str" cm="1">
-        <f t="array" ref="K118">_xlfn.REGEXEXTRACT(A118,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="B119" s="2">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>177</v>
+        <v>667</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>49</v>
@@ -6928,34 +6968,33 @@
         <v>3</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="K119" s="2" t="str" cm="1">
-        <f t="array" ref="K119">_xlfn.REGEXEXTRACT(A119,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>103</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="B120" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>69</v>
+        <v>248</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>682</v>
+        <v>528</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>49</v>
@@ -6964,34 +7003,33 @@
         <v>3</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="K120" s="2" t="str" cm="1">
-        <f t="array" ref="K120">_xlfn.REGEXEXTRACT(A120,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="B121" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>684</v>
+        <v>594</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>49</v>
@@ -7000,34 +7038,33 @@
         <v>3</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K121" s="2" t="str" cm="1">
-        <f t="array" ref="K121">_xlfn.REGEXEXTRACT(A121,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>106</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B122" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>685</v>
+        <v>227</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>49</v>
@@ -7036,34 +7073,33 @@
         <v>3</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K122" s="2" t="str" cm="1">
-        <f t="array" ref="K122">_xlfn.REGEXEXTRACT(A122,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>228</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>41</v>
+        <v>332</v>
       </c>
       <c r="B123" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>170</v>
+        <v>328</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>49</v>
@@ -7072,70 +7108,68 @@
         <v>3</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K123" s="2" t="str" cm="1">
-        <f t="array" ref="K123">_xlfn.REGEXEXTRACT(A123,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="B124" s="2">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="I124" s="2">
         <v>3</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K124" s="2" t="str" cm="1">
-        <f t="array" ref="K124">_xlfn.REGEXEXTRACT(A124,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>107</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="B125" s="2">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>69</v>
+        <v>177</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>49</v>
@@ -7144,34 +7178,33 @@
         <v>3</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="K125" s="2" t="str" cm="1">
-        <f t="array" ref="K125">_xlfn.REGEXEXTRACT(A125,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>219</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>49</v>
@@ -7180,34 +7213,33 @@
         <v>3</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="K126" s="2" t="str" cm="1">
-        <f t="array" ref="K126">_xlfn.REGEXEXTRACT(A126,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="B127" s="2">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>697</v>
+        <v>190</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>109</v>
+        <v>684</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>49</v>
@@ -7216,34 +7248,33 @@
         <v>3</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K127" s="2" t="str" cm="1">
-        <f t="array" ref="K127">_xlfn.REGEXEXTRACT(A127,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B128" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>163</v>
+        <v>685</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>59</v>
+        <v>687</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>49</v>
@@ -7252,34 +7283,33 @@
         <v>3</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="K128" s="2" t="str" cm="1">
-        <f t="array" ref="K128">_xlfn.REGEXEXTRACT(A128,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>182</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="B129" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>152</v>
+        <v>688</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>49</v>
@@ -7288,34 +7318,33 @@
         <v>3</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K129" s="2" t="str" cm="1">
-        <f t="array" ref="K129">_xlfn.REGEXEXTRACT(A129,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>174</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B130" s="2">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>52</v>
+        <v>692</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>49</v>
@@ -7324,70 +7353,68 @@
         <v>3</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K130" s="2" t="str" cm="1">
-        <f t="array" ref="K130">_xlfn.REGEXEXTRACT(A130,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>347</v>
+        <v>2</v>
       </c>
       <c r="B131" s="2">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>328</v>
+        <v>168</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>328</v>
+        <v>69</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>203</v>
+        <v>694</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>348</v>
+        <v>49</v>
       </c>
       <c r="I131" s="2">
         <v>3</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="K131" s="2" t="str" cm="1">
-        <f t="array" ref="K131">_xlfn.REGEXEXTRACT(A131,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>344</v>
+        <v>122</v>
       </c>
       <c r="B132" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>345</v>
+        <v>211</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>72</v>
+        <v>696</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>49</v>
@@ -7396,34 +7423,33 @@
         <v>3</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="K132" s="2" t="str" cm="1">
-        <f t="array" ref="K132">_xlfn.REGEXEXTRACT(A132,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
+        <v>166</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>436</v>
+        <v>88</v>
       </c>
       <c r="B133" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>385</v>
+        <v>89</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>159</v>
+        <v>697</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>706</v>
+        <v>109</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>49</v>
@@ -7432,34 +7458,33 @@
         <v>3</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="K133" s="2" t="str" cm="1">
-        <f t="array" ref="K133">_xlfn.REGEXEXTRACT(A133,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>110</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>438</v>
+        <v>6</v>
       </c>
       <c r="B134" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>385</v>
+        <v>160</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>708</v>
+        <v>59</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>49</v>
@@ -7468,202 +7493,196 @@
         <v>3</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="K134" s="2" t="str" cm="1">
-        <f t="array" ref="K134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="B135" s="2">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>283</v>
+        <v>151</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>284</v>
+        <v>152</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I135" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K135" s="2" t="str" cm="1">
-        <f t="array" ref="K135">_xlfn.REGEXEXTRACT(A135,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
+        <v>153</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>266</v>
+        <v>24</v>
       </c>
       <c r="B136" s="2">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>267</v>
+        <v>53</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>268</v>
+        <v>210</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>713</v>
+        <v>52</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I136" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K136" s="2" t="str" cm="1">
-        <f t="array" ref="K136">_xlfn.REGEXEXTRACT(A136,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="B137" s="2">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>226</v>
+        <v>328</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>714</v>
+        <v>328</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>716</v>
+        <v>203</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>49</v>
+        <v>348</v>
       </c>
       <c r="I137" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="K137" s="2" t="str" cm="1">
-        <f t="array" ref="K137">_xlfn.REGEXEXTRACT(A137,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>125</v>
+        <v>344</v>
       </c>
       <c r="B138" s="2">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>717</v>
+        <v>345</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>719</v>
+        <v>72</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I138" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="K138" s="2" t="str" cm="1">
-        <f t="array" ref="K138">_xlfn.REGEXEXTRACT(A138,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>346</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>32</v>
+        <v>436</v>
       </c>
       <c r="B139" s="2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>64</v>
+        <v>385</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I139" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="K139" s="2" t="str" cm="1">
-        <f t="array" ref="K139">_xlfn.REGEXEXTRACT(A139,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>437</v>
+      </c>
+      <c r="K139" s="2" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>133</v>
+        <v>438</v>
       </c>
       <c r="B140" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>62</v>
+        <v>385</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>183</v>
@@ -7672,46 +7691,45 @@
         <v>57</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>258</v>
+        <v>708</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I140" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="K140" s="2" t="str" cm="1">
-        <f t="array" ref="K140">_xlfn.REGEXEXTRACT(A140,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>709</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>143</v>
+        <v>282</v>
       </c>
       <c r="B141" s="2">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>89</v>
+        <v>283</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>723</v>
+        <v>284</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>72</v>
+        <v>711</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>49</v>
@@ -7720,34 +7738,33 @@
         <v>2</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K141" s="2" t="str" cm="1">
-        <f t="array" ref="K141">_xlfn.REGEXEXTRACT(A141,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>285</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="B142" s="2">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>328</v>
+        <v>267</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>725</v>
+        <v>268</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>49</v>
@@ -7756,34 +7773,33 @@
         <v>2</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="K142" s="2" t="str" cm="1">
-        <f t="array" ref="K142">_xlfn.REGEXEXTRACT(A142,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>269</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>116</v>
+        <v>270</v>
       </c>
       <c r="B143" s="2">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>118</v>
+        <v>714</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>72</v>
+        <v>716</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>49</v>
@@ -7792,130 +7808,353 @@
         <v>2</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="K143" s="2" t="str" cm="1">
-        <f t="array" ref="K143">_xlfn.REGEXEXTRACT(A143,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>271</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B144" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>89</v>
+        <v>717</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>233</v>
+        <v>718</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I144" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="K144" s="2" t="str" cm="1">
-        <f t="array" ref="K144">_xlfn.REGEXEXTRACT(A144,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>236</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="B145" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>697</v>
+        <v>81</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>90</v>
+        <v>721</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I145" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K145" s="2" t="str" cm="1">
-        <f t="array" ref="K145">_xlfn.REGEXEXTRACT(A145,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>222</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B146" s="2">
+        <v>32</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I146" s="2">
+        <v>2</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B147" s="2">
+        <v>23</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I147" s="2">
+        <v>2</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B148" s="2">
+        <v>18</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I148" s="2">
+        <v>2</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B149" s="2">
+        <v>14</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I149" s="2">
+        <v>2</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B150" s="2">
+        <v>48</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I150" s="2">
+        <v>1</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B151" s="2">
+        <v>34</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I151" s="2">
+        <v>1</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B146" s="2">
+      <c r="B152" s="2">
         <v>11</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C152" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="D152" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="E152" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F146" s="2" t="s">
+      <c r="F152" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="G146" s="2" t="s">
+      <c r="G152" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="H146" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I146" s="2">
+      <c r="H152" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I152" s="2">
         <v>1</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="J152" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K146" s="2" t="str" cm="1">
-        <f t="array" ref="K146">_xlfn.REGEXEXTRACT(A146,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+      <c r="K152" s="2" t="s">
+        <v>790</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:K146">
+  <conditionalFormatting sqref="A1:K1">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:K152">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I146">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="I2:I152">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A222CD5-FD0C-4C0D-9991-AB458C137A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45237DF-8917-4FE2-9FCD-49B47685F01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="811">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -1196,12 +1196,6 @@
     <t>https://tube.perverzija.com/studio/kink/</t>
   </si>
   <si>
-    <t>websitelink</t>
-  </si>
-  <si>
-    <t>zstar</t>
-  </si>
-  <si>
     <t>several full length kink.com videos with good quality and loading,mix of lesdom and maledom</t>
   </si>
   <si>
@@ -1322,9 +1316,6 @@
     <t>kink classic</t>
   </si>
   <si>
-    <t>dani daniels</t>
-  </si>
-  <si>
     <t>decent sized collection of full length femdom videos from kink classic</t>
   </si>
   <si>
@@ -1334,9 +1325,6 @@
     <t>average quality humiliation videos, mostly feet and cum service</t>
   </si>
   <si>
-    <t>https://netfapx.net/63721/</t>
-  </si>
-  <si>
     <t>lot of long length videos across several categories</t>
   </si>
   <si>
@@ -1466,12 +1454,6 @@
     <t>doggy,kneeling,doggy</t>
   </si>
   <si>
-    <t>side fuck,reverse cowgirl,prone bone</t>
-  </si>
-  <si>
-    <t>prone bone,side fuck,doggy</t>
-  </si>
-  <si>
     <t>gia dimarco,ariel x</t>
   </si>
   <si>
@@ -1997,12 +1979,6 @@
     <t>sitting ,missionary,doggy</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>https://pornzog</t>
-  </si>
-  <si>
     <t>japanese,foot worship,cbt,flogging,pegging,gangbang</t>
   </si>
   <si>
@@ -2402,9 +2378,6 @@
     <t>netfapx.net</t>
   </si>
   <si>
-    <t>pornzog</t>
-  </si>
-  <si>
     <t>www.tubegalore.com</t>
   </si>
   <si>
@@ -2424,6 +2397,81 @@
   </si>
   <si>
     <t>www.omg.xxx</t>
+  </si>
+  <si>
+    <t>general-website-link</t>
+  </si>
+  <si>
+    <t>z-nstars</t>
+  </si>
+  <si>
+    <t>tube porn site</t>
+  </si>
+  <si>
+    <t>https://www.fapcat.com/videos/2647059/mistress-makes-slave-be-in-chastity-him-too/?utm_source=pbweb&amp;utm_campaign=pbweb</t>
+  </si>
+  <si>
+    <t>cunnilingus,flogging,nipple bite,ball clamps,face dildo,pegging,face underground</t>
+  </si>
+  <si>
+    <t>standing,laying down</t>
+  </si>
+  <si>
+    <t>cunnilingus at 10m,flogging at 14m,nipple bite at 15m.ball clamp at 18m,pussy on chastity at 24m,face dildo at 27m,pegging at 32m,face underground</t>
+  </si>
+  <si>
+    <t>www.fapcat.com</t>
+  </si>
+  <si>
+    <t>z-nstars,presley dawson</t>
+  </si>
+  <si>
+    <t>https://tube.perverzija.com/meninpain-bobbi-starr-and-isis-love-the-reward/</t>
+  </si>
+  <si>
+    <t>bobbi starr,isis love</t>
+  </si>
+  <si>
+    <t>body clothespin,wax,face dildo,spitroast,ice</t>
+  </si>
+  <si>
+    <t>standing,doggy,laying down</t>
+  </si>
+  <si>
+    <t>balls tied to ground at 8m,ice on back at 19m,spitroast at 31m,face dildo at 39m</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/videos.php?p=1&amp;q=Divine%20Bitches%20Couple%20Dominated</t>
+  </si>
+  <si>
+    <t>pegging,cbt,gangbang,vibrator,flogging,canning</t>
+  </si>
+  <si>
+    <t>doggy,lay down,suspended</t>
+  </si>
+  <si>
+    <t>good quality divine bitches femdom porn</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/videos.php?p=1&amp;q=Divine%20Bitches%20Chastity%20Videos</t>
+  </si>
+  <si>
+    <t>chastity,cbt,pegging,flogging,canning,vibrator</t>
+  </si>
+  <si>
+    <t>good quality divine bitches femdom porn with chastity</t>
+  </si>
+  <si>
+    <t>z-nstars,dani daniels</t>
+  </si>
+  <si>
+    <t>https://netfapx.net/</t>
+  </si>
+  <si>
+    <t>https://pornzog.com</t>
+  </si>
+  <si>
+    <t>pornzog.com</t>
   </si>
 </sst>
 </file>
@@ -2506,14 +2554,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6161"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -2797,7 +2838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <dimension ref="A1:K152"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" style="1" customWidth="1"/>
@@ -2865,10 +2906,10 @@
         <v>57</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>49</v>
@@ -2880,7 +2921,7 @@
         <v>294</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -2900,10 +2941,10 @@
         <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>49</v>
@@ -2915,7 +2956,7 @@
         <v>362</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2926,19 +2967,19 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>49</v>
@@ -2947,33 +2988,33 @@
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>49</v>
@@ -2982,33 +3023,33 @@
         <v>8</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>49</v>
@@ -3017,33 +3058,33 @@
         <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>49</v>
@@ -3052,15 +3093,15 @@
         <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="B8" s="2">
         <v>11</v>
@@ -3075,10 +3116,10 @@
         <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>49</v>
@@ -3087,10 +3128,10 @@
         <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3110,10 +3151,10 @@
         <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>49</v>
@@ -3125,7 +3166,7 @@
         <v>299</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3139,16 +3180,16 @@
         <v>208</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>49</v>
@@ -3160,7 +3201,7 @@
         <v>100</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3180,10 +3221,10 @@
         <v>57</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
@@ -3195,7 +3236,7 @@
         <v>297</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3215,10 +3256,10 @@
         <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>49</v>
@@ -3230,7 +3271,7 @@
         <v>262</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3250,10 +3291,10 @@
         <v>57</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>49</v>
@@ -3265,7 +3306,7 @@
         <v>67</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3285,10 +3326,10 @@
         <v>57</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>49</v>
@@ -3300,7 +3341,7 @@
         <v>245</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3320,7 +3361,7 @@
         <v>58</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>95</v>
@@ -3335,7 +3376,7 @@
         <v>108</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3355,10 +3396,10 @@
         <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>49</v>
@@ -3370,7 +3411,7 @@
         <v>235</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3390,10 +3431,10 @@
         <v>75</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>49</v>
@@ -3405,12 +3446,12 @@
         <v>356</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B18" s="2">
         <v>0</v>
@@ -3419,16 +3460,16 @@
         <v>73</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -3437,33 +3478,33 @@
         <v>7</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>49</v>
@@ -3472,15 +3513,15 @@
         <v>7</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
@@ -3489,16 +3530,16 @@
         <v>73</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>49</v>
@@ -3507,33 +3548,33 @@
         <v>7</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B21" s="2">
         <v>0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>49</v>
@@ -3542,31 +3583,33 @@
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B22" s="2">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F22" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>788</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>49</v>
@@ -3575,31 +3618,33 @@
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B23" s="2">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F23" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>788</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>49</v>
@@ -3608,10 +3653,10 @@
         <v>7</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3625,16 +3670,16 @@
         <v>65</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>49</v>
@@ -3646,30 +3691,30 @@
         <v>377</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B25" s="2">
         <v>0</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>173</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>49</v>
@@ -3678,21 +3723,21 @@
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>336</v>
+        <v>789</v>
       </c>
       <c r="B26" s="2">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>328</v>
+        <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>328</v>
@@ -3701,80 +3746,80 @@
         <v>75</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>482</v>
+        <v>790</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>483</v>
+        <v>791</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="2">
+        <v>113</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="I26" s="2">
-        <v>6</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="2">
-        <v>83</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="I27" s="2">
         <v>6</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>105</v>
+        <v>337</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="B28" s="2">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>290</v>
+        <v>211</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>49</v>
@@ -3783,33 +3828,33 @@
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>291</v>
+        <v>105</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="B29" s="2">
+        <v>66</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>49</v>
@@ -3818,33 +3863,33 @@
         <v>6</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="B30" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>62</v>
+        <v>240</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>49</v>
@@ -3853,33 +3898,33 @@
         <v>6</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>49</v>
@@ -3888,33 +3933,33 @@
         <v>6</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>97</v>
+        <v>256</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2">
         <v>53</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>494</v>
+        <v>212</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>49</v>
@@ -3923,33 +3968,33 @@
         <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B33" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>69</v>
+        <v>488</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>49</v>
@@ -3958,33 +4003,33 @@
         <v>6</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>238</v>
+        <v>69</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>49</v>
@@ -3993,33 +4038,33 @@
         <v>6</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>239</v>
+        <v>102</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B35" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>49</v>
@@ -4028,21 +4073,21 @@
         <v>6</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="B36" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>226</v>
+        <v>93</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>159</v>
@@ -4051,10 +4096,10 @@
         <v>57</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>49</v>
@@ -4063,33 +4108,33 @@
         <v>6</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>749</v>
+        <v>725</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="B37" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>49</v>
@@ -4098,33 +4143,33 @@
         <v>6</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="B38" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>49</v>
@@ -4133,33 +4178,33 @@
         <v>6</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>757</v>
+        <v>725</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="B39" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>49</v>
@@ -4168,103 +4213,103 @@
         <v>6</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>733</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>313</v>
+        <v>10</v>
       </c>
       <c r="B40" s="2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>328</v>
+        <v>64</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>328</v>
+        <v>192</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>314</v>
+        <v>49</v>
       </c>
       <c r="I40" s="2">
         <v>6</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>315</v>
+        <v>193</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>409</v>
+        <v>313</v>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>385</v>
+        <v>328</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>49</v>
+        <v>314</v>
       </c>
       <c r="I41" s="2">
         <v>6</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>410</v>
+        <v>315</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>326</v>
+        <v>786</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>386</v>
+        <v>794</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>49</v>
@@ -4273,33 +4318,33 @@
         <v>6</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>226</v>
+        <v>326</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>49</v>
@@ -4308,33 +4353,33 @@
         <v>6</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B44" s="2">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>385</v>
+        <v>226</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>49</v>
@@ -4343,33 +4388,33 @@
         <v>6</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B45" s="2">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>49</v>
@@ -4378,33 +4423,33 @@
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B46" s="2">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>49</v>
@@ -4413,33 +4458,33 @@
         <v>6</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B47" s="2">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>49</v>
@@ -4448,33 +4493,33 @@
         <v>6</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B48" s="2">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>326</v>
+        <v>786</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>49</v>
@@ -4483,33 +4528,33 @@
         <v>6</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="B49" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>326</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>364</v>
+        <v>787</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>49</v>
@@ -4518,33 +4563,33 @@
         <v>6</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>759</v>
+        <v>363</v>
       </c>
       <c r="B50" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>760</v>
+        <v>523</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>761</v>
+        <v>524</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>49</v>
@@ -4553,33 +4598,33 @@
         <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>762</v>
+        <v>365</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="B51" s="2">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>385</v>
+        <v>786</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>49</v>
@@ -4588,33 +4633,33 @@
         <v>6</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="B52" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>328</v>
+        <v>786</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>328</v>
+        <v>787</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>49</v>
@@ -4623,33 +4668,33 @@
         <v>6</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>771</v>
+        <v>729</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="B53" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>773</v>
+        <v>328</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>773</v>
+        <v>328</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>49</v>
@@ -4658,208 +4703,208 @@
         <v>6</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>317</v>
+        <v>764</v>
       </c>
       <c r="B54" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>318</v>
+        <v>765</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>531</v>
+        <v>765</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>532</v>
+        <v>766</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>533</v>
+        <v>767</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I54" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>320</v>
+        <v>768</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>331</v>
+        <v>795</v>
       </c>
       <c r="B55" s="2">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>531</v>
+        <v>796</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>534</v>
+        <v>797</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>535</v>
+        <v>798</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I55" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>316</v>
+        <v>799</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>302</v>
+        <v>800</v>
       </c>
       <c r="B56" s="2">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>303</v>
+        <v>73</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>304</v>
+        <v>787</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>536</v>
+        <v>801</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>537</v>
+        <v>802</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I56" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>305</v>
+        <v>803</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>300</v>
+        <v>804</v>
       </c>
       <c r="B57" s="2">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>538</v>
+        <v>787</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" s="2">
+        <v>6</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B58" s="2">
+        <v>129</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I57" s="2">
-        <v>5</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B58" s="2">
-        <v>65</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="I58" s="2">
         <v>5</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="B59" s="2">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>280</v>
+        <v>525</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>49</v>
@@ -4868,33 +4913,33 @@
         <v>5</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="B60" s="2">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>240</v>
+        <v>303</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>49</v>
@@ -4903,33 +4948,33 @@
         <v>5</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="B61" s="2">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>49</v>
@@ -4938,33 +4983,33 @@
         <v>5</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>748</v>
+        <v>725</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>42</v>
+        <v>286</v>
       </c>
       <c r="B62" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>214</v>
+        <v>287</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>49</v>
@@ -4973,33 +5018,33 @@
         <v>5</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="B63" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>183</v>
+        <v>280</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>49</v>
@@ -5008,33 +5053,33 @@
         <v>5</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>777</v>
+        <v>725</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>27</v>
+        <v>276</v>
       </c>
       <c r="B64" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>328</v>
+        <v>240</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>49</v>
@@ -5043,33 +5088,33 @@
         <v>5</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B65" s="2">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>242</v>
+        <v>541</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>49</v>
@@ -5078,33 +5123,33 @@
         <v>5</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>243</v>
+        <v>84</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B66" s="2">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>49</v>
@@ -5113,33 +5158,33 @@
         <v>5</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="B67" s="2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>49</v>
@@ -5148,33 +5193,33 @@
         <v>5</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>733</v>
+        <v>769</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>357</v>
+        <v>27</v>
       </c>
       <c r="B68" s="2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>226</v>
+        <v>328</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>49</v>
@@ -5183,33 +5228,33 @@
         <v>5</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>359</v>
+        <v>254</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="B69" s="2">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>563</v>
+        <v>242</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>49</v>
@@ -5218,33 +5263,33 @@
         <v>5</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B70" s="2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>566</v>
+        <v>211</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>49</v>
@@ -5253,33 +5298,33 @@
         <v>5</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B71" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>569</v>
+        <v>231</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>49</v>
@@ -5288,33 +5333,33 @@
         <v>5</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>14</v>
+        <v>357</v>
       </c>
       <c r="B72" s="2">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>64</v>
+        <v>226</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>70</v>
+        <v>358</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>49</v>
@@ -5323,33 +5368,33 @@
         <v>5</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>101</v>
+        <v>359</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="B73" s="2">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>49</v>
@@ -5358,33 +5403,33 @@
         <v>5</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>329</v>
+        <v>8</v>
       </c>
       <c r="B74" s="2">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>328</v>
+        <v>196</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>328</v>
+        <v>560</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>49</v>
@@ -5393,33 +5438,33 @@
         <v>5</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>330</v>
+        <v>197</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="B75" s="2">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>341</v>
+        <v>185</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>328</v>
+        <v>563</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>342</v>
+        <v>58</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>60</v>
+        <v>565</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>49</v>
@@ -5428,33 +5473,33 @@
         <v>5</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>343</v>
+        <v>186</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="B76" s="2">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>109</v>
+        <v>567</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>49</v>
@@ -5463,33 +5508,33 @@
         <v>5</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>257</v>
+        <v>101</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="B77" s="2">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>146</v>
+        <v>568</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>49</v>
@@ -5498,18 +5543,18 @@
         <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B78" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>328</v>
@@ -5521,45 +5566,45 @@
         <v>75</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>327</v>
+        <v>572</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I78" s="2">
         <v>5</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>425</v>
+        <v>340</v>
       </c>
       <c r="B79" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>426</v>
+        <v>341</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>427</v>
+        <v>328</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>57</v>
+        <v>342</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>585</v>
+        <v>60</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>49</v>
@@ -5568,33 +5613,33 @@
         <v>5</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>428</v>
+        <v>343</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>752</v>
+        <v>725</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>429</v>
+        <v>142</v>
       </c>
       <c r="B80" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>385</v>
+        <v>148</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>386</v>
+        <v>149</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>587</v>
+        <v>109</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>49</v>
@@ -5603,33 +5648,33 @@
         <v>5</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>366</v>
+        <v>132</v>
       </c>
       <c r="B81" s="2">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>326</v>
+        <v>145</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>367</v>
+        <v>146</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>49</v>
@@ -5638,68 +5683,68 @@
         <v>5</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>368</v>
+        <v>147</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="B82" s="2">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>590</v>
+        <v>328</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>592</v>
+        <v>327</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="I82" s="2">
         <v>5</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="B83" s="2">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>73</v>
+        <v>424</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>379</v>
+        <v>807</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>49</v>
@@ -5708,173 +5753,173 @@
         <v>5</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>324</v>
+        <v>426</v>
       </c>
       <c r="B84" s="2">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>328</v>
+        <v>786</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>328</v>
+        <v>787</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I84" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>325</v>
+        <v>427</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="B85" s="2">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>597</v>
+        <v>367</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I85" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>323</v>
+        <v>368</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>781</v>
+        <v>746</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>114</v>
+        <v>369</v>
       </c>
       <c r="B86" s="2">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>111</v>
+        <v>326</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I86" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>115</v>
+        <v>370</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>35</v>
+        <v>378</v>
       </c>
       <c r="B87" s="2">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>74</v>
+        <v>379</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I87" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>76</v>
+        <v>380</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="B88" s="2">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>49</v>
@@ -5883,33 +5928,33 @@
         <v>4</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>749</v>
+        <v>773</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="B89" s="2">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>49</v>
@@ -5918,33 +5963,33 @@
         <v>4</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>733</v>
+        <v>773</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="B90" s="2">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>49</v>
@@ -5953,33 +5998,33 @@
         <v>4</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>272</v>
+        <v>35</v>
       </c>
       <c r="B91" s="2">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>613</v>
+        <v>74</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>49</v>
@@ -5988,33 +6033,33 @@
         <v>4</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>273</v>
+        <v>76</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="B92" s="2">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>64</v>
+        <v>307</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>213</v>
+        <v>308</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>49</v>
@@ -6023,33 +6068,33 @@
         <v>4</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>66</v>
+        <v>309</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
       <c r="B93" s="2">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>81</v>
+        <v>601</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>49</v>
@@ -6058,33 +6103,33 @@
         <v>4</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B94" s="2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>249</v>
+        <v>604</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>49</v>
@@ -6093,33 +6138,33 @@
         <v>4</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>251</v>
+        <v>61</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>7</v>
+        <v>272</v>
       </c>
       <c r="B95" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>328</v>
+        <v>607</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>49</v>
@@ -6128,33 +6173,33 @@
         <v>4</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B96" s="2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>49</v>
@@ -6163,33 +6208,33 @@
         <v>4</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>230</v>
+        <v>66</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B97" s="2">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>65</v>
+        <v>205</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>49</v>
@@ -6198,33 +6243,33 @@
         <v>4</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B98" s="2">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>49</v>
@@ -6233,33 +6278,33 @@
         <v>4</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="B99" s="2">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>630</v>
-      </c>
       <c r="E99" s="2" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>49</v>
@@ -6268,33 +6313,33 @@
         <v>4</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="B100" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>49</v>
@@ -6303,33 +6348,33 @@
         <v>4</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B101" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>635</v>
+        <v>620</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>49</v>
@@ -6338,33 +6383,33 @@
         <v>4</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>748</v>
+        <v>725</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="B102" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>49</v>
@@ -6373,33 +6418,33 @@
         <v>4</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B103" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>179</v>
+        <v>328</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>180</v>
+        <v>624</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>72</v>
+        <v>626</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>49</v>
@@ -6408,33 +6453,33 @@
         <v>4</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B104" s="2">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>640</v>
+        <v>198</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>49</v>
@@ -6443,33 +6488,33 @@
         <v>4</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>352</v>
+        <v>31</v>
       </c>
       <c r="B105" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>49</v>
@@ -6478,33 +6523,33 @@
         <v>4</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>354</v>
+        <v>144</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B106" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>49</v>
@@ -6513,33 +6558,33 @@
         <v>4</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="B107" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>49</v>
@@ -6548,33 +6593,33 @@
         <v>4</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>733</v>
+        <v>775</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B108" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>69</v>
+        <v>634</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>49</v>
@@ -6583,33 +6628,33 @@
         <v>4</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="B109" s="2">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>49</v>
@@ -6618,33 +6663,33 @@
         <v>4</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>150</v>
+        <v>354</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>785</v>
+        <v>725</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>431</v>
+        <v>135</v>
       </c>
       <c r="B110" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>385</v>
+        <v>160</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>386</v>
+        <v>159</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>403</v>
+        <v>57</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>49</v>
@@ -6653,33 +6698,33 @@
         <v>4</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>432</v>
+        <v>162</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>653</v>
+        <v>4</v>
       </c>
       <c r="B111" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>385</v>
+        <v>160</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>386</v>
+        <v>158</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>403</v>
+        <v>57</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>652</v>
+        <v>199</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>49</v>
@@ -6688,68 +6733,68 @@
         <v>4</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>433</v>
+        <v>161</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>787</v>
+        <v>725</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>434</v>
+        <v>140</v>
       </c>
       <c r="B112" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>385</v>
+        <v>154</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>386</v>
+        <v>69</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>319</v>
+        <v>49</v>
       </c>
       <c r="I112" s="2">
         <v>4</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>435</v>
+        <v>155</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="B113" s="2">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>326</v>
+        <v>209</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>372</v>
+        <v>149</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>594</v>
+        <v>645</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>49</v>
@@ -6758,33 +6803,33 @@
         <v>4</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>373</v>
+        <v>150</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>754</v>
+        <v>777</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>374</v>
+        <v>808</v>
       </c>
       <c r="B114" s="2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>326</v>
+        <v>786</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>657</v>
+        <v>787</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>75</v>
+        <v>401</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>658</v>
+        <v>788</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>659</v>
+        <v>508</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>49</v>
@@ -6793,208 +6838,208 @@
         <v>4</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>754</v>
+        <v>778</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>350</v>
+        <v>809</v>
       </c>
       <c r="B115" s="2">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>328</v>
+        <v>786</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>531</v>
+        <v>787</v>
       </c>
       <c r="E115" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I115" s="2">
+        <v>4</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B116" s="2">
+        <v>0</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F115" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="H115" s="2" t="s">
+      <c r="F116" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="I115" s="2">
-        <v>3</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B116" s="2">
-        <v>102</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="I116" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>98</v>
+        <v>431</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>748</v>
+        <v>779</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>137</v>
+        <v>371</v>
       </c>
       <c r="B117" s="2">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>62</v>
+        <v>326</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>183</v>
+        <v>372</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>72</v>
+        <v>588</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I117" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>253</v>
+        <v>373</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="B118" s="2">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>64</v>
+        <v>326</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>311</v>
+        <v>649</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>666</v>
+        <v>651</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I118" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>36</v>
+        <v>350</v>
       </c>
       <c r="B119" s="2">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>208</v>
+        <v>328</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>667</v>
+        <v>525</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>49</v>
+        <v>319</v>
       </c>
       <c r="I119" s="2">
         <v>3</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>103</v>
+        <v>351</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>748</v>
+        <v>726</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>247</v>
+        <v>23</v>
       </c>
       <c r="B120" s="2">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>528</v>
+        <v>655</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>49</v>
@@ -7003,33 +7048,33 @@
         <v>3</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>333</v>
+        <v>98</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>789</v>
+        <v>740</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="B121" s="2">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>594</v>
+        <v>72</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>49</v>
@@ -7038,33 +7083,33 @@
         <v>3</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>106</v>
+        <v>253</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>750</v>
+        <v>769</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>18</v>
+        <v>310</v>
       </c>
       <c r="B122" s="2">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>672</v>
+        <v>657</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>49</v>
@@ -7073,33 +7118,33 @@
         <v>3</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>332</v>
+        <v>36</v>
       </c>
       <c r="B123" s="2">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>328</v>
+        <v>208</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>676</v>
+        <v>661</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>49</v>
@@ -7108,68 +7153,68 @@
         <v>3</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>234</v>
+        <v>103</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>83</v>
+        <v>247</v>
       </c>
       <c r="B124" s="2">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>85</v>
+        <v>248</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>678</v>
+        <v>522</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="I124" s="2">
         <v>3</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>748</v>
+        <v>780</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="B125" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>680</v>
+        <v>588</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>49</v>
@@ -7178,33 +7223,33 @@
         <v>3</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>219</v>
+        <v>106</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B126" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>49</v>
@@ -7213,33 +7258,33 @@
         <v>3</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>790</v>
+        <v>725</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>141</v>
+        <v>332</v>
       </c>
       <c r="B127" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>189</v>
+        <v>328</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>190</v>
+        <v>666</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>49</v>
@@ -7248,68 +7293,68 @@
         <v>3</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="B128" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>685</v>
+        <v>85</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="I128" s="2">
         <v>3</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="B129" s="2">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>688</v>
+        <v>177</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>49</v>
@@ -7318,33 +7363,33 @@
         <v>3</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>177</v>
+        <v>69</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>49</v>
@@ -7353,33 +7398,33 @@
         <v>3</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>2</v>
+        <v>141</v>
       </c>
       <c r="B131" s="2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>49</v>
@@ -7388,33 +7433,33 @@
         <v>3</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="B132" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>211</v>
+        <v>677</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>49</v>
@@ -7423,33 +7468,33 @@
         <v>3</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B133" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>109</v>
+        <v>682</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>49</v>
@@ -7458,33 +7503,33 @@
         <v>3</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>110</v>
+        <v>174</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B134" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>57</v>
+        <v>173</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>59</v>
+        <v>684</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>49</v>
@@ -7493,33 +7538,33 @@
         <v>3</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>138</v>
+        <v>2</v>
       </c>
       <c r="B135" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>49</v>
@@ -7528,33 +7573,33 @@
         <v>3</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="B136" s="2">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>52</v>
+        <v>688</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>49</v>
@@ -7563,68 +7608,68 @@
         <v>3</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>347</v>
+        <v>88</v>
       </c>
       <c r="B137" s="2">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>328</v>
+        <v>89</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>328</v>
+        <v>689</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>203</v>
+        <v>109</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>348</v>
+        <v>49</v>
       </c>
       <c r="I137" s="2">
         <v>3</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>349</v>
+        <v>110</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>344</v>
+        <v>6</v>
       </c>
       <c r="B138" s="2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>49</v>
@@ -7633,33 +7678,33 @@
         <v>3</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>346</v>
+        <v>164</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>436</v>
+        <v>138</v>
       </c>
       <c r="B139" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>385</v>
+        <v>151</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>49</v>
@@ -7668,33 +7713,33 @@
         <v>3</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>437</v>
+        <v>153</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>438</v>
+        <v>24</v>
       </c>
       <c r="B140" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>385</v>
+        <v>53</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>708</v>
+        <v>52</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>49</v>
@@ -7703,173 +7748,173 @@
         <v>3</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>709</v>
+        <v>54</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>282</v>
+        <v>347</v>
       </c>
       <c r="B141" s="2">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>710</v>
+        <v>695</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>711</v>
+        <v>203</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>49</v>
+        <v>348</v>
       </c>
       <c r="I141" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>266</v>
+        <v>344</v>
       </c>
       <c r="B142" s="2">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>713</v>
+        <v>72</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>733</v>
+        <v>783</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>270</v>
+        <v>432</v>
       </c>
       <c r="B143" s="2">
+        <v>0</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="F143" s="2" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>271</v>
+        <v>433</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>794</v>
+        <v>769</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>125</v>
+        <v>434</v>
       </c>
       <c r="B144" s="2">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>111</v>
+        <v>786</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>717</v>
+        <v>183</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I144" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>236</v>
+        <v>701</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>32</v>
+        <v>282</v>
       </c>
       <c r="B145" s="2">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>64</v>
+        <v>283</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>49</v>
@@ -7878,33 +7923,33 @@
         <v>2</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>222</v>
+        <v>285</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="B146" s="2">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>62</v>
+        <v>267</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>183</v>
+        <v>268</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>258</v>
+        <v>705</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>49</v>
@@ -7913,33 +7958,33 @@
         <v>2</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>184</v>
+        <v>269</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>143</v>
+        <v>270</v>
       </c>
       <c r="B147" s="2">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>72</v>
+        <v>708</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>49</v>
@@ -7948,33 +7993,33 @@
         <v>2</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>733</v>
+        <v>785</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B148" s="2">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>328</v>
+        <v>111</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>726</v>
+        <v>710</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>49</v>
@@ -7983,33 +8028,33 @@
         <v>2</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>335</v>
+        <v>236</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="B149" s="2">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>72</v>
+        <v>713</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>49</v>
@@ -8018,126 +8063,266 @@
         <v>2</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B150" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>233</v>
+        <v>714</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>729</v>
+        <v>258</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I150" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="B151" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>697</v>
+        <v>715</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="G151" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I151" s="2">
+        <v>2</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B152" s="2">
+        <v>18</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I152" s="2">
+        <v>2</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B153" s="2">
+        <v>14</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I153" s="2">
+        <v>2</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B154" s="2">
+        <v>48</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I154" s="2">
+        <v>1</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B155" s="2">
+        <v>34</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="G155" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H151" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I151" s="2">
+      <c r="H155" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I155" s="2">
         <v>1</v>
       </c>
-      <c r="J151" s="2" t="s">
+      <c r="J155" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K151" s="2" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
+      <c r="K155" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B156" s="2">
         <v>11</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C156" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D156" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="E156" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F152" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I152" s="2">
+      <c r="F156" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I156" s="2">
         <v>1</v>
       </c>
-      <c r="J152" s="2" t="s">
+      <c r="J156" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K152" s="2" t="s">
-        <v>790</v>
+      <c r="K156" s="2" t="s">
+        <v>781</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:K1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="A1:K156">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8148,13 +8333,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:K152">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I152">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="I2:I156">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E10B52-92F6-411F-9765-CA37246420E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353394E6-2F6F-484F-88E4-72891156061E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1365,9 +1365,6 @@
     <t>gangbang,blackout contacts,body clothespin,flogging,nipple clamps,drinking game</t>
   </si>
   <si>
-    <t>standing,lay down legs to side,doggy</t>
-  </si>
-  <si>
     <t>flogging,vibrator,pegging,spanking,face riding,leash</t>
   </si>
   <si>
@@ -2509,6 +2506,9 @@
   </si>
   <si>
     <t>spanking at 5m,electric at 21m,electric wand anal at 23m,pegging at 30m,cunnilingus at 36m,face dildo at 42m</t>
+  </si>
+  <si>
+    <t>standing,lay down, legs to side,doggy</t>
   </si>
 </sst>
 </file>
@@ -2591,14 +2591,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6161"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -2953,7 +2946,7 @@
         <v>433</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>434</v>
+        <v>815</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>49</v>
@@ -2977,19 +2970,19 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>49</v>
@@ -3013,19 +3006,19 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>49</v>
@@ -3043,7 +3036,7 @@
     </row>
     <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B5" s="2">
         <v>11</v>
@@ -3058,10 +3051,10 @@
         <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>49</v>
@@ -3070,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K5" s="2" t="str" cm="1">
         <f t="array" ref="K5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
@@ -3079,7 +3072,7 @@
     </row>
     <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B6" s="2">
         <v>53</v>
@@ -3088,16 +3081,16 @@
         <v>145</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>49</v>
@@ -3106,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K6" s="2" t="str" cm="1">
         <f t="array" ref="K6">_xlfn.REGEXEXTRACT(A6,"(?&lt;=//)[^/]+")</f>
@@ -3130,10 +3123,10 @@
         <v>75</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>49</v>
@@ -3157,19 +3150,19 @@
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>49</v>
@@ -3187,25 +3180,25 @@
     </row>
     <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>724</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>49</v>
@@ -3214,7 +3207,7 @@
         <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K9" s="2" t="str" cm="1">
         <f t="array" ref="K9">_xlfn.REGEXEXTRACT(A9,"(?&lt;=//)[^/]+")</f>
@@ -3238,10 +3231,10 @@
         <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>49</v>
@@ -3250,7 +3243,7 @@
         <v>7</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K10" s="2" t="str" cm="1">
         <f t="array" ref="K10">_xlfn.REGEXEXTRACT(A10,"(?&lt;=//)[^/]+")</f>
@@ -3268,16 +3261,16 @@
         <v>208</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
@@ -3310,10 +3303,10 @@
         <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>49</v>
@@ -3346,10 +3339,10 @@
         <v>57</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>49</v>
@@ -3382,10 +3375,10 @@
         <v>57</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>49</v>
@@ -3418,10 +3411,10 @@
         <v>57</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>49</v>
@@ -3454,7 +3447,7 @@
         <v>58</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>95</v>
@@ -3490,10 +3483,10 @@
         <v>57</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>49</v>
@@ -3517,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>391</v>
@@ -3526,10 +3519,10 @@
         <v>392</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -3553,19 +3546,19 @@
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>49</v>
@@ -3589,19 +3582,19 @@
         <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>399</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>49</v>
@@ -3625,19 +3618,19 @@
         <v>0</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>399</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>49</v>
@@ -3664,16 +3657,16 @@
         <v>65</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>49</v>
@@ -3697,19 +3690,19 @@
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>173</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>49</v>
@@ -3742,10 +3735,10 @@
         <v>75</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>49</v>
@@ -3763,7 +3756,7 @@
     </row>
     <row r="25" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B25" s="2">
         <v>44</v>
@@ -3778,10 +3771,10 @@
         <v>75</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>49</v>
@@ -3790,7 +3783,7 @@
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="K25" s="2" t="str" cm="1">
         <f t="array" ref="K25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
@@ -3799,7 +3792,7 @@
     </row>
     <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B26" s="2">
         <v>48</v>
@@ -3808,16 +3801,16 @@
         <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>49</v>
@@ -3826,7 +3819,7 @@
         <v>7</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K26" s="2" t="str" cm="1">
         <f t="array" ref="K26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
@@ -3844,16 +3837,16 @@
         <v>73</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>49</v>
@@ -3880,16 +3873,16 @@
         <v>73</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>49</v>
@@ -3907,7 +3900,7 @@
     </row>
     <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B29" s="2">
         <v>99</v>
@@ -3922,10 +3915,10 @@
         <v>57</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>49</v>
@@ -3934,7 +3927,7 @@
         <v>7</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K29" s="2" t="str" cm="1">
         <f t="array" ref="K29">_xlfn.REGEXEXTRACT(A29,"(?&lt;=//)[^/]+")</f>
@@ -3958,10 +3951,10 @@
         <v>75</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>317</v>
@@ -3985,19 +3978,19 @@
         <v>0</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>49</v>
@@ -4030,10 +4023,10 @@
         <v>57</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>49</v>
@@ -4066,10 +4059,10 @@
         <v>57</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>49</v>
@@ -4102,10 +4095,10 @@
         <v>58</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>49</v>
@@ -4138,10 +4131,10 @@
         <v>58</v>
       </c>
       <c r="F35" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>49</v>
@@ -4174,10 +4167,10 @@
         <v>57</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>49</v>
@@ -4204,16 +4197,16 @@
         <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F37" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>49</v>
@@ -4246,10 +4239,10 @@
         <v>56</v>
       </c>
       <c r="F38" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>49</v>
@@ -4282,10 +4275,10 @@
         <v>57</v>
       </c>
       <c r="F39" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>49</v>
@@ -4318,10 +4311,10 @@
         <v>57</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>49</v>
@@ -4354,10 +4347,10 @@
         <v>57</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>49</v>
@@ -4390,10 +4383,10 @@
         <v>57</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>49</v>
@@ -4426,10 +4419,10 @@
         <v>173</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>49</v>
@@ -4462,10 +4455,10 @@
         <v>57</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>49</v>
@@ -4498,10 +4491,10 @@
         <v>57</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>312</v>
@@ -4525,19 +4518,19 @@
         <v>0</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>49</v>
@@ -4555,7 +4548,7 @@
     </row>
     <row r="47" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B47" s="2">
         <v>50</v>
@@ -4564,16 +4557,16 @@
         <v>324</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>49</v>
@@ -4582,7 +4575,7 @@
         <v>6</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K47" s="2" t="str" cm="1">
         <f t="array" ref="K47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
@@ -4600,16 +4593,16 @@
         <v>226</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>49</v>
@@ -4636,16 +4629,16 @@
         <v>324</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>49</v>
@@ -4669,19 +4662,19 @@
         <v>0</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F50" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>49</v>
@@ -4699,25 +4692,25 @@
     </row>
     <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B51" s="2">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F51" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>732</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>49</v>
@@ -4726,7 +4719,7 @@
         <v>6</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K51" s="2" t="str" cm="1">
         <f t="array" ref="K51">_xlfn.REGEXEXTRACT(A51,"(?&lt;=//)[^/]+")</f>
@@ -4735,7 +4728,7 @@
     </row>
     <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B52" s="2">
         <v>10</v>
@@ -4750,10 +4743,10 @@
         <v>57</v>
       </c>
       <c r="F52" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>49</v>
@@ -4762,7 +4755,7 @@
         <v>6</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="K52" s="2" t="str" cm="1">
         <f t="array" ref="K52">_xlfn.REGEXEXTRACT(A52,"(?&lt;=//)[^/]+")</f>
@@ -4777,19 +4770,19 @@
         <v>0</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F53" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>49</v>
@@ -4813,19 +4806,19 @@
         <v>0</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F54" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>49</v>
@@ -4843,7 +4836,7 @@
     </row>
     <row r="55" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B55" s="2">
         <v>58</v>
@@ -4852,16 +4845,16 @@
         <v>73</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F55" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>787</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>788</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>49</v>
@@ -4870,7 +4863,7 @@
         <v>6</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K55" s="2" t="str" cm="1">
         <f t="array" ref="K55">_xlfn.REGEXEXTRACT(A55,"(?&lt;=//)[^/]+")</f>
@@ -4879,7 +4872,7 @@
     </row>
     <row r="56" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B56" s="2">
         <v>0</v>
@@ -4888,16 +4881,16 @@
         <v>73</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>49</v>
@@ -4906,7 +4899,7 @@
         <v>6</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="K56" s="2" t="str" cm="1">
         <f t="array" ref="K56">_xlfn.REGEXEXTRACT(A56,"(?&lt;=//)[^/]+")</f>
@@ -4915,7 +4908,7 @@
     </row>
     <row r="57" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B57" s="2">
         <v>0</v>
@@ -4924,16 +4917,16 @@
         <v>73</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F57" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>49</v>
@@ -4942,7 +4935,7 @@
         <v>6</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="K57" s="2" t="str" cm="1">
         <f t="array" ref="K57">_xlfn.REGEXEXTRACT(A57,"(?&lt;=//)[^/]+")</f>
@@ -4966,10 +4959,10 @@
         <v>75</v>
       </c>
       <c r="F58" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>49</v>
@@ -4987,25 +4980,25 @@
     </row>
     <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B59" s="2">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>49</v>
@@ -5014,7 +5007,7 @@
         <v>6</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K59" s="2" t="str" cm="1">
         <f t="array" ref="K59">_xlfn.REGEXEXTRACT(A59,"(?&lt;=//)[^/]+")</f>
@@ -5032,16 +5025,16 @@
         <v>324</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F60" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>49</v>
@@ -5059,25 +5052,25 @@
     </row>
     <row r="61" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B61" s="2">
         <v>21</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F61" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>745</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>49</v>
@@ -5086,7 +5079,7 @@
         <v>6</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="K61" s="2" t="str" cm="1">
         <f t="array" ref="K61">_xlfn.REGEXEXTRACT(A61,"(?&lt;=//)[^/]+")</f>
@@ -5095,7 +5088,7 @@
     </row>
     <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B62" s="2">
         <v>64</v>
@@ -5104,16 +5097,16 @@
         <v>73</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F62" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>813</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>814</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>49</v>
@@ -5122,7 +5115,7 @@
         <v>6</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="K62" s="2" t="str" cm="1">
         <f t="array" ref="K62">_xlfn.REGEXEXTRACT(A62,"(?&lt;=//)[^/]+")</f>
@@ -5146,10 +5139,10 @@
         <v>75</v>
       </c>
       <c r="F63" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>49</v>
@@ -5182,10 +5175,10 @@
         <v>75</v>
       </c>
       <c r="F64" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>49</v>
@@ -5209,19 +5202,19 @@
         <v>0</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F65" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>49</v>
@@ -5248,16 +5241,16 @@
         <v>316</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F66" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>317</v>
@@ -5284,16 +5277,16 @@
         <v>326</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F67" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>527</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>49</v>
@@ -5326,10 +5319,10 @@
         <v>57</v>
       </c>
       <c r="F68" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="G68" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>49</v>
@@ -5356,16 +5349,16 @@
         <v>62</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F69" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>49</v>
@@ -5398,10 +5391,10 @@
         <v>58</v>
       </c>
       <c r="F70" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>49</v>
@@ -5434,10 +5427,10 @@
         <v>57</v>
       </c>
       <c r="F71" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>49</v>
@@ -5470,10 +5463,10 @@
         <v>58</v>
       </c>
       <c r="F72" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>49</v>
@@ -5500,13 +5493,13 @@
         <v>62</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>82</v>
@@ -5542,10 +5535,10 @@
         <v>57</v>
       </c>
       <c r="F74" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>49</v>
@@ -5578,10 +5571,10 @@
         <v>58</v>
       </c>
       <c r="F75" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>49</v>
@@ -5614,10 +5607,10 @@
         <v>57</v>
       </c>
       <c r="F76" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>49</v>
@@ -5650,10 +5643,10 @@
         <v>58</v>
       </c>
       <c r="F77" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="G77" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>49</v>
@@ -5686,10 +5679,10 @@
         <v>57</v>
       </c>
       <c r="F78" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>49</v>
@@ -5722,10 +5715,10 @@
         <v>57</v>
       </c>
       <c r="F79" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>49</v>
@@ -5752,16 +5745,16 @@
         <v>65</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F80" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>49</v>
@@ -5788,16 +5781,16 @@
         <v>196</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>49</v>
@@ -5824,16 +5817,16 @@
         <v>185</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F82" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>49</v>
@@ -5866,10 +5859,10 @@
         <v>57</v>
       </c>
       <c r="F83" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>49</v>
@@ -5896,16 +5889,16 @@
         <v>64</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F84" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>568</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>49</v>
@@ -5938,7 +5931,7 @@
         <v>340</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>60</v>
@@ -5974,7 +5967,7 @@
         <v>57</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>109</v>
@@ -6010,10 +6003,10 @@
         <v>57</v>
       </c>
       <c r="F87" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>49</v>
@@ -6040,16 +6033,16 @@
         <v>422</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F88" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>49</v>
@@ -6067,25 +6060,25 @@
     </row>
     <row r="89" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B89" s="2">
         <v>54</v>
       </c>
       <c r="C89" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F89" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>49</v>
@@ -6094,7 +6087,7 @@
         <v>5</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="K89" s="2" t="str" cm="1">
         <f t="array" ref="K89">_xlfn.REGEXEXTRACT(A89,"(?&lt;=//)[^/]+")</f>
@@ -6112,16 +6105,16 @@
         <v>324</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F90" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>49</v>
@@ -6154,10 +6147,10 @@
         <v>75</v>
       </c>
       <c r="F91" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>49</v>
@@ -6190,10 +6183,10 @@
         <v>75</v>
       </c>
       <c r="F92" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="G92" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>49</v>
@@ -6226,7 +6219,7 @@
         <v>75</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>325</v>
@@ -6247,7 +6240,7 @@
     </row>
     <row r="94" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B94" s="2">
         <v>64</v>
@@ -6256,16 +6249,16 @@
         <v>73</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>49</v>
@@ -6274,7 +6267,7 @@
         <v>5</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K94" s="2" t="str" cm="1">
         <f t="array" ref="K94">_xlfn.REGEXEXTRACT(A94,"(?&lt;=//)[^/]+")</f>
@@ -6298,10 +6291,10 @@
         <v>75</v>
       </c>
       <c r="F95" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>49</v>
@@ -6334,10 +6327,10 @@
         <v>75</v>
       </c>
       <c r="F96" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>49</v>
@@ -6355,7 +6348,7 @@
     </row>
     <row r="97" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B97" s="2">
         <v>52</v>
@@ -6364,16 +6357,16 @@
         <v>73</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>49</v>
@@ -6382,7 +6375,7 @@
         <v>4</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K97" s="2" t="str" cm="1">
         <f t="array" ref="K97">_xlfn.REGEXEXTRACT(A97,"(?&lt;=//)[^/]+")</f>
@@ -6406,10 +6399,10 @@
         <v>57</v>
       </c>
       <c r="F98" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>49</v>
@@ -6436,16 +6429,16 @@
         <v>320</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F99" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>49</v>
@@ -6472,16 +6465,16 @@
         <v>111</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F100" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>594</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>49</v>
@@ -6514,10 +6507,10 @@
         <v>172</v>
       </c>
       <c r="F101" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>49</v>
@@ -6544,16 +6537,16 @@
         <v>145</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F102" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>49</v>
@@ -6580,16 +6573,16 @@
         <v>112</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F103" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>49</v>
@@ -6616,16 +6609,16 @@
         <v>62</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F104" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>49</v>
@@ -6658,10 +6651,10 @@
         <v>57</v>
       </c>
       <c r="F105" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>49</v>
@@ -6694,10 +6687,10 @@
         <v>58</v>
       </c>
       <c r="F106" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>49</v>
@@ -6730,10 +6723,10 @@
         <v>57</v>
       </c>
       <c r="F107" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>613</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>49</v>
@@ -6766,10 +6759,10 @@
         <v>57</v>
       </c>
       <c r="F108" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>49</v>
@@ -6802,10 +6795,10 @@
         <v>57</v>
       </c>
       <c r="F109" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>49</v>
@@ -6838,10 +6831,10 @@
         <v>57</v>
       </c>
       <c r="F110" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>49</v>
@@ -6874,10 +6867,10 @@
         <v>57</v>
       </c>
       <c r="F111" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>49</v>
@@ -6904,16 +6897,16 @@
         <v>326</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>220</v>
       </c>
       <c r="F112" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>49</v>
@@ -6946,10 +6939,10 @@
         <v>57</v>
       </c>
       <c r="F113" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>626</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>49</v>
@@ -6982,10 +6975,10 @@
         <v>57</v>
       </c>
       <c r="F114" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>49</v>
@@ -7018,10 +7011,10 @@
         <v>172</v>
       </c>
       <c r="F115" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="G115" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>49</v>
@@ -7054,7 +7047,7 @@
         <v>175</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>72</v>
@@ -7084,16 +7077,16 @@
         <v>62</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F117" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="G117" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>634</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>49</v>
@@ -7126,10 +7119,10 @@
         <v>57</v>
       </c>
       <c r="F118" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>49</v>
@@ -7162,7 +7155,7 @@
         <v>57</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>199</v>
@@ -7198,10 +7191,10 @@
         <v>172</v>
       </c>
       <c r="F120" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="G120" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>49</v>
@@ -7234,10 +7227,10 @@
         <v>173</v>
       </c>
       <c r="F121" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="G121" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>49</v>
@@ -7255,25 +7248,25 @@
     </row>
     <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B122" s="2">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>399</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>49</v>
@@ -7291,25 +7284,25 @@
     </row>
     <row r="123" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B123" s="2">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>399</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>49</v>
@@ -7336,16 +7329,16 @@
         <v>324</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F124" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="G124" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>49</v>
@@ -7378,10 +7371,10 @@
         <v>75</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>49</v>
@@ -7405,19 +7398,19 @@
         <v>0</v>
       </c>
       <c r="C126" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F126" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="G126" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>317</v>
@@ -7450,10 +7443,10 @@
         <v>75</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>49</v>
@@ -7486,7 +7479,7 @@
         <v>75</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>203</v>
@@ -7516,16 +7509,16 @@
         <v>326</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F129" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="G129" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>317</v>
@@ -7558,10 +7551,10 @@
         <v>75</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>49</v>
@@ -7579,7 +7572,7 @@
     </row>
     <row r="131" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B131" s="2">
         <v>56</v>
@@ -7588,16 +7581,16 @@
         <v>73</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F131" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="G131" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>49</v>
@@ -7606,7 +7599,7 @@
         <v>3</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K131" s="2" t="str" cm="1">
         <f t="array" ref="K131">_xlfn.REGEXEXTRACT(A131,"(?&lt;=//)[^/]+")</f>
@@ -7630,7 +7623,7 @@
         <v>75</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>72</v>
@@ -7666,10 +7659,10 @@
         <v>57</v>
       </c>
       <c r="F133" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>49</v>
@@ -7702,7 +7695,7 @@
         <v>57</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>72</v>
@@ -7714,7 +7707,7 @@
         <v>3</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="K134" s="2" t="str" cm="1">
         <f t="array" ref="K134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
@@ -7738,10 +7731,10 @@
         <v>57</v>
       </c>
       <c r="F135" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="G135" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>49</v>
@@ -7768,16 +7761,16 @@
         <v>208</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F136" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="G136" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>49</v>
@@ -7810,10 +7803,10 @@
         <v>57</v>
       </c>
       <c r="F137" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="G137" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>49</v>
@@ -7840,16 +7833,16 @@
         <v>326</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F138" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G138" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>49</v>
@@ -7882,10 +7875,10 @@
         <v>56</v>
       </c>
       <c r="F139" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>92</v>
@@ -7918,10 +7911,10 @@
         <v>172</v>
       </c>
       <c r="F140" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="G140" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>49</v>
@@ -7954,10 +7947,10 @@
         <v>172</v>
       </c>
       <c r="F141" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="G141" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>672</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>49</v>
@@ -7990,10 +7983,10 @@
         <v>172</v>
       </c>
       <c r="F142" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="G142" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>49</v>
@@ -8020,16 +8013,16 @@
         <v>89</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F143" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="G143" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>49</v>
@@ -8056,16 +8049,16 @@
         <v>170</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F144" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="G144" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>49</v>
@@ -8098,10 +8091,10 @@
         <v>173</v>
       </c>
       <c r="F145" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G145" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>49</v>
@@ -8134,10 +8127,10 @@
         <v>172</v>
       </c>
       <c r="F146" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="G146" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>49</v>
@@ -8170,10 +8163,10 @@
         <v>57</v>
       </c>
       <c r="F147" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="G147" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>686</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>49</v>
@@ -8200,13 +8193,13 @@
         <v>89</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>109</v>
@@ -8242,7 +8235,7 @@
         <v>57</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>59</v>
@@ -8278,10 +8271,10 @@
         <v>172</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>49</v>
@@ -8314,7 +8307,7 @@
         <v>57</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>52</v>
@@ -8341,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>159</v>
@@ -8350,10 +8343,10 @@
         <v>57</v>
       </c>
       <c r="F152" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="G152" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>49</v>
@@ -8377,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>183</v>
@@ -8386,10 +8379,10 @@
         <v>57</v>
       </c>
       <c r="F153" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="G153" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>697</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>49</v>
@@ -8398,7 +8391,7 @@
         <v>3</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K153" s="2" t="str" cm="1">
         <f t="array" ref="K153">_xlfn.REGEXEXTRACT(A153,"(?&lt;=//)[^/]+")</f>
@@ -8422,7 +8415,7 @@
         <v>75</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>72</v>
@@ -8458,10 +8451,10 @@
         <v>172</v>
       </c>
       <c r="F155" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G155" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>49</v>
@@ -8494,10 +8487,10 @@
         <v>57</v>
       </c>
       <c r="F156" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="G156" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>49</v>
@@ -8524,16 +8517,16 @@
         <v>226</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F157" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="G157" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>49</v>
@@ -8560,16 +8553,16 @@
         <v>111</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F158" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="G158" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>49</v>
@@ -8602,10 +8595,10 @@
         <v>58</v>
       </c>
       <c r="F159" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="G159" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>49</v>
@@ -8638,7 +8631,7 @@
         <v>57</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>257</v>
@@ -8668,13 +8661,13 @@
         <v>89</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>72</v>
@@ -8704,16 +8697,16 @@
         <v>326</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F162" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="G162" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>49</v>
@@ -8749,7 +8742,7 @@
         <v>233</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>49</v>
@@ -8776,13 +8769,13 @@
         <v>89</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>90</v>
@@ -8818,10 +8811,10 @@
         <v>172</v>
       </c>
       <c r="F165" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="G165" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>49</v>
@@ -8839,8 +8832,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:K1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="A1:K165">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8854,11 +8847,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:K165">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I165">

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECBFB88-45B3-45D5-A30F-85D9B2080B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89B2F31-4EA4-46DC-A90E-249AF3FBAA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="2145" windowWidth="20730" windowHeight="11760" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NSFW_Links" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="819">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -1191,9 +1191,6 @@
     <t>ash,allie</t>
   </si>
   <si>
-    <t>2f,lesbian strapon pretzel,toilet,toe in pussy,inverted ass fuck</t>
-  </si>
-  <si>
     <t>arms up tied,vertical m legs,joined legs up</t>
   </si>
   <si>
@@ -1395,9 +1392,6 @@
     <t>cassandra cruz,samantha sin</t>
   </si>
   <si>
-    <t>body licking,bikini,foot worship,call girls,non nude,multiple girls</t>
-  </si>
-  <si>
     <t>stand on ice,wooden horse,bent froward</t>
   </si>
   <si>
@@ -1467,9 +1461,6 @@
     <t>lily's full length bdsm videos but smaller collection and not very exciting</t>
   </si>
   <si>
-    <t>gangbang,piss drinking,double penetration,fingering,anal,blowjob</t>
-  </si>
-  <si>
     <t>casey calvert,tommy king</t>
   </si>
   <si>
@@ -1689,9 +1680,6 @@
     <t>spank at 1m,wedgie at 2m,hair tied to wedgie,enema at 3m,inverted pussy over face at 5m,missionary at 9m</t>
   </si>
   <si>
-    <t>gangbang,blackout contacts,body clothespin,flog,nipple clamps,drinking game</t>
-  </si>
-  <si>
     <t>stand,lay down, legs to side,doggy</t>
   </si>
   <si>
@@ -2016,9 +2004,6 @@
     <t>humiliation,chastity,feet on head,outdoor,ball kick,feminization</t>
   </si>
   <si>
-    <t>spank,face sitting,fondle,nipple sucking</t>
-  </si>
-  <si>
     <t>inverted,lay down,kneel</t>
   </si>
   <si>
@@ -2076,9 +2061,6 @@
     <t>lay on side one leg up,stand,doggy</t>
   </si>
   <si>
-    <t>face sitting,pussy eat,nipple sucking,fondle,fingering</t>
-  </si>
-  <si>
     <t>leg up stand,69,inverted</t>
   </si>
   <si>
@@ -2406,9 +2388,6 @@
     <t>stand</t>
   </si>
   <si>
-    <t>fist,ass eat,pussy eat,fingering,anal fingering,kissing</t>
-  </si>
-  <si>
     <t>flog,rubber band feet,piv,vibrator</t>
   </si>
   <si>
@@ -2443,6 +2422,102 @@
   </si>
   <si>
     <t>https://beeg.com/FemDom?f=pegging</t>
+  </si>
+  <si>
+    <t>https://www.eporner.com/profile/Peterboni/</t>
+  </si>
+  <si>
+    <t>massage,ball gag, tit suction cups,tanlines,oiled,vibrator</t>
+  </si>
+  <si>
+    <t>doggy,missionary,pretzel</t>
+  </si>
+  <si>
+    <t>uploads and favorites lot of good maledom and lesdom content full length</t>
+  </si>
+  <si>
+    <t>https://www.eporner.com/video-DyzpntUTPNR/anna-bell-peaks/</t>
+  </si>
+  <si>
+    <t>ball gag,cane,flog,spank,spike wheel,nipple suction,panty gag,cunnilingus,electric</t>
+  </si>
+  <si>
+    <t>stand, lay down</t>
+  </si>
+  <si>
+    <t>undressing at 2m,spank at 6m,spike wheel at 8m,flog at 10m,smothered in tits at 14m,nipple suction at 15m,panty gag at 15m,electric at 31m</t>
+  </si>
+  <si>
+    <t>https://www.eporner.com/video-CJgRBHS0tZK/lesbian-bondage-massage/</t>
+  </si>
+  <si>
+    <t>massage,oiled,vibrator</t>
+  </si>
+  <si>
+    <t>oiled up at 8m,not enough bondage or stuff to jerk off to</t>
+  </si>
+  <si>
+    <t>gangbang,blackout contacts,body clothespin,flog,nipple clamps,drink game</t>
+  </si>
+  <si>
+    <t>2f,pretzel,toilet,toe in pussy,inverted ass fuck</t>
+  </si>
+  <si>
+    <t>spank,face sitting,fondle,nipple suck</t>
+  </si>
+  <si>
+    <t>face sitting,pussy eat,nipple suck,fondle,fingering</t>
+  </si>
+  <si>
+    <t>body lick,bikini,foot worship,call girls,non nude,multiple girls</t>
+  </si>
+  <si>
+    <t>fist,ass eat,pussy eat,fingering,anal fingering,kiss</t>
+  </si>
+  <si>
+    <t>gangbang,piss drink,double penetration,fingering,anal,blowjob</t>
+  </si>
+  <si>
+    <t>https://bdsmmansion.com/video/11127/08-04-04-5181-daisy-marie-aiden-starr-daisy-s-promotion/</t>
+  </si>
+  <si>
+    <t>aiden star,daisy marie</t>
+  </si>
+  <si>
+    <t>cunnilingus,fingering,panty gag,spank,tit flog,pussy flog,ball gag,flog,vibrator,strapon,open mouth gag,pussy clamps,clit suction,nipple suction</t>
+  </si>
+  <si>
+    <t>kneel,lay down,frog,missionary</t>
+  </si>
+  <si>
+    <t>undress at 5m,spank at 11m,flog at 14m,ass flog at 16m,clit and nipple suction at 31m,</t>
+  </si>
+  <si>
+    <t>https://www.eporner.com/video-0Jc4FNhL6Tz/katrina-fucks-her-brunette-girlfriend-aidra-with-a-strap-on/</t>
+  </si>
+  <si>
+    <t>spit,vibrator,armpits,cunnilingus,fingering,nipple bite,strapon,leash,hitachi</t>
+  </si>
+  <si>
+    <t>lay down,kneel,missionary,doggy</t>
+  </si>
+  <si>
+    <t>spit at 1m,strapon at 24m,leash at 31m,hitachi at 31m</t>
+  </si>
+  <si>
+    <t>https://www.eporner.com/video-YF6E7Jl9juO/river-lynn-bondage-sex/?trx=1227735290aee694b81473a256bea12420712</t>
+  </si>
+  <si>
+    <t>river lynn</t>
+  </si>
+  <si>
+    <t>spank,flog,cane,blowjob,piv,vibrator,pussy fist,nipple clamps</t>
+  </si>
+  <si>
+    <t>pillory,missionary</t>
+  </si>
+  <si>
+    <t>spank at 7m,blowjob at 10m,flog at 11m,nipple clamps at 32m,very generic piv bdsm</t>
   </si>
 </sst>
 </file>
@@ -2525,14 +2600,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6161"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -2823,7 +2891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <dimension ref="A1:K165"/>
+  <dimension ref="A1:K171"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" style="1" customWidth="1"/>
@@ -2876,7 +2944,7 @@
     </row>
     <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B2" s="2">
         <v>11</v>
@@ -2885,16 +2953,16 @@
         <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>49</v>
@@ -2903,7 +2971,7 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="K2" s="2" t="str" cm="1">
         <f t="array" ref="K2">_xlfn.REGEXEXTRACT(A2,"(?&lt;=//)[^/]+")</f>
@@ -2927,10 +2995,10 @@
         <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>542</v>
+        <v>798</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>49</v>
@@ -2948,7 +3016,7 @@
     </row>
     <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B4" s="2">
         <v>53</v>
@@ -2957,16 +3025,16 @@
         <v>133</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>49</v>
@@ -2975,7 +3043,7 @@
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="K4" s="2" t="str" cm="1">
         <f t="array" ref="K4">_xlfn.REGEXEXTRACT(A4,"(?&lt;=//)[^/]+")</f>
@@ -2999,7 +3067,7 @@
         <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>357</v>
@@ -3011,7 +3079,7 @@
         <v>8</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="K5" s="2" t="str" cm="1">
         <f t="array" ref="K5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
@@ -3029,13 +3097,13 @@
         <v>197</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>358</v>
@@ -3062,16 +3130,16 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>359</v>
@@ -3098,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>54</v>
@@ -3128,25 +3196,25 @@
     </row>
     <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>49</v>
@@ -3155,7 +3223,7 @@
         <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="K9" s="2" t="str" cm="1">
         <f t="array" ref="K9">_xlfn.REGEXEXTRACT(A9,"(?&lt;=//)[^/]+")</f>
@@ -3170,19 +3238,19 @@
         <v>0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>327</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>49</v>
@@ -3206,19 +3274,19 @@
         <v>0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
@@ -3251,10 +3319,10 @@
         <v>53</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>49</v>
@@ -3287,10 +3355,10 @@
         <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>49</v>
@@ -3299,7 +3367,7 @@
         <v>7</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K13" s="2" t="str" cm="1">
         <f t="array" ref="K13">_xlfn.REGEXEXTRACT(A13,"(?&lt;=//)[^/]+")</f>
@@ -3323,7 +3391,7 @@
         <v>54</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>363</v>
@@ -3335,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="K14" s="2" t="str" cm="1">
         <f t="array" ref="K14">_xlfn.REGEXEXTRACT(A14,"(?&lt;=//)[^/]+")</f>
@@ -3359,10 +3427,10 @@
         <v>54</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>49</v>
@@ -3371,7 +3439,7 @@
         <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="K15" s="2" t="str" cm="1">
         <f t="array" ref="K15">_xlfn.REGEXEXTRACT(A15,"(?&lt;=//)[^/]+")</f>
@@ -3395,10 +3463,10 @@
         <v>54</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>49</v>
@@ -3407,7 +3475,7 @@
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="K16" s="2" t="str" cm="1">
         <f t="array" ref="K16">_xlfn.REGEXEXTRACT(A16,"(?&lt;=//)[^/]+")</f>
@@ -3416,7 +3484,7 @@
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B17" s="2">
         <v>48</v>
@@ -3425,16 +3493,16 @@
         <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>49</v>
@@ -3443,7 +3511,7 @@
         <v>7</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="K17" s="2" t="str" cm="1">
         <f t="array" ref="K17">_xlfn.REGEXEXTRACT(A17,"(?&lt;=//)[^/]+")</f>
@@ -3458,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>319</v>
@@ -3470,7 +3538,7 @@
         <v>367</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -3494,19 +3562,19 @@
         <v>111</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>49</v>
@@ -3515,7 +3583,7 @@
         <v>7</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="K19" s="2" t="str" cm="1">
         <f t="array" ref="K19">_xlfn.REGEXEXTRACT(A19,"(?&lt;=//)[^/]+")</f>
@@ -3539,10 +3607,10 @@
         <v>54</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>49</v>
@@ -3560,7 +3628,7 @@
     </row>
     <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B21" s="2">
         <v>44</v>
@@ -3569,16 +3637,16 @@
         <v>67</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>49</v>
@@ -3587,7 +3655,7 @@
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="K21" s="2" t="str" cm="1">
         <f t="array" ref="K21">_xlfn.REGEXEXTRACT(A21,"(?&lt;=//)[^/]+")</f>
@@ -3596,25 +3664,25 @@
     </row>
     <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B22" s="2">
         <v>99</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>49</v>
@@ -3623,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="K22" s="2" t="str" cm="1">
         <f t="array" ref="K22">_xlfn.REGEXEXTRACT(A22,"(?&lt;=//)[^/]+")</f>
@@ -3638,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>327</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>49</v>
@@ -3695,7 +3763,7 @@
         <v>7</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="K24" s="2" t="str" cm="1">
         <f t="array" ref="K24">_xlfn.REGEXEXTRACT(A24,"(?&lt;=//)[^/]+")</f>
@@ -3719,7 +3787,7 @@
         <v>54</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>364</v>
@@ -3731,7 +3799,7 @@
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="K25" s="2" t="str" cm="1">
         <f t="array" ref="K25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
@@ -3755,7 +3823,7 @@
         <v>55</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>369</v>
@@ -3767,7 +3835,7 @@
         <v>7</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="K26" s="2" t="str" cm="1">
         <f t="array" ref="K26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
@@ -3785,13 +3853,13 @@
         <v>67</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>366</v>
@@ -3818,10 +3886,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>154</v>
@@ -3857,16 +3925,16 @@
         <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>49</v>
@@ -3884,97 +3952,97 @@
     </row>
     <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="B30" s="2">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>601</v>
+        <v>788</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>386</v>
+        <v>789</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I30" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>339</v>
+        <v>790</v>
       </c>
       <c r="K30" s="2" t="str" cm="1">
         <f t="array" ref="K30">_xlfn.REGEXEXTRACT(A30,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>333</v>
+        <v>805</v>
       </c>
       <c r="B31" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>534</v>
+        <v>101</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>164</v>
+        <v>806</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>383</v>
+        <v>807</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>384</v>
+        <v>808</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I31" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>334</v>
+        <v>809</v>
       </c>
       <c r="K31" s="2" t="str" cm="1">
         <f t="array" ref="K31">_xlfn.REGEXEXTRACT(A31,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmmansion.com</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>71</v>
+        <v>786</v>
       </c>
       <c r="B32" s="2">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>72</v>
+        <v>526</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>183</v>
+        <v>525</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>588</v>
+        <v>385</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>49</v>
@@ -3983,34 +4051,34 @@
         <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>96</v>
+        <v>339</v>
       </c>
       <c r="K32" s="2" t="str" cm="1">
         <f t="array" ref="K32">_xlfn.REGEXEXTRACT(A32,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>112</v>
+        <v>333</v>
       </c>
       <c r="B33" s="2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>197</v>
+        <v>531</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>589</v>
+        <v>382</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>49</v>
@@ -4019,34 +4087,34 @@
         <v>6</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>590</v>
+        <v>334</v>
       </c>
       <c r="K33" s="2" t="str" cm="1">
         <f t="array" ref="K33">_xlfn.REGEXEXTRACT(A33,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B34" s="2">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>533</v>
+        <v>72</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>377</v>
+        <v>584</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>49</v>
@@ -4055,34 +4123,34 @@
         <v>6</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K34" s="2" t="str" cm="1">
         <f t="array" ref="K34">_xlfn.REGEXEXTRACT(A34,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>342</v>
+        <v>112</v>
       </c>
       <c r="B35" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>529</v>
+        <v>197</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>528</v>
+        <v>143</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>388</v>
+        <v>585</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>596</v>
+        <v>379</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>49</v>
@@ -4091,34 +4159,34 @@
         <v>6</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>343</v>
+        <v>586</v>
       </c>
       <c r="K35" s="2" t="str" cm="1">
         <f t="array" ref="K35">_xlfn.REGEXEXTRACT(A35,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>512</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>67</v>
+        <v>530</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>513</v>
+        <v>64</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>514</v>
+        <v>376</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>49</v>
@@ -4127,34 +4195,34 @@
         <v>6</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>595</v>
+        <v>93</v>
       </c>
       <c r="K36" s="2" t="str" cm="1">
         <f t="array" ref="K36">_xlfn.REGEXEXTRACT(A36,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B37" s="2">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>628</v>
+        <v>387</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>629</v>
+        <v>592</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>49</v>
@@ -4163,34 +4231,34 @@
         <v>6</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K37" s="2" t="str" cm="1">
         <f t="array" ref="K37">_xlfn.REGEXEXTRACT(A37,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>792</v>
+        <v>509</v>
       </c>
       <c r="B38" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>529</v>
+        <v>67</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>387</v>
+        <v>511</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>49</v>
@@ -4199,34 +4267,34 @@
         <v>6</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="K38" s="2" t="str" cm="1">
         <f t="array" ref="K38">_xlfn.REGEXEXTRACT(A38,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>503</v>
+        <v>340</v>
       </c>
       <c r="B39" s="2">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>67</v>
+        <v>526</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>501</v>
+        <v>625</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>49</v>
@@ -4235,34 +4303,34 @@
         <v>6</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>504</v>
+        <v>341</v>
       </c>
       <c r="K39" s="2" t="str" cm="1">
         <f t="array" ref="K39">_xlfn.REGEXEXTRACT(A39,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>488</v>
+        <v>785</v>
       </c>
       <c r="B40" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>489</v>
+        <v>386</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>49</v>
@@ -4271,34 +4339,34 @@
         <v>6</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="K40" s="2" t="str" cm="1">
         <f t="array" ref="K40">_xlfn.REGEXEXTRACT(A40,"(?&lt;=//)[^/]+")</f>
-        <v>abbdsm.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>124</v>
+        <v>500</v>
       </c>
       <c r="B41" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>152</v>
+        <v>525</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>381</v>
+        <v>498</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>49</v>
@@ -4307,34 +4375,34 @@
         <v>6</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>171</v>
+        <v>501</v>
       </c>
       <c r="K41" s="2" t="str" cm="1">
         <f t="array" ref="K41">_xlfn.REGEXEXTRACT(A41,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>15</v>
+        <v>485</v>
       </c>
       <c r="B42" s="2">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>375</v>
+        <v>527</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>376</v>
+        <v>598</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>605</v>
+        <v>486</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>49</v>
@@ -4343,34 +4411,34 @@
         <v>6</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>90</v>
+        <v>599</v>
       </c>
       <c r="K42" s="2" t="str" cm="1">
         <f t="array" ref="K42">_xlfn.REGEXEXTRACT(A42,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>abbdsm.com</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="B43" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>49</v>
@@ -4379,34 +4447,34 @@
         <v>6</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K43" s="2" t="str" cm="1">
         <f t="array" ref="K43">_xlfn.REGEXEXTRACT(A43,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.tnaflix.com</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>526</v>
+        <v>15</v>
       </c>
       <c r="B44" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>67</v>
+        <v>530</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>527</v>
+        <v>375</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>607</v>
+        <v>799</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>49</v>
@@ -4415,34 +4483,34 @@
         <v>6</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>609</v>
+        <v>90</v>
       </c>
       <c r="K44" s="2" t="str" cm="1">
         <f t="array" ref="K44">_xlfn.REGEXEXTRACT(A44,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="B45" s="2">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>611</v>
+        <v>381</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>49</v>
@@ -4451,7 +4519,7 @@
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="K45" s="2" t="str" cm="1">
         <f t="array" ref="K45">_xlfn.REGEXEXTRACT(A45,"(?&lt;=//)[^/]+")</f>
@@ -4460,61 +4528,61 @@
     </row>
     <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>276</v>
+        <v>523</v>
       </c>
       <c r="B46" s="2">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>532</v>
+        <v>67</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I46" s="2">
         <v>6</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="K46" s="2" t="str" cm="1">
         <f t="array" ref="K46">_xlfn.REGEXEXTRACT(A46,"(?&lt;=//)[^/]+")</f>
-        <v>abjav.com</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="B47" s="2">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>67</v>
+        <v>208</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>528</v>
+        <v>226</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>501</v>
+        <v>607</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>49</v>
@@ -4523,70 +4591,70 @@
         <v>6</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>502</v>
+        <v>227</v>
       </c>
       <c r="K47" s="2" t="str" cm="1">
         <f t="array" ref="K47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>344</v>
+        <v>276</v>
       </c>
       <c r="B48" s="2">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>269</v>
+        <v>529</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>49</v>
+        <v>265</v>
       </c>
       <c r="I48" s="2">
         <v>6</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>345</v>
+        <v>610</v>
       </c>
       <c r="K48" s="2" t="str" cm="1">
         <f t="array" ref="K48">_xlfn.REGEXEXTRACT(A48,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>abjav.com</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>9</v>
+        <v>497</v>
       </c>
       <c r="B49" s="2">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>219</v>
+        <v>525</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>373</v>
+        <v>498</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>49</v>
@@ -4595,34 +4663,34 @@
         <v>6</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>619</v>
+        <v>499</v>
       </c>
       <c r="K49" s="2" t="str" cm="1">
         <f t="array" ref="K49">_xlfn.REGEXEXTRACT(A49,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>5</v>
+        <v>344</v>
       </c>
       <c r="B50" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>144</v>
+        <v>269</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>207</v>
+        <v>525</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>378</v>
+        <v>612</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>49</v>
@@ -4631,34 +4699,34 @@
         <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>623</v>
+        <v>345</v>
       </c>
       <c r="K50" s="2" t="str" cm="1">
         <f t="array" ref="K50">_xlfn.REGEXEXTRACT(A50,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B51" s="2">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>49</v>
@@ -4667,7 +4735,7 @@
         <v>6</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>222</v>
+        <v>615</v>
       </c>
       <c r="K51" s="2" t="str" cm="1">
         <f t="array" ref="K51">_xlfn.REGEXEXTRACT(A51,"(?&lt;=//)[^/]+")</f>
@@ -4676,25 +4744,25 @@
     </row>
     <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>490</v>
+        <v>5</v>
       </c>
       <c r="B52" s="2">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>533</v>
+        <v>144</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>491</v>
+        <v>207</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>492</v>
+        <v>618</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>493</v>
+        <v>377</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>49</v>
@@ -4703,25 +4771,25 @@
         <v>6</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>494</v>
+        <v>619</v>
       </c>
       <c r="K52" s="2" t="str" cm="1">
         <f t="array" ref="K52">_xlfn.REGEXEXTRACT(A52,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>484</v>
+        <v>12</v>
       </c>
       <c r="B53" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>529</v>
+        <v>87</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>528</v>
+        <v>143</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>54</v>
@@ -4730,7 +4798,7 @@
         <v>620</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>621</v>
+        <v>378</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>49</v>
@@ -4739,34 +4807,34 @@
         <v>6</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>485</v>
+        <v>222</v>
       </c>
       <c r="K53" s="2" t="str" cm="1">
         <f t="array" ref="K53">_xlfn.REGEXEXTRACT(A53,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B54" s="2">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>269</v>
+        <v>530</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>627</v>
+        <v>490</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>49</v>
@@ -4775,34 +4843,34 @@
         <v>6</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="K54" s="2" t="str" cm="1">
         <f t="array" ref="K54">_xlfn.REGEXEXTRACT(A54,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>xhamster44.desi</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>30</v>
+        <v>481</v>
       </c>
       <c r="B55" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>177</v>
+        <v>526</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>178</v>
+        <v>525</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>49</v>
@@ -4811,34 +4879,34 @@
         <v>6</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>179</v>
+        <v>482</v>
       </c>
       <c r="K55" s="2" t="str" cm="1">
         <f t="array" ref="K55">_xlfn.REGEXEXTRACT(A55,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>297</v>
+        <v>493</v>
       </c>
       <c r="B56" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>269</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>186</v>
+        <v>494</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>632</v>
+        <v>495</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>49</v>
@@ -4847,70 +4915,70 @@
         <v>6</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>634</v>
+        <v>496</v>
       </c>
       <c r="K56" s="2" t="str" cm="1">
         <f t="array" ref="K56">_xlfn.REGEXEXTRACT(A56,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>262</v>
+        <v>30</v>
       </c>
       <c r="B57" s="2">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>532</v>
+        <v>177</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>530</v>
+        <v>178</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>263</v>
+        <v>49</v>
       </c>
       <c r="I57" s="2">
         <v>6</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>637</v>
+        <v>179</v>
       </c>
       <c r="K57" s="2" t="str" cm="1">
         <f t="array" ref="K57">_xlfn.REGEXEXTRACT(A57,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>245</v>
+        <v>297</v>
       </c>
       <c r="B58" s="2">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>61</v>
+        <v>269</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>372</v>
+        <v>629</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>49</v>
@@ -4919,70 +4987,70 @@
         <v>6</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="K58" s="2" t="str" cm="1">
         <f t="array" ref="K58">_xlfn.REGEXEXTRACT(A58,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>59</v>
+        <v>262</v>
       </c>
       <c r="B59" s="2">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>58</v>
+        <v>529</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>184</v>
+        <v>527</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>374</v>
+        <v>632</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>49</v>
+        <v>263</v>
       </c>
       <c r="I59" s="2">
         <v>6</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="K59" s="2" t="str" cm="1">
         <f t="array" ref="K59">_xlfn.REGEXEXTRACT(A59,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>486</v>
+        <v>245</v>
       </c>
       <c r="B60" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>529</v>
+        <v>61</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>528</v>
+        <v>246</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>599</v>
+        <v>634</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>600</v>
+        <v>372</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>49</v>
@@ -4991,34 +5059,34 @@
         <v>6</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>487</v>
+        <v>635</v>
       </c>
       <c r="K60" s="2" t="str" cm="1">
         <f t="array" ref="K60">_xlfn.REGEXEXTRACT(A60,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>337</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>528</v>
+        <v>184</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>385</v>
+        <v>636</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>617</v>
+        <v>374</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>49</v>
@@ -5027,34 +5095,34 @@
         <v>6</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>338</v>
+        <v>637</v>
       </c>
       <c r="K61" s="2" t="str" cm="1">
         <f t="array" ref="K61">_xlfn.REGEXEXTRACT(A61,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>abxxx.com</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>335</v>
+        <v>483</v>
       </c>
       <c r="B62" s="2">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>269</v>
+        <v>526</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>625</v>
+        <v>595</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>49</v>
@@ -5063,142 +5131,142 @@
         <v>6</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>336</v>
+        <v>484</v>
       </c>
       <c r="K62" s="2" t="str" cm="1">
         <f t="array" ref="K62">_xlfn.REGEXEXTRACT(A62,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B63" s="2">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>529</v>
+        <v>197</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>650</v>
+        <v>384</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>408</v>
+        <v>613</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I63" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="K63" s="2" t="str" cm="1">
         <f t="array" ref="K63">_xlfn.REGEXEXTRACT(A63,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="B64" s="2">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>532</v>
+        <v>269</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>390</v>
+        <v>622</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I64" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>643</v>
+        <v>336</v>
       </c>
       <c r="K64" s="2" t="str" cm="1">
         <f t="array" ref="K64">_xlfn.REGEXEXTRACT(A64,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>253</v>
+        <v>791</v>
       </c>
       <c r="B65" s="2">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>58</v>
+        <v>530</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>392</v>
+        <v>527</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>644</v>
+        <v>792</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>393</v>
+        <v>793</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I65" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>645</v>
+        <v>794</v>
       </c>
       <c r="K65" s="2" t="str" cm="1">
         <f t="array" ref="K65">_xlfn.REGEXEXTRACT(A65,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>236</v>
+        <v>348</v>
       </c>
       <c r="B66" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>208</v>
+        <v>526</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>237</v>
+        <v>525</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>646</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>49</v>
@@ -5207,34 +5275,34 @@
         <v>5</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>647</v>
+        <v>349</v>
       </c>
       <c r="K66" s="2" t="str" cm="1">
         <f t="array" ref="K66">_xlfn.REGEXEXTRACT(A66,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="B67" s="2">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>133</v>
+        <v>529</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>134</v>
+        <v>527</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>49</v>
@@ -5243,34 +5311,34 @@
         <v>5</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>135</v>
+        <v>639</v>
       </c>
       <c r="K67" s="2" t="str" cm="1">
         <f t="array" ref="K67">_xlfn.REGEXEXTRACT(A67,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="B68" s="2">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>533</v>
+        <v>58</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>530</v>
+        <v>391</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>280</v>
+        <v>54</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>57</v>
+        <v>392</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>49</v>
@@ -5279,34 +5347,34 @@
         <v>5</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>281</v>
+        <v>641</v>
       </c>
       <c r="K68" s="2" t="str" cm="1">
         <f t="array" ref="K68">_xlfn.REGEXEXTRACT(A68,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>40</v>
+        <v>236</v>
       </c>
       <c r="B69" s="2">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>403</v>
+        <v>237</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>652</v>
+        <v>395</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>49</v>
@@ -5315,70 +5383,70 @@
         <v>5</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="K69" s="2" t="str" cm="1">
         <f t="array" ref="K69">_xlfn.REGEXEXTRACT(A69,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>277</v>
+        <v>120</v>
       </c>
       <c r="B70" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>532</v>
+        <v>133</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>530</v>
+        <v>134</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>655</v>
+        <v>405</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I70" s="2">
         <v>5</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>278</v>
+        <v>135</v>
       </c>
       <c r="K70" s="2" t="str" cm="1">
         <f t="array" ref="K70">_xlfn.REGEXEXTRACT(A70,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B71" s="2">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>197</v>
+        <v>530</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>294</v>
+        <v>527</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>54</v>
+        <v>280</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>657</v>
+        <v>57</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>49</v>
@@ -5387,34 +5455,34 @@
         <v>5</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>658</v>
+        <v>281</v>
       </c>
       <c r="K71" s="2" t="str" cm="1">
         <f t="array" ref="K71">_xlfn.REGEXEXTRACT(A71,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntrex.com</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B72" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>60</v>
+        <v>163</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>65</v>
+        <v>402</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>404</v>
+        <v>800</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>49</v>
@@ -5423,70 +5491,70 @@
         <v>5</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>92</v>
+        <v>648</v>
       </c>
       <c r="K72" s="2" t="str" cm="1">
         <f t="array" ref="K72">_xlfn.REGEXEXTRACT(A72,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>tube.perverzija.com</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>42</v>
+        <v>277</v>
       </c>
       <c r="B73" s="2">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>67</v>
+        <v>529</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>186</v>
+        <v>527</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>49</v>
+        <v>265</v>
       </c>
       <c r="I73" s="2">
         <v>5</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>95</v>
+        <v>278</v>
       </c>
       <c r="K73" s="2" t="str" cm="1">
         <f t="array" ref="K73">_xlfn.REGEXEXTRACT(A73,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>243</v>
+        <v>293</v>
       </c>
       <c r="B74" s="2">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>394</v>
+        <v>652</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>49</v>
@@ -5495,34 +5563,34 @@
         <v>5</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="K74" s="2" t="str" cm="1">
         <f t="array" ref="K74">_xlfn.REGEXEXTRACT(A74,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.porntrex.com</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B75" s="2">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>532</v>
+        <v>60</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>530</v>
+        <v>65</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>664</v>
+        <v>403</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>398</v>
+        <v>654</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>49</v>
@@ -5531,34 +5599,34 @@
         <v>5</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="K75" s="2" t="str" cm="1">
         <f t="array" ref="K75">_xlfn.REGEXEXTRACT(A75,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>238</v>
+        <v>42</v>
       </c>
       <c r="B76" s="2">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>395</v>
+        <v>656</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>49</v>
@@ -5567,34 +5635,34 @@
         <v>5</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>666</v>
+        <v>95</v>
       </c>
       <c r="K76" s="2" t="str" cm="1">
         <f t="array" ref="K76">_xlfn.REGEXEXTRACT(A76,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>305</v>
+        <v>243</v>
       </c>
       <c r="B77" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>306</v>
+        <v>244</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>49</v>
@@ -5603,34 +5671,34 @@
         <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="K77" s="2" t="str" cm="1">
         <f t="array" ref="K77">_xlfn.REGEXEXTRACT(A77,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B78" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>208</v>
+        <v>529</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>183</v>
+        <v>527</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>670</v>
+        <v>397</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>49</v>
@@ -5639,34 +5707,34 @@
         <v>5</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="K78" s="2" t="str" cm="1">
         <f t="array" ref="K78">_xlfn.REGEXEXTRACT(A78,"(?&lt;=//)[^/]+")</f>
-        <v>hcbdsm.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>8</v>
+        <v>238</v>
       </c>
       <c r="B79" s="2">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>533</v>
+        <v>61</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>402</v>
+        <v>239</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>672</v>
+        <v>394</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>49</v>
@@ -5675,34 +5743,34 @@
         <v>5</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="K79" s="2" t="str" cm="1">
         <f t="array" ref="K79">_xlfn.REGEXEXTRACT(A79,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>254</v>
+        <v>305</v>
       </c>
       <c r="B80" s="2">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>533</v>
+        <v>67</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>49</v>
@@ -5711,34 +5779,34 @@
         <v>5</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>256</v>
+        <v>663</v>
       </c>
       <c r="K80" s="2" t="str" cm="1">
         <f t="array" ref="K80">_xlfn.REGEXEXTRACT(A80,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B81" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>399</v>
+        <v>665</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>49</v>
@@ -5747,34 +5815,34 @@
         <v>5</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K81" s="2" t="str" cm="1">
         <f t="array" ref="K81">_xlfn.REGEXEXTRACT(A81,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>hcbdsm.com</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B82" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>58</v>
+        <v>530</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>202</v>
+        <v>401</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>677</v>
+        <v>801</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>400</v>
+        <v>666</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>49</v>
@@ -5783,34 +5851,34 @@
         <v>5</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="K82" s="2" t="str" cm="1">
         <f t="array" ref="K82">_xlfn.REGEXEXTRACT(A82,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="B83" s="2">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>269</v>
+        <v>530</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>410</v>
+        <v>255</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>49</v>
@@ -5819,34 +5887,34 @@
         <v>5</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>680</v>
+        <v>256</v>
       </c>
       <c r="K83" s="2" t="str" cm="1">
         <f t="array" ref="K83">_xlfn.REGEXEXTRACT(A83,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B84" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>405</v>
+        <v>210</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>682</v>
+        <v>398</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>49</v>
@@ -5855,70 +5923,70 @@
         <v>5</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>683</v>
+        <v>211</v>
       </c>
       <c r="K84" s="2" t="str" cm="1">
         <f t="array" ref="K84">_xlfn.REGEXEXTRACT(A84,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="B85" s="2">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>533</v>
+        <v>58</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>530</v>
+        <v>202</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I85" s="2">
         <v>5</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="K85" s="2" t="str" cm="1">
         <f t="array" ref="K85">_xlfn.REGEXEXTRACT(A85,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>524</v>
+        <v>300</v>
       </c>
       <c r="B86" s="2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>67</v>
+        <v>269</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>525</v>
+        <v>409</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>627</v>
+        <v>410</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>49</v>
@@ -5927,34 +5995,34 @@
         <v>5</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="K86" s="2" t="str" cm="1">
         <f t="array" ref="K86">_xlfn.REGEXEXTRACT(A86,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>270</v>
+        <v>28</v>
       </c>
       <c r="B87" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>532</v>
+        <v>60</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>530</v>
+        <v>404</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>49</v>
@@ -5963,70 +6031,70 @@
         <v>5</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>271</v>
+        <v>677</v>
       </c>
       <c r="K87" s="2" t="str" cm="1">
         <f t="array" ref="K87">_xlfn.REGEXEXTRACT(A87,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>116</v>
+        <v>264</v>
       </c>
       <c r="B88" s="2">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>61</v>
+        <v>530</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>401</v>
+        <v>527</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>691</v>
+        <v>388</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>49</v>
+        <v>265</v>
       </c>
       <c r="I88" s="2">
         <v>5</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>176</v>
+        <v>679</v>
       </c>
       <c r="K88" s="2" t="str" cm="1">
         <f t="array" ref="K88">_xlfn.REGEXEXTRACT(A88,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>122</v>
+        <v>521</v>
       </c>
       <c r="B89" s="2">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>161</v>
+        <v>522</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>693</v>
+        <v>623</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>49</v>
@@ -6035,34 +6103,34 @@
         <v>5</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="K89" s="2" t="str" cm="1">
         <f t="array" ref="K89">_xlfn.REGEXEXTRACT(A89,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>515</v>
+        <v>270</v>
       </c>
       <c r="B90" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>197</v>
+        <v>529</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>49</v>
@@ -6071,34 +6139,34 @@
         <v>5</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>697</v>
+        <v>271</v>
       </c>
       <c r="K90" s="2" t="str" cm="1">
         <f t="array" ref="K90">_xlfn.REGEXEXTRACT(A90,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="B91" s="2">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>76</v>
+        <v>685</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>49</v>
@@ -6107,7 +6175,7 @@
         <v>5</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="K91" s="2" t="str" cm="1">
         <f t="array" ref="K91">_xlfn.REGEXEXTRACT(A91,"(?&lt;=//)[^/]+")</f>
@@ -6116,25 +6184,25 @@
     </row>
     <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>298</v>
+        <v>122</v>
       </c>
       <c r="B92" s="2">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>269</v>
+        <v>58</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>299</v>
+        <v>161</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>409</v>
+        <v>687</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>49</v>
@@ -6143,34 +6211,34 @@
         <v>5</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="K92" s="2" t="str" cm="1">
         <f t="array" ref="K92">_xlfn.REGEXEXTRACT(A92,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>130</v>
+        <v>512</v>
       </c>
       <c r="B93" s="2">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>136</v>
+        <v>513</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>98</v>
+        <v>690</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>49</v>
@@ -6179,34 +6247,34 @@
         <v>5</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>220</v>
+        <v>691</v>
       </c>
       <c r="K93" s="2" t="str" cm="1">
         <f t="array" ref="K93">_xlfn.REGEXEXTRACT(A93,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="B94" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>535</v>
+        <v>396</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>407</v>
+        <v>76</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>49</v>
@@ -6215,178 +6283,178 @@
         <v>5</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="K94" s="2" t="str" cm="1">
         <f t="array" ref="K94">_xlfn.REGEXEXTRACT(A94,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>505</v>
+        <v>298</v>
       </c>
       <c r="B95" s="2">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>529</v>
+        <v>269</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>528</v>
+        <v>299</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>327</v>
+        <v>69</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>529</v>
+        <v>693</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I95" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>350</v>
+        <v>694</v>
       </c>
       <c r="K95" s="2" t="str" cm="1">
         <f t="array" ref="K95">_xlfn.REGEXEXTRACT(A95,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>506</v>
+        <v>130</v>
       </c>
       <c r="B96" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>529</v>
+        <v>177</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>528</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>327</v>
+        <v>54</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>529</v>
+        <v>695</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I96" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>351</v>
+        <v>220</v>
       </c>
       <c r="K96" s="2" t="str" cm="1">
         <f t="array" ref="K96">_xlfn.REGEXEXTRACT(A96,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>128</v>
+        <v>346</v>
       </c>
       <c r="B97" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>64</v>
+        <v>532</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>702</v>
+        <v>670</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>441</v>
+        <v>406</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I97" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>141</v>
+        <v>347</v>
       </c>
       <c r="K97" s="2" t="str" cm="1">
         <f t="array" ref="K97">_xlfn.REGEXEXTRACT(A97,"(?&lt;=//)[^/]+")</f>
-        <v>www.porndead.org</v>
+        <v>www.txxx.porn</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>33</v>
+        <v>795</v>
       </c>
       <c r="B98" s="2">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>177</v>
+        <v>530</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>75</v>
+        <v>527</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>703</v>
+        <v>796</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>429</v>
+        <v>66</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>49</v>
+        <v>286</v>
       </c>
       <c r="I98" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>704</v>
+        <v>797</v>
       </c>
       <c r="K98" s="2" t="str" cm="1">
         <f t="array" ref="K98">_xlfn.REGEXEXTRACT(A98,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>34</v>
+        <v>502</v>
       </c>
       <c r="B99" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>60</v>
+        <v>526</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>200</v>
+        <v>525</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>54</v>
+        <v>327</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>705</v>
+        <v>526</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>431</v>
+        <v>383</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>49</v>
@@ -6395,34 +6463,34 @@
         <v>4</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>201</v>
+        <v>350</v>
       </c>
       <c r="K99" s="2" t="str" cm="1">
         <f t="array" ref="K99">_xlfn.REGEXEXTRACT(A99,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>netfapx.net</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>16</v>
+        <v>503</v>
       </c>
       <c r="B100" s="2">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>101</v>
+        <v>526</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>423</v>
+        <v>525</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>55</v>
+        <v>327</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>706</v>
+        <v>526</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>49</v>
@@ -6431,34 +6499,34 @@
         <v>4</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>707</v>
+        <v>351</v>
       </c>
       <c r="K100" s="2" t="str" cm="1">
         <f t="array" ref="K100">_xlfn.REGEXEXTRACT(A100,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>pornzog.com</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B101" s="2">
         <v>11</v>
       </c>
-      <c r="B101" s="2">
-        <v>44</v>
-      </c>
       <c r="C101" s="2" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>433</v>
+        <v>696</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>708</v>
+        <v>440</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>49</v>
@@ -6467,34 +6535,34 @@
         <v>4</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="K101" s="2" t="str" cm="1">
         <f t="array" ref="K101">_xlfn.REGEXEXTRACT(A101,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.porndead.org</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="B102" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>49</v>
@@ -6503,34 +6571,34 @@
         <v>4</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>165</v>
+        <v>698</v>
       </c>
       <c r="K102" s="2" t="str" cm="1">
         <f t="array" ref="K102">_xlfn.REGEXEXTRACT(A102,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B103" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>530</v>
+        <v>200</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>562</v>
+        <v>430</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>49</v>
@@ -6539,34 +6607,34 @@
         <v>4</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="K103" s="2" t="str" cm="1">
         <f t="array" ref="K103">_xlfn.REGEXEXTRACT(A103,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B104" s="2">
+        <v>59</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F104" s="2" t="s">
-        <v>427</v>
+        <v>700</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>49</v>
@@ -6575,7 +6643,7 @@
         <v>4</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>62</v>
+        <v>701</v>
       </c>
       <c r="K104" s="2" t="str" cm="1">
         <f t="array" ref="K104">_xlfn.REGEXEXTRACT(A104,"(?&lt;=//)[^/]+")</f>
@@ -6584,25 +6652,25 @@
     </row>
     <row r="105" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="B105" s="2">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>711</v>
+        <v>432</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>440</v>
+        <v>702</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>49</v>
@@ -6611,7 +6679,7 @@
         <v>4</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="K105" s="2" t="str" cm="1">
         <f t="array" ref="K105">_xlfn.REGEXEXTRACT(A105,"(?&lt;=//)[^/]+")</f>
@@ -6620,25 +6688,25 @@
     </row>
     <row r="106" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="B106" s="2">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>49</v>
@@ -6647,34 +6715,34 @@
         <v>4</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="K106" s="2" t="str" cm="1">
         <f t="array" ref="K106">_xlfn.REGEXEXTRACT(A106,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B107" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>75</v>
+        <v>527</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>714</v>
+        <v>558</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>49</v>
@@ -6683,34 +6751,34 @@
         <v>4</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="K107" s="2" t="str" cm="1">
         <f t="array" ref="K107">_xlfn.REGEXEXTRACT(A107,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.party</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>289</v>
+        <v>20</v>
       </c>
       <c r="B108" s="2">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>290</v>
+        <v>185</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>715</v>
+        <v>426</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>716</v>
+        <v>427</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>49</v>
@@ -6719,34 +6787,34 @@
         <v>4</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>291</v>
+        <v>62</v>
       </c>
       <c r="K108" s="2" t="str" cm="1">
         <f t="array" ref="K108">_xlfn.REGEXEXTRACT(A108,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B109" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>533</v>
+        <v>144</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>437</v>
+        <v>705</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>66</v>
+        <v>439</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>49</v>
@@ -6755,34 +6823,34 @@
         <v>4</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="K109" s="2" t="str" cm="1">
         <f t="array" ref="K109">_xlfn.REGEXEXTRACT(A109,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B110" s="2">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>142</v>
+        <v>68</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>173</v>
+        <v>419</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>49</v>
@@ -6791,34 +6859,34 @@
         <v>4</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="K110" s="2" t="str" cm="1">
         <f t="array" ref="K110">_xlfn.REGEXEXTRACT(A110,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="B111" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>58</v>
+        <v>177</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>435</v>
+        <v>708</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>49</v>
@@ -6827,7 +6895,7 @@
         <v>4</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="K111" s="2" t="str" cm="1">
         <f t="array" ref="K111">_xlfn.REGEXEXTRACT(A111,"(?&lt;=//)[^/]+")</f>
@@ -6836,25 +6904,25 @@
     </row>
     <row r="112" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>115</v>
+        <v>289</v>
       </c>
       <c r="B112" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>532</v>
+        <v>105</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>719</v>
+        <v>290</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>434</v>
+        <v>710</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>49</v>
@@ -6863,34 +6931,34 @@
         <v>4</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="K112" s="2" t="str" cm="1">
         <f t="array" ref="K112">_xlfn.REGEXEXTRACT(A112,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>301</v>
+        <v>119</v>
       </c>
       <c r="B113" s="2">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>269</v>
+        <v>530</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>302</v>
+        <v>159</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>721</v>
+        <v>436</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>412</v>
+        <v>66</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>49</v>
@@ -6899,34 +6967,34 @@
         <v>4</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>722</v>
+        <v>160</v>
       </c>
       <c r="K113" s="2" t="str" cm="1">
         <f t="array" ref="K113">_xlfn.REGEXEXTRACT(A113,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>txxx.me</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>235</v>
+        <v>4</v>
       </c>
       <c r="B114" s="2">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>421</v>
+        <v>142</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>422</v>
+        <v>173</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>49</v>
@@ -6935,7 +7003,7 @@
         <v>4</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>724</v>
+        <v>145</v>
       </c>
       <c r="K114" s="2" t="str" cm="1">
         <f t="array" ref="K114">_xlfn.REGEXEXTRACT(A114,"(?&lt;=//)[^/]+")</f>
@@ -6944,25 +7012,25 @@
     </row>
     <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>517</v>
+        <v>108</v>
       </c>
       <c r="B115" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>518</v>
+        <v>172</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>616</v>
+        <v>434</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>49</v>
@@ -6971,34 +7039,34 @@
         <v>4</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>726</v>
+        <v>174</v>
       </c>
       <c r="K115" s="2" t="str" cm="1">
         <f t="array" ref="K115">_xlfn.REGEXEXTRACT(A115,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>266</v>
+        <v>115</v>
       </c>
       <c r="B116" s="2">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>415</v>
+        <v>713</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>416</v>
+        <v>714</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>49</v>
@@ -7007,34 +7075,34 @@
         <v>4</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>727</v>
+        <v>193</v>
       </c>
       <c r="K116" s="2" t="str" cm="1">
         <f t="array" ref="K116">_xlfn.REGEXEXTRACT(A116,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B117" s="2">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>532</v>
+        <v>269</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>530</v>
+        <v>302</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>413</v>
+        <v>715</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>49</v>
@@ -7043,34 +7111,34 @@
         <v>4</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>268</v>
+        <v>716</v>
       </c>
       <c r="K117" s="2" t="str" cm="1">
         <f t="array" ref="K117">_xlfn.REGEXEXTRACT(A117,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="B118" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>729</v>
+        <v>421</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>49</v>
@@ -7079,34 +7147,34 @@
         <v>4</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="K118" s="2" t="str" cm="1">
         <f t="array" ref="K118">_xlfn.REGEXEXTRACT(A118,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>22</v>
+        <v>514</v>
       </c>
       <c r="B119" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>195</v>
+        <v>515</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>432</v>
+        <v>612</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>49</v>
@@ -7115,34 +7183,34 @@
         <v>4</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>196</v>
+        <v>720</v>
       </c>
       <c r="K119" s="2" t="str" cm="1">
         <f t="array" ref="K119">_xlfn.REGEXEXTRACT(A119,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="B120" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>100</v>
+        <v>530</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>732</v>
+        <v>415</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>49</v>
@@ -7151,70 +7219,70 @@
         <v>4</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>103</v>
+        <v>721</v>
       </c>
       <c r="K120" s="2" t="str" cm="1">
         <f t="array" ref="K120">_xlfn.REGEXEXTRACT(A120,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>punishbang.com</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>352</v>
+        <v>267</v>
       </c>
       <c r="B121" s="2">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>529</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>742</v>
+        <v>412</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>743</v>
+        <v>413</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I121" s="2">
         <v>4</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>353</v>
+        <v>268</v>
       </c>
       <c r="K121" s="2" t="str" cm="1">
         <f t="array" ref="K121">_xlfn.REGEXEXTRACT(A121,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>punishbang.com</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="B122" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>425</v>
+        <v>259</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>426</v>
+        <v>723</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>49</v>
@@ -7223,34 +7291,34 @@
         <v>4</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="K122" s="2" t="str" cm="1">
         <f t="array" ref="K122">_xlfn.REGEXEXTRACT(A122,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B123" s="2">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>181</v>
+        <v>61</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>49</v>
@@ -7259,34 +7327,34 @@
         <v>4</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="K123" s="2" t="str" cm="1">
         <f t="array" ref="K123">_xlfn.REGEXEXTRACT(A123,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster18.desi</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B124" s="2">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>49</v>
@@ -7295,70 +7363,70 @@
         <v>4</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>737</v>
+        <v>103</v>
       </c>
       <c r="K124" s="2" t="str" cm="1">
         <f t="array" ref="K124">_xlfn.REGEXEXTRACT(A124,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>13</v>
+        <v>352</v>
       </c>
       <c r="B125" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>61</v>
+        <v>526</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>216</v>
+        <v>525</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>430</v>
+        <v>736</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>49</v>
+        <v>265</v>
       </c>
       <c r="I125" s="2">
         <v>4</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>217</v>
+        <v>353</v>
       </c>
       <c r="K125" s="2" t="str" cm="1">
         <f t="array" ref="K125">_xlfn.REGEXEXTRACT(A125,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.tubegalore.com</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="B126" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>269</v>
+        <v>58</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>740</v>
+        <v>425</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>49</v>
@@ -7367,250 +7435,250 @@
         <v>4</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="K126" s="2" t="str" cm="1">
         <f t="array" ref="K126">_xlfn.REGEXEXTRACT(A126,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="B127" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>529</v>
+        <v>181</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>772</v>
+        <v>729</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>773</v>
+        <v>441</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I127" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>355</v>
+        <v>137</v>
       </c>
       <c r="K127" s="2" t="str" cm="1">
         <f t="array" ref="K127">_xlfn.REGEXEXTRACT(A127,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>xhamster18.desi</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>356</v>
+        <v>111</v>
       </c>
       <c r="B128" s="2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>529</v>
+        <v>58</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>161</v>
+        <v>437</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>764</v>
+        <v>730</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>466</v>
+        <v>438</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I128" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>467</v>
+        <v>731</v>
       </c>
       <c r="K128" s="2" t="str" cm="1">
         <f t="array" ref="K128">_xlfn.REGEXEXTRACT(A128,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>273</v>
+        <v>13</v>
       </c>
       <c r="B129" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>532</v>
+        <v>61</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>450</v>
+        <v>216</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>744</v>
+        <v>429</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>451</v>
+        <v>732</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I129" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="K129" s="2" t="str" cm="1">
         <f t="array" ref="K129">_xlfn.REGEXEXTRACT(A129,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>110</v>
+        <v>303</v>
       </c>
       <c r="B130" s="2">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>58</v>
+        <v>269</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>183</v>
+        <v>442</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I130" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="K130" s="2" t="str" cm="1">
         <f t="array" ref="K130">_xlfn.REGEXEXTRACT(A130,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>6</v>
+        <v>810</v>
       </c>
       <c r="B131" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>144</v>
+        <v>530</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>147</v>
+        <v>527</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>748</v>
+        <v>811</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>56</v>
+        <v>812</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I131" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>148</v>
+        <v>813</v>
       </c>
       <c r="K131" s="2" t="str" cm="1">
         <f t="array" ref="K131">_xlfn.REGEXEXTRACT(A131,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>36</v>
+        <v>814</v>
       </c>
       <c r="B132" s="2">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>447</v>
+        <v>815</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>749</v>
+        <v>816</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>448</v>
+        <v>817</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I132" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>94</v>
+        <v>818</v>
       </c>
       <c r="K132" s="2" t="str" cm="1">
         <f t="array" ref="K132">_xlfn.REGEXEXTRACT(A132,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>18</v>
+        <v>354</v>
       </c>
       <c r="B133" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>133</v>
+        <v>526</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>449</v>
+        <v>767</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>49</v>
@@ -7619,34 +7687,34 @@
         <v>3</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>199</v>
+        <v>355</v>
       </c>
       <c r="K133" s="2" t="str" cm="1">
         <f t="array" ref="K133">_xlfn.REGEXEXTRACT(A133,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>41</v>
+        <v>356</v>
       </c>
       <c r="B134" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>457</v>
+        <v>161</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>49</v>
@@ -7655,34 +7723,34 @@
         <v>3</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>155</v>
+        <v>465</v>
       </c>
       <c r="K134" s="2" t="str" cm="1">
         <f t="array" ref="K134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B135" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>60</v>
+        <v>529</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>261</v>
+        <v>448</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>49</v>
@@ -7691,34 +7759,34 @@
         <v>3</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>753</v>
+        <v>204</v>
       </c>
       <c r="K135" s="2" t="str" cm="1">
         <f t="array" ref="K135">_xlfn.REGEXEXTRACT(A135,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="B136" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>283</v>
+        <v>183</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>465</v>
+        <v>739</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>66</v>
+        <v>740</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>49</v>
@@ -7727,34 +7795,34 @@
         <v>3</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>284</v>
+        <v>741</v>
       </c>
       <c r="K136" s="2" t="str" cm="1">
         <f t="array" ref="K136">_xlfn.REGEXEXTRACT(A136,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="B137" s="2">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>49</v>
@@ -7763,34 +7831,34 @@
         <v>3</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>522</v>
+        <v>148</v>
       </c>
       <c r="K137" s="2" t="str" cm="1">
         <f t="array" ref="K137">_xlfn.REGEXEXTRACT(A137,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B138" s="2">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>533</v>
+        <v>180</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>64</v>
+        <v>445</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>49</v>
@@ -7799,34 +7867,34 @@
         <v>3</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="K138" s="2" t="str" cm="1">
         <f t="array" ref="K138">_xlfn.REGEXEXTRACT(A138,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="B139" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>49</v>
@@ -7835,34 +7903,34 @@
         <v>3</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>757</v>
+        <v>199</v>
       </c>
       <c r="K139" s="2" t="str" cm="1">
         <f t="array" ref="K139">_xlfn.REGEXEXTRACT(A139,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
       <c r="B140" s="2">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>67</v>
+        <v>530</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>215</v>
+        <v>455</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>616</v>
+        <v>456</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>49</v>
@@ -7871,34 +7939,34 @@
         <v>3</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>759</v>
+        <v>155</v>
       </c>
       <c r="K140" s="2" t="str" cm="1">
         <f t="array" ref="K140">_xlfn.REGEXEXTRACT(A140,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>39</v>
+        <v>260</v>
       </c>
       <c r="B141" s="2">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>455</v>
+        <v>261</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>49</v>
@@ -7907,34 +7975,34 @@
         <v>3</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="K141" s="2" t="str" cm="1">
         <f t="array" ref="K141">_xlfn.REGEXEXTRACT(A141,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>26</v>
+        <v>282</v>
       </c>
       <c r="B142" s="2">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>533</v>
+        <v>67</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>460</v>
+        <v>66</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>49</v>
@@ -7943,106 +8011,106 @@
         <v>3</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>158</v>
+        <v>284</v>
       </c>
       <c r="K142" s="2" t="str" cm="1">
         <f t="array" ref="K142">_xlfn.REGEXEXTRACT(A142,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntopedia.com</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>288</v>
+        <v>125</v>
       </c>
       <c r="B143" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>532</v>
+        <v>58</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>530</v>
+        <v>161</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>444</v>
+        <v>748</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>762</v>
+        <v>66</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I143" s="2">
         <v>3</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>763</v>
+        <v>519</v>
       </c>
       <c r="K143" s="2" t="str" cm="1">
         <f t="array" ref="K143">_xlfn.REGEXEXTRACT(A143,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="B144" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>72</v>
+        <v>530</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>766</v>
+        <v>450</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="I144" s="2">
         <v>3</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="K144" s="2" t="str" cm="1">
         <f t="array" ref="K144">_xlfn.REGEXEXTRACT(A144,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="B145" s="2">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>767</v>
+        <v>750</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>768</v>
+        <v>411</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>49</v>
@@ -8051,34 +8119,34 @@
         <v>3</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>151</v>
+        <v>751</v>
       </c>
       <c r="K145" s="2" t="str" cm="1">
         <f t="array" ref="K145">_xlfn.REGEXEXTRACT(A145,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="B146" s="2">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>533</v>
+        <v>67</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>523</v>
+        <v>752</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>769</v>
+        <v>612</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>49</v>
@@ -8087,34 +8155,34 @@
         <v>3</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>139</v>
+        <v>753</v>
       </c>
       <c r="K146" s="2" t="str" cm="1">
         <f t="array" ref="K146">_xlfn.REGEXEXTRACT(A146,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pervtube.net</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="B147" s="2">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>157</v>
+        <v>453</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>771</v>
+        <v>454</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>49</v>
@@ -8123,34 +8191,34 @@
         <v>3</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>191</v>
+        <v>755</v>
       </c>
       <c r="K147" s="2" t="str" cm="1">
         <f t="array" ref="K147">_xlfn.REGEXEXTRACT(A147,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="B148" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>49</v>
@@ -8159,106 +8227,106 @@
         <v>3</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="K148" s="2" t="str" cm="1">
         <f t="array" ref="K148">_xlfn.REGEXEXTRACT(A148,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>24</v>
+        <v>288</v>
       </c>
       <c r="B149" s="2">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>52</v>
+        <v>529</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>182</v>
+        <v>527</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>463</v>
+        <v>802</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>49</v>
+        <v>265</v>
       </c>
       <c r="I149" s="2">
         <v>3</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="K149" s="2" t="str" cm="1">
         <f t="array" ref="K149">_xlfn.REGEXEXTRACT(A149,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>519</v>
+        <v>77</v>
       </c>
       <c r="B150" s="2">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>520</v>
+        <v>79</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>776</v>
+        <v>759</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>521</v>
+        <v>760</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="I150" s="2">
         <v>3</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>777</v>
+        <v>97</v>
       </c>
       <c r="K150" s="2" t="str" cm="1">
         <f t="array" ref="K150">_xlfn.REGEXEXTRACT(A150,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B151" s="2">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>533</v>
+        <v>150</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>778</v>
+        <v>761</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>445</v>
+        <v>762</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>49</v>
@@ -8267,70 +8335,70 @@
         <v>3</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>779</v>
+        <v>151</v>
       </c>
       <c r="K151" s="2" t="str" cm="1">
         <f t="array" ref="K151">_xlfn.REGEXEXTRACT(A151,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>285</v>
+        <v>126</v>
       </c>
       <c r="B152" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>530</v>
+        <v>138</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>464</v>
+        <v>520</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>780</v>
+        <v>763</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>286</v>
+        <v>49</v>
       </c>
       <c r="I152" s="2">
         <v>3</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>287</v>
+        <v>139</v>
       </c>
       <c r="K152" s="2" t="str" cm="1">
         <f t="array" ref="K152">_xlfn.REGEXEXTRACT(A152,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>www.tnaflix.com</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="B153" s="2">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>461</v>
+        <v>157</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>462</v>
+        <v>764</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>98</v>
+        <v>765</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>49</v>
@@ -8339,250 +8407,250 @@
         <v>3</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>99</v>
+        <v>191</v>
       </c>
       <c r="K153" s="2" t="str" cm="1">
         <f t="array" ref="K153">_xlfn.REGEXEXTRACT(A153,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B154" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>100</v>
+        <v>530</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>471</v>
+        <v>166</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>781</v>
+        <v>451</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I154" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="K154" s="2" t="str" cm="1">
         <f t="array" ref="K154">_xlfn.REGEXEXTRACT(A154,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="B155" s="2">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>782</v>
+        <v>461</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>221</v>
+        <v>768</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I155" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>162</v>
+        <v>769</v>
       </c>
       <c r="K155" s="2" t="str" cm="1">
         <f t="array" ref="K155">_xlfn.REGEXEXTRACT(A155,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>anyporn.com</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>131</v>
+        <v>516</v>
       </c>
       <c r="B156" s="2">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>475</v>
+        <v>517</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>66</v>
+        <v>518</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I156" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>149</v>
+        <v>771</v>
       </c>
       <c r="K156" s="2" t="str" cm="1">
         <f t="array" ref="K156">_xlfn.REGEXEXTRACT(A156,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="B157" s="2">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>105</v>
+        <v>530</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>66</v>
+        <v>443</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I157" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>274</v>
+        <v>773</v>
       </c>
       <c r="K157" s="2" t="str" cm="1">
         <f t="array" ref="K157">_xlfn.REGEXEXTRACT(A157,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="B158" s="2">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>60</v>
+        <v>529</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>75</v>
+        <v>527</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>474</v>
+        <v>774</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>49</v>
+        <v>286</v>
       </c>
       <c r="I158" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="K158" s="2" t="str" cm="1">
         <f t="array" ref="K158">_xlfn.REGEXEXTRACT(A158,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="B159" s="2">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>785</v>
+        <v>460</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>470</v>
+        <v>98</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I159" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="K159" s="2" t="str" cm="1">
         <f t="array" ref="K159">_xlfn.REGEXEXTRACT(A159,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>240</v>
+        <v>113</v>
       </c>
       <c r="B160" s="2">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>533</v>
+        <v>100</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>241</v>
+        <v>468</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>468</v>
+        <v>803</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>786</v>
+        <v>469</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>49</v>
@@ -8591,34 +8659,34 @@
         <v>2</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="K160" s="2" t="str" cm="1">
         <f t="array" ref="K160">_xlfn.REGEXEXTRACT(A160,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B161" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>532</v>
+        <v>58</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>476</v>
+        <v>161</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>477</v>
+        <v>775</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>478</v>
+        <v>221</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>49</v>
@@ -8627,34 +8695,34 @@
         <v>2</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>275</v>
+        <v>162</v>
       </c>
       <c r="K161" s="2" t="str" cm="1">
         <f t="array" ref="K161">_xlfn.REGEXEXTRACT(A161,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>228</v>
+        <v>131</v>
       </c>
       <c r="B162" s="2">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>229</v>
+        <v>83</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>230</v>
+        <v>472</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>788</v>
+        <v>66</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>49</v>
@@ -8663,43 +8731,43 @@
         <v>2</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>231</v>
+        <v>149</v>
       </c>
       <c r="K162" s="2" t="str" cm="1">
         <f t="array" ref="K162">_xlfn.REGEXEXTRACT(A162,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="B163" s="2">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>461</v>
+        <v>106</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>480</v>
+        <v>777</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I163" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>85</v>
+        <v>274</v>
       </c>
       <c r="K163" s="2" t="str" cm="1">
         <f t="array" ref="K163">_xlfn.REGEXEXTRACT(A163,"(?&lt;=//)[^/]+")</f>
@@ -8708,73 +8776,289 @@
     </row>
     <row r="164" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B164" s="2">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>533</v>
+        <v>60</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>789</v>
+        <v>470</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>790</v>
+        <v>471</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I164" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>791</v>
+        <v>194</v>
       </c>
       <c r="K164" s="2" t="str" cm="1">
         <f t="array" ref="K164">_xlfn.REGEXEXTRACT(A164,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="B165" s="2">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>83</v>
+        <v>466</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>203</v>
+        <v>778</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I165" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="K165" s="2" t="str" cm="1">
         <f t="array" ref="K165">_xlfn.REGEXEXTRACT(A165,"(?&lt;=//)[^/]+")</f>
+        <v>www.omg.xxx</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B166" s="2">
+        <v>64</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I166" s="2">
+        <v>2</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K166" s="2" t="str" cm="1">
+        <f t="array" ref="K166">_xlfn.REGEXEXTRACT(A166,"(?&lt;=//)[^/]+")</f>
+        <v>www.peekvids.com</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B167" s="2">
+        <v>18</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I167" s="2">
+        <v>2</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K167" s="2" t="str" cm="1">
+        <f t="array" ref="K167">_xlfn.REGEXEXTRACT(A167,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B168" s="2">
+        <v>57</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I168" s="2">
+        <v>2</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K168" s="2" t="str" cm="1">
+        <f t="array" ref="K168">_xlfn.REGEXEXTRACT(A168,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B169" s="2">
+        <v>34</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I169" s="2">
+        <v>1</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K169" s="2" t="str" cm="1">
+        <f t="array" ref="K169">_xlfn.REGEXEXTRACT(A169,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B170" s="2">
+        <v>11</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I170" s="2">
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="K170" s="2" t="str" cm="1">
+        <f t="array" ref="K170">_xlfn.REGEXEXTRACT(A170,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B171" s="2">
+        <v>48</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I171" s="2">
+        <v>1</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K171" s="2" t="str" cm="1">
+        <f t="array" ref="K171">_xlfn.REGEXEXTRACT(A171,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
@@ -8784,12 +9068,12 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:K1">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="colorScale" priority="25">
+    <cfRule type="colorScale" priority="35">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8800,18 +9084,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G165">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:F165 H2:K165">
+  <conditionalFormatting sqref="J2:K168">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I165">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="I2:I171">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89B2F31-4EA4-46DC-A90E-249AF3FBAA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B36337-7141-4A05-9B7D-B27B750765C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="2145" windowWidth="20730" windowHeight="11760" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="835">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -537,9 +537,6 @@
     <t>melody marks</t>
   </si>
   <si>
-    <t>tit job at 12m,oiled footjob at 14m</t>
-  </si>
-  <si>
     <t>elle d</t>
   </si>
   <si>
@@ -915,9 +912,6 @@
     <t>lorelei lee</t>
   </si>
   <si>
-    <t>mid tit job with hands tied</t>
-  </si>
-  <si>
     <t>https://www.eporner.com/video-J7qRDyI3Im5/permanent-chastity/?trx=1227735290aee694b81473a256bea12420712</t>
   </si>
   <si>
@@ -1452,9 +1446,6 @@
     <t>chastity,pa piercing</t>
   </si>
   <si>
-    <t>bite gag,blowjob,tit job</t>
-  </si>
-  <si>
     <t>lay down,suspended face down,bent</t>
   </si>
   <si>
@@ -1773,9 +1764,6 @@
     <t>pussy slap at 0m,flog femdom at 25m,wax at 42m,flame on ass at 43m,bent at 52m,wooden horse at 88m</t>
   </si>
   <si>
-    <t>flog,nipple weights,ball gag,blindfold,nipple string,fingering</t>
-  </si>
-  <si>
     <t>sitting split,pretzel vertical,inverted split</t>
   </si>
   <si>
@@ -2518,6 +2506,66 @@
   </si>
   <si>
     <t>spank at 7m,blowjob at 10m,flog at 11m,nipple clamps at 32m,very generic piv bdsm</t>
+  </si>
+  <si>
+    <t>https://abxxx.com/video/338120/april-olsen-in-pegging-strapon-anal/?campaign_id=520379779</t>
+  </si>
+  <si>
+    <t>april olsen</t>
+  </si>
+  <si>
+    <t>rubber,latex,butt plug,peg,blindfold,asphyxiation,titjob,footjob,trample,piv</t>
+  </si>
+  <si>
+    <t>missionary,sit, lay down</t>
+  </si>
+  <si>
+    <t>INSANELY hot rubber wearing actress,butt plug at 8m,peg at 11m,blindfold at 22m,asphyxiation at 25m,titjob at 20m,footjob at 35m,piv at end</t>
+  </si>
+  <si>
+    <t>https://www.amateur8.com/videos/716960/spank-me-lascivious/?utm_source=donnie</t>
+  </si>
+  <si>
+    <t>spank,paddle,hair pull</t>
+  </si>
+  <si>
+    <t>doggy,over knee,pretzel,inverted pussy over face</t>
+  </si>
+  <si>
+    <t>spank,paddle,hair pull,large paddle at 19m,inverted pussy over face at 28m</t>
+  </si>
+  <si>
+    <t>https://www.xozilla.xxx/videos/811128/shameless-dykes-lesdom-breathtaking-xxx-scene/</t>
+  </si>
+  <si>
+    <t>oiled,feet,foot in ass,foot in pussy,silver powder,fishnet,scissor</t>
+  </si>
+  <si>
+    <t>foot in pussy at 2m,doggy foot in pussy at 6m,silver powder on feet and pussy at 10m,fishnet inside pussy at 14m,scissor at end</t>
+  </si>
+  <si>
+    <t>bite gag,blowjob,titjob</t>
+  </si>
+  <si>
+    <t>mid titjob with hands tied</t>
+  </si>
+  <si>
+    <t>titjob at 12m,oiled footjob at 14m</t>
+  </si>
+  <si>
+    <t>https://www.eporner.com/video-XNmcInOIKaz/tied-bitch/?trx=1227735290aee694b81473a256bea12420712</t>
+  </si>
+  <si>
+    <t>nose hook,ball gag, pussy wedgie,flog,cane,vibrator,anal hook,spank,clit suction,pussy clamps,slap,tit slap,dp dildo,nipple clamps weight,oiled,one bar prison,spit,fucking machine</t>
+  </si>
+  <si>
+    <t>doggy,missionary legs tied together,a legs stand</t>
+  </si>
+  <si>
+    <t>pussy wedgie at 3m,flog at 3m, anal hook at 9m, spank at 20m, clit suction at 24m, slap at 26m,smothered in tits at 29m,tit slap at 33m, dp dildo at 39m,nipple clamps weight at 43m,oiled at 46m,one bar prison at 46m,oil spit at 47m,ass cane at 47,fucking machine at 51m</t>
+  </si>
+  <si>
+    <t>flog,nipple clamps weight,ball gag,blindfold,nipple string,fingering</t>
   </si>
 </sst>
 </file>
@@ -2600,7 +2648,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6161"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2891,7 +2946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <dimension ref="A1:K171"/>
+  <dimension ref="A1:K175"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" style="1" customWidth="1"/>
@@ -2918,16 +2973,16 @@
         <v>46</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>47</v>
@@ -2942,45 +2997,45 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>480</v>
+        <v>830</v>
       </c>
       <c r="B2" s="2">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>536</v>
+        <v>831</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>537</v>
+        <v>832</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>538</v>
+        <v>833</v>
       </c>
       <c r="K2" s="2" t="str" cm="1">
         <f t="array" ref="K2">_xlfn.REGEXEXTRACT(A2,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B3" s="2">
         <v>87</v>
@@ -2989,88 +3044,88 @@
         <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K3" s="2" t="str" cm="1">
         <f t="array" ref="K3">_xlfn.REGEXEXTRACT(A3,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>504</v>
+        <v>293</v>
       </c>
       <c r="B4" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>505</v>
+        <v>294</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>540</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="K4" s="2" t="str" cm="1">
         <f t="array" ref="K4">_xlfn.REGEXEXTRACT(A4,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>295</v>
+        <v>477</v>
       </c>
       <c r="B5" s="2">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>197</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>296</v>
+        <v>524</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>357</v>
+        <v>534</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>49</v>
@@ -3079,34 +3134,34 @@
         <v>8</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="K5" s="2" t="str" cm="1">
         <f t="array" ref="K5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>xhamster44.desi</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>310</v>
+        <v>501</v>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>358</v>
+        <v>538</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>49</v>
@@ -3115,34 +3170,34 @@
         <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>311</v>
+        <v>539</v>
       </c>
       <c r="K6" s="2" t="str" cm="1">
         <f t="array" ref="K6">_xlfn.REGEXEXTRACT(A6,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>abxxx.com</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>526</v>
+        <v>196</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>49</v>
@@ -3151,34 +3206,34 @@
         <v>8</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K7" s="2" t="str" cm="1">
         <f t="array" ref="K7">_xlfn.REGEXEXTRACT(A7,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B8" s="2">
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>360</v>
+        <v>530</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>49</v>
@@ -3187,34 +3242,34 @@
         <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K8" s="2" t="str" cm="1">
         <f t="array" ref="K8">_xlfn.REGEXEXTRACT(A8,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>478</v>
+        <v>312</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>534</v>
+        <v>358</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>535</v>
+        <v>359</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>49</v>
@@ -3223,7 +3278,7 @@
         <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>479</v>
+        <v>313</v>
       </c>
       <c r="K9" s="2" t="str" cm="1">
         <f t="array" ref="K9">_xlfn.REGEXEXTRACT(A9,"(?&lt;=//)[^/]+")</f>
@@ -3232,97 +3287,97 @@
     </row>
     <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>326</v>
+        <v>475</v>
       </c>
       <c r="B10" s="2">
         <v>0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>327</v>
+        <v>69</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>383</v>
+        <v>532</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>328</v>
+        <v>476</v>
       </c>
       <c r="K10" s="2" t="str" cm="1">
         <f t="array" ref="K10">_xlfn.REGEXEXTRACT(A10,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>324</v>
+        <v>815</v>
       </c>
       <c r="B11" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>528</v>
+        <v>196</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>525</v>
+        <v>816</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>548</v>
+        <v>817</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>549</v>
+        <v>818</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>325</v>
+        <v>819</v>
       </c>
       <c r="K11" s="2" t="str" cm="1">
         <f t="array" ref="K11">_xlfn.REGEXEXTRACT(A11,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>abxxx.com</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>324</v>
       </c>
       <c r="B12" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>180</v>
+        <v>523</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>362</v>
+        <v>522</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>53</v>
+        <v>325</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>547</v>
+        <v>381</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>49</v>
@@ -3331,34 +3386,34 @@
         <v>7</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>91</v>
+        <v>326</v>
       </c>
       <c r="K12" s="2" t="str" cm="1">
         <f t="array" ref="K12">_xlfn.REGEXEXTRACT(A12,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="B13" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>525</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>224</v>
+        <v>522</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>49</v>
@@ -3367,34 +3422,34 @@
         <v>7</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>552</v>
+        <v>323</v>
       </c>
       <c r="K13" s="2" t="str" cm="1">
         <f t="array" ref="K13">_xlfn.REGEXEXTRACT(A13,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>363</v>
+        <v>544</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>49</v>
@@ -3403,34 +3458,34 @@
         <v>7</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>556</v>
+        <v>91</v>
       </c>
       <c r="K14" s="2" t="str" cm="1">
         <f t="array" ref="K14">_xlfn.REGEXEXTRACT(A14,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="B15" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>49</v>
@@ -3439,34 +3494,34 @@
         <v>7</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="K15" s="2" t="str" cm="1">
         <f t="array" ref="K15">_xlfn.REGEXEXTRACT(A15,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="B16" s="2">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>561</v>
+        <v>361</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>49</v>
@@ -3475,34 +3530,34 @@
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="K16" s="2" t="str" cm="1">
         <f t="array" ref="K16">_xlfn.REGEXEXTRACT(A16,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>506</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>507</v>
+        <v>157</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>49</v>
@@ -3511,34 +3566,34 @@
         <v>7</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="K17" s="2" t="str" cm="1">
         <f t="array" ref="K17">_xlfn.REGEXEXTRACT(A17,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>318</v>
+        <v>222</v>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>526</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>319</v>
+        <v>223</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>320</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>367</v>
+        <v>557</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>49</v>
@@ -3547,34 +3602,34 @@
         <v>7</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>321</v>
+        <v>559</v>
       </c>
       <c r="K18" s="2" t="str" cm="1">
         <f t="array" ref="K18">_xlfn.REGEXEXTRACT(A18,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>252</v>
+        <v>503</v>
       </c>
       <c r="B19" s="2">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>529</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>49</v>
@@ -3583,34 +3638,34 @@
         <v>7</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="K19" s="2" t="str" cm="1">
         <f t="array" ref="K19">_xlfn.REGEXEXTRACT(A19,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="B20" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>523</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>183</v>
+        <v>317</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>54</v>
+        <v>318</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>570</v>
+        <v>365</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>49</v>
@@ -3619,34 +3674,34 @@
         <v>7</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>63</v>
+        <v>319</v>
       </c>
       <c r="K20" s="2" t="str" cm="1">
         <f t="array" ref="K20">_xlfn.REGEXEXTRACT(A20,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>492</v>
+        <v>251</v>
       </c>
       <c r="B21" s="2">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>67</v>
+        <v>526</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>475</v>
+        <v>565</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>49</v>
@@ -3655,34 +3710,34 @@
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="K21" s="2" t="str" cm="1">
         <f t="array" ref="K21">_xlfn.REGEXEXTRACT(A21,"(?&lt;=//)[^/]+")</f>
-        <v>www.fapcat.com</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>508</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>529</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>527</v>
+        <v>182</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>574</v>
+        <v>834</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>49</v>
@@ -3691,34 +3746,34 @@
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>576</v>
+        <v>63</v>
       </c>
       <c r="K22" s="2" t="str" cm="1">
         <f t="array" ref="K22">_xlfn.REGEXEXTRACT(A22,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>526</v>
+        <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>327</v>
+        <v>69</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>526</v>
+        <v>568</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>383</v>
+        <v>472</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>49</v>
@@ -3727,34 +3782,34 @@
         <v>7</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>330</v>
+        <v>569</v>
       </c>
       <c r="K23" s="2" t="str" cm="1">
         <f t="array" ref="K23">_xlfn.REGEXEXTRACT(A23,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fapcat.com</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="B24" s="2">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>87</v>
+        <v>526</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>88</v>
+        <v>524</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>365</v>
+        <v>570</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>49</v>
@@ -3763,34 +3818,34 @@
         <v>7</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="K24" s="2" t="str" cm="1">
         <f t="array" ref="K24">_xlfn.REGEXEXTRACT(A24,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>xhamster44.desi</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>114</v>
+        <v>327</v>
       </c>
       <c r="B25" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>58</v>
+        <v>523</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>212</v>
+        <v>522</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>54</v>
+        <v>325</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>579</v>
+        <v>523</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>49</v>
@@ -3799,34 +3854,34 @@
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>580</v>
+        <v>328</v>
       </c>
       <c r="K25" s="2" t="str" cm="1">
         <f t="array" ref="K25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>368</v>
+        <v>88</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>581</v>
+        <v>363</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>369</v>
+        <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>49</v>
@@ -3835,34 +3890,34 @@
         <v>7</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="K26" s="2" t="str" cm="1">
         <f t="array" ref="K26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>316</v>
+        <v>114</v>
       </c>
       <c r="B27" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>525</v>
+        <v>211</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>49</v>
@@ -3871,34 +3926,34 @@
         <v>7</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>317</v>
+        <v>576</v>
       </c>
       <c r="K27" s="2" t="str" cm="1">
         <f t="array" ref="K27">_xlfn.REGEXEXTRACT(A27,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="B28" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>525</v>
+        <v>366</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>370</v>
+        <v>577</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>49</v>
@@ -3907,16 +3962,16 @@
         <v>7</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>332</v>
+        <v>578</v>
       </c>
       <c r="K28" s="2" t="str" cm="1">
         <f t="array" ref="K28">_xlfn.REGEXEXTRACT(A28,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B29" s="2">
         <v>0</v>
@@ -3925,16 +3980,16 @@
         <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>554</v>
+        <v>364</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>49</v>
@@ -3943,34 +3998,34 @@
         <v>7</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="K29" s="2" t="str" cm="1">
         <f t="array" ref="K29">_xlfn.REGEXEXTRACT(A29,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>787</v>
+        <v>329</v>
       </c>
       <c r="B30" s="2">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>788</v>
+        <v>368</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>789</v>
+        <v>369</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>49</v>
@@ -3979,34 +4034,34 @@
         <v>7</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>790</v>
+        <v>330</v>
       </c>
       <c r="K30" s="2" t="str" cm="1">
         <f t="array" ref="K30">_xlfn.REGEXEXTRACT(A30,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>805</v>
+        <v>320</v>
       </c>
       <c r="B31" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>806</v>
+        <v>522</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>807</v>
+        <v>550</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>808</v>
+        <v>551</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>49</v>
@@ -4015,142 +4070,142 @@
         <v>7</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>809</v>
+        <v>321</v>
       </c>
       <c r="K31" s="2" t="str" cm="1">
         <f t="array" ref="K31">_xlfn.REGEXEXTRACT(A31,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>www.txxx.porn</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B32" s="2">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>597</v>
+        <v>784</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>385</v>
+        <v>785</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I32" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>339</v>
+        <v>786</v>
       </c>
       <c r="K32" s="2" t="str" cm="1">
         <f t="array" ref="K32">_xlfn.REGEXEXTRACT(A32,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>333</v>
+        <v>801</v>
       </c>
       <c r="B33" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>531</v>
+        <v>101</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>164</v>
+        <v>802</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>382</v>
+        <v>803</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>383</v>
+        <v>804</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I33" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>334</v>
+        <v>805</v>
       </c>
       <c r="K33" s="2" t="str" cm="1">
         <f t="array" ref="K33">_xlfn.REGEXEXTRACT(A33,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmmansion.com</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>71</v>
+        <v>820</v>
       </c>
       <c r="B34" s="2">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>526</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>183</v>
+        <v>524</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>583</v>
+        <v>821</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>584</v>
+        <v>822</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I34" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>96</v>
+        <v>823</v>
       </c>
       <c r="K34" s="2" t="str" cm="1">
         <f t="array" ref="K34">_xlfn.REGEXEXTRACT(A34,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>www.amateur8.com</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>782</v>
       </c>
       <c r="B35" s="2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>197</v>
+        <v>523</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>143</v>
+        <v>522</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>49</v>
@@ -4159,34 +4214,34 @@
         <v>6</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>586</v>
+        <v>337</v>
       </c>
       <c r="K35" s="2" t="str" cm="1">
         <f t="array" ref="K35">_xlfn.REGEXEXTRACT(A35,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>331</v>
       </c>
       <c r="B36" s="2">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>587</v>
+        <v>380</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>49</v>
@@ -4195,34 +4250,34 @@
         <v>6</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>93</v>
+        <v>332</v>
       </c>
       <c r="K36" s="2" t="str" cm="1">
         <f t="array" ref="K36">_xlfn.REGEXEXTRACT(A36,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>342</v>
+        <v>71</v>
       </c>
       <c r="B37" s="2">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>526</v>
+        <v>72</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>525</v>
+        <v>182</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>387</v>
+        <v>579</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>49</v>
@@ -4231,34 +4286,34 @@
         <v>6</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>343</v>
+        <v>96</v>
       </c>
       <c r="K37" s="2" t="str" cm="1">
         <f t="array" ref="K37">_xlfn.REGEXEXTRACT(A37,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>509</v>
+        <v>112</v>
       </c>
       <c r="B38" s="2">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>510</v>
+        <v>143</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>511</v>
+        <v>377</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>49</v>
@@ -4267,34 +4322,34 @@
         <v>6</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="K38" s="2" t="str" cm="1">
         <f t="array" ref="K38">_xlfn.REGEXEXTRACT(A38,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>340</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>525</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>624</v>
+        <v>583</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>625</v>
+        <v>374</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>49</v>
@@ -4303,34 +4358,34 @@
         <v>6</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>341</v>
+        <v>93</v>
       </c>
       <c r="K39" s="2" t="str" cm="1">
         <f t="array" ref="K39">_xlfn.REGEXEXTRACT(A39,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>785</v>
+        <v>340</v>
       </c>
       <c r="B40" s="2">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>49</v>
@@ -4339,34 +4394,34 @@
         <v>6</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>589</v>
+        <v>341</v>
       </c>
       <c r="K40" s="2" t="str" cm="1">
         <f t="array" ref="K40">_xlfn.REGEXEXTRACT(A40,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>49</v>
@@ -4375,34 +4430,34 @@
         <v>6</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>501</v>
+        <v>587</v>
       </c>
       <c r="K41" s="2" t="str" cm="1">
         <f t="array" ref="K41">_xlfn.REGEXEXTRACT(A41,"(?&lt;=//)[^/]+")</f>
         <v>www.pornhits.com</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>485</v>
+        <v>338</v>
       </c>
       <c r="B42" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>486</v>
+        <v>621</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>49</v>
@@ -4411,34 +4466,34 @@
         <v>6</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>599</v>
+        <v>339</v>
       </c>
       <c r="K42" s="2" t="str" cm="1">
         <f t="array" ref="K42">_xlfn.REGEXEXTRACT(A42,"(?&lt;=//)[^/]+")</f>
-        <v>abbdsm.com</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>124</v>
+        <v>781</v>
       </c>
       <c r="B43" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>170</v>
+        <v>523</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>152</v>
+        <v>522</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>49</v>
@@ -4447,34 +4502,34 @@
         <v>6</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>171</v>
+        <v>585</v>
       </c>
       <c r="K43" s="2" t="str" cm="1">
         <f t="array" ref="K43">_xlfn.REGEXEXTRACT(A43,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>15</v>
+        <v>497</v>
       </c>
       <c r="B44" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>530</v>
+        <v>67</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>375</v>
+        <v>522</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>799</v>
+        <v>589</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>601</v>
+        <v>495</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>49</v>
@@ -4483,34 +4538,34 @@
         <v>6</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>90</v>
+        <v>498</v>
       </c>
       <c r="K44" s="2" t="str" cm="1">
         <f t="array" ref="K44">_xlfn.REGEXEXTRACT(A44,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B45" s="2">
         <v>10</v>
       </c>
-      <c r="B45" s="2">
-        <v>39</v>
-      </c>
       <c r="C45" s="2" t="s">
-        <v>60</v>
+        <v>526</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>168</v>
+        <v>524</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>381</v>
+        <v>483</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>49</v>
@@ -4519,34 +4574,34 @@
         <v>6</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>169</v>
+        <v>595</v>
       </c>
       <c r="K45" s="2" t="str" cm="1">
         <f t="array" ref="K45">_xlfn.REGEXEXTRACT(A45,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>abbdsm.com</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>523</v>
+        <v>124</v>
       </c>
       <c r="B46" s="2">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>67</v>
+        <v>169</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>524</v>
+        <v>152</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>604</v>
+        <v>378</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>49</v>
@@ -4555,34 +4610,34 @@
         <v>6</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>605</v>
+        <v>170</v>
       </c>
       <c r="K46" s="2" t="str" cm="1">
         <f t="array" ref="K46">_xlfn.REGEXEXTRACT(A46,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="B47" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>208</v>
+        <v>527</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>226</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>606</v>
+        <v>795</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>49</v>
@@ -4591,70 +4646,70 @@
         <v>6</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>227</v>
+        <v>90</v>
       </c>
       <c r="K47" s="2" t="str" cm="1">
         <f t="array" ref="K47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>276</v>
+        <v>10</v>
       </c>
       <c r="B48" s="2">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>529</v>
+        <v>60</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>527</v>
+        <v>167</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>609</v>
+        <v>379</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I48" s="2">
         <v>6</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>610</v>
+        <v>168</v>
       </c>
       <c r="K48" s="2" t="str" cm="1">
         <f t="array" ref="K48">_xlfn.REGEXEXTRACT(A48,"(?&lt;=//)[^/]+")</f>
-        <v>abjav.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="B49" s="2">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>498</v>
+        <v>600</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>49</v>
@@ -4663,34 +4718,34 @@
         <v>6</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>499</v>
+        <v>601</v>
       </c>
       <c r="K49" s="2" t="str" cm="1">
         <f t="array" ref="K49">_xlfn.REGEXEXTRACT(A49,"(?&lt;=//)[^/]+")</f>
         <v>www.pornhits.com</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>344</v>
+        <v>224</v>
       </c>
       <c r="B50" s="2">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>269</v>
+        <v>207</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>525</v>
+        <v>225</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>49</v>
@@ -4699,70 +4754,70 @@
         <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>345</v>
+        <v>226</v>
       </c>
       <c r="K50" s="2" t="str" cm="1">
         <f t="array" ref="K50">_xlfn.REGEXEXTRACT(A50,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
       <c r="B51" s="2">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>58</v>
+        <v>526</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>219</v>
+        <v>524</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>373</v>
+        <v>605</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="I51" s="2">
         <v>6</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="K51" s="2" t="str" cm="1">
         <f t="array" ref="K51">_xlfn.REGEXEXTRACT(A51,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>abjav.com</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>5</v>
+        <v>494</v>
       </c>
       <c r="B52" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>207</v>
+        <v>522</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>377</v>
+        <v>495</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>49</v>
@@ -4771,34 +4826,34 @@
         <v>6</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>619</v>
+        <v>496</v>
       </c>
       <c r="K52" s="2" t="str" cm="1">
         <f t="array" ref="K52">_xlfn.REGEXEXTRACT(A52,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>12</v>
+        <v>342</v>
       </c>
       <c r="B53" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>87</v>
+        <v>268</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>143</v>
+        <v>522</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>378</v>
+        <v>608</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>49</v>
@@ -4807,34 +4862,34 @@
         <v>6</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>222</v>
+        <v>343</v>
       </c>
       <c r="K53" s="2" t="str" cm="1">
         <f t="array" ref="K53">_xlfn.REGEXEXTRACT(A53,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>487</v>
+        <v>9</v>
       </c>
       <c r="B54" s="2">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>530</v>
+        <v>58</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>488</v>
+        <v>218</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>489</v>
+        <v>610</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>490</v>
+        <v>371</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>49</v>
@@ -4843,34 +4898,34 @@
         <v>6</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>491</v>
+        <v>611</v>
       </c>
       <c r="K54" s="2" t="str" cm="1">
         <f t="array" ref="K54">_xlfn.REGEXEXTRACT(A54,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>481</v>
+        <v>5</v>
       </c>
       <c r="B55" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>526</v>
+        <v>144</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>525</v>
+        <v>206</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>617</v>
+        <v>375</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>49</v>
@@ -4879,34 +4934,34 @@
         <v>6</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>482</v>
+        <v>615</v>
       </c>
       <c r="K55" s="2" t="str" cm="1">
         <f t="array" ref="K55">_xlfn.REGEXEXTRACT(A55,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>493</v>
+        <v>12</v>
       </c>
       <c r="B56" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>269</v>
+        <v>87</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>494</v>
+        <v>143</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>495</v>
+        <v>616</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>623</v>
+        <v>376</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>49</v>
@@ -4915,34 +4970,34 @@
         <v>6</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>496</v>
+        <v>221</v>
       </c>
       <c r="K56" s="2" t="str" cm="1">
         <f t="array" ref="K56">_xlfn.REGEXEXTRACT(A56,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>30</v>
+        <v>484</v>
       </c>
       <c r="B57" s="2">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>177</v>
+        <v>527</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>178</v>
+        <v>485</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>626</v>
+        <v>486</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>627</v>
+        <v>487</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>49</v>
@@ -4951,34 +5006,34 @@
         <v>6</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>179</v>
+        <v>488</v>
       </c>
       <c r="K57" s="2" t="str" cm="1">
         <f t="array" ref="K57">_xlfn.REGEXEXTRACT(A57,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>297</v>
+        <v>478</v>
       </c>
       <c r="B58" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>269</v>
+        <v>523</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>186</v>
+        <v>522</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>49</v>
@@ -4987,70 +5042,70 @@
         <v>6</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>630</v>
+        <v>479</v>
       </c>
       <c r="K58" s="2" t="str" cm="1">
         <f t="array" ref="K58">_xlfn.REGEXEXTRACT(A58,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>262</v>
+        <v>490</v>
       </c>
       <c r="B59" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>529</v>
+        <v>268</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>527</v>
+        <v>491</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>631</v>
+        <v>492</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>263</v>
+        <v>49</v>
       </c>
       <c r="I59" s="2">
         <v>6</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>633</v>
+        <v>493</v>
       </c>
       <c r="K59" s="2" t="str" cm="1">
         <f t="array" ref="K59">_xlfn.REGEXEXTRACT(A59,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>245</v>
+        <v>30</v>
       </c>
       <c r="B60" s="2">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>372</v>
+        <v>623</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>49</v>
@@ -5059,34 +5114,34 @@
         <v>6</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>635</v>
+        <v>178</v>
       </c>
       <c r="K60" s="2" t="str" cm="1">
         <f t="array" ref="K60">_xlfn.REGEXEXTRACT(A60,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>59</v>
+        <v>295</v>
       </c>
       <c r="B61" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>374</v>
+        <v>625</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>49</v>
@@ -5095,70 +5150,70 @@
         <v>6</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="K61" s="2" t="str" cm="1">
         <f t="array" ref="K61">_xlfn.REGEXEXTRACT(A61,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>483</v>
+        <v>261</v>
       </c>
       <c r="B62" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>526</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>49</v>
+        <v>262</v>
       </c>
       <c r="I62" s="2">
         <v>6</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>484</v>
+        <v>629</v>
       </c>
       <c r="K62" s="2" t="str" cm="1">
         <f t="array" ref="K62">_xlfn.REGEXEXTRACT(A62,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>punishworld.com</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>337</v>
+        <v>244</v>
       </c>
       <c r="B63" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>525</v>
+        <v>245</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>384</v>
+        <v>630</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>613</v>
+        <v>370</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>49</v>
@@ -5167,34 +5222,34 @@
         <v>6</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>338</v>
+        <v>631</v>
       </c>
       <c r="K63" s="2" t="str" cm="1">
         <f t="array" ref="K63">_xlfn.REGEXEXTRACT(A63,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>335</v>
+        <v>59</v>
       </c>
       <c r="B64" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>269</v>
+        <v>58</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>525</v>
+        <v>183</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>622</v>
+        <v>372</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>49</v>
@@ -5203,34 +5258,34 @@
         <v>6</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>336</v>
+        <v>633</v>
       </c>
       <c r="K64" s="2" t="str" cm="1">
         <f t="array" ref="K64">_xlfn.REGEXEXTRACT(A64,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>abxxx.com</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>791</v>
+        <v>480</v>
       </c>
       <c r="B65" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>792</v>
+        <v>591</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>793</v>
+        <v>592</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>49</v>
@@ -5239,142 +5294,142 @@
         <v>6</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>794</v>
+        <v>481</v>
       </c>
       <c r="K65" s="2" t="str" cm="1">
         <f t="array" ref="K65">_xlfn.REGEXEXTRACT(A65,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B66" s="2">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>526</v>
+        <v>196</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>646</v>
+        <v>382</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>407</v>
+        <v>609</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I66" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="K66" s="2" t="str" cm="1">
         <f t="array" ref="K66">_xlfn.REGEXEXTRACT(A66,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="B67" s="2">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>529</v>
+        <v>268</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>389</v>
+        <v>618</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I67" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>639</v>
+        <v>334</v>
       </c>
       <c r="K67" s="2" t="str" cm="1">
         <f t="array" ref="K67">_xlfn.REGEXEXTRACT(A67,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>253</v>
+        <v>787</v>
       </c>
       <c r="B68" s="2">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>58</v>
+        <v>527</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>391</v>
+        <v>524</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>640</v>
+        <v>788</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>392</v>
+        <v>789</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I68" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>641</v>
+        <v>790</v>
       </c>
       <c r="K68" s="2" t="str" cm="1">
         <f t="array" ref="K68">_xlfn.REGEXEXTRACT(A68,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>236</v>
+        <v>346</v>
       </c>
       <c r="B69" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>208</v>
+        <v>523</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>237</v>
+        <v>522</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>642</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>49</v>
@@ -5383,34 +5438,34 @@
         <v>5</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>643</v>
+        <v>347</v>
       </c>
       <c r="K69" s="2" t="str" cm="1">
         <f t="array" ref="K69">_xlfn.REGEXEXTRACT(A69,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>120</v>
+        <v>271</v>
       </c>
       <c r="B70" s="2">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>133</v>
+        <v>526</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>134</v>
+        <v>524</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>49</v>
@@ -5419,34 +5474,34 @@
         <v>5</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>135</v>
+        <v>635</v>
       </c>
       <c r="K70" s="2" t="str" cm="1">
         <f t="array" ref="K70">_xlfn.REGEXEXTRACT(A70,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="B71" s="2">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>530</v>
+        <v>58</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>527</v>
+        <v>389</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>280</v>
+        <v>54</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>57</v>
+        <v>390</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>49</v>
@@ -5455,34 +5510,34 @@
         <v>5</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>281</v>
+        <v>637</v>
       </c>
       <c r="K71" s="2" t="str" cm="1">
         <f t="array" ref="K71">_xlfn.REGEXEXTRACT(A71,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>40</v>
+        <v>235</v>
       </c>
       <c r="B72" s="2">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>402</v>
+        <v>236</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>800</v>
+        <v>638</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>647</v>
+        <v>393</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>49</v>
@@ -5491,70 +5546,70 @@
         <v>5</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="K72" s="2" t="str" cm="1">
         <f t="array" ref="K72">_xlfn.REGEXEXTRACT(A72,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>277</v>
+        <v>120</v>
       </c>
       <c r="B73" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>529</v>
+        <v>133</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>527</v>
+        <v>134</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>650</v>
+        <v>403</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I73" s="2">
         <v>5</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>278</v>
+        <v>135</v>
       </c>
       <c r="K73" s="2" t="str" cm="1">
         <f t="array" ref="K73">_xlfn.REGEXEXTRACT(A73,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B74" s="2">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>197</v>
+        <v>527</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>294</v>
+        <v>524</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>54</v>
+        <v>279</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>652</v>
+        <v>57</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>49</v>
@@ -5563,34 +5618,34 @@
         <v>5</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>653</v>
+        <v>280</v>
       </c>
       <c r="K74" s="2" t="str" cm="1">
         <f t="array" ref="K74">_xlfn.REGEXEXTRACT(A74,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntrex.com</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B75" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>403</v>
+        <v>796</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>49</v>
@@ -5599,70 +5654,70 @@
         <v>5</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>92</v>
+        <v>644</v>
       </c>
       <c r="K75" s="2" t="str" cm="1">
         <f t="array" ref="K75">_xlfn.REGEXEXTRACT(A75,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>tube.perverzija.com</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>42</v>
+        <v>276</v>
       </c>
       <c r="B76" s="2">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>67</v>
+        <v>526</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>186</v>
+        <v>524</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="I76" s="2">
         <v>5</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>95</v>
+        <v>277</v>
       </c>
       <c r="K76" s="2" t="str" cm="1">
         <f t="array" ref="K76">_xlfn.REGEXEXTRACT(A76,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="B77" s="2">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>393</v>
+        <v>648</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>49</v>
@@ -5671,34 +5726,34 @@
         <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="K77" s="2" t="str" cm="1">
         <f t="array" ref="K77">_xlfn.REGEXEXTRACT(A77,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.porntrex.com</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B78" s="2">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>529</v>
+        <v>60</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>527</v>
+        <v>65</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>659</v>
+        <v>401</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>397</v>
+        <v>650</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>49</v>
@@ -5707,34 +5762,34 @@
         <v>5</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="K78" s="2" t="str" cm="1">
         <f t="array" ref="K78">_xlfn.REGEXEXTRACT(A78,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>238</v>
+        <v>42</v>
       </c>
       <c r="B79" s="2">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>394</v>
+        <v>652</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>49</v>
@@ -5743,34 +5798,34 @@
         <v>5</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>661</v>
+        <v>95</v>
       </c>
       <c r="K79" s="2" t="str" cm="1">
         <f t="array" ref="K79">_xlfn.REGEXEXTRACT(A79,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>305</v>
+        <v>242</v>
       </c>
       <c r="B80" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>49</v>
@@ -5779,34 +5834,34 @@
         <v>5</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="K80" s="2" t="str" cm="1">
         <f t="array" ref="K80">_xlfn.REGEXEXTRACT(A80,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B81" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>208</v>
+        <v>526</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>183</v>
+        <v>524</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>665</v>
+        <v>395</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>49</v>
@@ -5815,34 +5870,34 @@
         <v>5</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="K81" s="2" t="str" cm="1">
         <f t="array" ref="K81">_xlfn.REGEXEXTRACT(A81,"(?&lt;=//)[^/]+")</f>
-        <v>hcbdsm.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>8</v>
+        <v>237</v>
       </c>
       <c r="B82" s="2">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>530</v>
+        <v>61</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>401</v>
+        <v>238</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>801</v>
+        <v>656</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>666</v>
+        <v>392</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>49</v>
@@ -5851,34 +5906,34 @@
         <v>5</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="K82" s="2" t="str" cm="1">
         <f t="array" ref="K82">_xlfn.REGEXEXTRACT(A82,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="B83" s="2">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>530</v>
+        <v>67</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>49</v>
@@ -5887,34 +5942,34 @@
         <v>5</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>256</v>
+        <v>659</v>
       </c>
       <c r="K83" s="2" t="str" cm="1">
         <f t="array" ref="K83">_xlfn.REGEXEXTRACT(A83,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B84" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>398</v>
+        <v>661</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>49</v>
@@ -5923,34 +5978,34 @@
         <v>5</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K84" s="2" t="str" cm="1">
         <f t="array" ref="K84">_xlfn.REGEXEXTRACT(A84,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>hcbdsm.com</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B85" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>58</v>
+        <v>527</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>202</v>
+        <v>399</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>671</v>
+        <v>797</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>399</v>
+        <v>662</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>49</v>
@@ -5959,34 +6014,34 @@
         <v>5</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="K85" s="2" t="str" cm="1">
         <f t="array" ref="K85">_xlfn.REGEXEXTRACT(A85,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="B86" s="2">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>269</v>
+        <v>527</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>409</v>
+        <v>254</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>49</v>
@@ -5995,34 +6050,34 @@
         <v>5</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>674</v>
+        <v>255</v>
       </c>
       <c r="K86" s="2" t="str" cm="1">
         <f t="array" ref="K86">_xlfn.REGEXEXTRACT(A86,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B87" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>404</v>
+        <v>209</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>676</v>
+        <v>396</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>49</v>
@@ -6031,70 +6086,70 @@
         <v>5</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>677</v>
+        <v>210</v>
       </c>
       <c r="K87" s="2" t="str" cm="1">
         <f t="array" ref="K87">_xlfn.REGEXEXTRACT(A87,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="B88" s="2">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>530</v>
+        <v>58</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>527</v>
+        <v>201</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I88" s="2">
         <v>5</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="K88" s="2" t="str" cm="1">
         <f t="array" ref="K88">_xlfn.REGEXEXTRACT(A88,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>521</v>
+        <v>298</v>
       </c>
       <c r="B89" s="2">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>67</v>
+        <v>268</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>522</v>
+        <v>407</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>623</v>
+        <v>408</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>49</v>
@@ -6103,34 +6158,34 @@
         <v>5</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="K89" s="2" t="str" cm="1">
         <f t="array" ref="K89">_xlfn.REGEXEXTRACT(A89,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>270</v>
+        <v>28</v>
       </c>
       <c r="B90" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>529</v>
+        <v>60</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>527</v>
+        <v>402</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>49</v>
@@ -6139,70 +6194,70 @@
         <v>5</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>271</v>
+        <v>673</v>
       </c>
       <c r="K90" s="2" t="str" cm="1">
         <f t="array" ref="K90">_xlfn.REGEXEXTRACT(A90,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>116</v>
+        <v>263</v>
       </c>
       <c r="B91" s="2">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>61</v>
+        <v>527</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>400</v>
+        <v>524</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>685</v>
+        <v>386</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="I91" s="2">
         <v>5</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>176</v>
+        <v>675</v>
       </c>
       <c r="K91" s="2" t="str" cm="1">
         <f t="array" ref="K91">_xlfn.REGEXEXTRACT(A91,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>122</v>
+        <v>518</v>
       </c>
       <c r="B92" s="2">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>161</v>
+        <v>519</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>687</v>
+        <v>619</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>49</v>
@@ -6211,34 +6266,34 @@
         <v>5</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="K92" s="2" t="str" cm="1">
         <f t="array" ref="K92">_xlfn.REGEXEXTRACT(A92,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>512</v>
+        <v>269</v>
       </c>
       <c r="B93" s="2">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>197</v>
+        <v>526</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>49</v>
@@ -6247,34 +6302,34 @@
         <v>5</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>691</v>
+        <v>270</v>
       </c>
       <c r="K93" s="2" t="str" cm="1">
         <f t="array" ref="K93">_xlfn.REGEXEXTRACT(A93,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="B94" s="2">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>76</v>
+        <v>681</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>49</v>
@@ -6283,7 +6338,7 @@
         <v>5</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="K94" s="2" t="str" cm="1">
         <f t="array" ref="K94">_xlfn.REGEXEXTRACT(A94,"(?&lt;=//)[^/]+")</f>
@@ -6292,25 +6347,25 @@
     </row>
     <row r="95" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>298</v>
+        <v>122</v>
       </c>
       <c r="B95" s="2">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>269</v>
+        <v>58</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>299</v>
+        <v>160</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>408</v>
+        <v>683</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>49</v>
@@ -6319,34 +6374,34 @@
         <v>5</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="K95" s="2" t="str" cm="1">
         <f t="array" ref="K95">_xlfn.REGEXEXTRACT(A95,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>130</v>
+        <v>509</v>
       </c>
       <c r="B96" s="2">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>136</v>
+        <v>510</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>98</v>
+        <v>686</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>49</v>
@@ -6355,34 +6410,34 @@
         <v>5</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>220</v>
+        <v>687</v>
       </c>
       <c r="K96" s="2" t="str" cm="1">
         <f t="array" ref="K96">_xlfn.REGEXEXTRACT(A96,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="B97" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>532</v>
+        <v>394</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>406</v>
+        <v>76</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>49</v>
@@ -6391,214 +6446,214 @@
         <v>5</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="K97" s="2" t="str" cm="1">
         <f t="array" ref="K97">_xlfn.REGEXEXTRACT(A97,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>795</v>
+        <v>296</v>
       </c>
       <c r="B98" s="2">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>530</v>
+        <v>268</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>527</v>
+        <v>297</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>796</v>
+        <v>689</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>66</v>
+        <v>406</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>286</v>
+        <v>49</v>
       </c>
       <c r="I98" s="2">
         <v>5</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>797</v>
+        <v>690</v>
       </c>
       <c r="K98" s="2" t="str" cm="1">
         <f t="array" ref="K98">_xlfn.REGEXEXTRACT(A98,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>502</v>
+        <v>130</v>
       </c>
       <c r="B99" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>526</v>
+        <v>176</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>525</v>
+        <v>136</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>327</v>
+        <v>54</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>526</v>
+        <v>691</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>383</v>
+        <v>98</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I99" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>350</v>
+        <v>219</v>
       </c>
       <c r="K99" s="2" t="str" cm="1">
         <f t="array" ref="K99">_xlfn.REGEXEXTRACT(A99,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>503</v>
+        <v>344</v>
       </c>
       <c r="B100" s="2">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>526</v>
+        <v>196</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>327</v>
+        <v>54</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>526</v>
+        <v>666</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I100" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="K100" s="2" t="str" cm="1">
         <f t="array" ref="K100">_xlfn.REGEXEXTRACT(A100,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog.com</v>
+        <v>www.txxx.porn</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>128</v>
+        <v>791</v>
       </c>
       <c r="B101" s="2">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>140</v>
+        <v>527</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>64</v>
+        <v>524</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>696</v>
+        <v>792</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>440</v>
+        <v>66</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>49</v>
+        <v>284</v>
       </c>
       <c r="I101" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>141</v>
+        <v>793</v>
       </c>
       <c r="K101" s="2" t="str" cm="1">
         <f t="array" ref="K101">_xlfn.REGEXEXTRACT(A101,"(?&lt;=//)[^/]+")</f>
-        <v>www.porndead.org</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>33</v>
+        <v>824</v>
       </c>
       <c r="B102" s="2">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>177</v>
+        <v>526</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>75</v>
+        <v>524</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>697</v>
+        <v>825</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I102" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>698</v>
+        <v>826</v>
       </c>
       <c r="K102" s="2" t="str" cm="1">
         <f t="array" ref="K102">_xlfn.REGEXEXTRACT(A102,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.xozilla.xxx</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>34</v>
+        <v>499</v>
       </c>
       <c r="B103" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>60</v>
+        <v>523</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>200</v>
+        <v>522</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>54</v>
+        <v>325</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>699</v>
+        <v>523</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>430</v>
+        <v>381</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>49</v>
@@ -6607,34 +6662,34 @@
         <v>4</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>201</v>
+        <v>348</v>
       </c>
       <c r="K103" s="2" t="str" cm="1">
         <f t="array" ref="K103">_xlfn.REGEXEXTRACT(A103,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>netfapx.net</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="B104" s="2">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>101</v>
+        <v>523</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>55</v>
+        <v>325</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>700</v>
+        <v>523</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>423</v>
+        <v>381</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>49</v>
@@ -6643,34 +6698,34 @@
         <v>4</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>701</v>
+        <v>349</v>
       </c>
       <c r="K104" s="2" t="str" cm="1">
         <f t="array" ref="K104">_xlfn.REGEXEXTRACT(A104,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>pornzog.com</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B105" s="2">
         <v>11</v>
       </c>
-      <c r="B105" s="2">
-        <v>44</v>
-      </c>
       <c r="C105" s="2" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>188</v>
+        <v>64</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>432</v>
+        <v>692</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>702</v>
+        <v>438</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>49</v>
@@ -6679,34 +6734,34 @@
         <v>4</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="K105" s="2" t="str" cm="1">
         <f t="array" ref="K105">_xlfn.REGEXEXTRACT(A105,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.porndead.org</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="B106" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>49</v>
@@ -6715,34 +6770,34 @@
         <v>4</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>165</v>
+        <v>694</v>
       </c>
       <c r="K106" s="2" t="str" cm="1">
         <f t="array" ref="K106">_xlfn.REGEXEXTRACT(A106,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B107" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>527</v>
+        <v>199</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>558</v>
+        <v>428</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>49</v>
@@ -6751,34 +6806,34 @@
         <v>4</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="K107" s="2" t="str" cm="1">
         <f t="array" ref="K107">_xlfn.REGEXEXTRACT(A107,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B108" s="2">
+        <v>59</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F108" s="2" t="s">
-        <v>426</v>
+        <v>696</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>49</v>
@@ -6787,7 +6842,7 @@
         <v>4</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>62</v>
+        <v>697</v>
       </c>
       <c r="K108" s="2" t="str" cm="1">
         <f t="array" ref="K108">_xlfn.REGEXEXTRACT(A108,"(?&lt;=//)[^/]+")</f>
@@ -6796,25 +6851,25 @@
     </row>
     <row r="109" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="B109" s="2">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>705</v>
+        <v>430</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>439</v>
+        <v>698</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>49</v>
@@ -6823,7 +6878,7 @@
         <v>4</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="K109" s="2" t="str" cm="1">
         <f t="array" ref="K109">_xlfn.REGEXEXTRACT(A109,"(?&lt;=//)[^/]+")</f>
@@ -6832,25 +6887,25 @@
     </row>
     <row r="110" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="B110" s="2">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>49</v>
@@ -6859,34 +6914,34 @@
         <v>4</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="K110" s="2" t="str" cm="1">
         <f t="array" ref="K110">_xlfn.REGEXEXTRACT(A110,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B111" s="2">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>75</v>
+        <v>524</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>708</v>
+        <v>555</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>49</v>
@@ -6895,34 +6950,34 @@
         <v>4</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="K111" s="2" t="str" cm="1">
         <f t="array" ref="K111">_xlfn.REGEXEXTRACT(A111,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.party</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>289</v>
+        <v>20</v>
       </c>
       <c r="B112" s="2">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>290</v>
+        <v>184</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>709</v>
+        <v>424</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>710</v>
+        <v>425</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>49</v>
@@ -6931,34 +6986,34 @@
         <v>4</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>291</v>
+        <v>62</v>
       </c>
       <c r="K112" s="2" t="str" cm="1">
         <f t="array" ref="K112">_xlfn.REGEXEXTRACT(A112,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B113" s="2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>530</v>
+        <v>144</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>436</v>
+        <v>701</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>66</v>
+        <v>437</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>49</v>
@@ -6967,34 +7022,34 @@
         <v>4</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="K113" s="2" t="str" cm="1">
         <f t="array" ref="K113">_xlfn.REGEXEXTRACT(A113,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B114" s="2">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>142</v>
+        <v>68</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>173</v>
+        <v>417</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>49</v>
@@ -7003,34 +7058,34 @@
         <v>4</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="K114" s="2" t="str" cm="1">
         <f t="array" ref="K114">_xlfn.REGEXEXTRACT(A114,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="B115" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>434</v>
+        <v>704</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>49</v>
@@ -7039,7 +7094,7 @@
         <v>4</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="K115" s="2" t="str" cm="1">
         <f t="array" ref="K115">_xlfn.REGEXEXTRACT(A115,"(?&lt;=//)[^/]+")</f>
@@ -7048,25 +7103,25 @@
     </row>
     <row r="116" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="B116" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>529</v>
+        <v>105</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>713</v>
+        <v>288</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>433</v>
+        <v>706</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>49</v>
@@ -7075,34 +7130,34 @@
         <v>4</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="K116" s="2" t="str" cm="1">
         <f t="array" ref="K116">_xlfn.REGEXEXTRACT(A116,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>301</v>
+        <v>119</v>
       </c>
       <c r="B117" s="2">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>269</v>
+        <v>527</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>302</v>
+        <v>158</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>715</v>
+        <v>434</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>411</v>
+        <v>66</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>49</v>
@@ -7111,34 +7166,34 @@
         <v>4</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>716</v>
+        <v>159</v>
       </c>
       <c r="K117" s="2" t="str" cm="1">
         <f t="array" ref="K117">_xlfn.REGEXEXTRACT(A117,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>txxx.me</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>235</v>
+        <v>4</v>
       </c>
       <c r="B118" s="2">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>420</v>
+        <v>142</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>421</v>
+        <v>172</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>49</v>
@@ -7147,7 +7202,7 @@
         <v>4</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>718</v>
+        <v>145</v>
       </c>
       <c r="K118" s="2" t="str" cm="1">
         <f t="array" ref="K118">_xlfn.REGEXEXTRACT(A118,"(?&lt;=//)[^/]+")</f>
@@ -7156,25 +7211,25 @@
     </row>
     <row r="119" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="B119" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>515</v>
+        <v>171</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>612</v>
+        <v>432</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>49</v>
@@ -7183,34 +7238,34 @@
         <v>4</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>720</v>
+        <v>173</v>
       </c>
       <c r="K119" s="2" t="str" cm="1">
         <f t="array" ref="K119">_xlfn.REGEXEXTRACT(A119,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>266</v>
+        <v>115</v>
       </c>
       <c r="B120" s="2">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>414</v>
+        <v>709</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>55</v>
+        <v>191</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>415</v>
+        <v>710</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>49</v>
@@ -7219,34 +7274,34 @@
         <v>4</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>721</v>
+        <v>192</v>
       </c>
       <c r="K120" s="2" t="str" cm="1">
         <f t="array" ref="K120">_xlfn.REGEXEXTRACT(A120,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="B121" s="2">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>529</v>
+        <v>268</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>527</v>
+        <v>300</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>412</v>
+        <v>711</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>49</v>
@@ -7255,34 +7310,34 @@
         <v>4</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>268</v>
+        <v>712</v>
       </c>
       <c r="K121" s="2" t="str" cm="1">
         <f t="array" ref="K121">_xlfn.REGEXEXTRACT(A121,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B122" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>259</v>
+        <v>418</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>723</v>
+        <v>419</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>49</v>
@@ -7291,34 +7346,34 @@
         <v>4</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="K122" s="2" t="str" cm="1">
         <f t="array" ref="K122">_xlfn.REGEXEXTRACT(A122,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>22</v>
+        <v>511</v>
       </c>
       <c r="B123" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>195</v>
+        <v>512</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>431</v>
+        <v>608</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>49</v>
@@ -7327,34 +7382,34 @@
         <v>4</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>196</v>
+        <v>716</v>
       </c>
       <c r="K123" s="2" t="str" cm="1">
         <f t="array" ref="K123">_xlfn.REGEXEXTRACT(A123,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>102</v>
+        <v>265</v>
       </c>
       <c r="B124" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>100</v>
+        <v>527</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>726</v>
+        <v>413</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>49</v>
@@ -7363,70 +7418,70 @@
         <v>4</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>103</v>
+        <v>717</v>
       </c>
       <c r="K124" s="2" t="str" cm="1">
         <f t="array" ref="K124">_xlfn.REGEXEXTRACT(A124,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>punishbang.com</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>352</v>
+        <v>266</v>
       </c>
       <c r="B125" s="2">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>526</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>736</v>
+        <v>410</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>737</v>
+        <v>411</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I125" s="2">
         <v>4</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>353</v>
+        <v>267</v>
       </c>
       <c r="K125" s="2" t="str" cm="1">
         <f t="array" ref="K125">_xlfn.REGEXEXTRACT(A125,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>punishbang.com</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="B126" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>58</v>
+        <v>257</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>424</v>
+        <v>258</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>425</v>
+        <v>719</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>49</v>
@@ -7435,34 +7490,34 @@
         <v>4</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="K126" s="2" t="str" cm="1">
         <f t="array" ref="K126">_xlfn.REGEXEXTRACT(A126,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B127" s="2">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>181</v>
+        <v>61</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>49</v>
@@ -7471,34 +7526,34 @@
         <v>4</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="K127" s="2" t="str" cm="1">
         <f t="array" ref="K127">_xlfn.REGEXEXTRACT(A127,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster18.desi</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B128" s="2">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>49</v>
@@ -7507,70 +7562,70 @@
         <v>4</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>731</v>
+        <v>103</v>
       </c>
       <c r="K128" s="2" t="str" cm="1">
         <f t="array" ref="K128">_xlfn.REGEXEXTRACT(A128,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>13</v>
+        <v>350</v>
       </c>
       <c r="B129" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>61</v>
+        <v>523</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>216</v>
+        <v>522</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>429</v>
+        <v>732</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="I129" s="2">
         <v>4</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>217</v>
+        <v>351</v>
       </c>
       <c r="K129" s="2" t="str" cm="1">
         <f t="array" ref="K129">_xlfn.REGEXEXTRACT(A129,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.tubegalore.com</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>303</v>
+        <v>233</v>
       </c>
       <c r="B130" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>269</v>
+        <v>58</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>734</v>
+        <v>423</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>49</v>
@@ -7579,34 +7634,34 @@
         <v>4</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="K130" s="2" t="str" cm="1">
         <f t="array" ref="K130">_xlfn.REGEXEXTRACT(A130,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="B131" s="2">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>530</v>
+        <v>180</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>527</v>
+        <v>136</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>811</v>
+        <v>725</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>812</v>
+        <v>439</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>49</v>
@@ -7615,34 +7670,34 @@
         <v>4</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>813</v>
+        <v>137</v>
       </c>
       <c r="K131" s="2" t="str" cm="1">
         <f t="array" ref="K131">_xlfn.REGEXEXTRACT(A131,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>xhamster18.desi</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>814</v>
+        <v>111</v>
       </c>
       <c r="B132" s="2">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>815</v>
+        <v>435</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>816</v>
+        <v>726</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>817</v>
+        <v>436</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>49</v>
@@ -7651,178 +7706,178 @@
         <v>4</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>818</v>
+        <v>727</v>
       </c>
       <c r="K132" s="2" t="str" cm="1">
         <f t="array" ref="K132">_xlfn.REGEXEXTRACT(A132,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>354</v>
+        <v>13</v>
       </c>
       <c r="B133" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>766</v>
+        <v>427</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>767</v>
+        <v>728</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I133" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>355</v>
+        <v>216</v>
       </c>
       <c r="K133" s="2" t="str" cm="1">
         <f t="array" ref="K133">_xlfn.REGEXEXTRACT(A133,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>356</v>
+        <v>301</v>
       </c>
       <c r="B134" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>526</v>
+        <v>268</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>161</v>
+        <v>440</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>758</v>
+        <v>729</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>464</v>
+        <v>730</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I134" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>465</v>
+        <v>731</v>
       </c>
       <c r="K134" s="2" t="str" cm="1">
         <f t="array" ref="K134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>273</v>
+        <v>806</v>
       </c>
       <c r="B135" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>738</v>
+        <v>807</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>449</v>
+        <v>808</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I135" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>204</v>
+        <v>809</v>
       </c>
       <c r="K135" s="2" t="str" cm="1">
         <f t="array" ref="K135">_xlfn.REGEXEXTRACT(A135,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>110</v>
+        <v>810</v>
       </c>
       <c r="B136" s="2">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>58</v>
+        <v>196</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>183</v>
+        <v>811</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>739</v>
+        <v>812</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>740</v>
+        <v>813</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I136" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>741</v>
+        <v>814</v>
       </c>
       <c r="K136" s="2" t="str" cm="1">
         <f t="array" ref="K136">_xlfn.REGEXEXTRACT(A136,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>6</v>
+        <v>352</v>
       </c>
       <c r="B137" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>144</v>
+        <v>523</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>56</v>
+        <v>763</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>49</v>
@@ -7831,34 +7886,34 @@
         <v>3</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>148</v>
+        <v>353</v>
       </c>
       <c r="K137" s="2" t="str" cm="1">
         <f t="array" ref="K137">_xlfn.REGEXEXTRACT(A137,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>36</v>
+        <v>354</v>
       </c>
       <c r="B138" s="2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>180</v>
+        <v>523</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>445</v>
+        <v>160</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>49</v>
@@ -7867,31 +7922,31 @@
         <v>3</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>94</v>
+        <v>462</v>
       </c>
       <c r="K138" s="2" t="str" cm="1">
         <f t="array" ref="K138">_xlfn.REGEXEXTRACT(A138,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="B139" s="2">
         <v>46</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>133</v>
+        <v>526</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>198</v>
+        <v>446</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>447</v>
@@ -7903,34 +7958,34 @@
         <v>3</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K139" s="2" t="str" cm="1">
         <f t="array" ref="K139">_xlfn.REGEXEXTRACT(A139,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="B140" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>530</v>
+        <v>58</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>455</v>
+        <v>182</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>456</v>
+        <v>736</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>49</v>
@@ -7939,34 +7994,34 @@
         <v>3</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>155</v>
+        <v>737</v>
       </c>
       <c r="K140" s="2" t="str" cm="1">
         <f t="array" ref="K140">_xlfn.REGEXEXTRACT(A140,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>260</v>
+        <v>6</v>
       </c>
       <c r="B141" s="2">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>261</v>
+        <v>147</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>444</v>
+        <v>56</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>49</v>
@@ -7975,34 +8030,34 @@
         <v>3</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>747</v>
+        <v>148</v>
       </c>
       <c r="K141" s="2" t="str" cm="1">
         <f t="array" ref="K141">_xlfn.REGEXEXTRACT(A141,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>282</v>
+        <v>36</v>
       </c>
       <c r="B142" s="2">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>463</v>
+        <v>739</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>66</v>
+        <v>444</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>49</v>
@@ -8011,34 +8066,34 @@
         <v>3</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>284</v>
+        <v>94</v>
       </c>
       <c r="K142" s="2" t="str" cm="1">
         <f t="array" ref="K142">_xlfn.REGEXEXTRACT(A142,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="B143" s="2">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>66</v>
+        <v>445</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>49</v>
@@ -8047,34 +8102,34 @@
         <v>3</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>519</v>
+        <v>198</v>
       </c>
       <c r="K143" s="2" t="str" cm="1">
         <f t="array" ref="K143">_xlfn.REGEXEXTRACT(A143,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B144" s="2">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>64</v>
+        <v>453</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>49</v>
@@ -8083,34 +8138,34 @@
         <v>3</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="K144" s="2" t="str" cm="1">
         <f t="array" ref="K144">_xlfn.REGEXEXTRACT(A144,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>tube.perverzija.com</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="B145" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>49</v>
@@ -8119,34 +8174,34 @@
         <v>3</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="K145" s="2" t="str" cm="1">
         <f t="array" ref="K145">_xlfn.REGEXEXTRACT(A145,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="B146" s="2">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>752</v>
+        <v>827</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>612</v>
+        <v>66</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>49</v>
@@ -8155,34 +8210,34 @@
         <v>3</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>753</v>
+        <v>828</v>
       </c>
       <c r="K146" s="2" t="str" cm="1">
         <f t="array" ref="K146">_xlfn.REGEXEXTRACT(A146,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntopedia.com</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="B147" s="2">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>453</v>
+        <v>160</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>454</v>
+        <v>66</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>49</v>
@@ -8191,34 +8246,34 @@
         <v>3</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>755</v>
+        <v>516</v>
       </c>
       <c r="K147" s="2" t="str" cm="1">
         <f t="array" ref="K147">_xlfn.REGEXEXTRACT(A147,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="B148" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>157</v>
+        <v>64</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>457</v>
+        <v>745</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>49</v>
@@ -8227,106 +8282,106 @@
         <v>3</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="K148" s="2" t="str" cm="1">
         <f t="array" ref="K148">_xlfn.REGEXEXTRACT(A148,"(?&lt;=//)[^/]+")</f>
         <v>www.pornhub.com</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>288</v>
+        <v>73</v>
       </c>
       <c r="B149" s="2">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>529</v>
+        <v>67</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>527</v>
+        <v>74</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>802</v>
+        <v>746</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>756</v>
+        <v>409</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="I149" s="2">
         <v>3</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="K149" s="2" t="str" cm="1">
         <f t="array" ref="K149">_xlfn.REGEXEXTRACT(A149,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="B150" s="2">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>760</v>
+        <v>608</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="I150" s="2">
         <v>3</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>97</v>
+        <v>749</v>
       </c>
       <c r="K150" s="2" t="str" cm="1">
         <f t="array" ref="K150">_xlfn.REGEXEXTRACT(A150,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pervtube.net</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B151" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>64</v>
+        <v>451</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>762</v>
+        <v>452</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>49</v>
@@ -8335,34 +8390,34 @@
         <v>3</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>151</v>
+        <v>751</v>
       </c>
       <c r="K151" s="2" t="str" cm="1">
         <f t="array" ref="K151">_xlfn.REGEXEXTRACT(A151,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="B152" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>520</v>
+        <v>455</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>763</v>
+        <v>456</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>49</v>
@@ -8371,106 +8426,106 @@
         <v>3</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>139</v>
+        <v>829</v>
       </c>
       <c r="K152" s="2" t="str" cm="1">
         <f t="array" ref="K152">_xlfn.REGEXEXTRACT(A152,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>118</v>
+        <v>286</v>
       </c>
       <c r="B153" s="2">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>190</v>
+        <v>526</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>157</v>
+        <v>524</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>764</v>
+        <v>798</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="I153" s="2">
         <v>3</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>191</v>
+        <v>753</v>
       </c>
       <c r="K153" s="2" t="str" cm="1">
         <f t="array" ref="K153">_xlfn.REGEXEXTRACT(A153,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="B154" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>530</v>
+        <v>72</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>451</v>
+        <v>755</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>452</v>
+        <v>756</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="I154" s="2">
         <v>3</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="K154" s="2" t="str" cm="1">
         <f t="array" ref="K154">_xlfn.REGEXEXTRACT(A154,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B155" s="2">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>461</v>
+        <v>757</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>49</v>
@@ -8479,34 +8534,34 @@
         <v>3</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>769</v>
+        <v>151</v>
       </c>
       <c r="K155" s="2" t="str" cm="1">
         <f t="array" ref="K155">_xlfn.REGEXEXTRACT(A155,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>516</v>
+        <v>126</v>
       </c>
       <c r="B156" s="2">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>67</v>
+        <v>527</v>
       </c>
       <c r="D156" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E156" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>770</v>
-      </c>
       <c r="G156" s="2" t="s">
-        <v>518</v>
+        <v>759</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>49</v>
@@ -8515,34 +8570,34 @@
         <v>3</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>771</v>
+        <v>139</v>
       </c>
       <c r="K156" s="2" t="str" cm="1">
         <f t="array" ref="K156">_xlfn.REGEXEXTRACT(A156,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>www.tnaflix.com</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="B157" s="2">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>530</v>
+        <v>189</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>443</v>
+        <v>761</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>49</v>
@@ -8551,70 +8606,70 @@
         <v>3</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>773</v>
+        <v>190</v>
       </c>
       <c r="K157" s="2" t="str" cm="1">
         <f t="array" ref="K157">_xlfn.REGEXEXTRACT(A157,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>285</v>
+        <v>129</v>
       </c>
       <c r="B158" s="2">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>527</v>
+        <v>165</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>774</v>
+        <v>450</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>286</v>
+        <v>49</v>
       </c>
       <c r="I158" s="2">
         <v>3</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>287</v>
+        <v>166</v>
       </c>
       <c r="K158" s="2" t="str" cm="1">
         <f t="array" ref="K158">_xlfn.REGEXEXTRACT(A158,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="B159" s="2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="D159" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="E159" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="G159" s="2" t="s">
-        <v>98</v>
+        <v>764</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>49</v>
@@ -8623,178 +8678,178 @@
         <v>3</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>99</v>
+        <v>765</v>
       </c>
       <c r="K159" s="2" t="str" cm="1">
         <f t="array" ref="K159">_xlfn.REGEXEXTRACT(A159,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>anyporn.com</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>113</v>
+        <v>513</v>
       </c>
       <c r="B160" s="2">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>803</v>
+        <v>766</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>469</v>
+        <v>515</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I160" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>205</v>
+        <v>767</v>
       </c>
       <c r="K160" s="2" t="str" cm="1">
         <f t="array" ref="K160">_xlfn.REGEXEXTRACT(A160,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="B161" s="2">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>58</v>
+        <v>527</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>221</v>
+        <v>441</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I161" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>162</v>
+        <v>769</v>
       </c>
       <c r="K161" s="2" t="str" cm="1">
         <f t="array" ref="K161">_xlfn.REGEXEXTRACT(A161,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="B162" s="2">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>83</v>
+        <v>526</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>472</v>
+        <v>524</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>776</v>
+        <v>460</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>66</v>
+        <v>770</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>49</v>
+        <v>284</v>
       </c>
       <c r="I162" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>149</v>
+        <v>285</v>
       </c>
       <c r="K162" s="2" t="str" cm="1">
         <f t="array" ref="K162">_xlfn.REGEXEXTRACT(A162,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B163" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>106</v>
+        <v>457</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>777</v>
+        <v>458</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I163" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>274</v>
+        <v>99</v>
       </c>
       <c r="K163" s="2" t="str" cm="1">
         <f t="array" ref="K163">_xlfn.REGEXEXTRACT(A163,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="B164" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>75</v>
+        <v>465</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>470</v>
+        <v>799</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>49</v>
@@ -8803,34 +8858,34 @@
         <v>2</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="K164" s="2" t="str" cm="1">
         <f t="array" ref="K164">_xlfn.REGEXEXTRACT(A164,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>232</v>
+        <v>121</v>
       </c>
       <c r="B165" s="2">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>466</v>
+        <v>160</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>467</v>
+        <v>220</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>49</v>
@@ -8839,34 +8894,34 @@
         <v>2</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="K165" s="2" t="str" cm="1">
         <f t="array" ref="K165">_xlfn.REGEXEXTRACT(A165,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>240</v>
+        <v>131</v>
       </c>
       <c r="B166" s="2">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>530</v>
+        <v>83</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>241</v>
+        <v>469</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>804</v>
+        <v>772</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>779</v>
+        <v>66</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>49</v>
@@ -8875,34 +8930,34 @@
         <v>2</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>242</v>
+        <v>149</v>
       </c>
       <c r="K166" s="2" t="str" cm="1">
         <f t="array" ref="K166">_xlfn.REGEXEXTRACT(A166,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B167" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>529</v>
+        <v>105</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>473</v>
+        <v>106</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>474</v>
+        <v>773</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>475</v>
+        <v>66</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>49</v>
@@ -8911,34 +8966,34 @@
         <v>2</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K167" s="2" t="str" cm="1">
         <f t="array" ref="K167">_xlfn.REGEXEXTRACT(A167,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="B168" s="2">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>229</v>
+        <v>60</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>780</v>
+        <v>467</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>781</v>
+        <v>468</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>49</v>
@@ -8947,118 +9002,262 @@
         <v>2</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="K168" s="2" t="str" cm="1">
         <f t="array" ref="K168">_xlfn.REGEXEXTRACT(A168,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>80</v>
+        <v>231</v>
       </c>
       <c r="B169" s="2">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>477</v>
+        <v>774</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I169" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>85</v>
+        <v>232</v>
       </c>
       <c r="K169" s="2" t="str" cm="1">
         <f t="array" ref="K169">_xlfn.REGEXEXTRACT(A169,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.omg.xxx</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>3</v>
+        <v>239</v>
       </c>
       <c r="B170" s="2">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>64</v>
+        <v>240</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>153</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>782</v>
+        <v>800</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I170" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>784</v>
+        <v>241</v>
       </c>
       <c r="K170" s="2" t="str" cm="1">
         <f t="array" ref="K170">_xlfn.REGEXEXTRACT(A170,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>www.peekvids.com</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B171" s="2">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>83</v>
+        <v>526</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>203</v>
+        <v>471</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>49</v>
       </c>
       <c r="I171" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="K171" s="2" t="str" cm="1">
         <f t="array" ref="K171">_xlfn.REGEXEXTRACT(A171,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B172" s="2">
+        <v>57</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I172" s="2">
+        <v>2</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="K172" s="2" t="str" cm="1">
+        <f t="array" ref="K172">_xlfn.REGEXEXTRACT(A172,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B173" s="2">
+        <v>34</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I173" s="2">
+        <v>1</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K173" s="2" t="str" cm="1">
+        <f t="array" ref="K173">_xlfn.REGEXEXTRACT(A173,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B174" s="2">
+        <v>11</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I174" s="2">
+        <v>1</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="K174" s="2" t="str" cm="1">
+        <f t="array" ref="K174">_xlfn.REGEXEXTRACT(A174,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B175" s="2">
+        <v>48</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I175" s="2">
+        <v>1</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K175" s="2" t="str" cm="1">
+        <f t="array" ref="K175">_xlfn.REGEXEXTRACT(A175,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
@@ -9067,13 +9266,8 @@
     <sortCondition descending="1" ref="I20:I165"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:K1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1">
-    <cfRule type="colorScale" priority="35">
+  <conditionalFormatting sqref="I1:I175">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9089,18 +9283,6 @@
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I171">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED9F8AA-D058-4C57-AEFC-3953DC920FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F53F25-A11E-414B-8CEB-B3051F2060D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1B2C5C-AE53-40A7-AB5D-1DA107E5DFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B44FC09-4700-4901-B703-8747F7569C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2475" windowWidth="20730" windowHeight="11760" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NSFW_Links" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="940">
   <si>
     <t>main_link</t>
   </si>
@@ -96,9 +96,6 @@
     <t>website</t>
   </si>
   <si>
-    <t>device bondage</t>
-  </si>
-  <si>
     <t>z-unknown-stars</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>https://heavyfetish.com/videos/86573/tall-blonde-amateur-gets-fucked-while-wearing-blackout-contact-lenses/</t>
   </si>
   <si>
-    <t>public disgrace</t>
-  </si>
-  <si>
     <t>natasha lyn</t>
   </si>
   <si>
@@ -135,9 +129,6 @@
     <t>stand,lay down, legs to side,doggy</t>
   </si>
   <si>
-    <t>kink</t>
-  </si>
-  <si>
     <t>adria rae</t>
   </si>
   <si>
@@ -171,9 +162,6 @@
     <t>https://xhamster44.desi/videos/clean-and-clear-xhUNQAP?pw=</t>
   </si>
   <si>
-    <t>everything butt</t>
-  </si>
-  <si>
     <t>spank,wedgie,enema,oiled,vibrator,strapon</t>
   </si>
   <si>
@@ -186,9 +174,6 @@
     <t>https://abxxx.com/video/376062/sex-amp-submission-audrey-rose/?campaign_id=520379779</t>
   </si>
   <si>
-    <t>sex and submission</t>
-  </si>
-  <si>
     <t>audrey rose</t>
   </si>
   <si>
@@ -297,9 +282,6 @@
     <t>https://bdsmstreak.com/video/47891/piper-perri-and-phoenix-marie-submit</t>
   </si>
   <si>
-    <t>the upper floor</t>
-  </si>
-  <si>
     <t>piper perri,phoenix marie</t>
   </si>
   <si>
@@ -318,9 +300,6 @@
     <t>https://heavyfetish.com/videos/102397/divine-bitches-training-of-a-bitchboy/</t>
   </si>
   <si>
-    <t>divine bitches</t>
-  </si>
-  <si>
     <t>aiden ashley</t>
   </si>
   <si>
@@ -501,9 +480,6 @@
     <t>https://www.porntry.com/videos/22500252/dceae482c25e7ba144d7049394deb6c5/</t>
   </si>
   <si>
-    <t>hogtied</t>
-  </si>
-  <si>
     <t>gia dimarco,ariel x</t>
   </si>
   <si>
@@ -567,9 +543,6 @@
     <t>https://bdsmmansion.com/video/11127/08-04-04-5181-daisy-marie-aiden-starr-daisy-s-promotion/</t>
   </si>
   <si>
-    <t>whipped ass</t>
-  </si>
-  <si>
     <t>aiden star,daisy marie</t>
   </si>
   <si>
@@ -807,9 +780,6 @@
     <t>https://heavyfetish.com/videos/2325/wired-pussy-annabelle-lee/</t>
   </si>
   <si>
-    <t>wired pussy</t>
-  </si>
-  <si>
     <t>annabelle lee</t>
   </si>
   <si>
@@ -849,9 +819,6 @@
     <t>https://www.porntry.com/sites/men-in-pain/most-popular/</t>
   </si>
   <si>
-    <t>men in pain</t>
-  </si>
-  <si>
     <t>spank,peg,nipple clamps,vibrator</t>
   </si>
   <si>
@@ -1323,9 +1290,6 @@
     <t>https://www.porntry.com/videos/22496998/e3ddcb0614bd2e35f425251178c9885f/</t>
   </si>
   <si>
-    <t>aiden starr,madison young</t>
-  </si>
-  <si>
     <t>ball gag,cock ring,body clothespin,flog,peg,2f-1m</t>
   </si>
   <si>
@@ -1458,9 +1422,6 @@
     <t>https://spankbang.com/5p9k8/video/rope+walk</t>
   </si>
   <si>
-    <t>maddy o'reilly</t>
-  </si>
-  <si>
     <t>crotch rope walk,tiger balm,nipple clamps,ball gag,fondle</t>
   </si>
   <si>
@@ -1800,9 +1761,6 @@
     <t>https://m.hqporner.com/hdporn/110221-a_ruthless_work_environment.html</t>
   </si>
   <si>
-    <t>hardcore gangbang</t>
-  </si>
-  <si>
     <t>ava addams</t>
   </si>
   <si>
@@ -2022,9 +1980,6 @@
     <t>bent,lay down</t>
   </si>
   <si>
-    <t>bent over at 25m,chain inside pussy and ass at  41m</t>
-  </si>
-  <si>
     <t>https://heavyfetish.com/videos/3264/sex-and-submission-joslyn-james-ki-chodai/</t>
   </si>
   <si>
@@ -2412,9 +2367,6 @@
     <t>https://heavyfetish.com/videos/24728/thetrainingofo-daisy-ducati-2/</t>
   </si>
   <si>
-    <t>the training of o</t>
-  </si>
-  <si>
     <t>daisy ducati</t>
   </si>
   <si>
@@ -2634,9 +2586,6 @@
     <t>chastity,fingering,balls in pussy,footjob,blowjob,piv</t>
   </si>
   <si>
-    <t>laydown</t>
-  </si>
-  <si>
     <t>melody marks in gentle femdom</t>
   </si>
   <si>
@@ -2679,9 +2628,6 @@
     <t>drug,flog,nipple suction toothpick,vibrator,tit slap,tit pull,cane,suffocation,step on,waterboard</t>
   </si>
   <si>
-    <t>law down</t>
-  </si>
-  <si>
     <t>flog at 8m,nipple suction toothpick at 14m,tit pull at 24m,pussy cane at 26m,suffocation at 34m,step on stomach at 48m,waterboard at 54m</t>
   </si>
   <si>
@@ -2890,6 +2836,51 @@
   </si>
   <si>
     <t>flog at 14m,peg at 23m</t>
+  </si>
+  <si>
+    <t>kink device bondage</t>
+  </si>
+  <si>
+    <t>kink hogtied</t>
+  </si>
+  <si>
+    <t>kink originals</t>
+  </si>
+  <si>
+    <t>kink public disgrace</t>
+  </si>
+  <si>
+    <t>kink everything butt</t>
+  </si>
+  <si>
+    <t>kink sex and submission</t>
+  </si>
+  <si>
+    <t>kink divine bitches</t>
+  </si>
+  <si>
+    <t>kink the training of o</t>
+  </si>
+  <si>
+    <t>kink whipped ass</t>
+  </si>
+  <si>
+    <t>kink men in pain</t>
+  </si>
+  <si>
+    <t>kink wired pussy</t>
+  </si>
+  <si>
+    <t>maddy oreilly</t>
+  </si>
+  <si>
+    <t>aiden star,madison young</t>
+  </si>
+  <si>
+    <t>kink hardcore gangbang</t>
+  </si>
+  <si>
+    <t>bent over at 25m,chain inside pussy and ass at 41m</t>
   </si>
 </sst>
 </file>
@@ -3328,288 +3319,288 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>821</v>
       </c>
       <c r="B2" s="2">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>925</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>822</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2">
         <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>859</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2" t="str" cm="1">
         <f t="array" ref="K2">_xlfn.REGEXEXTRACT(A2,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmlust.com</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="B3" s="2">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>925</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>446</v>
+        <v>844</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2">
         <v>9</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="K3" s="2" t="str" cm="1">
         <f t="array" ref="K3">_xlfn.REGEXEXTRACT(A3,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="B4" s="2">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>925</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>838</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>849</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>850</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2">
         <v>9</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>17</v>
+        <v>851</v>
       </c>
       <c r="K4" s="2" t="str" cm="1">
         <f t="array" ref="K4">_xlfn.REGEXEXTRACT(A4,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmlust.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>823</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>824</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>825</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2">
         <v>9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>826</v>
       </c>
       <c r="K5" s="2" t="str" cm="1">
         <f t="array" ref="K5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
-        <v>www.hqbdsm.com</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmlust.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>839</v>
+        <v>865</v>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>926</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>866</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>841</v>
+        <v>868</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" s="2">
         <v>9</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="K6" s="2" t="str" cm="1">
         <f t="array" ref="K6">_xlfn.REGEXEXTRACT(A6,"(?&lt;=//)[^/]+")</f>
         <v>bdsmlust.com</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>860</v>
+        <v>817</v>
       </c>
       <c r="B7" s="2">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>927</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>861</v>
+        <v>434</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>862</v>
+        <v>818</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>863</v>
+        <v>819</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7" s="2">
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>864</v>
+        <v>820</v>
       </c>
       <c r="K7" s="2" t="str" cm="1">
         <f t="array" ref="K7">_xlfn.REGEXEXTRACT(A7,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>bdsmmansion.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>865</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>927</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>866</v>
+        <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>867</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2">
         <v>9</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>868</v>
+        <v>31</v>
       </c>
       <c r="K8" s="2" t="str" cm="1">
         <f t="array" ref="K8">_xlfn.REGEXEXTRACT(A8,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.hqbdsm.com</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="B9" s="2">
         <v>77</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>927</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>870</v>
+        <v>853</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>871</v>
+        <v>854</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>872</v>
+        <v>463</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I9" s="2">
         <v>9</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>873</v>
+        <v>855</v>
       </c>
       <c r="K9" s="2" t="str" cm="1">
         <f t="array" ref="K9">_xlfn.REGEXEXTRACT(A9,"(?&lt;=//)[^/]+")</f>
@@ -3618,2554 +3609,2554 @@
     </row>
     <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>928</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>45</v>
+        <v>842</v>
       </c>
       <c r="K10" s="2" t="str" cm="1">
         <f t="array" ref="K10">_xlfn.REGEXEXTRACT(A10,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>856</v>
       </c>
       <c r="B11" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>925</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>834</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>857</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>67</v>
+        <v>858</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>68</v>
+        <v>859</v>
       </c>
       <c r="K11" s="2" t="str" cm="1">
         <f t="array" ref="K11">_xlfn.REGEXEXTRACT(A11,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2">
         <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K12" s="2" t="str" cm="1">
         <f t="array" ref="K12">_xlfn.REGEXEXTRACT(A12,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K13" s="2" t="str" cm="1">
         <f t="array" ref="K13">_xlfn.REGEXEXTRACT(A13,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2">
         <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K14" s="2" t="str" cm="1">
         <f t="array" ref="K14">_xlfn.REGEXEXTRACT(A14,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>929</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I15" s="2">
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="K15" s="2" t="str" cm="1">
         <f t="array" ref="K15">_xlfn.REGEXEXTRACT(A15,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>860</v>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>929</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>861</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>862</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>62</v>
+        <v>863</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2">
         <v>8</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>63</v>
+        <v>864</v>
       </c>
       <c r="K16" s="2" t="str" cm="1">
         <f t="array" ref="K16">_xlfn.REGEXEXTRACT(A16,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>874</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>927</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>850</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>875</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>876</v>
+        <v>62</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I17" s="2">
         <v>8</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>877</v>
+        <v>63</v>
       </c>
       <c r="K17" s="2" t="str" cm="1">
         <f t="array" ref="K17">_xlfn.REGEXEXTRACT(A17,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>abxxx.com</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>878</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>927</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>879</v>
+        <v>42</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>880</v>
+        <v>43</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>881</v>
+        <v>44</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I18" s="2">
         <v>8</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>882</v>
+        <v>45</v>
       </c>
       <c r="K18" s="2" t="str" cm="1">
         <f t="array" ref="K18">_xlfn.REGEXEXTRACT(A18,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>883</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>146</v>
+        <v>930</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>884</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>885</v>
+        <v>38</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>886</v>
+        <v>39</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I19" s="2">
         <v>8</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>887</v>
+        <v>40</v>
       </c>
       <c r="K19" s="2" t="str" cm="1">
         <f t="array" ref="K19">_xlfn.REGEXEXTRACT(A19,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmlust.com</v>
+        <v>abxxx.com</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>843</v>
+        <v>94</v>
       </c>
       <c r="B20" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>925</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I20" s="2">
         <v>7</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="K20" s="2" t="str" cm="1">
         <f t="array" ref="K20">_xlfn.REGEXEXTRACT(A20,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="2">
+        <v>53</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="2">
-        <v>111</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>785</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21" s="2">
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K21" s="2" t="str" cm="1">
         <f t="array" ref="K21">_xlfn.REGEXEXTRACT(A21,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B22" s="2">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>117</v>
+        <v>925</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I22" s="2">
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>132</v>
+        <v>870</v>
       </c>
       <c r="K22" s="2" t="str" cm="1">
         <f t="array" ref="K22">_xlfn.REGEXEXTRACT(A22,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>828</v>
       </c>
       <c r="B23" s="2">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>925</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>79</v>
+        <v>829</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>81</v>
+        <v>830</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>831</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2">
         <v>7</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>83</v>
+        <v>832</v>
       </c>
       <c r="K23" s="2" t="str" cm="1">
         <f t="array" ref="K23">_xlfn.REGEXEXTRACT(A23,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B24" s="2">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I24" s="2">
         <v>7</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="K24" s="2" t="str" cm="1">
         <f t="array" ref="K24">_xlfn.REGEXEXTRACT(A24,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="B25" s="2">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I25" s="2">
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="K25" s="2" t="str" cm="1">
         <f t="array" ref="K25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>11</v>
+        <v>931</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>801</v>
+        <v>101</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I26" s="2">
         <v>7</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="K26" s="2" t="str" cm="1">
         <f t="array" ref="K26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>931</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I27" s="2">
         <v>7</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>888</v>
+        <v>82</v>
       </c>
       <c r="K27" s="2" t="str" cm="1">
         <f t="array" ref="K27">_xlfn.REGEXEXTRACT(A27,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="B28" s="2">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>168</v>
+        <v>931</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I28" s="2">
         <v>7</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="K28" s="2" t="str" cm="1">
         <f t="array" ref="K28">_xlfn.REGEXEXTRACT(A28,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.fapcat.com</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="B29" s="2">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>108</v>
+        <v>871</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I29" s="2">
         <v>7</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>109</v>
+        <v>872</v>
       </c>
       <c r="K29" s="2" t="str" cm="1">
         <f t="array" ref="K29">_xlfn.REGEXEXTRACT(A29,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>www.amateur8.com</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>135</v>
+        <v>833</v>
       </c>
       <c r="B30" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>137</v>
+        <v>834</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>138</v>
+        <v>835</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>139</v>
+        <v>836</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I30" s="2">
         <v>7</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>140</v>
+        <v>837</v>
       </c>
       <c r="K30" s="2" t="str" cm="1">
         <f t="array" ref="K30">_xlfn.REGEXEXTRACT(A30,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmmansion.com</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I31" s="2">
         <v>7</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="K31" s="2" t="str" cm="1">
         <f t="array" ref="K31">_xlfn.REGEXEXTRACT(A31,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B32" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>87</v>
+        <v>784</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I32" s="2">
         <v>7</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="K32" s="2" t="str" cm="1">
         <f t="array" ref="K32">_xlfn.REGEXEXTRACT(A32,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="B33" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I33" s="2">
         <v>7</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="K33" s="2" t="str" cm="1">
         <f t="array" ref="K33">_xlfn.REGEXEXTRACT(A33,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>844</v>
+        <v>126</v>
       </c>
       <c r="B34" s="2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>845</v>
+        <v>42</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>846</v>
+        <v>47</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>847</v>
+        <v>66</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I34" s="2">
         <v>7</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>848</v>
+        <v>127</v>
       </c>
       <c r="K34" s="2" t="str" cm="1">
         <f t="array" ref="K34">_xlfn.REGEXEXTRACT(A34,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B35" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>85</v>
+        <v>931</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I35" s="2">
         <v>7</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="K35" s="2" t="str" cm="1">
         <f t="array" ref="K35">_xlfn.REGEXEXTRACT(A35,"(?&lt;=//)[^/]+")</f>
-        <v>www.fapcat.com</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="B36" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>889</v>
+        <v>150</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I36" s="2">
         <v>7</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>890</v>
+        <v>151</v>
       </c>
       <c r="K36" s="2" t="str" cm="1">
         <f t="array" ref="K36">_xlfn.REGEXEXTRACT(A36,"(?&lt;=//)[^/]+")</f>
-        <v>www.amateur8.com</v>
+        <v>www.tubebdsm.com</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>849</v>
+        <v>152</v>
       </c>
       <c r="B37" s="2">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>52</v>
+        <v>931</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>850</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>851</v>
+        <v>153</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>852</v>
+        <v>786</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I37" s="2">
         <v>7</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>853</v>
+        <v>154</v>
       </c>
       <c r="K37" s="2" t="str" cm="1">
         <f t="array" ref="K37">_xlfn.REGEXEXTRACT(A37,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>www.txxx.porn</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="B38" s="2">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I38" s="2">
         <v>7</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="K38" s="2" t="str" cm="1">
         <f t="array" ref="K38">_xlfn.REGEXEXTRACT(A38,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>800</v>
+        <v>91</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" s="2">
         <v>7</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="K39" s="2" t="str" cm="1">
         <f t="array" ref="K39">_xlfn.REGEXEXTRACT(A39,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="B40" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>926</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I40" s="2">
         <v>7</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="K40" s="2" t="str" cm="1">
         <f t="array" ref="K40">_xlfn.REGEXEXTRACT(A40,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" s="2">
         <v>7</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K41" s="2" t="str" cm="1">
         <f t="array" ref="K41">_xlfn.REGEXEXTRACT(A41,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>151</v>
+        <v>827</v>
       </c>
       <c r="B42" s="2">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>85</v>
+        <v>927</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I42" s="2">
         <v>7</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="K42" s="2" t="str" cm="1">
         <f t="array" ref="K42">_xlfn.REGEXEXTRACT(A42,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmmansion.com</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>155</v>
+        <v>873</v>
       </c>
       <c r="B43" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>52</v>
+        <v>927</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>47</v>
+        <v>874</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>157</v>
+        <v>875</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>158</v>
+        <v>876</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43" s="2">
         <v>7</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>159</v>
+        <v>877</v>
       </c>
       <c r="K43" s="2" t="str" cm="1">
         <f t="array" ref="K43">_xlfn.REGEXEXTRACT(A43,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="B44" s="2">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="G44" s="2" t="s">
-        <v>802</v>
+        <v>86</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I44" s="2">
         <v>7</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="K44" s="2" t="str" cm="1">
         <f t="array" ref="K44">_xlfn.REGEXEXTRACT(A44,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="B45" s="2">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>52</v>
+        <v>932</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" s="2">
         <v>7</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="K45" s="2" t="str" cm="1">
         <f t="array" ref="K45">_xlfn.REGEXEXTRACT(A45,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>891</v>
+        <v>159</v>
       </c>
       <c r="B46" s="2">
         <v>51</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>24</v>
+        <v>933</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>892</v>
+        <v>160</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>893</v>
+        <v>161</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>894</v>
+        <v>162</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I46" s="2">
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>895</v>
+        <v>163</v>
       </c>
       <c r="K46" s="2" t="str" cm="1">
         <f t="array" ref="K46">_xlfn.REGEXEXTRACT(A46,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>896</v>
+        <v>878</v>
       </c>
       <c r="B47" s="2">
         <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>168</v>
+        <v>933</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>897</v>
+        <v>879</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>898</v>
+        <v>880</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>899</v>
+        <v>881</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I47" s="2">
         <v>7</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="K47" s="2" t="str" cm="1">
         <f t="array" ref="K47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>901</v>
+        <v>255</v>
       </c>
       <c r="B48" s="2">
+        <v>56</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>903</v>
+        <v>257</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>804</v>
+        <v>258</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I48" s="2">
         <v>6</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>904</v>
+        <v>259</v>
       </c>
       <c r="K48" s="2" t="str" cm="1">
         <f t="array" ref="K48">_xlfn.REGEXEXTRACT(A48,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>905</v>
+        <v>303</v>
       </c>
       <c r="B49" s="2">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>196</v>
+        <v>925</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>902</v>
+        <v>304</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>906</v>
+        <v>305</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>804</v>
+        <v>306</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I49" s="2">
         <v>6</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>907</v>
+        <v>307</v>
       </c>
       <c r="K49" s="2" t="str" cm="1">
         <f t="array" ref="K49">_xlfn.REGEXEXTRACT(A49,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>abxxx.com</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>253</v>
+        <v>891</v>
       </c>
       <c r="B50" s="2">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>925</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>12</v>
+        <v>892</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>254</v>
+        <v>893</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>255</v>
+        <v>894</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="I50" s="2">
         <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>257</v>
+        <v>895</v>
       </c>
       <c r="K50" s="2" t="str" cm="1">
         <f t="array" ref="K50">_xlfn.REGEXEXTRACT(A50,"(?&lt;=//)[^/]+")</f>
-        <v>abjav.com</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="B51" s="2">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>19</v>
+        <v>931</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I51" s="2">
         <v>6</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="K51" s="2" t="str" cm="1">
         <f t="array" ref="K51">_xlfn.REGEXEXTRACT(A51,"(?&lt;=//)[^/]+")</f>
         <v>www.pornhits.com</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="B52" s="2">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>146</v>
+        <v>931</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>310</v>
+        <v>197</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>311</v>
+        <v>198</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>312</v>
+        <v>199</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I52" s="2">
         <v>6</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>313</v>
+        <v>200</v>
       </c>
       <c r="K52" s="2" t="str" cm="1">
         <f t="array" ref="K52">_xlfn.REGEXEXTRACT(A52,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>242</v>
+        <v>883</v>
       </c>
       <c r="B53" s="2">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>243</v>
+        <v>884</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>244</v>
+        <v>885</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>245</v>
+        <v>788</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I53" s="2">
         <v>6</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>246</v>
+        <v>886</v>
       </c>
       <c r="K53" s="2" t="str" cm="1">
         <f t="array" ref="K53">_xlfn.REGEXEXTRACT(A53,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>205</v>
+        <v>887</v>
       </c>
       <c r="B54" s="2">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>206</v>
+        <v>884</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>207</v>
+        <v>888</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>208</v>
+        <v>788</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I54" s="2">
         <v>6</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>209</v>
+        <v>889</v>
       </c>
       <c r="K54" s="2" t="str" cm="1">
         <f t="array" ref="K54">_xlfn.REGEXEXTRACT(A54,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B55" s="2">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>248</v>
+        <v>110</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>249</v>
+        <v>11</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="I55" s="2">
         <v>6</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="K55" s="2" t="str" cm="1">
         <f t="array" ref="K55">_xlfn.REGEXEXTRACT(A55,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>abjav.com</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="B56" s="2">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>11</v>
+        <v>931</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>267</v>
+        <v>42</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I56" s="2">
         <v>6</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="K56" s="2" t="str" cm="1">
         <f t="array" ref="K56">_xlfn.REGEXEXTRACT(A56,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B57" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>196</v>
+        <v>931</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>232</v>
+        <v>42</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I57" s="2">
         <v>6</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="K57" s="2" t="str" cm="1">
         <f t="array" ref="K57">_xlfn.REGEXEXTRACT(A57,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>314</v>
+        <v>222</v>
       </c>
       <c r="B58" s="2">
         <v>53</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>315</v>
+        <v>223</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>316</v>
+        <v>224</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>317</v>
+        <v>225</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I58" s="2">
         <v>6</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>318</v>
+        <v>226</v>
       </c>
       <c r="K58" s="2" t="str" cm="1">
         <f t="array" ref="K58">_xlfn.REGEXEXTRACT(A58,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>299</v>
+        <v>186</v>
       </c>
       <c r="B59" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>300</v>
+        <v>188</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>301</v>
+        <v>189</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>302</v>
+        <v>190</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I59" s="2">
         <v>6</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="K59" s="2" t="str" cm="1">
         <f t="array" ref="K59">_xlfn.REGEXEXTRACT(A59,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="B60" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>289</v>
+        <v>218</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>290</v>
+        <v>219</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>291</v>
+        <v>220</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I60" s="2">
         <v>6</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="K60" s="2" t="str" cm="1">
         <f t="array" ref="K60">_xlfn.REGEXEXTRACT(A60,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="B61" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>196</v>
+        <v>89</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>199</v>
+        <v>263</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I61" s="2">
         <v>6</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="K61" s="2" t="str" cm="1">
         <f t="array" ref="K61">_xlfn.REGEXEXTRACT(A61,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="B62" s="2">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>272</v>
+        <v>11</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I62" s="2">
         <v>6</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>275</v>
+        <v>890</v>
       </c>
       <c r="K62" s="2" t="str" cm="1">
         <f t="array" ref="K62">_xlfn.REGEXEXTRACT(A62,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B63" s="2">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>191</v>
+        <v>270</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>278</v>
+        <v>788</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I63" s="2">
         <v>6</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="K63" s="2" t="str" cm="1">
         <f t="array" ref="K63">_xlfn.REGEXEXTRACT(A63,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>190</v>
+        <v>293</v>
       </c>
       <c r="B64" s="2">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>191</v>
+        <v>11</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>192</v>
+        <v>294</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="I64" s="2">
         <v>6</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>194</v>
+        <v>297</v>
       </c>
       <c r="K64" s="2" t="str" cm="1">
         <f t="array" ref="K64">_xlfn.REGEXEXTRACT(A64,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="B65" s="2">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>294</v>
+        <v>110</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>295</v>
+        <v>11</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>297</v>
+        <v>214</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I65" s="2">
         <v>6</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>298</v>
+        <v>215</v>
       </c>
       <c r="K65" s="2" t="str" cm="1">
         <f t="array" ref="K65">_xlfn.REGEXEXTRACT(A65,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>abbdsm.com</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="B66" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>227</v>
+        <v>42</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>229</v>
+        <v>169</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I66" s="2">
         <v>6</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="K66" s="2" t="str" cm="1">
         <f t="array" ref="K66">_xlfn.REGEXEXTRACT(A66,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>236</v>
+        <v>171</v>
       </c>
       <c r="B67" s="2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>240</v>
+        <v>66</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I67" s="2">
         <v>6</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="K67" s="2" t="str" cm="1">
         <f t="array" ref="K67">_xlfn.REGEXEXTRACT(A67,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>829</v>
+        <v>192</v>
       </c>
       <c r="B68" s="2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>830</v>
+        <v>47</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>831</v>
+        <v>193</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>537</v>
+        <v>194</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I68" s="2">
         <v>6</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>832</v>
+        <v>195</v>
       </c>
       <c r="K68" s="2" t="str" cm="1">
         <f t="array" ref="K68">_xlfn.REGEXEXTRACT(A68,"(?&lt;=//)[^/]+")</f>
-        <v>www.xozilla.xxx</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>330</v>
+        <v>201</v>
       </c>
       <c r="B69" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>332</v>
+        <v>787</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I69" s="2">
         <v>6</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>908</v>
+        <v>203</v>
       </c>
       <c r="K69" s="2" t="str" cm="1">
         <f t="array" ref="K69">_xlfn.REGEXEXTRACT(A69,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="B70" s="2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>281</v>
+        <v>42</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>282</v>
+        <v>205</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>804</v>
+        <v>206</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I70" s="2">
         <v>6</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="K70" s="2" t="str" cm="1">
         <f t="array" ref="K70">_xlfn.REGEXEXTRACT(A70,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="B71" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>307</v>
+        <v>15</v>
       </c>
       <c r="I71" s="2">
         <v>6</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="K71" s="2" t="str" cm="1">
         <f t="array" ref="K71">_xlfn.REGEXEXTRACT(A71,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>221</v>
+        <v>308</v>
       </c>
       <c r="B72" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>222</v>
+        <v>309</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>223</v>
+        <v>310</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I72" s="2">
         <v>6</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>224</v>
+        <v>311</v>
       </c>
       <c r="K72" s="2" t="str" cm="1">
         <f t="array" ref="K72">_xlfn.REGEXEXTRACT(A72,"(?&lt;=//)[^/]+")</f>
-        <v>abbdsm.com</v>
+        <v>www.tubebdsm.com</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="B73" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>47</v>
+        <v>284</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>177</v>
+        <v>285</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" s="2">
         <v>6</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="K73" s="2" t="str" cm="1">
         <f t="array" ref="K73">_xlfn.REGEXEXTRACT(A73,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>180</v>
+        <v>813</v>
       </c>
       <c r="B74" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>181</v>
+        <v>814</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>182</v>
+        <v>11</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>184</v>
+        <v>815</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>71</v>
+        <v>524</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I74" s="2">
         <v>6</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>185</v>
+        <v>816</v>
       </c>
       <c r="K74" s="2" t="str" cm="1">
         <f t="array" ref="K74">_xlfn.REGEXEXTRACT(A74,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.xozilla.xxx</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="B75" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>52</v>
+        <v>926</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>202</v>
+        <v>300</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>203</v>
+        <v>301</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" s="2">
         <v>6</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="K75" s="2" t="str" cm="1">
         <f t="array" ref="K75">_xlfn.REGEXEXTRACT(A75,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="B76" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>803</v>
+        <v>267</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I76" s="2">
         <v>6</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="K76" s="2" t="str" cm="1">
         <f t="array" ref="K76">_xlfn.REGEXEXTRACT(A76,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B77" s="2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>52</v>
+        <v>228</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I77" s="2">
         <v>6</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="K77" s="2" t="str" cm="1">
         <f t="array" ref="K77">_xlfn.REGEXEXTRACT(A77,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="B78" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>85</v>
+        <v>927</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I78" s="2">
         <v>6</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="K78" s="2" t="str" cm="1">
         <f t="array" ref="K78">_xlfn.REGEXEXTRACT(A78,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="B79" s="2">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>85</v>
+        <v>927</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>259</v>
+        <v>313</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>219</v>
+        <v>789</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I79" s="2">
         <v>6</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>260</v>
+        <v>314</v>
       </c>
       <c r="K79" s="2" t="str" cm="1">
         <f t="array" ref="K79">_xlfn.REGEXEXTRACT(A79,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="B80" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>262</v>
+        <v>934</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I80" s="2">
         <v>6</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="K80" s="2" t="str" cm="1">
         <f t="array" ref="K80">_xlfn.REGEXEXTRACT(A80,"(?&lt;=//)[^/]+")</f>
@@ -6174,322 +6165,322 @@
     </row>
     <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B81" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>52</v>
+        <v>934</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>47</v>
+        <v>278</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I81" s="2">
         <v>6</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K81" s="2" t="str" cm="1">
         <f t="array" ref="K81">_xlfn.REGEXEXTRACT(A81,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>tube.perverzija.com</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>319</v>
+        <v>251</v>
       </c>
       <c r="B82" s="2">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>52</v>
+        <v>934</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>321</v>
+        <v>253</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I82" s="2">
         <v>6</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>322</v>
+        <v>254</v>
       </c>
       <c r="K82" s="2" t="str" cm="1">
         <f t="array" ref="K82">_xlfn.REGEXEXTRACT(A82,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B83" s="2">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>24</v>
+        <v>934</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>805</v>
+        <v>317</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I83" s="2">
         <v>6</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="K83" s="2" t="str" cm="1">
         <f t="array" ref="K83">_xlfn.REGEXEXTRACT(A83,"(?&lt;=//)[^/]+")</f>
         <v>www.txxx.porn</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>326</v>
+        <v>177</v>
       </c>
       <c r="B84" s="2">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>262</v>
+        <v>928</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>327</v>
+        <v>178</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>328</v>
+        <v>179</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I84" s="2">
         <v>6</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>329</v>
+        <v>180</v>
       </c>
       <c r="K84" s="2" t="str" cm="1">
         <f t="array" ref="K84">_xlfn.REGEXEXTRACT(A84,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>909</v>
+        <v>238</v>
       </c>
       <c r="B85" s="2">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>11</v>
+        <v>935</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>910</v>
+        <v>239</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>911</v>
+        <v>240</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>912</v>
+        <v>241</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I85" s="2">
         <v>6</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>913</v>
+        <v>242</v>
       </c>
       <c r="K85" s="2" t="str" cm="1">
         <f t="array" ref="K85">_xlfn.REGEXEXTRACT(A85,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>428</v>
+        <v>329</v>
       </c>
       <c r="B86" s="2">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>196</v>
+        <v>925</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>12</v>
+        <v>330</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>429</v>
+        <v>896</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>430</v>
+        <v>331</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="I86" s="2">
         <v>5</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>431</v>
+        <v>332</v>
       </c>
       <c r="K86" s="2" t="str" cm="1">
         <f t="array" ref="K86">_xlfn.REGEXEXTRACT(A86,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>336</v>
+        <v>443</v>
       </c>
       <c r="B87" s="2">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>117</v>
+        <v>925</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>12</v>
+        <v>444</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>337</v>
+        <v>19</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>807</v>
+        <v>445</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>338</v>
+        <v>446</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I87" s="2">
         <v>5</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>339</v>
+        <v>447</v>
       </c>
       <c r="K87" s="2" t="str" cm="1">
         <f t="array" ref="K87">_xlfn.REGEXEXTRACT(A87,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="B88" s="2">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>196</v>
+        <v>925</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>811</v>
+        <v>436</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I88" s="2">
         <v>5</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="K88" s="2" t="str" cm="1">
         <f t="array" ref="K88">_xlfn.REGEXEXTRACT(A88,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>340</v>
+        <v>405</v>
       </c>
       <c r="B89" s="2">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>11</v>
+        <v>925</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>341</v>
+        <v>406</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>914</v>
+        <v>407</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>342</v>
+        <v>796</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I89" s="2">
         <v>5</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>343</v>
+        <v>897</v>
       </c>
       <c r="K89" s="2" t="str" cm="1">
         <f t="array" ref="K89">_xlfn.REGEXEXTRACT(A89,"(?&lt;=//)[^/]+")</f>
@@ -6498,1402 +6489,1402 @@
     </row>
     <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="B90" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>146</v>
+        <v>931</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>382</v>
+        <v>422</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>383</v>
+        <v>280</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I90" s="2">
         <v>5</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="K90" s="2" t="str" cm="1">
         <f t="array" ref="K90">_xlfn.REGEXEXTRACT(A90,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>432</v>
+        <v>365</v>
       </c>
       <c r="B91" s="2">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>85</v>
+        <v>931</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>433</v>
+        <v>289</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>291</v>
+        <v>367</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I91" s="2">
         <v>5</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>435</v>
+        <v>368</v>
       </c>
       <c r="K91" s="2" t="str" cm="1">
         <f t="array" ref="K91">_xlfn.REGEXEXTRACT(A91,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B92" s="2">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>146</v>
+        <v>931</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I92" s="2">
         <v>5</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="K92" s="2" t="str" cm="1">
         <f t="array" ref="K92">_xlfn.REGEXEXTRACT(A92,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>344</v>
+        <v>416</v>
       </c>
       <c r="B93" s="2">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>345</v>
+        <v>11</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>346</v>
+        <v>417</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>347</v>
+        <v>418</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="I93" s="2">
         <v>5</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>348</v>
+        <v>419</v>
       </c>
       <c r="K93" s="2" t="str" cm="1">
         <f t="array" ref="K93">_xlfn.REGEXEXTRACT(A93,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>455</v>
+        <v>325</v>
       </c>
       <c r="B94" s="2">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="C94" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="E94" s="2" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>457</v>
+        <v>791</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>458</v>
+        <v>327</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I94" s="2">
         <v>5</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>459</v>
+        <v>328</v>
       </c>
       <c r="K94" s="2" t="str" cm="1">
         <f t="array" ref="K94">_xlfn.REGEXEXTRACT(A94,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B95" s="2">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>378</v>
+        <v>795</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I95" s="2">
         <v>5</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="K95" s="2" t="str" cm="1">
         <f t="array" ref="K95">_xlfn.REGEXEXTRACT(A95,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>385</v>
+        <v>452</v>
       </c>
       <c r="B96" s="2">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>117</v>
+        <v>283</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>12</v>
+        <v>936</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>386</v>
+        <v>453</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>387</v>
+        <v>454</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I96" s="2">
         <v>5</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>388</v>
+        <v>455</v>
       </c>
       <c r="K96" s="2" t="str" cm="1">
         <f t="array" ref="K96">_xlfn.REGEXEXTRACT(A96,"(?&lt;=//)[^/]+")</f>
         <v>spankbang.com</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>445</v>
+        <v>374</v>
       </c>
       <c r="B97" s="2">
         <v>55</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="E97" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>447</v>
+        <v>375</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>448</v>
+        <v>376</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I97" s="2">
         <v>5</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>449</v>
+        <v>377</v>
       </c>
       <c r="K97" s="2" t="str" cm="1">
         <f t="array" ref="K97">_xlfn.REGEXEXTRACT(A97,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="B98" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>85</v>
+        <v>926</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I98" s="2">
         <v>5</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="K98" s="2" t="str" cm="1">
         <f t="array" ref="K98">_xlfn.REGEXEXTRACT(A98,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>450</v>
+        <v>378</v>
       </c>
       <c r="B99" s="2">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>24</v>
+        <v>926</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>452</v>
+        <v>380</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I99" s="2">
         <v>5</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>454</v>
+        <v>382</v>
       </c>
       <c r="K99" s="2" t="str" cm="1">
         <f t="array" ref="K99">_xlfn.REGEXEXTRACT(A99,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="B100" s="2">
         <v>51</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>146</v>
+        <v>926</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I100" s="2">
         <v>5</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="K100" s="2" t="str" cm="1">
         <f t="array" ref="K100">_xlfn.REGEXEXTRACT(A100,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="B101" s="2">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>248</v>
+        <v>926</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>122</v>
+        <v>429</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I101" s="2">
         <v>5</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="K101" s="2" t="str" cm="1">
         <f t="array" ref="K101">_xlfn.REGEXEXTRACT(A101,"(?&lt;=//)[^/]+")</f>
-        <v>hcbdsm.com</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>460</v>
+        <v>392</v>
       </c>
       <c r="B102" s="2">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>461</v>
+        <v>393</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>26</v>
+        <v>326</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>462</v>
+        <v>794</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>814</v>
+        <v>394</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I102" s="2">
         <v>5</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>463</v>
+        <v>395</v>
       </c>
       <c r="K102" s="2" t="str" cm="1">
         <f t="array" ref="K102">_xlfn.REGEXEXTRACT(A102,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="B103" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>24</v>
+        <v>348</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>368</v>
+        <v>792</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I103" s="2">
         <v>5</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>370</v>
+        <v>793</v>
       </c>
       <c r="K103" s="2" t="str" cm="1">
         <f t="array" ref="K103">_xlfn.REGEXEXTRACT(A103,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntrex.com</v>
+        <v>tube.perverzija.com</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="B104" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="E104" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>812</v>
+        <v>463</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>16</v>
+        <v>464</v>
       </c>
       <c r="I104" s="2">
         <v>5</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>915</v>
+        <v>465</v>
       </c>
       <c r="K104" s="2" t="str" cm="1">
         <f t="array" ref="K104">_xlfn.REGEXEXTRACT(A104,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="B105" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>420</v>
+        <v>11</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>813</v>
+        <v>386</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I105" s="2">
         <v>5</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="K105" s="2" t="str" cm="1">
         <f t="array" ref="K105">_xlfn.REGEXEXTRACT(A105,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>www.xozilla.xxx</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>440</v>
+        <v>838</v>
       </c>
       <c r="B106" s="2">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>441</v>
+        <v>90</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>21</v>
+        <v>839</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>442</v>
+        <v>840</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I106" s="2">
         <v>5</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>444</v>
+        <v>841</v>
       </c>
       <c r="K106" s="2" t="str" cm="1">
         <f t="array" ref="K106">_xlfn.REGEXEXTRACT(A106,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="B107" s="2">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>404</v>
+        <v>11</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>337</v>
+        <v>23</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>810</v>
+        <v>425</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I107" s="2">
         <v>5</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="K107" s="2" t="str" cm="1">
         <f t="array" ref="K107">_xlfn.REGEXEXTRACT(A107,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="B108" s="2">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>359</v>
+        <v>187</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>360</v>
+        <v>11</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>13</v>
+        <v>343</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>808</v>
+        <v>344</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I108" s="2">
         <v>5</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>809</v>
+        <v>346</v>
       </c>
       <c r="K108" s="2" t="str" cm="1">
         <f t="array" ref="K108">_xlfn.REGEXEXTRACT(A108,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B109" s="2">
         <v>33</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I109" s="2">
         <v>5</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="K109" s="2" t="str" cm="1">
         <f t="array" ref="K109">_xlfn.REGEXEXTRACT(A109,"(?&lt;=//)[^/]+")</f>
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>423</v>
+        <v>351</v>
       </c>
       <c r="B110" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>237</v>
+        <v>110</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>424</v>
+        <v>11</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>425</v>
+        <v>352</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>426</v>
+        <v>353</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="I110" s="2">
         <v>5</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>427</v>
+        <v>354</v>
       </c>
       <c r="K110" s="2" t="str" cm="1">
         <f t="array" ref="K110">_xlfn.REGEXEXTRACT(A110,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>xhamster44.desi</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>474</v>
+        <v>322</v>
       </c>
       <c r="B111" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>475</v>
+        <v>323</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>476</v>
+        <v>790</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>477</v>
+        <v>15</v>
       </c>
       <c r="I111" s="2">
         <v>5</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>478</v>
+        <v>324</v>
       </c>
       <c r="K111" s="2" t="str" cm="1">
         <f t="array" ref="K111">_xlfn.REGEXEXTRACT(A111,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>479</v>
+        <v>411</v>
       </c>
       <c r="B112" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>12</v>
+        <v>412</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>480</v>
+        <v>413</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I112" s="2">
         <v>5</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="K112" s="2" t="str" cm="1">
         <f t="array" ref="K112">_xlfn.REGEXEXTRACT(A112,"(?&lt;=//)[^/]+")</f>
-        <v>www.xozilla.xxx</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>854</v>
+        <v>438</v>
       </c>
       <c r="B113" s="2">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>196</v>
+        <v>927</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>97</v>
+        <v>439</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>855</v>
+        <v>19</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>856</v>
+        <v>440</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>857</v>
+        <v>441</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I113" s="2">
         <v>5</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>858</v>
+        <v>442</v>
       </c>
       <c r="K113" s="2" t="str" cm="1">
         <f t="array" ref="K113">_xlfn.REGEXEXTRACT(A113,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>436</v>
+        <v>355</v>
       </c>
       <c r="B114" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>117</v>
+        <v>927</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>12</v>
+        <v>356</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>437</v>
+        <v>357</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>438</v>
+        <v>358</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I114" s="2">
         <v>5</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>439</v>
+        <v>359</v>
       </c>
       <c r="K114" s="2" t="str" cm="1">
         <f t="array" ref="K114">_xlfn.REGEXEXTRACT(A114,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntrex.com</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>353</v>
+        <v>456</v>
       </c>
       <c r="B115" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>196</v>
+        <v>927</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>12</v>
+        <v>457</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>355</v>
+        <v>458</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>356</v>
+        <v>459</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I115" s="2">
         <v>5</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>357</v>
+        <v>460</v>
       </c>
       <c r="K115" s="2" t="str" cm="1">
         <f t="array" ref="K115">_xlfn.REGEXEXTRACT(A115,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>464</v>
+        <v>899</v>
       </c>
       <c r="B116" s="2">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>294</v>
+        <v>927</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>465</v>
+        <v>900</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>466</v>
+        <v>901</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>467</v>
+        <v>902</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I116" s="2">
         <v>5</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>468</v>
+        <v>903</v>
       </c>
       <c r="K116" s="2" t="str" cm="1">
         <f t="array" ref="K116">_xlfn.REGEXEXTRACT(A116,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>349</v>
+        <v>448</v>
       </c>
       <c r="B117" s="2">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>41</v>
+        <v>934</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>350</v>
+        <v>449</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>351</v>
+        <v>450</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>352</v>
+        <v>798</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I117" s="2">
         <v>5</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>916</v>
+        <v>451</v>
       </c>
       <c r="K117" s="2" t="str" cm="1">
         <f t="array" ref="K117">_xlfn.REGEXEXTRACT(A117,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="B118" s="2">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>117</v>
+        <v>934</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>12</v>
+        <v>937</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>363</v>
+        <v>409</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>364</v>
+        <v>797</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="I118" s="2">
         <v>5</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="K118" s="2" t="str" cm="1">
         <f t="array" ref="K118">_xlfn.REGEXEXTRACT(A118,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B119" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>52</v>
+        <v>930</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>47</v>
+        <v>339</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>806</v>
+        <v>341</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I119" s="2">
         <v>5</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>335</v>
+        <v>898</v>
       </c>
       <c r="K119" s="2" t="str" cm="1">
         <f t="array" ref="K119">_xlfn.REGEXEXTRACT(A119,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>469</v>
+        <v>333</v>
       </c>
       <c r="B120" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>24</v>
+        <v>935</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>470</v>
+        <v>334</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>471</v>
+        <v>335</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>472</v>
+        <v>336</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I120" s="2">
         <v>5</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>473</v>
+        <v>337</v>
       </c>
       <c r="K120" s="2" t="str" cm="1">
         <f t="array" ref="K120">_xlfn.REGEXEXTRACT(A120,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>917</v>
+        <v>388</v>
       </c>
       <c r="B121" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>24</v>
+        <v>935</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>918</v>
+        <v>115</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>919</v>
+        <v>389</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>920</v>
+        <v>390</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I121" s="2">
         <v>5</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>921</v>
+        <v>391</v>
       </c>
       <c r="K121" s="2" t="str" cm="1">
         <f t="array" ref="K121">_xlfn.REGEXEXTRACT(A121,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>hcbdsm.com</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B122" s="2">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>117</v>
+        <v>925</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F122" s="2" t="s">
-        <v>576</v>
+        <v>803</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>817</v>
+        <v>585</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I122" s="2">
         <v>4</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="K122" s="2" t="str" cm="1">
         <f t="array" ref="K122">_xlfn.REGEXEXTRACT(A122,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>570</v>
+        <v>535</v>
       </c>
       <c r="B123" s="2">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>196</v>
+        <v>925</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>571</v>
+        <v>536</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>572</v>
+        <v>537</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>573</v>
+        <v>800</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I123" s="2">
         <v>4</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>574</v>
+        <v>538</v>
       </c>
       <c r="K123" s="2" t="str" cm="1">
         <f t="array" ref="K123">_xlfn.REGEXEXTRACT(A123,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B124" s="2">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>36</v>
+        <v>925</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>818</v>
+        <v>594</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I124" s="2">
         <v>4</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="K124" s="2" t="str" cm="1">
         <f t="array" ref="K124">_xlfn.REGEXEXTRACT(A124,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>525</v>
+        <v>805</v>
       </c>
       <c r="B125" s="2">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>85</v>
+        <v>925</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>526</v>
+        <v>11</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>527</v>
+        <v>806</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I125" s="2">
         <v>4</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>528</v>
+        <v>808</v>
       </c>
       <c r="K125" s="2" t="str" cm="1">
         <f t="array" ref="K125">_xlfn.REGEXEXTRACT(A125,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>578</v>
+        <v>913</v>
       </c>
       <c r="B126" s="2">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>579</v>
+        <v>925</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>580</v>
+        <v>914</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>581</v>
+        <v>915</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>582</v>
+        <v>788</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I126" s="2">
         <v>4</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>583</v>
+        <v>916</v>
       </c>
       <c r="K126" s="2" t="str" cm="1">
         <f t="array" ref="K126">_xlfn.REGEXEXTRACT(A126,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>561</v>
+        <v>917</v>
       </c>
       <c r="B127" s="2">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>41</v>
+        <v>925</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>562</v>
+        <v>918</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>563</v>
+        <v>919</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>564</v>
+        <v>920</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I127" s="2">
         <v>4</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>565</v>
+        <v>921</v>
       </c>
       <c r="K127" s="2" t="str" cm="1">
         <f t="array" ref="K127">_xlfn.REGEXEXTRACT(A127,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="B128" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>168</v>
+        <v>931</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>502</v>
+        <v>799</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I128" s="2">
         <v>4</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="K128" s="2" t="str" cm="1">
         <f t="array" ref="K128">_xlfn.REGEXEXTRACT(A128,"(?&lt;=//)[^/]+")</f>
@@ -7902,106 +7893,106 @@
     </row>
     <row r="129" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>597</v>
+        <v>553</v>
       </c>
       <c r="B129" s="2">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>11</v>
+        <v>931</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>598</v>
+        <v>554</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>819</v>
+        <v>555</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>599</v>
+        <v>253</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I129" s="2">
         <v>4</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>600</v>
+        <v>556</v>
       </c>
       <c r="K129" s="2" t="str" cm="1">
         <f t="array" ref="K129">_xlfn.REGEXEXTRACT(A129,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="B130" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>237</v>
+        <v>89</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>517</v>
+        <v>11</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>519</v>
+        <v>92</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I130" s="2">
         <v>4</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="K130" s="2" t="str" cm="1">
         <f t="array" ref="K130">_xlfn.REGEXEXTRACT(A130,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>spankbang.party</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="B131" s="2">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>294</v>
+        <v>89</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>492</v>
+        <v>182</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>922</v>
+        <v>509</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I131" s="2">
         <v>4</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>923</v>
+        <v>511</v>
       </c>
       <c r="K131" s="2" t="str" cm="1">
         <f t="array" ref="K131">_xlfn.REGEXEXTRACT(A131,"(?&lt;=//)[^/]+")</f>
@@ -8010,214 +8001,214 @@
     </row>
     <row r="132" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>610</v>
+        <v>530</v>
       </c>
       <c r="B132" s="2">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>611</v>
+        <v>531</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>612</v>
+        <v>532</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>613</v>
+        <v>533</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I132" s="2">
         <v>4</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>614</v>
+        <v>534</v>
       </c>
       <c r="K132" s="2" t="str" cm="1">
         <f t="array" ref="K132">_xlfn.REGEXEXTRACT(A132,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>622</v>
+        <v>575</v>
       </c>
       <c r="B133" s="2">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>24</v>
+        <v>929</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>623</v>
+        <v>576</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>624</v>
+        <v>577</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>625</v>
+        <v>802</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I133" s="2">
         <v>4</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>626</v>
+        <v>578</v>
       </c>
       <c r="K133" s="2" t="str" cm="1">
         <f t="array" ref="K133">_xlfn.REGEXEXTRACT(A133,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="B134" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>96</v>
+        <v>283</v>
       </c>
       <c r="D134" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F134" s="2" t="s">
-        <v>514</v>
+        <v>904</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>99</v>
+        <v>480</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I134" s="2">
         <v>4</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>515</v>
+        <v>905</v>
       </c>
       <c r="K134" s="2" t="str" cm="1">
         <f t="array" ref="K134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>566</v>
+        <v>516</v>
       </c>
       <c r="B135" s="2">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>567</v>
+        <v>479</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>264</v>
+        <v>518</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I135" s="2">
         <v>4</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>569</v>
+        <v>519</v>
       </c>
       <c r="K135" s="2" t="str" cm="1">
         <f t="array" ref="K135">_xlfn.REGEXEXTRACT(A135,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>494</v>
+        <v>565</v>
       </c>
       <c r="B136" s="2">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>237</v>
+        <v>938</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>495</v>
+        <v>566</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>496</v>
+        <v>567</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>497</v>
+        <v>568</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I136" s="2">
         <v>4</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>498</v>
+        <v>569</v>
       </c>
       <c r="K136" s="2" t="str" cm="1">
         <f t="array" ref="K136">_xlfn.REGEXEXTRACT(A136,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="B137" s="2">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>146</v>
+        <v>926</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I137" s="2">
         <v>4</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="K137" s="2" t="str" cm="1">
         <f t="array" ref="K137">_xlfn.REGEXEXTRACT(A137,"(?&lt;=//)[^/]+")</f>
@@ -8226,466 +8217,466 @@
     </row>
     <row r="138" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="B138" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>237</v>
+        <v>926</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>505</v>
+        <v>571</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>506</v>
+        <v>572</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>507</v>
+        <v>573</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I138" s="2">
         <v>4</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>508</v>
+        <v>574</v>
       </c>
       <c r="K138" s="2" t="str" cm="1">
         <f t="array" ref="K138">_xlfn.REGEXEXTRACT(A138,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>552</v>
+        <v>503</v>
       </c>
       <c r="B139" s="2">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>553</v>
+        <v>504</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>554</v>
+        <v>505</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I139" s="2">
         <v>4</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>556</v>
+        <v>507</v>
       </c>
       <c r="K139" s="2" t="str" cm="1">
         <f t="array" ref="K139">_xlfn.REGEXEXTRACT(A139,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B140" s="2">
-        <v>44</v>
+        <v>182</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>558</v>
+        <v>11</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>397</v>
+        <v>801</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I140" s="2">
         <v>4</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="K140" s="2" t="str" cm="1">
         <f t="array" ref="K140">_xlfn.REGEXEXTRACT(A140,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>punishbang.com</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="B141" s="2">
-        <v>42</v>
+        <v>170</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>816</v>
+        <v>560</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I141" s="2">
         <v>4</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="K141" s="2" t="str" cm="1">
         <f t="array" ref="K141">_xlfn.REGEXEXTRACT(A141,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>punishbang.com</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>615</v>
+        <v>481</v>
       </c>
       <c r="B142" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>616</v>
+        <v>482</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>617</v>
+        <v>483</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>618</v>
+        <v>484</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I142" s="2">
         <v>4</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>619</v>
+        <v>485</v>
       </c>
       <c r="K142" s="2" t="str" cm="1">
         <f t="array" ref="K142">_xlfn.REGEXEXTRACT(A142,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="B143" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>510</v>
+        <v>228</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>182</v>
+        <v>492</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>924</v>
+        <v>493</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I143" s="2">
         <v>4</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="K143" s="2" t="str" cm="1">
         <f t="array" ref="K143">_xlfn.REGEXEXTRACT(A143,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="B144" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>294</v>
+        <v>110</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>492</v>
+        <v>540</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I144" s="2">
         <v>4</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="K144" s="2" t="str" cm="1">
         <f t="array" ref="K144">_xlfn.REGEXEXTRACT(A144,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="B145" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>196</v>
+        <v>927</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>12</v>
+        <v>609</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>925</v>
+        <v>610</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I145" s="2">
         <v>4</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>926</v>
+        <v>612</v>
       </c>
       <c r="K145" s="2" t="str" cm="1">
         <f t="array" ref="K145">_xlfn.REGEXEXTRACT(A145,"(?&lt;=//)[^/]+")</f>
         <v>www.eporner.com</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>539</v>
+        <v>496</v>
       </c>
       <c r="B146" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>196</v>
+        <v>497</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>540</v>
+        <v>173</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>337</v>
+        <v>174</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>541</v>
+        <v>906</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I146" s="2">
         <v>4</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>542</v>
+        <v>499</v>
       </c>
       <c r="K146" s="2" t="str" cm="1">
         <f t="array" ref="K146">_xlfn.REGEXEXTRACT(A146,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>605</v>
+        <v>909</v>
       </c>
       <c r="B147" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>11</v>
+        <v>927</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>606</v>
+        <v>60</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>607</v>
+        <v>910</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>608</v>
+        <v>911</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I147" s="2">
         <v>4</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>609</v>
+        <v>912</v>
       </c>
       <c r="K147" s="2" t="str" cm="1">
         <f t="array" ref="K147">_xlfn.REGEXEXTRACT(A147,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>533</v>
+        <v>606</v>
       </c>
       <c r="B148" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>534</v>
+        <v>187</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>535</v>
+        <v>11</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>536</v>
+        <v>907</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>537</v>
+        <v>607</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I148" s="2">
         <v>4</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>538</v>
+        <v>908</v>
       </c>
       <c r="K148" s="2" t="str" cm="1">
         <f t="array" ref="K148">_xlfn.REGEXEXTRACT(A148,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B149" s="2">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>191</v>
+        <v>527</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I149" s="2">
         <v>4</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="K149" s="2" t="str" cm="1">
         <f t="array" ref="K149">_xlfn.REGEXEXTRACT(A149,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>txxx.me</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="B150" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>96</v>
+        <v>521</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>546</v>
+        <v>524</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I150" s="2">
         <v>4</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="K150" s="2" t="str" cm="1">
         <f t="array" ref="K150">_xlfn.REGEXEXTRACT(A150,"(?&lt;=//)[^/]+")</f>
@@ -8694,34 +8685,34 @@
     </row>
     <row r="151" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="B151" s="2">
         <v>11</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I151" s="2">
         <v>4</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="K151" s="2" t="str" cm="1">
         <f t="array" ref="K151">_xlfn.REGEXEXTRACT(A151,"(?&lt;=//)[^/]+")</f>
@@ -8730,1222 +8721,1222 @@
     </row>
     <row r="152" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="B152" s="2">
         <v>9</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>465</v>
+        <v>936</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>820</v>
+        <v>804</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I152" s="2">
         <v>4</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="K152" s="2" t="str" cm="1">
         <f t="array" ref="K152">_xlfn.REGEXEXTRACT(A152,"(?&lt;=//)[^/]+")</f>
         <v>xhamster18.desi</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>821</v>
+        <v>469</v>
       </c>
       <c r="B153" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>822</v>
+        <v>47</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>823</v>
+        <v>66</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I153" s="2">
         <v>4</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>824</v>
+        <v>470</v>
       </c>
       <c r="K153" s="2" t="str" cm="1">
         <f t="array" ref="K153">_xlfn.REGEXEXTRACT(A153,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>netfapx.net</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B154" s="2">
         <v>0</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D154" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E154" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="G154" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I154" s="2">
         <v>4</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="K154" s="2" t="str" cm="1">
         <f t="array" ref="K154">_xlfn.REGEXEXTRACT(A154,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
+        <v>pornzog.com</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>484</v>
+        <v>579</v>
       </c>
       <c r="B155" s="2">
         <v>0</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>580</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>71</v>
+        <v>581</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="I155" s="2">
         <v>4</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>485</v>
+        <v>582</v>
       </c>
       <c r="K155" s="2" t="str" cm="1">
         <f t="array" ref="K155">_xlfn.REGEXEXTRACT(A155,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog.com</v>
+        <v>www.tubegalore.com</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>593</v>
+        <v>544</v>
       </c>
       <c r="B156" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>52</v>
+        <v>934</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>47</v>
+        <v>545</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>594</v>
+        <v>546</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>595</v>
+        <v>386</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="I156" s="2">
         <v>4</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>596</v>
+        <v>547</v>
       </c>
       <c r="K156" s="2" t="str" cm="1">
         <f t="array" ref="K156">_xlfn.REGEXEXTRACT(A156,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>927</v>
+        <v>601</v>
       </c>
       <c r="B157" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>24</v>
+        <v>934</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>65</v>
+        <v>602</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>928</v>
+        <v>603</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>929</v>
+        <v>604</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I157" s="2">
         <v>4</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>930</v>
+        <v>605</v>
       </c>
       <c r="K157" s="2" t="str" cm="1">
         <f t="array" ref="K157">_xlfn.REGEXEXTRACT(A157,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>931</v>
+        <v>548</v>
       </c>
       <c r="B158" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>11</v>
+        <v>930</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>932</v>
+        <v>549</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>933</v>
+        <v>550</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>804</v>
+        <v>551</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I158" s="2">
         <v>4</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>934</v>
+        <v>552</v>
       </c>
       <c r="K158" s="2" t="str" cm="1">
         <f t="array" ref="K158">_xlfn.REGEXEXTRACT(A158,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>935</v>
+        <v>486</v>
       </c>
       <c r="B159" s="2">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>11</v>
+        <v>933</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>936</v>
+        <v>487</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>937</v>
+        <v>488</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>938</v>
+        <v>489</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I159" s="2">
         <v>4</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>939</v>
+        <v>490</v>
       </c>
       <c r="K159" s="2" t="str" cm="1">
         <f t="array" ref="K159">_xlfn.REGEXEXTRACT(A159,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>695</v>
+        <v>656</v>
       </c>
       <c r="B160" s="2">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>117</v>
+        <v>925</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>12</v>
+        <v>434</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>696</v>
+        <v>657</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>697</v>
+        <v>463</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>256</v>
+        <v>15</v>
       </c>
       <c r="I160" s="2">
         <v>3</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>698</v>
+        <v>658</v>
       </c>
       <c r="K160" s="2" t="str" cm="1">
         <f t="array" ref="K160">_xlfn.REGEXEXTRACT(A160,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>735</v>
+        <v>626</v>
       </c>
       <c r="B161" s="2">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>196</v>
+        <v>925</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>736</v>
+        <v>115</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>737</v>
+        <v>627</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>738</v>
+        <v>628</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I161" s="2">
         <v>3</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>739</v>
+        <v>629</v>
       </c>
       <c r="K161" s="2" t="str" cm="1">
         <f t="array" ref="K161">_xlfn.REGEXEXTRACT(A161,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>671</v>
+        <v>715</v>
       </c>
       <c r="B162" s="2">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>11</v>
+        <v>931</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>446</v>
+        <v>716</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>672</v>
+        <v>717</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>476</v>
+        <v>718</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I162" s="2">
         <v>3</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>673</v>
+        <v>719</v>
       </c>
       <c r="K162" s="2" t="str" cm="1">
         <f t="array" ref="K162">_xlfn.REGEXEXTRACT(A162,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B163" s="2">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>237</v>
+        <v>931</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>665</v>
+        <v>253</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I163" s="2">
         <v>3</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K163" s="2" t="str" cm="1">
         <f t="array" ref="K163">_xlfn.REGEXEXTRACT(A163,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>pervtube.net</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="B164" s="2">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>78</v>
+        <v>931</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>652</v>
+        <v>386</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I164" s="2">
         <v>3</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="K164" s="2" t="str" cm="1">
         <f t="array" ref="K164">_xlfn.REGEXEXTRACT(A164,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>730</v>
+        <v>652</v>
       </c>
       <c r="B165" s="2">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>85</v>
+        <v>931</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>731</v>
+        <v>653</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>732</v>
+        <v>654</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>733</v>
+        <v>463</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I165" s="2">
         <v>3</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>734</v>
+        <v>655</v>
       </c>
       <c r="K165" s="2" t="str" cm="1">
         <f t="array" ref="K165">_xlfn.REGEXEXTRACT(A165,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntopedia.com</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>682</v>
+        <v>922</v>
       </c>
       <c r="B166" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>85</v>
+        <v>931</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>683</v>
+        <v>834</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>684</v>
+        <v>923</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I166" s="2">
         <v>3</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>685</v>
+        <v>924</v>
       </c>
       <c r="K166" s="2" t="str" cm="1">
         <f t="array" ref="K166">_xlfn.REGEXEXTRACT(A166,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="B167" s="2">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>679</v>
+        <v>631</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>680</v>
+        <v>632</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>397</v>
+        <v>633</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I167" s="2">
         <v>3</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>681</v>
+        <v>634</v>
       </c>
       <c r="K167" s="2" t="str" cm="1">
         <f t="array" ref="K167">_xlfn.REGEXEXTRACT(A167,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="B168" s="2">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>337</v>
+        <v>19</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I168" s="2">
         <v>3</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="K168" s="2" t="str" cm="1">
         <f t="array" ref="K168">_xlfn.REGEXEXTRACT(A168,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>654</v>
+        <v>680</v>
       </c>
       <c r="B169" s="2">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>655</v>
+        <v>11</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="I169" s="2">
         <v>3</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="K169" s="2" t="str" cm="1">
         <f t="array" ref="K169">_xlfn.REGEXEXTRACT(A169,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="B170" s="2">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="C170" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D170" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F170" s="2" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>703</v>
+        <v>15</v>
       </c>
       <c r="I170" s="2">
         <v>3</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="K170" s="2" t="str" cm="1">
         <f t="array" ref="K170">_xlfn.REGEXEXTRACT(A170,"(?&lt;=//)[^/]+")</f>
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="B171" s="2">
         <v>44</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>715</v>
+        <v>928</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>97</v>
+        <v>685</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>716</v>
+        <v>686</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>717</v>
+        <v>687</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>16</v>
+        <v>688</v>
       </c>
       <c r="I171" s="2">
         <v>3</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>718</v>
+        <v>689</v>
       </c>
       <c r="K171" s="2" t="str" cm="1">
         <f t="array" ref="K171">_xlfn.REGEXEXTRACT(A171,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>674</v>
+        <v>621</v>
       </c>
       <c r="B172" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>197</v>
+        <v>622</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>183</v>
+        <v>326</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>675</v>
+        <v>623</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>676</v>
+        <v>624</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I172" s="2">
         <v>3</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>677</v>
+        <v>625</v>
       </c>
       <c r="K172" s="2" t="str" cm="1">
         <f t="array" ref="K172">_xlfn.REGEXEXTRACT(A172,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="B173" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>196</v>
+        <v>700</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>720</v>
+        <v>90</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I173" s="2">
         <v>3</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="K173" s="2" t="str" cm="1">
         <f t="array" ref="K173">_xlfn.REGEXEXTRACT(A173,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>686</v>
+        <v>659</v>
       </c>
       <c r="B174" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>687</v>
+        <v>187</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>688</v>
+        <v>188</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>689</v>
+        <v>660</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>827</v>
+        <v>661</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I174" s="2">
         <v>3</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>690</v>
+        <v>662</v>
       </c>
       <c r="K174" s="2" t="str" cm="1">
         <f t="array" ref="K174">_xlfn.REGEXEXTRACT(A174,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="175" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>659</v>
+        <v>704</v>
       </c>
       <c r="B175" s="2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>660</v>
+        <v>705</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>337</v>
+        <v>174</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>661</v>
+        <v>706</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>825</v>
+        <v>707</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I175" s="2">
         <v>3</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>826</v>
+        <v>708</v>
       </c>
       <c r="K175" s="2" t="str" cm="1">
         <f t="array" ref="K175">_xlfn.REGEXEXTRACT(A175,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="176" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>691</v>
+        <v>671</v>
       </c>
       <c r="B176" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>196</v>
+        <v>672</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>97</v>
+        <v>673</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>693</v>
+        <v>811</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I176" s="2">
         <v>3</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="K176" s="2" t="str" cm="1">
         <f t="array" ref="K176">_xlfn.REGEXEXTRACT(A176,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>705</v>
+        <v>644</v>
       </c>
       <c r="B177" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>510</v>
+        <v>187</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>197</v>
+        <v>645</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>183</v>
+        <v>326</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>706</v>
+        <v>646</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>707</v>
+        <v>809</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I177" s="2">
         <v>3</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>708</v>
+        <v>810</v>
       </c>
       <c r="K177" s="2" t="str" cm="1">
         <f t="array" ref="K177">_xlfn.REGEXEXTRACT(A177,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="B178" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>641</v>
+        <v>677</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>642</v>
+        <v>678</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I178" s="2">
         <v>3</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>643</v>
+        <v>679</v>
       </c>
       <c r="K178" s="2" t="str" cm="1">
         <f t="array" ref="K178">_xlfn.REGEXEXTRACT(A178,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="179" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>744</v>
+        <v>690</v>
       </c>
       <c r="B179" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>687</v>
+        <v>497</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>745</v>
+        <v>188</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>746</v>
+        <v>691</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>467</v>
+        <v>692</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I179" s="2">
         <v>3</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>747</v>
+        <v>693</v>
       </c>
       <c r="K179" s="2" t="str" cm="1">
         <f t="array" ref="K179">_xlfn.REGEXEXTRACT(A179,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>644</v>
+        <v>729</v>
       </c>
       <c r="B180" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>96</v>
+        <v>672</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>645</v>
+        <v>730</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>646</v>
+        <v>731</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>647</v>
+        <v>454</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I180" s="2">
         <v>3</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>648</v>
+        <v>732</v>
       </c>
       <c r="K180" s="2" t="str" cm="1">
         <f t="array" ref="K180">_xlfn.REGEXEXTRACT(A180,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>709</v>
+        <v>639</v>
       </c>
       <c r="B181" s="2">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>196</v>
+        <v>930</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>710</v>
+        <v>640</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>711</v>
+        <v>641</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>712</v>
+        <v>642</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I181" s="2">
         <v>3</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>713</v>
+        <v>643</v>
       </c>
       <c r="K181" s="2" t="str" cm="1">
         <f t="array" ref="K181">_xlfn.REGEXEXTRACT(A181,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="182" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>724</v>
+        <v>694</v>
       </c>
       <c r="B182" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>725</v>
+        <v>187</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>726</v>
+        <v>695</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>727</v>
+        <v>696</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>728</v>
+        <v>697</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I182" s="2">
         <v>3</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>729</v>
+        <v>698</v>
       </c>
       <c r="K182" s="2" t="str" cm="1">
         <f t="array" ref="K182">_xlfn.REGEXEXTRACT(A182,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>740</v>
+        <v>709</v>
       </c>
       <c r="B183" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>117</v>
+        <v>710</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>12</v>
+        <v>711</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>741</v>
+        <v>712</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>742</v>
+        <v>713</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>477</v>
+        <v>15</v>
       </c>
       <c r="I183" s="2">
         <v>3</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>743</v>
+        <v>714</v>
       </c>
       <c r="K183" s="2" t="str" cm="1">
         <f t="array" ref="K183">_xlfn.REGEXEXTRACT(A183,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>anyporn.com</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>667</v>
+        <v>725</v>
       </c>
       <c r="B184" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>668</v>
+        <v>11</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>669</v>
+        <v>726</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>476</v>
+        <v>727</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>16</v>
+        <v>464</v>
       </c>
       <c r="I184" s="2">
         <v>3</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>670</v>
+        <v>728</v>
       </c>
       <c r="K184" s="2" t="str" cm="1">
         <f t="array" ref="K184">_xlfn.REGEXEXTRACT(A184,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="185" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B185" s="2">
         <v>0</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I185" s="2">
         <v>3</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="K185" s="2" t="str" cm="1">
         <f t="array" ref="K185">_xlfn.REGEXEXTRACT(A185,"(?&lt;=//)[^/]+")</f>
@@ -9954,178 +9945,178 @@
     </row>
     <row r="186" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="B186" s="2">
         <v>0</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I186" s="2">
         <v>3</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="K186" s="2" t="str" cm="1">
         <f t="array" ref="K186">_xlfn.REGEXEXTRACT(A186,"(?&lt;=//)[^/]+")</f>
         <v>curebdsm.com</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>940</v>
+        <v>635</v>
       </c>
       <c r="B187" s="2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>85</v>
+        <v>932</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>850</v>
+        <v>636</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>941</v>
+        <v>637</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>291</v>
+        <v>638</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I187" s="2">
         <v>3</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="K187" s="2" t="str" cm="1">
         <f t="array" ref="K187">_xlfn.REGEXEXTRACT(A187,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="B188" s="2">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>196</v>
+        <v>925</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>774</v>
+        <v>434</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>775</v>
+        <v>738</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>776</v>
+        <v>739</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I188" s="2">
         <v>2</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>777</v>
+        <v>740</v>
       </c>
       <c r="K188" s="2" t="str" cm="1">
         <f t="array" ref="K188">_xlfn.REGEXEXTRACT(A188,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="189" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="B189" s="2">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>24</v>
+        <v>929</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>771</v>
+        <v>812</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I189" s="2">
         <v>2</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>772</v>
+        <v>736</v>
       </c>
       <c r="K189" s="2" t="str" cm="1">
         <f t="array" ref="K189">_xlfn.REGEXEXTRACT(A189,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="B190" s="2">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>783</v>
+        <v>228</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>784</v>
+        <v>479</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>785</v>
+        <v>750</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>786</v>
+        <v>751</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I190" s="2">
         <v>2</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>787</v>
+        <v>752</v>
       </c>
       <c r="K190" s="2" t="str" cm="1">
         <f t="array" ref="K190">_xlfn.REGEXEXTRACT(A190,"(?&lt;=//)[^/]+")</f>
@@ -10134,142 +10125,142 @@
     </row>
     <row r="191" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="B191" s="2">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>36</v>
+        <v>927</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>828</v>
+        <v>756</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I191" s="2">
         <v>2</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="K191" s="2" t="str" cm="1">
         <f t="array" ref="K191">_xlfn.REGEXEXTRACT(A191,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.omg.xxx</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B192" s="2">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>237</v>
+        <v>932</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>492</v>
+        <v>768</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I192" s="2">
         <v>2</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="K192" s="2" t="str" cm="1">
         <f t="array" ref="K192">_xlfn.REGEXEXTRACT(A192,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="B193" s="2">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>11</v>
+        <v>187</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>446</v>
+        <v>759</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I193" s="2">
         <v>2</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="K193" s="2" t="str" cm="1">
         <f t="array" ref="K193">_xlfn.REGEXEXTRACT(A193,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.peekvids.com</v>
       </c>
     </row>
     <row r="194" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="B194" s="2">
         <v>23</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I194" s="2">
         <v>2</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="K194" s="2" t="str" cm="1">
         <f t="array" ref="K194">_xlfn.REGEXEXTRACT(A194,"(?&lt;=//)[^/]+")</f>
@@ -10278,34 +10269,34 @@
     </row>
     <row r="195" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="B195" s="2">
         <v>18</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I195" s="2">
         <v>2</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="K195" s="2" t="str" cm="1">
         <f t="array" ref="K195">_xlfn.REGEXEXTRACT(A195,"(?&lt;=//)[^/]+")</f>
@@ -10314,34 +10305,34 @@
     </row>
     <row r="196" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>760</v>
+        <v>745</v>
       </c>
       <c r="B196" s="2">
         <v>14</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>761</v>
+        <v>746</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I196" s="2">
         <v>2</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="K196" s="2" t="str" cm="1">
         <f t="array" ref="K196">_xlfn.REGEXEXTRACT(A196,"(?&lt;=//)[^/]+")</f>
@@ -10350,34 +10341,34 @@
     </row>
     <row r="197" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="B197" s="2">
         <v>48</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I197" s="2">
         <v>1</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="K197" s="2" t="str" cm="1">
         <f t="array" ref="K197">_xlfn.REGEXEXTRACT(A197,"(?&lt;=//)[^/]+")</f>
@@ -10386,34 +10377,34 @@
     </row>
     <row r="198" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="B198" s="2">
         <v>34</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>687</v>
+        <v>672</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I198" s="2">
         <v>1</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="K198" s="2" t="str" cm="1">
         <f t="array" ref="K198">_xlfn.REGEXEXTRACT(A198,"(?&lt;=//)[^/]+")</f>
@@ -10422,34 +10413,34 @@
     </row>
     <row r="199" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="B199" s="2">
         <v>11</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I199" s="2">
         <v>1</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="K199" s="2" t="str" cm="1">
         <f t="array" ref="K199">_xlfn.REGEXEXTRACT(A199,"(?&lt;=//)[^/]+")</f>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B44FC09-4700-4901-B703-8747F7569C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC2CA41-69B3-45E2-A0E1-6E2842DB0545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3345,7 +3345,7 @@
         <v>15</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>16</v>
@@ -3381,7 +3381,7 @@
         <v>15</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>847</v>
@@ -3391,171 +3391,171 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="B4" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>866</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>851</v>
+        <v>869</v>
       </c>
       <c r="K4" s="2" t="str" cm="1">
         <f t="array" ref="K4">_xlfn.REGEXEXTRACT(A4,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmlust.com</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B5" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>927</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>434</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I5" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="K5" s="2" t="str" cm="1">
         <f t="array" ref="K5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmlust.com</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmmansion.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="B6" s="2">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>868</v>
+        <v>463</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="K6" s="2" t="str" cm="1">
         <f t="array" ref="K6">_xlfn.REGEXEXTRACT(A6,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmlust.com</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>817</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>818</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>819</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="K7" s="2" t="str" cm="1">
         <f t="array" ref="K7">_xlfn.REGEXEXTRACT(A7,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>848</v>
       </c>
       <c r="B8" s="2">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
+        <v>849</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>850</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -3564,34 +3564,34 @@
         <v>9</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>31</v>
+        <v>851</v>
       </c>
       <c r="K8" s="2" t="str" cm="1">
         <f t="array" ref="K8">_xlfn.REGEXEXTRACT(A8,"(?&lt;=//)[^/]+")</f>
-        <v>www.hqbdsm.com</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="B9" s="2">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>927</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>853</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>854</v>
+        <v>824</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>463</v>
+        <v>825</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>15</v>
@@ -3600,34 +3600,34 @@
         <v>9</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>855</v>
+        <v>826</v>
       </c>
       <c r="K9" s="2" t="str" cm="1">
         <f t="array" ref="K9">_xlfn.REGEXEXTRACT(A9,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmlust.com</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -3636,70 +3636,70 @@
         <v>9</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>842</v>
+        <v>31</v>
       </c>
       <c r="K10" s="2" t="str" cm="1">
         <f t="array" ref="K10">_xlfn.REGEXEXTRACT(A10,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.hqbdsm.com</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>856</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>925</v>
+        <v>47</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>834</v>
+        <v>104</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>857</v>
+        <v>106</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>858</v>
+        <v>107</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>859</v>
+        <v>108</v>
       </c>
       <c r="K11" s="2" t="str" cm="1">
         <f t="array" ref="K11">_xlfn.REGEXEXTRACT(A11,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="B12" s="2">
         <v>46</v>
       </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>925</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>834</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>48</v>
+        <v>857</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>49</v>
+        <v>858</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
@@ -3708,16 +3708,16 @@
         <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>50</v>
+        <v>859</v>
       </c>
       <c r="K12" s="2" t="str" cm="1">
         <f t="array" ref="K12">_xlfn.REGEXEXTRACT(A12,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
@@ -3729,13 +3729,13 @@
         <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -3744,16 +3744,16 @@
         <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K13" s="2" t="str" cm="1">
         <f t="array" ref="K13">_xlfn.REGEXEXTRACT(A13,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
@@ -3780,34 +3780,34 @@
         <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K14" s="2" t="str" cm="1">
         <f t="array" ref="K14">_xlfn.REGEXEXTRACT(A14,"(?&lt;=//)[^/]+")</f>
         <v>www.tubebdsm.com</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>929</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
@@ -3816,34 +3816,34 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="K15" s="2" t="str" cm="1">
         <f t="array" ref="K15">_xlfn.REGEXEXTRACT(A15,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>www.tubebdsm.com</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>860</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>929</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>861</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>862</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>863</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -3852,34 +3852,34 @@
         <v>8</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>864</v>
+        <v>35</v>
       </c>
       <c r="K16" s="2" t="str" cm="1">
         <f t="array" ref="K16">_xlfn.REGEXEXTRACT(A16,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>860</v>
       </c>
       <c r="B17" s="2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>861</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>61</v>
+        <v>862</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>62</v>
+        <v>863</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -3888,34 +3888,34 @@
         <v>8</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>63</v>
+        <v>864</v>
       </c>
       <c r="K17" s="2" t="str" cm="1">
         <f t="array" ref="K17">_xlfn.REGEXEXTRACT(A17,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B18" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>927</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -3924,34 +3924,34 @@
         <v>8</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="K18" s="2" t="str" cm="1">
         <f t="array" ref="K18">_xlfn.REGEXEXTRACT(A18,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>abxxx.com</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3960,70 +3960,70 @@
         <v>8</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K19" s="2" t="str" cm="1">
         <f t="array" ref="K19">_xlfn.REGEXEXTRACT(A19,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="K20" s="2" t="str" cm="1">
         <f t="array" ref="K20">_xlfn.REGEXEXTRACT(A20,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>abxxx.com</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>925</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>785</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -4032,34 +4032,34 @@
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K21" s="2" t="str" cm="1">
         <f t="array" ref="K21">_xlfn.REGEXEXTRACT(A21,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B22" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>925</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>137</v>
+        <v>785</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -4068,34 +4068,34 @@
         <v>7</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>870</v>
+        <v>117</v>
       </c>
       <c r="K22" s="2" t="str" cm="1">
         <f t="array" ref="K22">_xlfn.REGEXEXTRACT(A22,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>828</v>
+        <v>134</v>
       </c>
       <c r="B23" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>925</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>829</v>
+        <v>135</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>830</v>
+        <v>136</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>831</v>
+        <v>137</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -4104,34 +4104,34 @@
         <v>7</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>832</v>
+        <v>870</v>
       </c>
       <c r="K23" s="2" t="str" cm="1">
         <f t="array" ref="K23">_xlfn.REGEXEXTRACT(A23,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>109</v>
+        <v>828</v>
       </c>
       <c r="B24" s="2">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>110</v>
+        <v>925</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>11</v>
+        <v>829</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>111</v>
+        <v>830</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>112</v>
+        <v>831</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -4140,19 +4140,19 @@
         <v>7</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>113</v>
+        <v>832</v>
       </c>
       <c r="K24" s="2" t="str" cm="1">
         <f t="array" ref="K24">_xlfn.REGEXEXTRACT(A24,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B25" s="2">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>110</v>
@@ -4164,10 +4164,10 @@
         <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -4176,34 +4176,34 @@
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K25" s="2" t="str" cm="1">
         <f t="array" ref="K25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>punishworld.com</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B26" s="2">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>931</v>
+        <v>110</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -4212,34 +4212,34 @@
         <v>7</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="K26" s="2" t="str" cm="1">
         <f t="array" ref="K26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B27" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>931</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -4248,34 +4248,34 @@
         <v>7</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="K27" s="2" t="str" cm="1">
         <f t="array" ref="K27">_xlfn.REGEXEXTRACT(A27,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>931</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -4284,34 +4284,34 @@
         <v>7</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="K28" s="2" t="str" cm="1">
         <f t="array" ref="K28">_xlfn.REGEXEXTRACT(A28,"(?&lt;=//)[^/]+")</f>
-        <v>www.fapcat.com</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="B29" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>110</v>
+        <v>931</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>871</v>
+        <v>120</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -4320,34 +4320,34 @@
         <v>7</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>872</v>
+        <v>121</v>
       </c>
       <c r="K29" s="2" t="str" cm="1">
         <f t="array" ref="K29">_xlfn.REGEXEXTRACT(A29,"(?&lt;=//)[^/]+")</f>
-        <v>www.amateur8.com</v>
+        <v>www.fapcat.com</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>833</v>
+        <v>164</v>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>834</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>835</v>
+        <v>166</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>836</v>
+        <v>871</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -4356,16 +4356,16 @@
         <v>7</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>837</v>
+        <v>872</v>
       </c>
       <c r="K30" s="2" t="str" cm="1">
         <f t="array" ref="K30">_xlfn.REGEXEXTRACT(A30,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.amateur8.com</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>64</v>
+        <v>833</v>
       </c>
       <c r="B31" s="2">
         <v>0</v>
@@ -4374,16 +4374,16 @@
         <v>47</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>42</v>
+        <v>834</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>47</v>
+        <v>835</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>66</v>
+        <v>836</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -4392,34 +4392,34 @@
         <v>7</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>67</v>
+        <v>837</v>
       </c>
       <c r="K31" s="2" t="str" cm="1">
         <f t="array" ref="K31">_xlfn.REGEXEXTRACT(A31,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B32" s="2">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>784</v>
+        <v>47</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -4428,34 +4428,34 @@
         <v>7</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K32" s="2" t="str" cm="1">
         <f t="array" ref="K32">_xlfn.REGEXEXTRACT(A32,"(?&lt;=//)[^/]+")</f>
         <v>beeg.com</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="B33" s="2">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>784</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -4464,11 +4464,11 @@
         <v>7</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="K33" s="2" t="str" cm="1">
         <f t="array" ref="K33">_xlfn.REGEXEXTRACT(A33,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="30" x14ac:dyDescent="0.25">

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3281AC45-D290-43BF-932B-092585CF8C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BEFA03-E015-4201-8AB2-E9529BA1A71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NSFW_Links" sheetId="2" r:id="rId1"/>
@@ -3045,21 +3045,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -10757,13 +10743,13 @@
     <sortCondition descending="1" ref="I1:I205"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:F205 H1:K205">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="A1:K205">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I205">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10772,11 +10758,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G205">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11819,7 +11800,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A205">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BEFA03-E015-4201-8AB2-E9529BA1A71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1381B02D-B60C-424F-8B6C-9C5D7D47AA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NSFW_Links" sheetId="2" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="972">
   <si>
     <t>main_link</t>
   </si>
@@ -2963,6 +2963,21 @@
   </si>
   <si>
     <t>pretzel,cowgirl,sit</t>
+  </si>
+  <si>
+    <t>https://m.hqporner.com/hdporn/20111-Hegre-art_-_Kiki_-_Volcano_Orgasm_Massage.html</t>
+  </si>
+  <si>
+    <t>hegre</t>
+  </si>
+  <si>
+    <t>kiki</t>
+  </si>
+  <si>
+    <t>massage,fingering</t>
+  </si>
+  <si>
+    <t>main fingering at 19m</t>
   </si>
 </sst>
 </file>
@@ -3343,7 +3358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K206"/>
   <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47" style="1" customWidth="1"/>
@@ -4150,63 +4165,63 @@
         <v>abxxx.com</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="B23" s="2">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>932</v>
+        <v>968</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>947</v>
+        <v>969</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>12</v>
+        <v>326</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>948</v>
+        <v>970</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>949</v>
+        <v>463</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="K23" s="2" t="str" cm="1">
         <f t="array" ref="K23">_xlfn.REGEXEXTRACT(A23,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>946</v>
       </c>
       <c r="B24" s="2">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>947</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>95</v>
+        <v>948</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>96</v>
+        <v>949</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -4215,34 +4230,34 @@
         <v>7</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>97</v>
+        <v>950</v>
       </c>
       <c r="K24" s="2" t="str" cm="1">
         <f t="array" ref="K24">_xlfn.REGEXEXTRACT(A24,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>784</v>
+        <v>96</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -4251,34 +4266,34 @@
         <v>7</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K25" s="2" t="str" cm="1">
         <f t="array" ref="K25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B26" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>137</v>
+        <v>784</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -4287,34 +4302,34 @@
         <v>7</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>868</v>
+        <v>117</v>
       </c>
       <c r="K26" s="2" t="str" cm="1">
         <f t="array" ref="K26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>827</v>
+        <v>134</v>
       </c>
       <c r="B27" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>828</v>
+        <v>135</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>829</v>
+        <v>136</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>830</v>
+        <v>137</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -4323,34 +4338,34 @@
         <v>7</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>831</v>
+        <v>868</v>
       </c>
       <c r="K27" s="2" t="str" cm="1">
         <f t="array" ref="K27">_xlfn.REGEXEXTRACT(A27,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>109</v>
+        <v>827</v>
       </c>
       <c r="B28" s="2">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>110</v>
+        <v>922</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>11</v>
+        <v>828</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>111</v>
+        <v>829</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>112</v>
+        <v>830</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -4359,19 +4374,19 @@
         <v>7</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>113</v>
+        <v>831</v>
       </c>
       <c r="K28" s="2" t="str" cm="1">
         <f t="array" ref="K28">_xlfn.REGEXEXTRACT(A28,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B29" s="2">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>110</v>
@@ -4383,10 +4398,10 @@
         <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -4395,34 +4410,34 @@
         <v>7</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="K29" s="2" t="str" cm="1">
         <f t="array" ref="K29">_xlfn.REGEXEXTRACT(A29,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>punishworld.com</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B30" s="2">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>928</v>
+        <v>110</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -4431,34 +4446,34 @@
         <v>7</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="K30" s="2" t="str" cm="1">
         <f t="array" ref="K30">_xlfn.REGEXEXTRACT(A30,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B31" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -4467,34 +4482,34 @@
         <v>7</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="K31" s="2" t="str" cm="1">
         <f t="array" ref="K31">_xlfn.REGEXEXTRACT(A31,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="B32" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -4503,34 +4518,34 @@
         <v>7</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="K32" s="2" t="str" cm="1">
         <f t="array" ref="K32">_xlfn.REGEXEXTRACT(A32,"(?&lt;=//)[^/]+")</f>
-        <v>www.fapcat.com</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="B33" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>110</v>
+        <v>928</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>869</v>
+        <v>120</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -4539,34 +4554,34 @@
         <v>7</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>870</v>
+        <v>121</v>
       </c>
       <c r="K33" s="2" t="str" cm="1">
         <f t="array" ref="K33">_xlfn.REGEXEXTRACT(A33,"(?&lt;=//)[^/]+")</f>
-        <v>www.amateur8.com</v>
+        <v>www.fapcat.com</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>832</v>
+        <v>164</v>
       </c>
       <c r="B34" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>833</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>834</v>
+        <v>166</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>835</v>
+        <v>869</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -4575,16 +4590,16 @@
         <v>7</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>836</v>
+        <v>870</v>
       </c>
       <c r="K34" s="2" t="str" cm="1">
         <f t="array" ref="K34">_xlfn.REGEXEXTRACT(A34,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.amateur8.com</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>64</v>
+        <v>832</v>
       </c>
       <c r="B35" s="2">
         <v>0</v>
@@ -4593,16 +4608,16 @@
         <v>47</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>42</v>
+        <v>833</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>47</v>
+        <v>834</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>66</v>
+        <v>835</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -4611,34 +4626,34 @@
         <v>7</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>67</v>
+        <v>836</v>
       </c>
       <c r="K35" s="2" t="str" cm="1">
         <f t="array" ref="K35">_xlfn.REGEXEXTRACT(A35,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B36" s="2">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>783</v>
+        <v>47</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -4647,7 +4662,7 @@
         <v>7</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K36" s="2" t="str" cm="1">
         <f t="array" ref="K36">_xlfn.REGEXEXTRACT(A36,"(?&lt;=//)[^/]+")</f>
@@ -4656,25 +4671,25 @@
     </row>
     <row r="37" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="B37" s="2">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>47</v>
+        <v>783</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -4683,34 +4698,34 @@
         <v>7</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="K37" s="2" t="str" cm="1">
         <f t="array" ref="K37">_xlfn.REGEXEXTRACT(A37,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B38" s="2">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>928</v>
+        <v>47</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -4719,34 +4734,34 @@
         <v>7</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="K38" s="2" t="str" cm="1">
         <f t="array" ref="K38">_xlfn.REGEXEXTRACT(A38,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B39" s="2">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>47</v>
+        <v>928</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -4755,34 +4770,34 @@
         <v>7</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K39" s="2" t="str" cm="1">
         <f t="array" ref="K39">_xlfn.REGEXEXTRACT(A39,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B40" s="2">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>928</v>
+        <v>47</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>785</v>
+        <v>150</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -4791,34 +4806,34 @@
         <v>7</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K40" s="2" t="str" cm="1">
         <f t="array" ref="K40">_xlfn.REGEXEXTRACT(A40,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B41" s="2">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>47</v>
+        <v>928</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>157</v>
+        <v>785</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -4827,34 +4842,34 @@
         <v>7</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K41" s="2" t="str" cm="1">
         <f t="array" ref="K41">_xlfn.REGEXEXTRACT(A41,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="B42" s="2">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -4863,34 +4878,34 @@
         <v>7</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="K42" s="2" t="str" cm="1">
         <f t="array" ref="K42">_xlfn.REGEXEXTRACT(A42,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="B43" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>923</v>
+        <v>89</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -4899,34 +4914,34 @@
         <v>7</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="K43" s="2" t="str" cm="1">
         <f t="array" ref="K43">_xlfn.REGEXEXTRACT(A43,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B44" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>129</v>
+        <v>923</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -4935,34 +4950,34 @@
         <v>7</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K44" s="2" t="str" cm="1">
         <f t="array" ref="K44">_xlfn.REGEXEXTRACT(A44,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>826</v>
+        <v>128</v>
       </c>
       <c r="B45" s="2">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>924</v>
+        <v>129</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -4971,34 +4986,34 @@
         <v>7</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="K45" s="2" t="str" cm="1">
         <f t="array" ref="K45">_xlfn.REGEXEXTRACT(A45,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>871</v>
+        <v>826</v>
       </c>
       <c r="B46" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>924</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>872</v>
+        <v>22</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>873</v>
+        <v>24</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>874</v>
+        <v>25</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -5007,34 +5022,34 @@
         <v>7</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>875</v>
+        <v>26</v>
       </c>
       <c r="K46" s="2" t="str" cm="1">
         <f t="array" ref="K46">_xlfn.REGEXEXTRACT(A46,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmmansion.com</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>83</v>
+        <v>871</v>
       </c>
       <c r="B47" s="2">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>84</v>
+        <v>872</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>85</v>
+        <v>873</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>86</v>
+        <v>874</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -5043,34 +5058,34 @@
         <v>7</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>87</v>
+        <v>875</v>
       </c>
       <c r="K47" s="2" t="str" cm="1">
         <f t="array" ref="K47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B48" s="2">
+        <v>73</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="G48" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -5079,34 +5094,34 @@
         <v>7</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K48" s="2" t="str" cm="1">
         <f t="array" ref="K48">_xlfn.REGEXEXTRACT(A48,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="B49" s="2">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -5115,16 +5130,16 @@
         <v>7</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="K49" s="2" t="str" cm="1">
         <f t="array" ref="K49">_xlfn.REGEXEXTRACT(A49,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>876</v>
+        <v>159</v>
       </c>
       <c r="B50" s="2">
         <v>51</v>
@@ -5133,16 +5148,16 @@
         <v>930</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>877</v>
+        <v>160</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>878</v>
+        <v>161</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>879</v>
+        <v>162</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -5151,34 +5166,34 @@
         <v>7</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>880</v>
+        <v>163</v>
       </c>
       <c r="K50" s="2" t="str" cm="1">
         <f t="array" ref="K50">_xlfn.REGEXEXTRACT(A50,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>951</v>
+        <v>876</v>
       </c>
       <c r="B51" s="2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>47</v>
+        <v>930</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>833</v>
+        <v>877</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>952</v>
+        <v>878</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>953</v>
+        <v>879</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -5187,70 +5202,70 @@
         <v>7</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>954</v>
+        <v>880</v>
       </c>
       <c r="K51" s="2" t="str" cm="1">
         <f t="array" ref="K51">_xlfn.REGEXEXTRACT(A51,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>255</v>
+        <v>951</v>
       </c>
       <c r="B52" s="2">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>922</v>
+        <v>47</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>256</v>
+        <v>833</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>257</v>
+        <v>952</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>258</v>
+        <v>953</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>259</v>
+        <v>954</v>
       </c>
       <c r="K52" s="2" t="str" cm="1">
         <f t="array" ref="K52">_xlfn.REGEXEXTRACT(A52,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>303</v>
+        <v>255</v>
       </c>
       <c r="B53" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>304</v>
+        <v>256</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>305</v>
+        <v>257</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -5259,34 +5274,34 @@
         <v>6</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="K53" s="2" t="str" cm="1">
         <f t="array" ref="K53">_xlfn.REGEXEXTRACT(A53,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>889</v>
+        <v>303</v>
       </c>
       <c r="B54" s="2">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>890</v>
+        <v>304</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>891</v>
+        <v>305</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>892</v>
+        <v>306</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -5295,34 +5310,34 @@
         <v>6</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>893</v>
+        <v>307</v>
       </c>
       <c r="K54" s="2" t="str" cm="1">
         <f t="array" ref="K54">_xlfn.REGEXEXTRACT(A54,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>abxxx.com</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>233</v>
+        <v>889</v>
       </c>
       <c r="B55" s="2">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>234</v>
+        <v>890</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>235</v>
+        <v>891</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>236</v>
+        <v>892</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -5331,34 +5346,34 @@
         <v>6</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>237</v>
+        <v>893</v>
       </c>
       <c r="K55" s="2" t="str" cm="1">
         <f t="array" ref="K55">_xlfn.REGEXEXTRACT(A55,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="B56" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -5367,34 +5382,34 @@
         <v>6</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="K56" s="2" t="str" cm="1">
         <f t="array" ref="K56">_xlfn.REGEXEXTRACT(A56,"(?&lt;=//)[^/]+")</f>
         <v>www.pornhits.com</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>881</v>
+        <v>196</v>
       </c>
       <c r="B57" s="2">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>187</v>
+        <v>928</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>882</v>
+        <v>197</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>883</v>
+        <v>198</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>787</v>
+        <v>199</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -5403,19 +5418,19 @@
         <v>6</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>884</v>
+        <v>200</v>
       </c>
       <c r="K57" s="2" t="str" cm="1">
         <f t="array" ref="K57">_xlfn.REGEXEXTRACT(A57,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B58" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>187</v>
@@ -5427,7 +5442,7 @@
         <v>19</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>787</v>
@@ -5439,88 +5454,88 @@
         <v>6</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="K58" s="2" t="str" cm="1">
         <f t="array" ref="K58">_xlfn.REGEXEXTRACT(A58,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>243</v>
+        <v>885</v>
       </c>
       <c r="B59" s="2">
-        <v>113</v>
+        <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>11</v>
+        <v>882</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>244</v>
+        <v>886</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>245</v>
+        <v>787</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="I59" s="2">
         <v>6</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>247</v>
+        <v>887</v>
       </c>
       <c r="K59" s="2" t="str" cm="1">
         <f t="array" ref="K59">_xlfn.REGEXEXTRACT(A59,"(?&lt;=//)[^/]+")</f>
-        <v>abjav.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="B60" s="2">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>928</v>
+        <v>110</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="I60" s="2">
         <v>6</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="K60" s="2" t="str" cm="1">
         <f t="array" ref="K60">_xlfn.REGEXEXTRACT(A60,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>abjav.com</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="B61" s="2">
         <v>0</v>
@@ -5535,7 +5550,7 @@
         <v>23</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>210</v>
@@ -5547,7 +5562,7 @@
         <v>6</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="K61" s="2" t="str" cm="1">
         <f t="array" ref="K61">_xlfn.REGEXEXTRACT(A61,"(?&lt;=//)[^/]+")</f>
@@ -5556,25 +5571,25 @@
     </row>
     <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="B62" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>187</v>
+        <v>928</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>223</v>
+        <v>42</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -5583,34 +5598,34 @@
         <v>6</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="K62" s="2" t="str" cm="1">
         <f t="array" ref="K62">_xlfn.REGEXEXTRACT(A62,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="B63" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>187</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -5619,34 +5634,34 @@
         <v>6</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="K63" s="2" t="str" cm="1">
         <f t="array" ref="K63">_xlfn.REGEXEXTRACT(A63,"(?&lt;=//)[^/]+")</f>
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="B64" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -5655,34 +5670,34 @@
         <v>6</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="K64" s="2" t="str" cm="1">
         <f t="array" ref="K64">_xlfn.REGEXEXTRACT(A64,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="B65" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -5691,34 +5706,34 @@
         <v>6</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="K65" s="2" t="str" cm="1">
         <f t="array" ref="K65">_xlfn.REGEXEXTRACT(A65,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>319</v>
+        <v>260</v>
       </c>
       <c r="B66" s="2">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>11</v>
+        <v>261</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>320</v>
+        <v>262</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>321</v>
+        <v>263</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -5727,34 +5742,34 @@
         <v>6</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>888</v>
+        <v>264</v>
       </c>
       <c r="K66" s="2" t="str" cm="1">
         <f t="array" ref="K66">_xlfn.REGEXEXTRACT(A66,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>269</v>
+        <v>319</v>
       </c>
       <c r="B67" s="2">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>187</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>270</v>
+        <v>11</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>271</v>
+        <v>320</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>787</v>
+        <v>321</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -5763,55 +5778,55 @@
         <v>6</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>272</v>
+        <v>888</v>
       </c>
       <c r="K67" s="2" t="str" cm="1">
         <f t="array" ref="K67">_xlfn.REGEXEXTRACT(A67,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="B68" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>11</v>
+        <v>270</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>295</v>
+        <v>787</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="I68" s="2">
         <v>6</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="K68" s="2" t="str" cm="1">
         <f t="array" ref="K68">_xlfn.REGEXEXTRACT(A68,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>xhamster44.desi</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>212</v>
+        <v>293</v>
       </c>
       <c r="B69" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>110</v>
@@ -5823,46 +5838,46 @@
         <v>19</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="I69" s="2">
         <v>6</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>215</v>
+        <v>297</v>
       </c>
       <c r="K69" s="2" t="str" cm="1">
         <f t="array" ref="K69">_xlfn.REGEXEXTRACT(A69,"(?&lt;=//)[^/]+")</f>
-        <v>abbdsm.com</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="B70" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -5871,34 +5886,34 @@
         <v>6</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="K70" s="2" t="str" cm="1">
         <f t="array" ref="K70">_xlfn.REGEXEXTRACT(A70,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>abbdsm.com</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B71" s="2">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -5907,34 +5922,34 @@
         <v>6</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="K71" s="2" t="str" cm="1">
         <f t="array" ref="K71">_xlfn.REGEXEXTRACT(A71,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="B72" s="2">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -5943,16 +5958,16 @@
         <v>6</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="K72" s="2" t="str" cm="1">
         <f t="array" ref="K72">_xlfn.REGEXEXTRACT(A72,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B73" s="2">
         <v>0</v>
@@ -5967,10 +5982,10 @@
         <v>23</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>786</v>
+        <v>194</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -5979,7 +5994,7 @@
         <v>6</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="K73" s="2" t="str" cm="1">
         <f t="array" ref="K73">_xlfn.REGEXEXTRACT(A73,"(?&lt;=//)[^/]+")</f>
@@ -5988,7 +6003,7 @@
     </row>
     <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B74" s="2">
         <v>0</v>
@@ -6003,10 +6018,10 @@
         <v>23</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>206</v>
+        <v>786</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -6015,7 +6030,7 @@
         <v>6</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K74" s="2" t="str" cm="1">
         <f t="array" ref="K74">_xlfn.REGEXEXTRACT(A74,"(?&lt;=//)[^/]+")</f>
@@ -6024,7 +6039,7 @@
     </row>
     <row r="75" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="B75" s="2">
         <v>0</v>
@@ -6036,13 +6051,13 @@
         <v>42</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -6051,16 +6066,16 @@
         <v>6</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
       <c r="K75" s="2" t="str" cm="1">
         <f t="array" ref="K75">_xlfn.REGEXEXTRACT(A75,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="B76" s="2">
         <v>0</v>
@@ -6072,13 +6087,13 @@
         <v>42</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -6087,7 +6102,7 @@
         <v>6</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="K76" s="2" t="str" cm="1">
         <f t="array" ref="K76">_xlfn.REGEXEXTRACT(A76,"(?&lt;=//)[^/]+")</f>
@@ -6096,25 +6111,25 @@
     </row>
     <row r="77" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="B77" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>283</v>
+        <v>47</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>284</v>
+        <v>42</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -6123,34 +6138,34 @@
         <v>6</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="K77" s="2" t="str" cm="1">
         <f t="array" ref="K77">_xlfn.REGEXEXTRACT(A77,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.tubebdsm.com</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>812</v>
+        <v>282</v>
       </c>
       <c r="B78" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>813</v>
+        <v>283</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>814</v>
+        <v>285</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>524</v>
+        <v>286</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -6159,34 +6174,34 @@
         <v>6</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>815</v>
+        <v>287</v>
       </c>
       <c r="K78" s="2" t="str" cm="1">
         <f t="array" ref="K78">_xlfn.REGEXEXTRACT(A78,"(?&lt;=//)[^/]+")</f>
-        <v>www.xozilla.xxx</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>298</v>
+        <v>812</v>
       </c>
       <c r="B79" s="2">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>923</v>
+        <v>813</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>299</v>
+        <v>11</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>300</v>
+        <v>814</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>301</v>
+        <v>524</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -6195,34 +6210,34 @@
         <v>6</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>302</v>
+        <v>815</v>
       </c>
       <c r="K79" s="2" t="str" cm="1">
         <f t="array" ref="K79">_xlfn.REGEXEXTRACT(A79,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.xozilla.xxx</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="B80" s="2">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>129</v>
+        <v>923</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -6231,34 +6246,34 @@
         <v>6</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="K80" s="2" t="str" cm="1">
         <f t="array" ref="K80">_xlfn.REGEXEXTRACT(A80,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="B81" s="2">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -6267,34 +6282,34 @@
         <v>6</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="K81" s="2" t="str" cm="1">
         <f t="array" ref="K81">_xlfn.REGEXEXTRACT(A81,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="B82" s="2">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>924</v>
+        <v>228</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -6303,34 +6318,34 @@
         <v>6</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="K82" s="2" t="str" cm="1">
         <f t="array" ref="K82">_xlfn.REGEXEXTRACT(A82,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="B83" s="2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>924</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>313</v>
+        <v>183</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>788</v>
+        <v>184</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -6339,34 +6354,34 @@
         <v>6</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>314</v>
+        <v>185</v>
       </c>
       <c r="K83" s="2" t="str" cm="1">
         <f t="array" ref="K83">_xlfn.REGEXEXTRACT(A83,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="B84" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>289</v>
+        <v>42</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>291</v>
+        <v>788</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -6375,34 +6390,34 @@
         <v>6</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="K84" s="2" t="str" cm="1">
         <f t="array" ref="K84">_xlfn.REGEXEXTRACT(A84,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B85" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>931</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -6411,34 +6426,34 @@
         <v>6</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="K85" s="2" t="str" cm="1">
         <f t="array" ref="K85">_xlfn.REGEXEXTRACT(A85,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="B86" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>931</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>42</v>
+        <v>278</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -6447,16 +6462,16 @@
         <v>6</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="K86" s="2" t="str" cm="1">
         <f t="array" ref="K86">_xlfn.REGEXEXTRACT(A86,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>tube.perverzija.com</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>315</v>
+        <v>251</v>
       </c>
       <c r="B87" s="2">
         <v>0</v>
@@ -6468,13 +6483,13 @@
         <v>42</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>316</v>
+        <v>252</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>317</v>
+        <v>253</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -6483,34 +6498,34 @@
         <v>6</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>318</v>
+        <v>254</v>
       </c>
       <c r="K87" s="2" t="str" cm="1">
         <f t="array" ref="K87">_xlfn.REGEXEXTRACT(A87,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>177</v>
+        <v>315</v>
       </c>
       <c r="B88" s="2">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>178</v>
+        <v>316</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>179</v>
+        <v>317</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -6519,34 +6534,34 @@
         <v>6</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>180</v>
+        <v>318</v>
       </c>
       <c r="K88" s="2" t="str" cm="1">
         <f t="array" ref="K88">_xlfn.REGEXEXTRACT(A88,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>www.txxx.porn</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>238</v>
+        <v>177</v>
       </c>
       <c r="B89" s="2">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>239</v>
+        <v>115</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>241</v>
+        <v>179</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -6555,70 +6570,70 @@
         <v>6</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="K89" s="2" t="str" cm="1">
         <f t="array" ref="K89">_xlfn.REGEXEXTRACT(A89,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>329</v>
+        <v>238</v>
       </c>
       <c r="B90" s="2">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>330</v>
+        <v>239</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>894</v>
+        <v>240</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>331</v>
+        <v>241</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>332</v>
+        <v>242</v>
       </c>
       <c r="K90" s="2" t="str" cm="1">
         <f t="array" ref="K90">_xlfn.REGEXEXTRACT(A90,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>443</v>
+        <v>329</v>
       </c>
       <c r="B91" s="2">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>444</v>
+        <v>330</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>445</v>
+        <v>894</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>446</v>
+        <v>331</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -6627,34 +6642,34 @@
         <v>5</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>447</v>
+        <v>332</v>
       </c>
       <c r="K91" s="2" t="str" cm="1">
         <f t="array" ref="K91">_xlfn.REGEXEXTRACT(A91,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="B92" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -6663,34 +6678,34 @@
         <v>5</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="K92" s="2" t="str" cm="1">
         <f t="array" ref="K92">_xlfn.REGEXEXTRACT(A92,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="B93" s="2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>795</v>
+        <v>436</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -6699,34 +6714,34 @@
         <v>5</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>895</v>
+        <v>437</v>
       </c>
       <c r="K93" s="2" t="str" cm="1">
         <f t="array" ref="K93">_xlfn.REGEXEXTRACT(A93,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="B94" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>280</v>
+        <v>795</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -6735,34 +6750,34 @@
         <v>5</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>423</v>
+        <v>895</v>
       </c>
       <c r="K94" s="2" t="str" cm="1">
         <f t="array" ref="K94">_xlfn.REGEXEXTRACT(A94,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="B95" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>366</v>
+        <v>422</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>367</v>
+        <v>280</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -6771,34 +6786,34 @@
         <v>5</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>368</v>
+        <v>423</v>
       </c>
       <c r="K95" s="2" t="str" cm="1">
         <f t="array" ref="K95">_xlfn.REGEXEXTRACT(A95,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="B96" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -6807,106 +6822,106 @@
         <v>5</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="K96" s="2" t="str" cm="1">
         <f t="array" ref="K96">_xlfn.REGEXEXTRACT(A96,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B97" s="2">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>187</v>
+        <v>928</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>11</v>
+        <v>384</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="I97" s="2">
         <v>5</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="K97" s="2" t="str" cm="1">
         <f t="array" ref="K97">_xlfn.REGEXEXTRACT(A97,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>325</v>
+        <v>416</v>
       </c>
       <c r="B98" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>790</v>
+        <v>417</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>327</v>
+        <v>418</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="I98" s="2">
         <v>5</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>328</v>
+        <v>419</v>
       </c>
       <c r="K98" s="2" t="str" cm="1">
         <f t="array" ref="K98">_xlfn.REGEXEXTRACT(A98,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>396</v>
+        <v>325</v>
       </c>
       <c r="B99" s="2">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>397</v>
+        <v>11</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>398</v>
+        <v>790</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>794</v>
+        <v>327</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -6915,34 +6930,34 @@
         <v>5</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
       <c r="K99" s="2" t="str" cm="1">
         <f t="array" ref="K99">_xlfn.REGEXEXTRACT(A99,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>452</v>
+        <v>396</v>
       </c>
       <c r="B100" s="2">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>933</v>
+        <v>397</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>453</v>
+        <v>398</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>454</v>
+        <v>794</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -6951,34 +6966,34 @@
         <v>5</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>455</v>
+        <v>399</v>
       </c>
       <c r="K100" s="2" t="str" cm="1">
         <f t="array" ref="K100">_xlfn.REGEXEXTRACT(A100,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>374</v>
+        <v>452</v>
       </c>
       <c r="B101" s="2">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>11</v>
+        <v>933</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>375</v>
+        <v>453</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>376</v>
+        <v>454</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -6987,7 +7002,7 @@
         <v>5</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>377</v>
+        <v>455</v>
       </c>
       <c r="K101" s="2" t="str" cm="1">
         <f t="array" ref="K101">_xlfn.REGEXEXTRACT(A101,"(?&lt;=//)[^/]+")</f>
@@ -6996,25 +7011,25 @@
     </row>
     <row r="102" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B102" s="2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>923</v>
+        <v>110</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -7023,34 +7038,34 @@
         <v>5</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K102" s="2" t="str" cm="1">
         <f t="array" ref="K102">_xlfn.REGEXEXTRACT(A102,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B103" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>923</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -7059,7 +7074,7 @@
         <v>5</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="K103" s="2" t="str" cm="1">
         <f t="array" ref="K103">_xlfn.REGEXEXTRACT(A103,"(?&lt;=//)[^/]+")</f>
@@ -7068,25 +7083,25 @@
     </row>
     <row r="104" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="B104" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>923</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -7095,7 +7110,7 @@
         <v>5</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="K104" s="2" t="str" cm="1">
         <f t="array" ref="K104">_xlfn.REGEXEXTRACT(A104,"(?&lt;=//)[^/]+")</f>
@@ -7104,25 +7119,25 @@
     </row>
     <row r="105" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="B105" s="2">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>923</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -7131,34 +7146,34 @@
         <v>5</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="K105" s="2" t="str" cm="1">
         <f t="array" ref="K105">_xlfn.REGEXEXTRACT(A105,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="B106" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>187</v>
+        <v>923</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>793</v>
+        <v>430</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -7167,34 +7182,34 @@
         <v>5</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="K106" s="2" t="str" cm="1">
         <f t="array" ref="K106">_xlfn.REGEXEXTRACT(A106,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>347</v>
+        <v>392</v>
       </c>
       <c r="B107" s="2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>348</v>
+        <v>187</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>12</v>
+        <v>326</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -7203,106 +7218,106 @@
         <v>5</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>792</v>
+        <v>395</v>
       </c>
       <c r="K107" s="2" t="str" cm="1">
         <f t="array" ref="K107">_xlfn.REGEXEXTRACT(A107,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="B108" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>187</v>
+        <v>348</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>11</v>
+        <v>349</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>165</v>
+        <v>12</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>462</v>
+        <v>791</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>463</v>
+        <v>350</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>464</v>
+        <v>15</v>
       </c>
       <c r="I108" s="2">
         <v>5</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>465</v>
+        <v>792</v>
       </c>
       <c r="K108" s="2" t="str" cm="1">
         <f t="array" ref="K108">_xlfn.REGEXEXTRACT(A108,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B109" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>386</v>
+        <v>463</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>15</v>
+        <v>464</v>
       </c>
       <c r="I109" s="2">
         <v>5</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K109" s="2" t="str" cm="1">
         <f t="array" ref="K109">_xlfn.REGEXEXTRACT(A109,"(?&lt;=//)[^/]+")</f>
-        <v>www.xozilla.xxx</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>837</v>
+        <v>466</v>
       </c>
       <c r="B110" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>838</v>
+        <v>12</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>839</v>
+        <v>467</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>463</v>
+        <v>386</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -7311,34 +7326,34 @@
         <v>5</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>840</v>
+        <v>468</v>
       </c>
       <c r="K110" s="2" t="str" cm="1">
         <f t="array" ref="K110">_xlfn.REGEXEXTRACT(A110,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>www.xozilla.xxx</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>424</v>
+        <v>837</v>
       </c>
       <c r="B111" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>23</v>
+        <v>838</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>425</v>
+        <v>839</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -7347,34 +7362,34 @@
         <v>5</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>427</v>
+        <v>840</v>
       </c>
       <c r="K111" s="2" t="str" cm="1">
         <f t="array" ref="K111">_xlfn.REGEXEXTRACT(A111,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>342</v>
+        <v>424</v>
       </c>
       <c r="B112" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>343</v>
+        <v>23</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>344</v>
+        <v>425</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>345</v>
+        <v>426</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -7383,34 +7398,34 @@
         <v>5</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>346</v>
+        <v>427</v>
       </c>
       <c r="K112" s="2" t="str" cm="1">
         <f t="array" ref="K112">_xlfn.REGEXEXTRACT(A112,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B113" s="2">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>361</v>
+        <v>11</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>19</v>
+        <v>343</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -7419,106 +7434,106 @@
         <v>5</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="K113" s="2" t="str" cm="1">
         <f t="array" ref="K113">_xlfn.REGEXEXTRACT(A113,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B114" s="2">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>11</v>
+        <v>361</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="I114" s="2">
         <v>5</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="K114" s="2" t="str" cm="1">
         <f t="array" ref="K114">_xlfn.REGEXEXTRACT(A114,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="B115" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>789</v>
+        <v>353</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="I115" s="2">
         <v>5</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="K115" s="2" t="str" cm="1">
         <f t="array" ref="K115">_xlfn.REGEXEXTRACT(A115,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="B116" s="2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>228</v>
+        <v>47</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>412</v>
+        <v>42</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>413</v>
+        <v>323</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>414</v>
+        <v>789</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -7527,34 +7542,34 @@
         <v>5</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>415</v>
+        <v>324</v>
       </c>
       <c r="K116" s="2" t="str" cm="1">
         <f t="array" ref="K116">_xlfn.REGEXEXTRACT(A116,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="B117" s="2">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>924</v>
+        <v>228</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -7563,34 +7578,34 @@
         <v>5</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="K117" s="2" t="str" cm="1">
         <f t="array" ref="K117">_xlfn.REGEXEXTRACT(A117,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>355</v>
+        <v>438</v>
       </c>
       <c r="B118" s="2">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>924</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>356</v>
+        <v>439</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>357</v>
+        <v>440</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>358</v>
+        <v>441</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -7599,34 +7614,34 @@
         <v>5</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>359</v>
+        <v>442</v>
       </c>
       <c r="K118" s="2" t="str" cm="1">
         <f t="array" ref="K118">_xlfn.REGEXEXTRACT(A118,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntrex.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>456</v>
+        <v>355</v>
       </c>
       <c r="B119" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>924</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>457</v>
+        <v>356</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>458</v>
+        <v>357</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>459</v>
+        <v>358</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -7635,34 +7650,34 @@
         <v>5</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="K119" s="2" t="str" cm="1">
         <f t="array" ref="K119">_xlfn.REGEXEXTRACT(A119,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntrex.com</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>897</v>
+        <v>456</v>
       </c>
       <c r="B120" s="2">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>924</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>898</v>
+        <v>457</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>899</v>
+        <v>458</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>900</v>
+        <v>459</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -7671,34 +7686,34 @@
         <v>5</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>901</v>
+        <v>460</v>
       </c>
       <c r="K120" s="2" t="str" cm="1">
         <f t="array" ref="K120">_xlfn.REGEXEXTRACT(A120,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>448</v>
+        <v>897</v>
       </c>
       <c r="B121" s="2">
         <v>47</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>449</v>
+        <v>898</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>450</v>
+        <v>899</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>797</v>
+        <v>900</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -7707,34 +7722,34 @@
         <v>5</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>451</v>
+        <v>901</v>
       </c>
       <c r="K121" s="2" t="str" cm="1">
         <f t="array" ref="K121">_xlfn.REGEXEXTRACT(A121,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="B122" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>931</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>934</v>
+        <v>449</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -7743,34 +7758,34 @@
         <v>5</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="K122" s="2" t="str" cm="1">
         <f t="array" ref="K122">_xlfn.REGEXEXTRACT(A122,"(?&lt;=//)[^/]+")</f>
         <v>www.porntry.com</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="B123" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>339</v>
+        <v>934</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>341</v>
+        <v>796</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -7779,34 +7794,34 @@
         <v>5</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>896</v>
+        <v>410</v>
       </c>
       <c r="K123" s="2" t="str" cm="1">
         <f t="array" ref="K123">_xlfn.REGEXEXTRACT(A123,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B124" s="2">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -7815,34 +7830,34 @@
         <v>5</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>337</v>
+        <v>896</v>
       </c>
       <c r="K124" s="2" t="str" cm="1">
         <f t="array" ref="K124">_xlfn.REGEXEXTRACT(A124,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>txxx.com</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>388</v>
+        <v>333</v>
       </c>
       <c r="B125" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>932</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>115</v>
+        <v>334</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>389</v>
+        <v>335</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -7851,34 +7866,34 @@
         <v>5</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="K125" s="2" t="str" cm="1">
         <f t="array" ref="K125">_xlfn.REGEXEXTRACT(A125,"(?&lt;=//)[^/]+")</f>
-        <v>hcbdsm.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>955</v>
+        <v>388</v>
       </c>
       <c r="B126" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>956</v>
+        <v>115</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>957</v>
+        <v>389</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>958</v>
+        <v>390</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -7887,34 +7902,34 @@
         <v>5</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>959</v>
+        <v>391</v>
       </c>
       <c r="K126" s="2" t="str" cm="1">
         <f t="array" ref="K126">_xlfn.REGEXEXTRACT(A126,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>hcbdsm.com</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B127" s="2">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -7923,70 +7938,70 @@
         <v>5</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="K127" s="2" t="str" cm="1">
         <f t="array" ref="K127">_xlfn.REGEXEXTRACT(A127,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornissimo.org</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>583</v>
+        <v>960</v>
       </c>
       <c r="B128" s="2">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>584</v>
+        <v>961</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>802</v>
+        <v>962</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>585</v>
+        <v>963</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>586</v>
+        <v>964</v>
       </c>
       <c r="K128" s="2" t="str" cm="1">
         <f t="array" ref="K128">_xlfn.REGEXEXTRACT(A128,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornissimo.org</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>535</v>
+        <v>583</v>
       </c>
       <c r="B129" s="2">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>536</v>
+        <v>584</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>537</v>
+        <v>802</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>799</v>
+        <v>585</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -7995,34 +8010,34 @@
         <v>4</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>538</v>
+        <v>586</v>
       </c>
       <c r="K129" s="2" t="str" cm="1">
         <f t="array" ref="K129">_xlfn.REGEXEXTRACT(A129,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>591</v>
+        <v>535</v>
       </c>
       <c r="B130" s="2">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>592</v>
+        <v>536</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>593</v>
+        <v>537</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>594</v>
+        <v>799</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -8031,34 +8046,34 @@
         <v>4</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>595</v>
+        <v>538</v>
       </c>
       <c r="K130" s="2" t="str" cm="1">
         <f t="array" ref="K130">_xlfn.REGEXEXTRACT(A130,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>804</v>
+        <v>591</v>
       </c>
       <c r="B131" s="2">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>11</v>
+        <v>592</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>805</v>
+        <v>593</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>806</v>
+        <v>594</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -8067,34 +8082,34 @@
         <v>4</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>807</v>
+        <v>595</v>
       </c>
       <c r="K131" s="2" t="str" cm="1">
         <f t="array" ref="K131">_xlfn.REGEXEXTRACT(A131,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>911</v>
+        <v>804</v>
       </c>
       <c r="B132" s="2">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>912</v>
+        <v>11</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>913</v>
+        <v>805</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>787</v>
+        <v>806</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -8103,34 +8118,34 @@
         <v>4</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>914</v>
+        <v>807</v>
       </c>
       <c r="K132" s="2" t="str" cm="1">
         <f t="array" ref="K132">_xlfn.REGEXEXTRACT(A132,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B133" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -8139,34 +8154,34 @@
         <v>4</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="K133" s="2" t="str" cm="1">
         <f t="array" ref="K133">_xlfn.REGEXEXTRACT(A133,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>512</v>
+        <v>915</v>
       </c>
       <c r="B134" s="2">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>513</v>
+        <v>916</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>514</v>
+        <v>917</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -8175,34 +8190,34 @@
         <v>4</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>515</v>
+        <v>918</v>
       </c>
       <c r="K134" s="2" t="str" cm="1">
         <f t="array" ref="K134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>553</v>
+        <v>512</v>
       </c>
       <c r="B135" s="2">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>554</v>
+        <v>513</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>555</v>
+        <v>514</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>253</v>
+        <v>798</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -8211,34 +8226,34 @@
         <v>4</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>556</v>
+        <v>515</v>
       </c>
       <c r="K135" s="2" t="str" cm="1">
         <f t="array" ref="K135">_xlfn.REGEXEXTRACT(A135,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="B136" s="2">
         <v>52</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>89</v>
+        <v>928</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>11</v>
+        <v>554</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>92</v>
+        <v>253</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -8247,34 +8262,34 @@
         <v>4</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="K136" s="2" t="str" cm="1">
         <f t="array" ref="K136">_xlfn.REGEXEXTRACT(A136,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="B137" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>182</v>
+        <v>11</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>510</v>
+        <v>92</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -8283,34 +8298,34 @@
         <v>4</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="K137" s="2" t="str" cm="1">
         <f t="array" ref="K137">_xlfn.REGEXEXTRACT(A137,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.party</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="B138" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>531</v>
+        <v>182</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -8319,7 +8334,7 @@
         <v>4</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="K138" s="2" t="str" cm="1">
         <f t="array" ref="K138">_xlfn.REGEXEXTRACT(A138,"(?&lt;=//)[^/]+")</f>
@@ -8328,25 +8343,25 @@
     </row>
     <row r="139" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>575</v>
+        <v>530</v>
       </c>
       <c r="B139" s="2">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>926</v>
+        <v>89</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>576</v>
+        <v>531</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>577</v>
+        <v>532</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>801</v>
+        <v>533</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -8355,34 +8370,34 @@
         <v>4</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="K139" s="2" t="str" cm="1">
         <f t="array" ref="K139">_xlfn.REGEXEXTRACT(A139,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>478</v>
+        <v>575</v>
       </c>
       <c r="B140" s="2">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>283</v>
+        <v>926</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>479</v>
+        <v>576</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>902</v>
+        <v>577</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>480</v>
+        <v>801</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -8391,19 +8406,19 @@
         <v>4</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>903</v>
+        <v>578</v>
       </c>
       <c r="K140" s="2" t="str" cm="1">
         <f t="array" ref="K140">_xlfn.REGEXEXTRACT(A140,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>516</v>
+        <v>478</v>
       </c>
       <c r="B141" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>283</v>
@@ -8412,13 +8427,13 @@
         <v>479</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>517</v>
+        <v>902</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>518</v>
+        <v>480</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -8427,34 +8442,34 @@
         <v>4</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>519</v>
+        <v>903</v>
       </c>
       <c r="K141" s="2" t="str" cm="1">
         <f t="array" ref="K141">_xlfn.REGEXEXTRACT(A141,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>565</v>
+        <v>516</v>
       </c>
       <c r="B142" s="2">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>935</v>
+        <v>283</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>566</v>
+        <v>479</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>567</v>
+        <v>517</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>568</v>
+        <v>518</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -8463,34 +8478,34 @@
         <v>4</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>569</v>
+        <v>519</v>
       </c>
       <c r="K142" s="2" t="str" cm="1">
         <f t="array" ref="K142">_xlfn.REGEXEXTRACT(A142,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="B143" s="2">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -8499,34 +8514,34 @@
         <v>4</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="K143" s="2" t="str" cm="1">
         <f t="array" ref="K143">_xlfn.REGEXEXTRACT(A143,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="B144" s="2">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>923</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -8535,7 +8550,7 @@
         <v>4</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="K144" s="2" t="str" cm="1">
         <f t="array" ref="K144">_xlfn.REGEXEXTRACT(A144,"(?&lt;=//)[^/]+")</f>
@@ -8544,25 +8559,25 @@
     </row>
     <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>503</v>
+        <v>570</v>
       </c>
       <c r="B145" s="2">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>228</v>
+        <v>923</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>504</v>
+        <v>571</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>505</v>
+        <v>572</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>506</v>
+        <v>573</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -8571,34 +8586,34 @@
         <v>4</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>507</v>
+        <v>574</v>
       </c>
       <c r="K145" s="2" t="str" cm="1">
         <f t="array" ref="K145">_xlfn.REGEXEXTRACT(A145,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>562</v>
+        <v>503</v>
       </c>
       <c r="B146" s="2">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>11</v>
+        <v>504</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>563</v>
+        <v>505</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>800</v>
+        <v>506</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -8607,34 +8622,34 @@
         <v>4</v>
       </c>
       <c r="J146" s="2" t="s">
-        <v>564</v>
+        <v>507</v>
       </c>
       <c r="K146" s="2" t="str" cm="1">
         <f t="array" ref="K146">_xlfn.REGEXEXTRACT(A146,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B147" s="2">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>558</v>
+        <v>11</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>560</v>
+        <v>800</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -8643,7 +8658,7 @@
         <v>4</v>
       </c>
       <c r="J147" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K147" s="2" t="str" cm="1">
         <f t="array" ref="K147">_xlfn.REGEXEXTRACT(A147,"(?&lt;=//)[^/]+")</f>
@@ -8652,25 +8667,25 @@
     </row>
     <row r="148" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>481</v>
+        <v>557</v>
       </c>
       <c r="B148" s="2">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>482</v>
+        <v>558</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>483</v>
+        <v>559</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>484</v>
+        <v>560</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -8679,34 +8694,34 @@
         <v>4</v>
       </c>
       <c r="J148" s="2" t="s">
-        <v>485</v>
+        <v>561</v>
       </c>
       <c r="K148" s="2" t="str" cm="1">
         <f t="array" ref="K148">_xlfn.REGEXEXTRACT(A148,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>punishbang.com</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="B149" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>228</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -8715,34 +8730,34 @@
         <v>4</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="K149" s="2" t="str" cm="1">
         <f t="array" ref="K149">_xlfn.REGEXEXTRACT(A149,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>539</v>
+        <v>491</v>
       </c>
       <c r="B150" s="2">
         <v>44</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>540</v>
+        <v>492</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>541</v>
+        <v>493</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>542</v>
+        <v>494</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -8751,34 +8766,34 @@
         <v>4</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>543</v>
+        <v>495</v>
       </c>
       <c r="K150" s="2" t="str" cm="1">
         <f t="array" ref="K150">_xlfn.REGEXEXTRACT(A150,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>608</v>
+        <v>539</v>
       </c>
       <c r="B151" s="2">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>924</v>
+        <v>110</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>609</v>
+        <v>540</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>610</v>
+        <v>541</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>611</v>
+        <v>542</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -8787,34 +8802,34 @@
         <v>4</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>612</v>
+        <v>543</v>
       </c>
       <c r="K151" s="2" t="str" cm="1">
         <f t="array" ref="K151">_xlfn.REGEXEXTRACT(A151,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>496</v>
+        <v>608</v>
       </c>
       <c r="B152" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>497</v>
+        <v>924</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>173</v>
+        <v>609</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>904</v>
+        <v>610</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>498</v>
+        <v>611</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -8823,34 +8838,34 @@
         <v>4</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>499</v>
+        <v>612</v>
       </c>
       <c r="K152" s="2" t="str" cm="1">
         <f t="array" ref="K152">_xlfn.REGEXEXTRACT(A152,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>907</v>
+        <v>496</v>
       </c>
       <c r="B153" s="2">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>924</v>
+        <v>497</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>909</v>
+        <v>498</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -8859,34 +8874,34 @@
         <v>4</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>910</v>
+        <v>499</v>
       </c>
       <c r="K153" s="2" t="str" cm="1">
         <f t="array" ref="K153">_xlfn.REGEXEXTRACT(A153,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>606</v>
+        <v>907</v>
       </c>
       <c r="B154" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>187</v>
+        <v>924</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>607</v>
+        <v>909</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -8895,34 +8910,34 @@
         <v>4</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="K154" s="2" t="str" cm="1">
         <f t="array" ref="K154">_xlfn.REGEXEXTRACT(A154,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>526</v>
+        <v>606</v>
       </c>
       <c r="B155" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>187</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>527</v>
+        <v>11</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>326</v>
+        <v>12</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>528</v>
+        <v>905</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>463</v>
+        <v>607</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -8931,34 +8946,34 @@
         <v>4</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>529</v>
+        <v>906</v>
       </c>
       <c r="K155" s="2" t="str" cm="1">
         <f t="array" ref="K155">_xlfn.REGEXEXTRACT(A155,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B156" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>521</v>
+        <v>187</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>23</v>
+        <v>326</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>524</v>
+        <v>463</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -8967,34 +8982,34 @@
         <v>4</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="K156" s="2" t="str" cm="1">
         <f t="array" ref="K156">_xlfn.REGEXEXTRACT(A156,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>txxx.me</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
       <c r="B157" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>188</v>
+        <v>522</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>475</v>
+        <v>523</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>476</v>
+        <v>524</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -9003,34 +9018,34 @@
         <v>4</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>477</v>
+        <v>525</v>
       </c>
       <c r="K157" s="2" t="str" cm="1">
         <f t="array" ref="K157">_xlfn.REGEXEXTRACT(A157,"(?&lt;=//)[^/]+")</f>
-        <v>www.porndead.org</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>587</v>
+        <v>473</v>
       </c>
       <c r="B158" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>588</v>
+        <v>474</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>933</v>
+        <v>188</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>589</v>
+        <v>475</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>803</v>
+        <v>476</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -9039,34 +9054,34 @@
         <v>4</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>590</v>
+        <v>477</v>
       </c>
       <c r="K158" s="2" t="str" cm="1">
         <f t="array" ref="K158">_xlfn.REGEXEXTRACT(A158,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster18.desi</v>
+        <v>www.porndead.org</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>469</v>
+        <v>587</v>
       </c>
       <c r="B159" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>47</v>
+        <v>588</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>42</v>
+        <v>933</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>47</v>
+        <v>589</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>66</v>
+        <v>803</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -9075,16 +9090,16 @@
         <v>4</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>470</v>
+        <v>590</v>
       </c>
       <c r="K159" s="2" t="str" cm="1">
         <f t="array" ref="K159">_xlfn.REGEXEXTRACT(A159,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
+        <v>xhamster18.desi</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B160" s="2">
         <v>0</v>
@@ -9111,16 +9126,16 @@
         <v>4</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K160" s="2" t="str" cm="1">
         <f t="array" ref="K160">_xlfn.REGEXEXTRACT(A160,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog.com</v>
+        <v>netfapx.net</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>579</v>
+        <v>471</v>
       </c>
       <c r="B161" s="2">
         <v>0</v>
@@ -9132,85 +9147,85 @@
         <v>42</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>580</v>
+        <v>47</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>581</v>
+        <v>66</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="I161" s="2">
         <v>4</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>582</v>
+        <v>472</v>
       </c>
       <c r="K161" s="2" t="str" cm="1">
         <f t="array" ref="K161">_xlfn.REGEXEXTRACT(A161,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
+        <v>pornzog.com</v>
       </c>
     </row>
     <row r="162" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>544</v>
+        <v>579</v>
       </c>
       <c r="B162" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>931</v>
+        <v>47</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>545</v>
+        <v>42</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>386</v>
+        <v>581</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="I162" s="2">
         <v>4</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>547</v>
+        <v>582</v>
       </c>
       <c r="K162" s="2" t="str" cm="1">
         <f t="array" ref="K162">_xlfn.REGEXEXTRACT(A162,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.tubegalore.com</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>601</v>
+        <v>544</v>
       </c>
       <c r="B163" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>931</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>602</v>
+        <v>545</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>603</v>
+        <v>546</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>604</v>
+        <v>386</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -9219,34 +9234,34 @@
         <v>4</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>605</v>
+        <v>547</v>
       </c>
       <c r="K163" s="2" t="str" cm="1">
         <f t="array" ref="K163">_xlfn.REGEXEXTRACT(A163,"(?&lt;=//)[^/]+")</f>
         <v>www.porntry.com</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>548</v>
+        <v>601</v>
       </c>
       <c r="B164" s="2">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>549</v>
+        <v>602</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>550</v>
+        <v>603</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>551</v>
+        <v>604</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -9255,34 +9270,34 @@
         <v>4</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="K164" s="2" t="str" cm="1">
         <f t="array" ref="K164">_xlfn.REGEXEXTRACT(A164,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>486</v>
+        <v>548</v>
       </c>
       <c r="B165" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>487</v>
+        <v>549</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>488</v>
+        <v>550</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>489</v>
+        <v>551</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -9291,70 +9306,70 @@
         <v>4</v>
       </c>
       <c r="J165" s="2" t="s">
-        <v>490</v>
+        <v>552</v>
       </c>
       <c r="K165" s="2" t="str" cm="1">
         <f t="array" ref="K165">_xlfn.REGEXEXTRACT(A165,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>656</v>
+        <v>486</v>
       </c>
       <c r="B166" s="2">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>657</v>
+        <v>488</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>658</v>
+        <v>490</v>
       </c>
       <c r="K166" s="2" t="str" cm="1">
         <f t="array" ref="K166">_xlfn.REGEXEXTRACT(A166,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="B167" s="2">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>922</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>115</v>
+        <v>434</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>627</v>
+        <v>657</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>628</v>
+        <v>463</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -9363,34 +9378,34 @@
         <v>3</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>629</v>
+        <v>658</v>
       </c>
       <c r="K167" s="2" t="str" cm="1">
         <f t="array" ref="K167">_xlfn.REGEXEXTRACT(A167,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>715</v>
+        <v>626</v>
       </c>
       <c r="B168" s="2">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>716</v>
+        <v>115</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>717</v>
+        <v>627</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>718</v>
+        <v>628</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -9399,34 +9414,34 @@
         <v>3</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>719</v>
+        <v>629</v>
       </c>
       <c r="K168" s="2" t="str" cm="1">
         <f t="array" ref="K168">_xlfn.REGEXEXTRACT(A168,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>667</v>
+        <v>715</v>
       </c>
       <c r="B169" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>668</v>
+        <v>716</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>669</v>
+        <v>717</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>253</v>
+        <v>718</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -9435,34 +9450,34 @@
         <v>3</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
       <c r="K169" s="2" t="str" cm="1">
         <f t="array" ref="K169">_xlfn.REGEXEXTRACT(A169,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B170" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>386</v>
+        <v>253</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -9471,34 +9486,34 @@
         <v>3</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K170" s="2" t="str" cm="1">
         <f t="array" ref="K170">_xlfn.REGEXEXTRACT(A170,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>pervtube.net</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="B171" s="2">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>463</v>
+        <v>386</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -9507,34 +9522,34 @@
         <v>3</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="K171" s="2" t="str" cm="1">
         <f t="array" ref="K171">_xlfn.REGEXEXTRACT(A171,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>919</v>
+        <v>652</v>
       </c>
       <c r="B172" s="2">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>833</v>
+        <v>653</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>920</v>
+        <v>654</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>280</v>
+        <v>463</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -9543,34 +9558,34 @@
         <v>3</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>921</v>
+        <v>655</v>
       </c>
       <c r="K172" s="2" t="str" cm="1">
         <f t="array" ref="K172">_xlfn.REGEXEXTRACT(A172,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntopedia.com</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>630</v>
+        <v>919</v>
       </c>
       <c r="B173" s="2">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>89</v>
+        <v>928</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>631</v>
+        <v>833</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>632</v>
+        <v>920</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>633</v>
+        <v>280</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -9579,34 +9594,34 @@
         <v>3</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>634</v>
+        <v>921</v>
       </c>
       <c r="K173" s="2" t="str" cm="1">
         <f t="array" ref="K173">_xlfn.REGEXEXTRACT(A173,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmmansion.com</v>
       </c>
     </row>
     <row r="174" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="B174" s="2">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>228</v>
+        <v>89</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -9615,115 +9630,115 @@
         <v>3</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="K174" s="2" t="str" cm="1">
         <f t="array" ref="K174">_xlfn.REGEXEXTRACT(A174,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>680</v>
+        <v>647</v>
       </c>
       <c r="B175" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>11</v>
+        <v>648</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>682</v>
+        <v>650</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="I175" s="2">
         <v>3</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>683</v>
+        <v>651</v>
       </c>
       <c r="K175" s="2" t="str" cm="1">
         <f t="array" ref="K175">_xlfn.REGEXEXTRACT(A175,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>720</v>
+        <v>680</v>
       </c>
       <c r="B176" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>721</v>
+        <v>11</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>722</v>
+        <v>681</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>723</v>
+        <v>682</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="I176" s="2">
         <v>3</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>724</v>
+        <v>683</v>
       </c>
       <c r="K176" s="2" t="str" cm="1">
         <f t="array" ref="K176">_xlfn.REGEXEXTRACT(A176,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="B177" s="2">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>925</v>
+        <v>187</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>686</v>
+        <v>722</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>687</v>
+        <v>723</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>688</v>
+        <v>15</v>
       </c>
       <c r="I177" s="2">
         <v>3</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>689</v>
+        <v>724</v>
       </c>
       <c r="K177" s="2" t="str" cm="1">
         <f t="array" ref="K177">_xlfn.REGEXEXTRACT(A177,"(?&lt;=//)[^/]+")</f>
@@ -9732,61 +9747,61 @@
     </row>
     <row r="178" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>621</v>
+        <v>684</v>
       </c>
       <c r="B178" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>110</v>
+        <v>925</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>622</v>
+        <v>685</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>326</v>
+        <v>74</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>623</v>
+        <v>686</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>624</v>
+        <v>687</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>15</v>
+        <v>688</v>
       </c>
       <c r="I178" s="2">
         <v>3</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>625</v>
+        <v>689</v>
       </c>
       <c r="K178" s="2" t="str" cm="1">
         <f t="array" ref="K178">_xlfn.REGEXEXTRACT(A178,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>699</v>
+        <v>621</v>
       </c>
       <c r="B179" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>90</v>
+        <v>622</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>174</v>
+        <v>326</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>701</v>
+        <v>623</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>702</v>
+        <v>624</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -9795,7 +9810,7 @@
         <v>3</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>703</v>
+        <v>625</v>
       </c>
       <c r="K179" s="2" t="str" cm="1">
         <f t="array" ref="K179">_xlfn.REGEXEXTRACT(A179,"(?&lt;=//)[^/]+")</f>
@@ -9804,25 +9819,25 @@
     </row>
     <row r="180" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>659</v>
+        <v>699</v>
       </c>
       <c r="B180" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>187</v>
+        <v>700</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>660</v>
+        <v>701</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>661</v>
+        <v>702</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -9831,34 +9846,34 @@
         <v>3</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>662</v>
+        <v>703</v>
       </c>
       <c r="K180" s="2" t="str" cm="1">
         <f t="array" ref="K180">_xlfn.REGEXEXTRACT(A180,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>704</v>
+        <v>659</v>
       </c>
       <c r="B181" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>187</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>705</v>
+        <v>188</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>706</v>
+        <v>660</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>707</v>
+        <v>661</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -9867,34 +9882,34 @@
         <v>3</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>708</v>
+        <v>662</v>
       </c>
       <c r="K181" s="2" t="str" cm="1">
         <f t="array" ref="K181">_xlfn.REGEXEXTRACT(A181,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="182" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>671</v>
+        <v>704</v>
       </c>
       <c r="B182" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>672</v>
+        <v>187</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>673</v>
+        <v>705</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>674</v>
+        <v>706</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>810</v>
+        <v>707</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -9903,34 +9918,34 @@
         <v>3</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>675</v>
+        <v>708</v>
       </c>
       <c r="K182" s="2" t="str" cm="1">
         <f t="array" ref="K182">_xlfn.REGEXEXTRACT(A182,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="183" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="B183" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>187</v>
+        <v>672</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>326</v>
+        <v>12</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -9939,16 +9954,16 @@
         <v>3</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>809</v>
+        <v>675</v>
       </c>
       <c r="K183" s="2" t="str" cm="1">
         <f t="array" ref="K183">_xlfn.REGEXEXTRACT(A183,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="184" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>676</v>
+        <v>644</v>
       </c>
       <c r="B184" s="2">
         <v>30</v>
@@ -9957,16 +9972,16 @@
         <v>187</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>90</v>
+        <v>645</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>148</v>
+        <v>326</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>678</v>
+        <v>808</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -9975,34 +9990,34 @@
         <v>3</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>679</v>
+        <v>809</v>
       </c>
       <c r="K184" s="2" t="str" cm="1">
         <f t="array" ref="K184">_xlfn.REGEXEXTRACT(A184,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="B185" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>497</v>
+        <v>187</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -10011,7 +10026,7 @@
         <v>3</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="K185" s="2" t="str" cm="1">
         <f t="array" ref="K185">_xlfn.REGEXEXTRACT(A185,"(?&lt;=//)[^/]+")</f>
@@ -10020,25 +10035,25 @@
     </row>
     <row r="186" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>729</v>
+        <v>690</v>
       </c>
       <c r="B186" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>672</v>
+        <v>497</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>730</v>
+        <v>188</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>731</v>
+        <v>691</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>454</v>
+        <v>692</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -10047,34 +10062,34 @@
         <v>3</v>
       </c>
       <c r="J186" s="2" t="s">
-        <v>732</v>
+        <v>693</v>
       </c>
       <c r="K186" s="2" t="str" cm="1">
         <f t="array" ref="K186">_xlfn.REGEXEXTRACT(A186,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>639</v>
+        <v>729</v>
       </c>
       <c r="B187" s="2">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>927</v>
+        <v>672</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>640</v>
+        <v>730</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>641</v>
+        <v>731</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>642</v>
+        <v>454</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -10083,34 +10098,34 @@
         <v>3</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>643</v>
+        <v>732</v>
       </c>
       <c r="K187" s="2" t="str" cm="1">
         <f t="array" ref="K187">_xlfn.REGEXEXTRACT(A187,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>694</v>
+        <v>639</v>
       </c>
       <c r="B188" s="2">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>187</v>
+        <v>927</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>695</v>
+        <v>640</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>696</v>
+        <v>641</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>697</v>
+        <v>642</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -10119,34 +10134,34 @@
         <v>3</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>698</v>
+        <v>643</v>
       </c>
       <c r="K188" s="2" t="str" cm="1">
         <f t="array" ref="K188">_xlfn.REGEXEXTRACT(A188,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="189" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="B189" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>710</v>
+        <v>187</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -10155,88 +10170,88 @@
         <v>3</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="K189" s="2" t="str" cm="1">
         <f t="array" ref="K189">_xlfn.REGEXEXTRACT(A189,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="B190" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>110</v>
+        <v>710</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>11</v>
+        <v>711</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>464</v>
+        <v>15</v>
       </c>
       <c r="I190" s="2">
         <v>3</v>
       </c>
       <c r="J190" s="2" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="K190" s="2" t="str" cm="1">
         <f t="array" ref="K190">_xlfn.REGEXEXTRACT(A190,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>anyporn.com</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>613</v>
+        <v>725</v>
       </c>
       <c r="B191" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>182</v>
+        <v>11</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>614</v>
+        <v>726</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>615</v>
+        <v>727</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>15</v>
+        <v>464</v>
       </c>
       <c r="I191" s="2">
         <v>3</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>616</v>
+        <v>728</v>
       </c>
       <c r="K191" s="2" t="str" cm="1">
         <f t="array" ref="K191">_xlfn.REGEXEXTRACT(A191,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B192" s="2">
         <v>0</v>
@@ -10245,16 +10260,16 @@
         <v>47</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>434</v>
+        <v>182</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -10263,34 +10278,34 @@
         <v>3</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="K192" s="2" t="str" cm="1">
         <f t="array" ref="K192">_xlfn.REGEXEXTRACT(A192,"(?&lt;=//)[^/]+")</f>
         <v>curebdsm.com</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="B193" s="2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>929</v>
+        <v>47</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>636</v>
+        <v>434</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>637</v>
+        <v>618</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -10299,70 +10314,70 @@
         <v>3</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>936</v>
+        <v>620</v>
       </c>
       <c r="K193" s="2" t="str" cm="1">
         <f t="array" ref="K193">_xlfn.REGEXEXTRACT(A193,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="194" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>737</v>
+        <v>635</v>
       </c>
       <c r="B194" s="2">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>434</v>
+        <v>636</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>738</v>
+        <v>637</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>739</v>
+        <v>638</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>740</v>
+        <v>936</v>
       </c>
       <c r="K194" s="2" t="str" cm="1">
         <f t="array" ref="K194">_xlfn.REGEXEXTRACT(A194,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="195" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B195" s="2">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>734</v>
+        <v>434</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>811</v>
+        <v>739</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -10371,34 +10386,34 @@
         <v>2</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="K195" s="2" t="str" cm="1">
         <f t="array" ref="K195">_xlfn.REGEXEXTRACT(A195,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="B196" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>228</v>
+        <v>926</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>479</v>
+        <v>734</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>966</v>
+        <v>811</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -10407,34 +10422,34 @@
         <v>2</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
       <c r="K196" s="2" t="str" cm="1">
         <f t="array" ref="K196">_xlfn.REGEXEXTRACT(A196,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B197" s="2">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>924</v>
+        <v>228</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>753</v>
+        <v>479</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>755</v>
+        <v>966</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -10443,34 +10458,34 @@
         <v>2</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="K197" s="2" t="str" cm="1">
         <f t="array" ref="K197">_xlfn.REGEXEXTRACT(A197,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="198" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="B198" s="2">
         <v>57</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -10479,34 +10494,34 @@
         <v>2</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="K198" s="2" t="str" cm="1">
         <f t="array" ref="K198">_xlfn.REGEXEXTRACT(A198,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>www.omg.xxx</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="B199" s="2">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>187</v>
+        <v>929</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -10515,34 +10530,34 @@
         <v>2</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="K199" s="2" t="str" cm="1">
         <f t="array" ref="K199">_xlfn.REGEXEXTRACT(A199,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>741</v>
+        <v>757</v>
       </c>
       <c r="B200" s="2">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>672</v>
+        <v>187</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>463</v>
+        <v>760</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -10551,34 +10566,34 @@
         <v>2</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>744</v>
+        <v>761</v>
       </c>
       <c r="K200" s="2" t="str" cm="1">
         <f t="array" ref="K200">_xlfn.REGEXEXTRACT(A200,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>www.peekvids.com</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
       <c r="B201" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>110</v>
+        <v>672</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>120</v>
+        <v>463</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -10587,7 +10602,7 @@
         <v>2</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
       <c r="K201" s="2" t="str" cm="1">
         <f t="array" ref="K201">_xlfn.REGEXEXTRACT(A201,"(?&lt;=//)[^/]+")</f>
@@ -10596,25 +10611,25 @@
     </row>
     <row r="202" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>745</v>
+        <v>762</v>
       </c>
       <c r="B202" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>521</v>
+        <v>110</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>746</v>
+        <v>763</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>463</v>
+        <v>120</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -10623,7 +10638,7 @@
         <v>2</v>
       </c>
       <c r="J202" s="2" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="K202" s="2" t="str" cm="1">
         <f t="array" ref="K202">_xlfn.REGEXEXTRACT(A202,"(?&lt;=//)[^/]+")</f>
@@ -10632,61 +10647,61 @@
     </row>
     <row r="203" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>779</v>
+        <v>745</v>
       </c>
       <c r="B203" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>672</v>
+        <v>521</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>672</v>
+        <v>746</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>780</v>
+        <v>747</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>781</v>
+        <v>463</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J203" s="2" t="s">
-        <v>782</v>
+        <v>748</v>
       </c>
       <c r="K203" s="2" t="str" cm="1">
         <f t="array" ref="K203">_xlfn.REGEXEXTRACT(A203,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="B204" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>672</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>730</v>
+        <v>672</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -10695,7 +10710,7 @@
         <v>1</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="K204" s="2" t="str" cm="1">
         <f t="array" ref="K204">_xlfn.REGEXEXTRACT(A204,"(?&lt;=//)[^/]+")</f>
@@ -10704,25 +10719,25 @@
     </row>
     <row r="205" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B205" s="2">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>187</v>
+        <v>672</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>188</v>
+        <v>730</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>174</v>
+        <v>12</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -10731,10 +10746,46 @@
         <v>1</v>
       </c>
       <c r="J205" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="K205" s="2" t="str" cm="1">
         <f t="array" ref="K205">_xlfn.REGEXEXTRACT(A205,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B206" s="2">
+        <v>11</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I206" s="2">
+        <v>1</v>
+      </c>
+      <c r="J206" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="K206" s="2" t="str" cm="1">
+        <f t="array" ref="K206">_xlfn.REGEXEXTRACT(A206,"(?&lt;=//)[^/]+")</f>
         <v>www.pornhub.com</v>
       </c>
     </row>
@@ -10743,12 +10794,12 @@
     <sortCondition descending="1" ref="I1:I205"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:K205">
+  <conditionalFormatting sqref="A1:K206">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I205">
+  <conditionalFormatting sqref="I1:I206">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>

--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1381B02D-B60C-424F-8B6C-9C5D7D47AA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE2FF4A-E4FE-4B53-8D0C-D5388D4AB259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NSFW_Links" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NSFW_Links!$A$1:$K$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NSFW_Links!$A$1:$K$206</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3060,14 +3060,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -10790,12 +10783,17 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K206" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K206">
+      <sortCondition descending="1" ref="I1:I206"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K205">
     <sortCondition descending="1" ref="I1:I205"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:K206">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11851,7 +11849,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A205">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
